--- a/Toplu_Mesai_Sablon.xlsx
+++ b/Toplu_Mesai_Sablon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECE8C5B-05A5-432E-B337-00BA6E45D8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88B87BD-AA30-4588-A9C1-A8596F0CF52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2DF94309-6D47-4284-9046-50F652E00677}"/>
   </bookViews>
@@ -187,7 +187,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -586,19 +586,6 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -636,17 +623,6 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -675,7 +651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -784,19 +760,19 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -808,13 +784,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -838,7 +814,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -853,13 +829,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -883,100 +895,61 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1306,133 +1279,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="73"/>
-      <c r="AI1" s="73"/>
-      <c r="AJ1" s="73"/>
-      <c r="AK1" s="73"/>
-      <c r="AL1" s="73"/>
-      <c r="AM1" s="73"/>
-      <c r="AN1" s="73"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
     </row>
     <row r="2" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="73"/>
-      <c r="X2" s="73"/>
-      <c r="Y2" s="73"/>
-      <c r="Z2" s="73"/>
-      <c r="AA2" s="73"/>
-      <c r="AB2" s="73"/>
-      <c r="AC2" s="73"/>
-      <c r="AD2" s="73"/>
-      <c r="AE2" s="73"/>
-      <c r="AF2" s="73"/>
-      <c r="AG2" s="73"/>
-      <c r="AH2" s="73"/>
-      <c r="AI2" s="73"/>
-      <c r="AJ2" s="73"/>
-      <c r="AK2" s="73"/>
-      <c r="AL2" s="73"/>
-      <c r="AM2" s="73"/>
-      <c r="AN2" s="73"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="63"/>
+      <c r="Y2" s="63"/>
+      <c r="Z2" s="63"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
+      <c r="AH2" s="63"/>
+      <c r="AI2" s="63"/>
+      <c r="AJ2" s="63"/>
+      <c r="AK2" s="63"/>
+      <c r="AL2" s="63"/>
+      <c r="AM2" s="63"/>
+      <c r="AN2" s="63"/>
     </row>
     <row r="3" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="73"/>
-      <c r="Y3" s="73"/>
-      <c r="Z3" s="73"/>
-      <c r="AA3" s="73"/>
-      <c r="AB3" s="73"/>
-      <c r="AC3" s="73"/>
-      <c r="AD3" s="73"/>
-      <c r="AE3" s="73"/>
-      <c r="AF3" s="73"/>
-      <c r="AG3" s="73"/>
-      <c r="AH3" s="73"/>
-      <c r="AI3" s="73"/>
-      <c r="AJ3" s="73"/>
-      <c r="AK3" s="73"/>
-      <c r="AL3" s="73"/>
-      <c r="AM3" s="73"/>
-      <c r="AN3" s="73"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="63"/>
+      <c r="Z3" s="63"/>
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="63"/>
+      <c r="AD3" s="63"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
+      <c r="AH3" s="63"/>
+      <c r="AI3" s="63"/>
+      <c r="AJ3" s="63"/>
+      <c r="AK3" s="63"/>
+      <c r="AL3" s="63"/>
+      <c r="AM3" s="63"/>
+      <c r="AN3" s="63"/>
     </row>
     <row r="4" spans="2:40" s="5" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
@@ -1472,20 +1445,20 @@
       <c r="AJ4" s="4"/>
     </row>
     <row r="5" spans="2:40" s="6" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="74"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="77"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="67"/>
       <c r="H5" s="47"/>
       <c r="I5" s="47"/>
       <c r="J5" s="47"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="65"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="70"/>
       <c r="P5" s="35"/>
       <c r="Q5" s="35"/>
       <c r="R5" s="35"/>
@@ -1508,7 +1481,7 @@
       <c r="AI5" s="35"/>
       <c r="AJ5" s="35"/>
       <c r="AK5" s="59"/>
-      <c r="AL5" s="79" t="s">
+      <c r="AL5" s="71" t="s">
         <v>3</v>
       </c>
       <c r="AM5" s="41" t="s">
@@ -1519,20 +1492,20 @@
       </c>
     </row>
     <row r="6" spans="2:40" s="6" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="67" t="s">
+      <c r="C6" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71">
+      <c r="F6" s="82"/>
+      <c r="G6" s="83">
         <v>24</v>
       </c>
       <c r="H6" s="35">
@@ -1553,10 +1526,10 @@
       <c r="M6" s="47">
         <v>30</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="69">
         <v>31</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="70">
         <v>1</v>
       </c>
       <c r="P6" s="35">
@@ -1625,27 +1598,27 @@
       <c r="AK6" s="59">
         <v>23</v>
       </c>
-      <c r="AL6" s="80"/>
-      <c r="AM6" s="82"/>
-      <c r="AN6" s="82"/>
+      <c r="AL6" s="72"/>
+      <c r="AM6" s="74"/>
+      <c r="AN6" s="74"/>
     </row>
     <row r="7" spans="2:40" s="6" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="84"/>
-      <c r="C7" s="68"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="61"/>
       <c r="E7" s="61" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="62"/>
-      <c r="G7" s="72"/>
+      <c r="G7" s="84"/>
       <c r="H7" s="51"/>
       <c r="I7" s="51"/>
       <c r="J7" s="51"/>
       <c r="K7" s="55"/>
       <c r="L7" s="55"/>
       <c r="M7" s="55"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="66"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="78"/>
       <c r="P7" s="51"/>
       <c r="Q7" s="51"/>
       <c r="R7" s="51"/>
@@ -1668,11 +1641,11 @@
       <c r="AI7" s="51"/>
       <c r="AJ7" s="51"/>
       <c r="AK7" s="60"/>
-      <c r="AL7" s="81"/>
+      <c r="AL7" s="73"/>
       <c r="AM7" s="54"/>
       <c r="AN7" s="54"/>
     </row>
-    <row r="8" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="33">
         <v>1</v>
       </c>
@@ -1684,36 +1657,36 @@
       <c r="F8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="85"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
       <c r="K8" s="87"/>
       <c r="L8" s="87"/>
       <c r="M8" s="87"/>
       <c r="N8" s="88"/>
       <c r="O8" s="89"/>
-      <c r="P8" s="86"/>
-      <c r="Q8" s="86"/>
-      <c r="R8" s="86"/>
-      <c r="S8" s="86"/>
-      <c r="T8" s="86"/>
-      <c r="U8" s="86"/>
-      <c r="V8" s="86"/>
-      <c r="W8" s="86"/>
-      <c r="X8" s="86"/>
-      <c r="Y8" s="86"/>
-      <c r="Z8" s="86"/>
-      <c r="AA8" s="86"/>
-      <c r="AB8" s="86"/>
-      <c r="AC8" s="86"/>
-      <c r="AD8" s="86"/>
-      <c r="AE8" s="86"/>
-      <c r="AF8" s="86"/>
-      <c r="AG8" s="86"/>
-      <c r="AH8" s="86"/>
-      <c r="AI8" s="86"/>
-      <c r="AJ8" s="86"/>
+      <c r="P8" s="85"/>
+      <c r="Q8" s="85"/>
+      <c r="R8" s="85"/>
+      <c r="S8" s="85"/>
+      <c r="T8" s="85"/>
+      <c r="U8" s="85"/>
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="85"/>
+      <c r="Y8" s="85"/>
+      <c r="Z8" s="85"/>
+      <c r="AA8" s="85"/>
+      <c r="AB8" s="85"/>
+      <c r="AC8" s="85"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="85"/>
+      <c r="AF8" s="85"/>
+      <c r="AG8" s="85"/>
+      <c r="AH8" s="85"/>
+      <c r="AI8" s="85"/>
+      <c r="AJ8" s="85"/>
       <c r="AK8" s="88"/>
       <c r="AL8" s="90"/>
       <c r="AM8" s="39"/>
@@ -1764,7 +1737,7 @@
       <c r="AM9" s="40"/>
       <c r="AN9" s="42"/>
     </row>
-    <row r="10" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="43">
         <v>2</v>
       </c>
@@ -1776,36 +1749,36 @@
       <c r="F10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="85"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
       <c r="K10" s="87"/>
       <c r="L10" s="87"/>
       <c r="M10" s="87"/>
       <c r="N10" s="88"/>
       <c r="O10" s="89"/>
-      <c r="P10" s="86"/>
-      <c r="Q10" s="86"/>
-      <c r="R10" s="86"/>
-      <c r="S10" s="86"/>
-      <c r="T10" s="86"/>
-      <c r="U10" s="86"/>
-      <c r="V10" s="86"/>
-      <c r="W10" s="86"/>
-      <c r="X10" s="86"/>
-      <c r="Y10" s="86"/>
-      <c r="Z10" s="86"/>
-      <c r="AA10" s="86"/>
-      <c r="AB10" s="86"/>
-      <c r="AC10" s="86"/>
-      <c r="AD10" s="86"/>
-      <c r="AE10" s="86"/>
-      <c r="AF10" s="86"/>
-      <c r="AG10" s="86"/>
-      <c r="AH10" s="86"/>
-      <c r="AI10" s="86"/>
-      <c r="AJ10" s="86"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="85"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="85"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="85"/>
+      <c r="Y10" s="85"/>
+      <c r="Z10" s="85"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="85"/>
+      <c r="AC10" s="85"/>
+      <c r="AD10" s="85"/>
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="85"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="85"/>
+      <c r="AJ10" s="85"/>
       <c r="AK10" s="88"/>
       <c r="AL10" s="90"/>
       <c r="AM10" s="39"/>
@@ -1852,11 +1825,11 @@
       <c r="AI11" s="98"/>
       <c r="AJ11" s="98"/>
       <c r="AK11" s="100"/>
-      <c r="AL11" s="102"/>
+      <c r="AL11" s="96"/>
       <c r="AM11" s="53"/>
       <c r="AN11" s="54"/>
     </row>
-    <row r="12" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="33">
         <v>3</v>
       </c>
@@ -1868,36 +1841,36 @@
       <c r="F12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="85"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
       <c r="K12" s="87"/>
       <c r="L12" s="87"/>
       <c r="M12" s="87"/>
       <c r="N12" s="88"/>
       <c r="O12" s="89"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
-      <c r="S12" s="86"/>
-      <c r="T12" s="86"/>
-      <c r="U12" s="86"/>
-      <c r="V12" s="86"/>
-      <c r="W12" s="86"/>
-      <c r="X12" s="86"/>
-      <c r="Y12" s="103"/>
-      <c r="Z12" s="86"/>
-      <c r="AA12" s="86"/>
-      <c r="AB12" s="86"/>
-      <c r="AC12" s="86"/>
-      <c r="AD12" s="86"/>
-      <c r="AE12" s="86"/>
-      <c r="AF12" s="86"/>
-      <c r="AG12" s="86"/>
-      <c r="AH12" s="86"/>
-      <c r="AI12" s="86"/>
-      <c r="AJ12" s="86"/>
+      <c r="P12" s="85"/>
+      <c r="Q12" s="85"/>
+      <c r="R12" s="85"/>
+      <c r="S12" s="85"/>
+      <c r="T12" s="85"/>
+      <c r="U12" s="85"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="85"/>
+      <c r="X12" s="85"/>
+      <c r="Y12" s="102"/>
+      <c r="Z12" s="85"/>
+      <c r="AA12" s="85"/>
+      <c r="AB12" s="85"/>
+      <c r="AC12" s="85"/>
+      <c r="AD12" s="85"/>
+      <c r="AE12" s="85"/>
+      <c r="AF12" s="85"/>
+      <c r="AG12" s="85"/>
+      <c r="AH12" s="85"/>
+      <c r="AI12" s="85"/>
+      <c r="AJ12" s="85"/>
       <c r="AK12" s="88"/>
       <c r="AL12" s="90"/>
       <c r="AM12" s="39"/>
@@ -1931,7 +1904,7 @@
       <c r="V13" s="92"/>
       <c r="W13" s="92"/>
       <c r="X13" s="92"/>
-      <c r="Y13" s="104"/>
+      <c r="Y13" s="103"/>
       <c r="Z13" s="92"/>
       <c r="AA13" s="92"/>
       <c r="AB13" s="92"/>
@@ -1948,7 +1921,7 @@
       <c r="AM13" s="40"/>
       <c r="AN13" s="42"/>
     </row>
-    <row r="14" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="43">
         <v>4</v>
       </c>
@@ -1960,36 +1933,36 @@
       <c r="F14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="85"/>
-      <c r="H14" s="86"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
       <c r="K14" s="87"/>
       <c r="L14" s="87"/>
       <c r="M14" s="87"/>
       <c r="N14" s="88"/>
       <c r="O14" s="89"/>
-      <c r="P14" s="86"/>
-      <c r="Q14" s="86"/>
-      <c r="R14" s="86"/>
-      <c r="S14" s="86"/>
-      <c r="T14" s="86"/>
-      <c r="U14" s="86"/>
-      <c r="V14" s="86"/>
-      <c r="W14" s="86"/>
-      <c r="X14" s="86"/>
-      <c r="Y14" s="86"/>
-      <c r="Z14" s="86"/>
-      <c r="AA14" s="86"/>
-      <c r="AB14" s="86"/>
-      <c r="AC14" s="86"/>
-      <c r="AD14" s="86"/>
-      <c r="AE14" s="86"/>
-      <c r="AF14" s="86"/>
-      <c r="AG14" s="86"/>
-      <c r="AH14" s="86"/>
-      <c r="AI14" s="86"/>
-      <c r="AJ14" s="86"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="85"/>
+      <c r="R14" s="85"/>
+      <c r="S14" s="85"/>
+      <c r="T14" s="85"/>
+      <c r="U14" s="85"/>
+      <c r="V14" s="85"/>
+      <c r="W14" s="85"/>
+      <c r="X14" s="85"/>
+      <c r="Y14" s="85"/>
+      <c r="Z14" s="85"/>
+      <c r="AA14" s="85"/>
+      <c r="AB14" s="85"/>
+      <c r="AC14" s="85"/>
+      <c r="AD14" s="85"/>
+      <c r="AE14" s="85"/>
+      <c r="AF14" s="85"/>
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85"/>
+      <c r="AI14" s="85"/>
+      <c r="AJ14" s="85"/>
       <c r="AK14" s="88"/>
       <c r="AL14" s="90"/>
       <c r="AM14" s="39"/>
@@ -2040,7 +2013,7 @@
       <c r="AM15" s="40"/>
       <c r="AN15" s="42"/>
     </row>
-    <row r="16" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="33">
         <v>5</v>
       </c>
@@ -2052,36 +2025,36 @@
       <c r="F16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="85"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="85"/>
       <c r="K16" s="87"/>
       <c r="L16" s="87"/>
       <c r="M16" s="87"/>
       <c r="N16" s="88"/>
       <c r="O16" s="89"/>
-      <c r="P16" s="86"/>
-      <c r="Q16" s="86"/>
-      <c r="R16" s="86"/>
-      <c r="S16" s="86"/>
-      <c r="T16" s="86"/>
-      <c r="U16" s="86"/>
-      <c r="V16" s="86"/>
-      <c r="W16" s="86"/>
-      <c r="X16" s="86"/>
-      <c r="Y16" s="86"/>
-      <c r="Z16" s="86"/>
-      <c r="AA16" s="86"/>
-      <c r="AB16" s="86"/>
-      <c r="AC16" s="86"/>
-      <c r="AD16" s="86"/>
-      <c r="AE16" s="86"/>
-      <c r="AF16" s="86"/>
-      <c r="AG16" s="86"/>
-      <c r="AH16" s="86"/>
-      <c r="AI16" s="86"/>
-      <c r="AJ16" s="86"/>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="85"/>
+      <c r="U16" s="85"/>
+      <c r="V16" s="85"/>
+      <c r="W16" s="85"/>
+      <c r="X16" s="85"/>
+      <c r="Y16" s="85"/>
+      <c r="Z16" s="85"/>
+      <c r="AA16" s="85"/>
+      <c r="AB16" s="85"/>
+      <c r="AC16" s="85"/>
+      <c r="AD16" s="85"/>
+      <c r="AE16" s="85"/>
+      <c r="AF16" s="85"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="85"/>
+      <c r="AJ16" s="85"/>
       <c r="AK16" s="88"/>
       <c r="AL16" s="90"/>
       <c r="AM16" s="39"/>
@@ -2132,7 +2105,7 @@
       <c r="AM17" s="40"/>
       <c r="AN17" s="42"/>
     </row>
-    <row r="18" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="43">
         <v>6</v>
       </c>
@@ -2144,36 +2117,36 @@
       <c r="F18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="85"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
       <c r="K18" s="87"/>
       <c r="L18" s="87"/>
       <c r="M18" s="87"/>
       <c r="N18" s="88"/>
       <c r="O18" s="89"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="86"/>
-      <c r="R18" s="86"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="86"/>
-      <c r="V18" s="86"/>
-      <c r="W18" s="86"/>
-      <c r="X18" s="86"/>
-      <c r="Y18" s="86"/>
-      <c r="Z18" s="86"/>
-      <c r="AA18" s="86"/>
-      <c r="AB18" s="86"/>
-      <c r="AC18" s="86"/>
-      <c r="AD18" s="86"/>
-      <c r="AE18" s="86"/>
-      <c r="AF18" s="86"/>
-      <c r="AG18" s="86"/>
-      <c r="AH18" s="86"/>
-      <c r="AI18" s="86"/>
-      <c r="AJ18" s="86"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="85"/>
+      <c r="X18" s="85"/>
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="85"/>
+      <c r="AE18" s="85"/>
+      <c r="AF18" s="85"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="85"/>
+      <c r="AJ18" s="85"/>
       <c r="AK18" s="88"/>
       <c r="AL18" s="90"/>
       <c r="AM18" s="39"/>
@@ -2224,7 +2197,7 @@
       <c r="AM19" s="40"/>
       <c r="AN19" s="42"/>
     </row>
-    <row r="20" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="33">
         <v>7</v>
       </c>
@@ -2236,36 +2209,36 @@
       <c r="F20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="85"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
       <c r="K20" s="87"/>
       <c r="L20" s="87"/>
       <c r="M20" s="87"/>
       <c r="N20" s="88"/>
       <c r="O20" s="89"/>
-      <c r="P20" s="86"/>
-      <c r="Q20" s="86"/>
-      <c r="R20" s="86"/>
-      <c r="S20" s="86"/>
-      <c r="T20" s="86"/>
-      <c r="U20" s="86"/>
-      <c r="V20" s="86"/>
-      <c r="W20" s="86"/>
-      <c r="X20" s="86"/>
-      <c r="Y20" s="86"/>
-      <c r="Z20" s="86"/>
-      <c r="AA20" s="86"/>
-      <c r="AB20" s="86"/>
-      <c r="AC20" s="86"/>
-      <c r="AD20" s="86"/>
-      <c r="AE20" s="86"/>
-      <c r="AF20" s="86"/>
-      <c r="AG20" s="86"/>
-      <c r="AH20" s="86"/>
-      <c r="AI20" s="86"/>
-      <c r="AJ20" s="86"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="85"/>
+      <c r="R20" s="85"/>
+      <c r="S20" s="85"/>
+      <c r="T20" s="85"/>
+      <c r="U20" s="85"/>
+      <c r="V20" s="85"/>
+      <c r="W20" s="85"/>
+      <c r="X20" s="85"/>
+      <c r="Y20" s="85"/>
+      <c r="Z20" s="85"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="85"/>
+      <c r="AF20" s="85"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="85"/>
+      <c r="AJ20" s="85"/>
       <c r="AK20" s="88"/>
       <c r="AL20" s="90"/>
       <c r="AM20" s="39"/>
@@ -2316,7 +2289,7 @@
       <c r="AM21" s="40"/>
       <c r="AN21" s="42"/>
     </row>
-    <row r="22" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="43">
         <v>8</v>
       </c>
@@ -2328,36 +2301,36 @@
       <c r="F22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="85"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="85"/>
       <c r="K22" s="87"/>
       <c r="L22" s="87"/>
       <c r="M22" s="87"/>
       <c r="N22" s="88"/>
       <c r="O22" s="89"/>
-      <c r="P22" s="86"/>
-      <c r="Q22" s="86"/>
-      <c r="R22" s="86"/>
-      <c r="S22" s="86"/>
-      <c r="T22" s="86"/>
-      <c r="U22" s="86"/>
-      <c r="V22" s="86"/>
-      <c r="W22" s="86"/>
-      <c r="X22" s="86"/>
-      <c r="Y22" s="86"/>
-      <c r="Z22" s="86"/>
-      <c r="AA22" s="86"/>
-      <c r="AB22" s="86"/>
-      <c r="AC22" s="86"/>
-      <c r="AD22" s="86"/>
-      <c r="AE22" s="86"/>
-      <c r="AF22" s="86"/>
-      <c r="AG22" s="86"/>
-      <c r="AH22" s="86"/>
-      <c r="AI22" s="86"/>
-      <c r="AJ22" s="86"/>
+      <c r="P22" s="85"/>
+      <c r="Q22" s="85"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="85"/>
+      <c r="T22" s="85"/>
+      <c r="U22" s="85"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="85"/>
+      <c r="X22" s="85"/>
+      <c r="Y22" s="85"/>
+      <c r="Z22" s="85"/>
+      <c r="AA22" s="85"/>
+      <c r="AB22" s="85"/>
+      <c r="AC22" s="85"/>
+      <c r="AD22" s="85"/>
+      <c r="AE22" s="85"/>
+      <c r="AF22" s="85"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="85"/>
+      <c r="AJ22" s="85"/>
       <c r="AK22" s="88"/>
       <c r="AL22" s="90"/>
       <c r="AM22" s="39"/>
@@ -2408,7 +2381,7 @@
       <c r="AM23" s="40"/>
       <c r="AN23" s="42"/>
     </row>
-    <row r="24" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="33">
         <v>9</v>
       </c>
@@ -2420,36 +2393,36 @@
       <c r="F24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="85"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="86"/>
-      <c r="J24" s="86"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
       <c r="K24" s="87"/>
       <c r="L24" s="87"/>
       <c r="M24" s="87"/>
       <c r="N24" s="88"/>
       <c r="O24" s="89"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="86"/>
-      <c r="R24" s="86"/>
-      <c r="S24" s="86"/>
-      <c r="T24" s="86"/>
-      <c r="U24" s="86"/>
-      <c r="V24" s="86"/>
-      <c r="W24" s="86"/>
-      <c r="X24" s="86"/>
-      <c r="Y24" s="86"/>
-      <c r="Z24" s="86"/>
-      <c r="AA24" s="86"/>
-      <c r="AB24" s="86"/>
-      <c r="AC24" s="86"/>
-      <c r="AD24" s="86"/>
-      <c r="AE24" s="86"/>
-      <c r="AF24" s="86"/>
-      <c r="AG24" s="86"/>
-      <c r="AH24" s="86"/>
-      <c r="AI24" s="86"/>
-      <c r="AJ24" s="86"/>
+      <c r="P24" s="85"/>
+      <c r="Q24" s="85"/>
+      <c r="R24" s="85"/>
+      <c r="S24" s="85"/>
+      <c r="T24" s="85"/>
+      <c r="U24" s="85"/>
+      <c r="V24" s="85"/>
+      <c r="W24" s="85"/>
+      <c r="X24" s="85"/>
+      <c r="Y24" s="85"/>
+      <c r="Z24" s="85"/>
+      <c r="AA24" s="85"/>
+      <c r="AB24" s="85"/>
+      <c r="AC24" s="85"/>
+      <c r="AD24" s="85"/>
+      <c r="AE24" s="85"/>
+      <c r="AF24" s="85"/>
+      <c r="AG24" s="85"/>
+      <c r="AH24" s="85"/>
+      <c r="AI24" s="85"/>
+      <c r="AJ24" s="85"/>
       <c r="AK24" s="88"/>
       <c r="AL24" s="90"/>
       <c r="AM24" s="39"/>
@@ -2500,7 +2473,7 @@
       <c r="AM25" s="40"/>
       <c r="AN25" s="42"/>
     </row>
-    <row r="26" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="43">
         <v>10</v>
       </c>
@@ -2512,36 +2485,36 @@
       <c r="F26" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="85"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="85"/>
+      <c r="I26" s="85"/>
+      <c r="J26" s="85"/>
       <c r="K26" s="87"/>
       <c r="L26" s="87"/>
       <c r="M26" s="87"/>
       <c r="N26" s="88"/>
       <c r="O26" s="89"/>
-      <c r="P26" s="86"/>
-      <c r="Q26" s="86"/>
-      <c r="R26" s="86"/>
-      <c r="S26" s="86"/>
-      <c r="T26" s="86"/>
-      <c r="U26" s="86"/>
-      <c r="V26" s="86"/>
-      <c r="W26" s="86"/>
-      <c r="X26" s="86"/>
-      <c r="Y26" s="86"/>
-      <c r="Z26" s="86"/>
-      <c r="AA26" s="86"/>
-      <c r="AB26" s="86"/>
-      <c r="AC26" s="86"/>
-      <c r="AD26" s="86"/>
-      <c r="AE26" s="86"/>
-      <c r="AF26" s="86"/>
-      <c r="AG26" s="86"/>
-      <c r="AH26" s="86"/>
-      <c r="AI26" s="86"/>
-      <c r="AJ26" s="86"/>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="85"/>
+      <c r="R26" s="85"/>
+      <c r="S26" s="85"/>
+      <c r="T26" s="85"/>
+      <c r="U26" s="85"/>
+      <c r="V26" s="85"/>
+      <c r="W26" s="85"/>
+      <c r="X26" s="85"/>
+      <c r="Y26" s="85"/>
+      <c r="Z26" s="85"/>
+      <c r="AA26" s="85"/>
+      <c r="AB26" s="85"/>
+      <c r="AC26" s="85"/>
+      <c r="AD26" s="85"/>
+      <c r="AE26" s="85"/>
+      <c r="AF26" s="85"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
+      <c r="AI26" s="85"/>
+      <c r="AJ26" s="85"/>
       <c r="AK26" s="88"/>
       <c r="AL26" s="90"/>
       <c r="AM26" s="39"/>
@@ -2588,11 +2561,11 @@
       <c r="AI27" s="98"/>
       <c r="AJ27" s="98"/>
       <c r="AK27" s="100"/>
-      <c r="AL27" s="102"/>
+      <c r="AL27" s="96"/>
       <c r="AM27" s="53"/>
       <c r="AN27" s="54"/>
     </row>
-    <row r="28" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="33">
         <v>11</v>
       </c>
@@ -2604,36 +2577,36 @@
       <c r="F28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="85"/>
-      <c r="H28" s="86"/>
-      <c r="I28" s="86"/>
-      <c r="J28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="85"/>
       <c r="K28" s="87"/>
       <c r="L28" s="87"/>
       <c r="M28" s="87"/>
       <c r="N28" s="88"/>
       <c r="O28" s="89"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="86"/>
-      <c r="S28" s="86"/>
-      <c r="T28" s="86"/>
-      <c r="U28" s="86"/>
-      <c r="V28" s="86"/>
-      <c r="W28" s="86"/>
-      <c r="X28" s="86"/>
-      <c r="Y28" s="86"/>
-      <c r="Z28" s="86"/>
-      <c r="AA28" s="86"/>
-      <c r="AB28" s="86"/>
-      <c r="AC28" s="86"/>
-      <c r="AD28" s="86"/>
-      <c r="AE28" s="86"/>
-      <c r="AF28" s="86"/>
-      <c r="AG28" s="86"/>
-      <c r="AH28" s="86"/>
-      <c r="AI28" s="86"/>
-      <c r="AJ28" s="86"/>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="85"/>
+      <c r="R28" s="85"/>
+      <c r="S28" s="85"/>
+      <c r="T28" s="85"/>
+      <c r="U28" s="85"/>
+      <c r="V28" s="85"/>
+      <c r="W28" s="85"/>
+      <c r="X28" s="85"/>
+      <c r="Y28" s="85"/>
+      <c r="Z28" s="85"/>
+      <c r="AA28" s="85"/>
+      <c r="AB28" s="85"/>
+      <c r="AC28" s="85"/>
+      <c r="AD28" s="85"/>
+      <c r="AE28" s="85"/>
+      <c r="AF28" s="85"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="85"/>
+      <c r="AJ28" s="85"/>
       <c r="AK28" s="88"/>
       <c r="AL28" s="90"/>
       <c r="AM28" s="39"/>
@@ -2684,7 +2657,7 @@
       <c r="AM29" s="40"/>
       <c r="AN29" s="42"/>
     </row>
-    <row r="30" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="43">
         <v>12</v>
       </c>
@@ -2696,36 +2669,36 @@
       <c r="F30" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="85"/>
-      <c r="H30" s="86"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
       <c r="K30" s="87"/>
       <c r="L30" s="87"/>
       <c r="M30" s="87"/>
       <c r="N30" s="88"/>
       <c r="O30" s="89"/>
-      <c r="P30" s="86"/>
-      <c r="Q30" s="86"/>
-      <c r="R30" s="86"/>
-      <c r="S30" s="86"/>
-      <c r="T30" s="86"/>
-      <c r="U30" s="86"/>
-      <c r="V30" s="86"/>
-      <c r="W30" s="86"/>
-      <c r="X30" s="86"/>
-      <c r="Y30" s="86"/>
-      <c r="Z30" s="86"/>
-      <c r="AA30" s="86"/>
-      <c r="AB30" s="86"/>
-      <c r="AC30" s="86"/>
-      <c r="AD30" s="86"/>
-      <c r="AE30" s="86"/>
-      <c r="AF30" s="86"/>
-      <c r="AG30" s="86"/>
-      <c r="AH30" s="86"/>
-      <c r="AI30" s="86"/>
-      <c r="AJ30" s="86"/>
+      <c r="P30" s="85"/>
+      <c r="Q30" s="85"/>
+      <c r="R30" s="85"/>
+      <c r="S30" s="85"/>
+      <c r="T30" s="85"/>
+      <c r="U30" s="85"/>
+      <c r="V30" s="85"/>
+      <c r="W30" s="85"/>
+      <c r="X30" s="85"/>
+      <c r="Y30" s="85"/>
+      <c r="Z30" s="85"/>
+      <c r="AA30" s="85"/>
+      <c r="AB30" s="85"/>
+      <c r="AC30" s="85"/>
+      <c r="AD30" s="85"/>
+      <c r="AE30" s="85"/>
+      <c r="AF30" s="85"/>
+      <c r="AG30" s="85"/>
+      <c r="AH30" s="85"/>
+      <c r="AI30" s="85"/>
+      <c r="AJ30" s="85"/>
       <c r="AK30" s="88"/>
       <c r="AL30" s="90"/>
       <c r="AM30" s="39"/>
@@ -2776,7 +2749,7 @@
       <c r="AM31" s="40"/>
       <c r="AN31" s="42"/>
     </row>
-    <row r="32" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="33">
         <v>13</v>
       </c>
@@ -2788,36 +2761,36 @@
       <c r="F32" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="85"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
       <c r="K32" s="87"/>
       <c r="L32" s="87"/>
       <c r="M32" s="87"/>
       <c r="N32" s="88"/>
       <c r="O32" s="89"/>
-      <c r="P32" s="86"/>
-      <c r="Q32" s="86"/>
-      <c r="R32" s="86"/>
-      <c r="S32" s="86"/>
-      <c r="T32" s="86"/>
-      <c r="U32" s="86"/>
-      <c r="V32" s="86"/>
-      <c r="W32" s="86"/>
-      <c r="X32" s="86"/>
-      <c r="Y32" s="86"/>
-      <c r="Z32" s="86"/>
-      <c r="AA32" s="86"/>
-      <c r="AB32" s="86"/>
-      <c r="AC32" s="86"/>
-      <c r="AD32" s="86"/>
-      <c r="AE32" s="86"/>
-      <c r="AF32" s="86"/>
-      <c r="AG32" s="86"/>
-      <c r="AH32" s="86"/>
-      <c r="AI32" s="86"/>
-      <c r="AJ32" s="86"/>
+      <c r="P32" s="85"/>
+      <c r="Q32" s="85"/>
+      <c r="R32" s="85"/>
+      <c r="S32" s="85"/>
+      <c r="T32" s="85"/>
+      <c r="U32" s="85"/>
+      <c r="V32" s="85"/>
+      <c r="W32" s="85"/>
+      <c r="X32" s="85"/>
+      <c r="Y32" s="85"/>
+      <c r="Z32" s="85"/>
+      <c r="AA32" s="85"/>
+      <c r="AB32" s="85"/>
+      <c r="AC32" s="85"/>
+      <c r="AD32" s="85"/>
+      <c r="AE32" s="85"/>
+      <c r="AF32" s="85"/>
+      <c r="AG32" s="85"/>
+      <c r="AH32" s="85"/>
+      <c r="AI32" s="85"/>
+      <c r="AJ32" s="85"/>
       <c r="AK32" s="88"/>
       <c r="AL32" s="90"/>
       <c r="AM32" s="39"/>
@@ -2868,7 +2841,7 @@
       <c r="AM33" s="40"/>
       <c r="AN33" s="42"/>
     </row>
-    <row r="34" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="43">
         <v>14</v>
       </c>
@@ -2880,36 +2853,36 @@
       <c r="F34" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="86"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
       <c r="K34" s="87"/>
       <c r="L34" s="87"/>
       <c r="M34" s="87"/>
       <c r="N34" s="88"/>
       <c r="O34" s="89"/>
-      <c r="P34" s="86"/>
-      <c r="Q34" s="86"/>
-      <c r="R34" s="86"/>
-      <c r="S34" s="86"/>
-      <c r="T34" s="86"/>
-      <c r="U34" s="86"/>
-      <c r="V34" s="86"/>
-      <c r="W34" s="86"/>
-      <c r="X34" s="86"/>
-      <c r="Y34" s="86"/>
-      <c r="Z34" s="86"/>
-      <c r="AA34" s="86"/>
-      <c r="AB34" s="86"/>
-      <c r="AC34" s="86"/>
-      <c r="AD34" s="86"/>
-      <c r="AE34" s="86"/>
-      <c r="AF34" s="86"/>
-      <c r="AG34" s="86"/>
-      <c r="AH34" s="86"/>
-      <c r="AI34" s="86"/>
-      <c r="AJ34" s="86"/>
+      <c r="P34" s="85"/>
+      <c r="Q34" s="85"/>
+      <c r="R34" s="85"/>
+      <c r="S34" s="85"/>
+      <c r="T34" s="85"/>
+      <c r="U34" s="85"/>
+      <c r="V34" s="85"/>
+      <c r="W34" s="85"/>
+      <c r="X34" s="85"/>
+      <c r="Y34" s="85"/>
+      <c r="Z34" s="85"/>
+      <c r="AA34" s="85"/>
+      <c r="AB34" s="85"/>
+      <c r="AC34" s="85"/>
+      <c r="AD34" s="85"/>
+      <c r="AE34" s="85"/>
+      <c r="AF34" s="85"/>
+      <c r="AG34" s="85"/>
+      <c r="AH34" s="85"/>
+      <c r="AI34" s="85"/>
+      <c r="AJ34" s="85"/>
       <c r="AK34" s="88"/>
       <c r="AL34" s="90"/>
       <c r="AM34" s="39"/>
@@ -2960,7 +2933,7 @@
       <c r="AM35" s="40"/>
       <c r="AN35" s="42"/>
     </row>
-    <row r="36" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="33">
         <v>15</v>
       </c>
@@ -2972,36 +2945,36 @@
       <c r="F36" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="85"/>
-      <c r="H36" s="86"/>
-      <c r="I36" s="86"/>
-      <c r="J36" s="86"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="85"/>
+      <c r="J36" s="85"/>
       <c r="K36" s="87"/>
       <c r="L36" s="87"/>
       <c r="M36" s="87"/>
       <c r="N36" s="88"/>
       <c r="O36" s="89"/>
-      <c r="P36" s="86"/>
-      <c r="Q36" s="86"/>
-      <c r="R36" s="86"/>
-      <c r="S36" s="86"/>
-      <c r="T36" s="86"/>
-      <c r="U36" s="86"/>
-      <c r="V36" s="86"/>
-      <c r="W36" s="86"/>
-      <c r="X36" s="86"/>
-      <c r="Y36" s="86"/>
-      <c r="Z36" s="86"/>
-      <c r="AA36" s="86"/>
-      <c r="AB36" s="86"/>
-      <c r="AC36" s="86"/>
-      <c r="AD36" s="86"/>
-      <c r="AE36" s="86"/>
-      <c r="AF36" s="86"/>
-      <c r="AG36" s="86"/>
-      <c r="AH36" s="86"/>
-      <c r="AI36" s="86"/>
-      <c r="AJ36" s="86"/>
+      <c r="P36" s="85"/>
+      <c r="Q36" s="85"/>
+      <c r="R36" s="85"/>
+      <c r="S36" s="85"/>
+      <c r="T36" s="85"/>
+      <c r="U36" s="85"/>
+      <c r="V36" s="85"/>
+      <c r="W36" s="85"/>
+      <c r="X36" s="85"/>
+      <c r="Y36" s="85"/>
+      <c r="Z36" s="85"/>
+      <c r="AA36" s="85"/>
+      <c r="AB36" s="85"/>
+      <c r="AC36" s="85"/>
+      <c r="AD36" s="85"/>
+      <c r="AE36" s="85"/>
+      <c r="AF36" s="85"/>
+      <c r="AG36" s="85"/>
+      <c r="AH36" s="85"/>
+      <c r="AI36" s="85"/>
+      <c r="AJ36" s="85"/>
       <c r="AK36" s="88"/>
       <c r="AL36" s="90"/>
       <c r="AM36" s="39"/>
@@ -3052,7 +3025,7 @@
       <c r="AM37" s="40"/>
       <c r="AN37" s="42"/>
     </row>
-    <row r="38" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="43">
         <v>16</v>
       </c>
@@ -3064,36 +3037,36 @@
       <c r="F38" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="85"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="86"/>
+      <c r="G38" s="86"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
       <c r="K38" s="87"/>
       <c r="L38" s="87"/>
       <c r="M38" s="87"/>
       <c r="N38" s="88"/>
       <c r="O38" s="89"/>
-      <c r="P38" s="86"/>
-      <c r="Q38" s="86"/>
-      <c r="R38" s="86"/>
-      <c r="S38" s="86"/>
-      <c r="T38" s="86"/>
-      <c r="U38" s="86"/>
-      <c r="V38" s="86"/>
-      <c r="W38" s="86"/>
-      <c r="X38" s="86"/>
-      <c r="Y38" s="86"/>
-      <c r="Z38" s="86"/>
-      <c r="AA38" s="86"/>
-      <c r="AB38" s="86"/>
-      <c r="AC38" s="86"/>
-      <c r="AD38" s="86"/>
-      <c r="AE38" s="86"/>
-      <c r="AF38" s="86"/>
-      <c r="AG38" s="86"/>
-      <c r="AH38" s="86"/>
-      <c r="AI38" s="86"/>
-      <c r="AJ38" s="86"/>
+      <c r="P38" s="85"/>
+      <c r="Q38" s="85"/>
+      <c r="R38" s="85"/>
+      <c r="S38" s="85"/>
+      <c r="T38" s="85"/>
+      <c r="U38" s="85"/>
+      <c r="V38" s="85"/>
+      <c r="W38" s="85"/>
+      <c r="X38" s="85"/>
+      <c r="Y38" s="85"/>
+      <c r="Z38" s="85"/>
+      <c r="AA38" s="85"/>
+      <c r="AB38" s="85"/>
+      <c r="AC38" s="85"/>
+      <c r="AD38" s="85"/>
+      <c r="AE38" s="85"/>
+      <c r="AF38" s="85"/>
+      <c r="AG38" s="85"/>
+      <c r="AH38" s="85"/>
+      <c r="AI38" s="85"/>
+      <c r="AJ38" s="85"/>
       <c r="AK38" s="88"/>
       <c r="AL38" s="90"/>
       <c r="AM38" s="39"/>
@@ -3144,7 +3117,7 @@
       <c r="AM39" s="40"/>
       <c r="AN39" s="42"/>
     </row>
-    <row r="40" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="33">
         <v>17</v>
       </c>
@@ -3156,36 +3129,36 @@
       <c r="F40" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="85"/>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="86"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="85"/>
       <c r="K40" s="87"/>
       <c r="L40" s="87"/>
       <c r="M40" s="87"/>
       <c r="N40" s="88"/>
       <c r="O40" s="89"/>
-      <c r="P40" s="86"/>
-      <c r="Q40" s="86"/>
-      <c r="R40" s="86"/>
-      <c r="S40" s="86"/>
-      <c r="T40" s="86"/>
-      <c r="U40" s="86"/>
-      <c r="V40" s="86"/>
-      <c r="W40" s="86"/>
-      <c r="X40" s="86"/>
-      <c r="Y40" s="86"/>
-      <c r="Z40" s="86"/>
-      <c r="AA40" s="86"/>
-      <c r="AB40" s="86"/>
-      <c r="AC40" s="86"/>
-      <c r="AD40" s="86"/>
-      <c r="AE40" s="86"/>
-      <c r="AF40" s="86"/>
-      <c r="AG40" s="86"/>
-      <c r="AH40" s="86"/>
-      <c r="AI40" s="86"/>
-      <c r="AJ40" s="86"/>
+      <c r="P40" s="85"/>
+      <c r="Q40" s="85"/>
+      <c r="R40" s="85"/>
+      <c r="S40" s="85"/>
+      <c r="T40" s="85"/>
+      <c r="U40" s="85"/>
+      <c r="V40" s="85"/>
+      <c r="W40" s="85"/>
+      <c r="X40" s="85"/>
+      <c r="Y40" s="85"/>
+      <c r="Z40" s="85"/>
+      <c r="AA40" s="85"/>
+      <c r="AB40" s="85"/>
+      <c r="AC40" s="85"/>
+      <c r="AD40" s="85"/>
+      <c r="AE40" s="85"/>
+      <c r="AF40" s="85"/>
+      <c r="AG40" s="85"/>
+      <c r="AH40" s="85"/>
+      <c r="AI40" s="85"/>
+      <c r="AJ40" s="85"/>
       <c r="AK40" s="88"/>
       <c r="AL40" s="90"/>
       <c r="AM40" s="39"/>
@@ -3236,7 +3209,7 @@
       <c r="AM41" s="40"/>
       <c r="AN41" s="42"/>
     </row>
-    <row r="42" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="43">
         <v>18</v>
       </c>
@@ -3248,36 +3221,36 @@
       <c r="F42" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="85"/>
-      <c r="H42" s="86"/>
-      <c r="I42" s="86"/>
-      <c r="J42" s="86"/>
+      <c r="G42" s="86"/>
+      <c r="H42" s="85"/>
+      <c r="I42" s="85"/>
+      <c r="J42" s="85"/>
       <c r="K42" s="87"/>
       <c r="L42" s="87"/>
       <c r="M42" s="87"/>
       <c r="N42" s="88"/>
       <c r="O42" s="89"/>
-      <c r="P42" s="86"/>
-      <c r="Q42" s="86"/>
-      <c r="R42" s="86"/>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
-      <c r="V42" s="86"/>
-      <c r="W42" s="86"/>
-      <c r="X42" s="86"/>
-      <c r="Y42" s="86"/>
-      <c r="Z42" s="86"/>
-      <c r="AA42" s="86"/>
-      <c r="AB42" s="86"/>
-      <c r="AC42" s="86"/>
-      <c r="AD42" s="86"/>
-      <c r="AE42" s="86"/>
-      <c r="AF42" s="86"/>
-      <c r="AG42" s="86"/>
-      <c r="AH42" s="86"/>
-      <c r="AI42" s="86"/>
-      <c r="AJ42" s="86"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="85"/>
+      <c r="R42" s="85"/>
+      <c r="S42" s="85"/>
+      <c r="T42" s="85"/>
+      <c r="U42" s="85"/>
+      <c r="V42" s="85"/>
+      <c r="W42" s="85"/>
+      <c r="X42" s="85"/>
+      <c r="Y42" s="85"/>
+      <c r="Z42" s="85"/>
+      <c r="AA42" s="85"/>
+      <c r="AB42" s="85"/>
+      <c r="AC42" s="85"/>
+      <c r="AD42" s="85"/>
+      <c r="AE42" s="85"/>
+      <c r="AF42" s="85"/>
+      <c r="AG42" s="85"/>
+      <c r="AH42" s="85"/>
+      <c r="AI42" s="85"/>
+      <c r="AJ42" s="85"/>
       <c r="AK42" s="88"/>
       <c r="AL42" s="90"/>
       <c r="AM42" s="39"/>
@@ -3328,7 +3301,7 @@
       <c r="AM43" s="40"/>
       <c r="AN43" s="42"/>
     </row>
-    <row r="44" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="33">
         <v>19</v>
       </c>
@@ -3340,36 +3313,36 @@
       <c r="F44" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="85"/>
-      <c r="H44" s="86"/>
-      <c r="I44" s="86"/>
-      <c r="J44" s="86"/>
+      <c r="G44" s="86"/>
+      <c r="H44" s="85"/>
+      <c r="I44" s="85"/>
+      <c r="J44" s="85"/>
       <c r="K44" s="87"/>
       <c r="L44" s="87"/>
       <c r="M44" s="87"/>
       <c r="N44" s="88"/>
       <c r="O44" s="89"/>
-      <c r="P44" s="86"/>
-      <c r="Q44" s="86"/>
-      <c r="R44" s="86"/>
-      <c r="S44" s="86"/>
-      <c r="T44" s="86"/>
-      <c r="U44" s="86"/>
-      <c r="V44" s="86"/>
-      <c r="W44" s="86"/>
-      <c r="X44" s="86"/>
-      <c r="Y44" s="86"/>
-      <c r="Z44" s="86"/>
-      <c r="AA44" s="86"/>
-      <c r="AB44" s="86"/>
-      <c r="AC44" s="86"/>
-      <c r="AD44" s="86"/>
-      <c r="AE44" s="86"/>
-      <c r="AF44" s="86"/>
-      <c r="AG44" s="86"/>
-      <c r="AH44" s="86"/>
-      <c r="AI44" s="86"/>
-      <c r="AJ44" s="86"/>
+      <c r="P44" s="85"/>
+      <c r="Q44" s="85"/>
+      <c r="R44" s="85"/>
+      <c r="S44" s="85"/>
+      <c r="T44" s="85"/>
+      <c r="U44" s="85"/>
+      <c r="V44" s="85"/>
+      <c r="W44" s="85"/>
+      <c r="X44" s="85"/>
+      <c r="Y44" s="85"/>
+      <c r="Z44" s="85"/>
+      <c r="AA44" s="85"/>
+      <c r="AB44" s="85"/>
+      <c r="AC44" s="85"/>
+      <c r="AD44" s="85"/>
+      <c r="AE44" s="85"/>
+      <c r="AF44" s="85"/>
+      <c r="AG44" s="85"/>
+      <c r="AH44" s="85"/>
+      <c r="AI44" s="85"/>
+      <c r="AJ44" s="85"/>
       <c r="AK44" s="88"/>
       <c r="AL44" s="90"/>
       <c r="AM44" s="39"/>
@@ -3420,7 +3393,7 @@
       <c r="AM45" s="40"/>
       <c r="AN45" s="42"/>
     </row>
-    <row r="46" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="43">
         <v>20</v>
       </c>
@@ -3432,36 +3405,36 @@
       <c r="F46" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="85"/>
-      <c r="H46" s="86"/>
-      <c r="I46" s="86"/>
-      <c r="J46" s="86"/>
+      <c r="G46" s="86"/>
+      <c r="H46" s="85"/>
+      <c r="I46" s="85"/>
+      <c r="J46" s="85"/>
       <c r="K46" s="87"/>
       <c r="L46" s="87"/>
       <c r="M46" s="87"/>
       <c r="N46" s="88"/>
       <c r="O46" s="89"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="86"/>
-      <c r="S46" s="86"/>
-      <c r="T46" s="86"/>
-      <c r="U46" s="86"/>
-      <c r="V46" s="86"/>
-      <c r="W46" s="86"/>
-      <c r="X46" s="86"/>
-      <c r="Y46" s="86"/>
-      <c r="Z46" s="86"/>
-      <c r="AA46" s="86"/>
-      <c r="AB46" s="86"/>
-      <c r="AC46" s="86"/>
-      <c r="AD46" s="86"/>
-      <c r="AE46" s="86"/>
-      <c r="AF46" s="86"/>
-      <c r="AG46" s="86"/>
-      <c r="AH46" s="86"/>
-      <c r="AI46" s="86"/>
-      <c r="AJ46" s="86"/>
+      <c r="P46" s="85"/>
+      <c r="Q46" s="85"/>
+      <c r="R46" s="85"/>
+      <c r="S46" s="85"/>
+      <c r="T46" s="85"/>
+      <c r="U46" s="85"/>
+      <c r="V46" s="85"/>
+      <c r="W46" s="85"/>
+      <c r="X46" s="85"/>
+      <c r="Y46" s="85"/>
+      <c r="Z46" s="85"/>
+      <c r="AA46" s="85"/>
+      <c r="AB46" s="85"/>
+      <c r="AC46" s="85"/>
+      <c r="AD46" s="85"/>
+      <c r="AE46" s="85"/>
+      <c r="AF46" s="85"/>
+      <c r="AG46" s="85"/>
+      <c r="AH46" s="85"/>
+      <c r="AI46" s="85"/>
+      <c r="AJ46" s="85"/>
       <c r="AK46" s="88"/>
       <c r="AL46" s="90"/>
       <c r="AM46" s="39"/>
@@ -3508,11 +3481,11 @@
       <c r="AI47" s="98"/>
       <c r="AJ47" s="98"/>
       <c r="AK47" s="100"/>
-      <c r="AL47" s="102"/>
+      <c r="AL47" s="96"/>
       <c r="AM47" s="53"/>
       <c r="AN47" s="54"/>
     </row>
-    <row r="48" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="33">
         <v>21</v>
       </c>
@@ -3524,36 +3497,36 @@
       <c r="F48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="85"/>
-      <c r="H48" s="86"/>
-      <c r="I48" s="86"/>
-      <c r="J48" s="86"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="85"/>
+      <c r="I48" s="85"/>
+      <c r="J48" s="85"/>
       <c r="K48" s="87"/>
       <c r="L48" s="87"/>
       <c r="M48" s="87"/>
       <c r="N48" s="88"/>
       <c r="O48" s="89"/>
-      <c r="P48" s="86"/>
-      <c r="Q48" s="86"/>
-      <c r="R48" s="86"/>
-      <c r="S48" s="86"/>
-      <c r="T48" s="86"/>
-      <c r="U48" s="86"/>
-      <c r="V48" s="86"/>
-      <c r="W48" s="86"/>
-      <c r="X48" s="86"/>
-      <c r="Y48" s="86"/>
-      <c r="Z48" s="86"/>
-      <c r="AA48" s="86"/>
-      <c r="AB48" s="86"/>
-      <c r="AC48" s="86"/>
-      <c r="AD48" s="86"/>
-      <c r="AE48" s="86"/>
-      <c r="AF48" s="86"/>
-      <c r="AG48" s="86"/>
-      <c r="AH48" s="86"/>
-      <c r="AI48" s="86"/>
-      <c r="AJ48" s="86"/>
+      <c r="P48" s="85"/>
+      <c r="Q48" s="85"/>
+      <c r="R48" s="85"/>
+      <c r="S48" s="85"/>
+      <c r="T48" s="85"/>
+      <c r="U48" s="85"/>
+      <c r="V48" s="85"/>
+      <c r="W48" s="85"/>
+      <c r="X48" s="85"/>
+      <c r="Y48" s="85"/>
+      <c r="Z48" s="85"/>
+      <c r="AA48" s="85"/>
+      <c r="AB48" s="85"/>
+      <c r="AC48" s="85"/>
+      <c r="AD48" s="85"/>
+      <c r="AE48" s="85"/>
+      <c r="AF48" s="85"/>
+      <c r="AG48" s="85"/>
+      <c r="AH48" s="85"/>
+      <c r="AI48" s="85"/>
+      <c r="AJ48" s="85"/>
       <c r="AK48" s="88"/>
       <c r="AL48" s="90"/>
       <c r="AM48" s="39"/>
@@ -3604,7 +3577,7 @@
       <c r="AM49" s="40"/>
       <c r="AN49" s="42"/>
     </row>
-    <row r="50" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B50" s="43">
         <v>22</v>
       </c>
@@ -3616,36 +3589,36 @@
       <c r="F50" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="85"/>
-      <c r="H50" s="86"/>
-      <c r="I50" s="86"/>
-      <c r="J50" s="86"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="85"/>
+      <c r="I50" s="85"/>
+      <c r="J50" s="85"/>
       <c r="K50" s="87"/>
       <c r="L50" s="87"/>
       <c r="M50" s="87"/>
       <c r="N50" s="88"/>
       <c r="O50" s="89"/>
-      <c r="P50" s="86"/>
-      <c r="Q50" s="86"/>
-      <c r="R50" s="86"/>
-      <c r="S50" s="86"/>
-      <c r="T50" s="86"/>
-      <c r="U50" s="86"/>
-      <c r="V50" s="86"/>
-      <c r="W50" s="86"/>
-      <c r="X50" s="86"/>
-      <c r="Y50" s="86"/>
-      <c r="Z50" s="86"/>
-      <c r="AA50" s="86"/>
-      <c r="AB50" s="86"/>
-      <c r="AC50" s="86"/>
-      <c r="AD50" s="86"/>
-      <c r="AE50" s="86"/>
-      <c r="AF50" s="86"/>
-      <c r="AG50" s="86"/>
-      <c r="AH50" s="86"/>
-      <c r="AI50" s="86"/>
-      <c r="AJ50" s="86"/>
+      <c r="P50" s="85"/>
+      <c r="Q50" s="85"/>
+      <c r="R50" s="85"/>
+      <c r="S50" s="85"/>
+      <c r="T50" s="85"/>
+      <c r="U50" s="85"/>
+      <c r="V50" s="85"/>
+      <c r="W50" s="85"/>
+      <c r="X50" s="85"/>
+      <c r="Y50" s="85"/>
+      <c r="Z50" s="85"/>
+      <c r="AA50" s="85"/>
+      <c r="AB50" s="85"/>
+      <c r="AC50" s="85"/>
+      <c r="AD50" s="85"/>
+      <c r="AE50" s="85"/>
+      <c r="AF50" s="85"/>
+      <c r="AG50" s="85"/>
+      <c r="AH50" s="85"/>
+      <c r="AI50" s="85"/>
+      <c r="AJ50" s="85"/>
       <c r="AK50" s="88"/>
       <c r="AL50" s="90"/>
       <c r="AM50" s="39"/>
@@ -3696,7 +3669,7 @@
       <c r="AM51" s="40"/>
       <c r="AN51" s="42"/>
     </row>
-    <row r="52" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="33">
         <v>23</v>
       </c>
@@ -3708,36 +3681,36 @@
       <c r="F52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="85"/>
-      <c r="H52" s="86"/>
-      <c r="I52" s="86"/>
-      <c r="J52" s="86"/>
+      <c r="G52" s="86"/>
+      <c r="H52" s="85"/>
+      <c r="I52" s="85"/>
+      <c r="J52" s="85"/>
       <c r="K52" s="87"/>
       <c r="L52" s="87"/>
       <c r="M52" s="87"/>
       <c r="N52" s="88"/>
       <c r="O52" s="89"/>
-      <c r="P52" s="86"/>
-      <c r="Q52" s="86"/>
-      <c r="R52" s="86"/>
-      <c r="S52" s="86"/>
-      <c r="T52" s="86"/>
-      <c r="U52" s="86"/>
-      <c r="V52" s="86"/>
-      <c r="W52" s="86"/>
-      <c r="X52" s="86"/>
-      <c r="Y52" s="86"/>
-      <c r="Z52" s="86"/>
-      <c r="AA52" s="86"/>
-      <c r="AB52" s="86"/>
-      <c r="AC52" s="86"/>
-      <c r="AD52" s="86"/>
-      <c r="AE52" s="86"/>
-      <c r="AF52" s="86"/>
-      <c r="AG52" s="86"/>
-      <c r="AH52" s="86"/>
-      <c r="AI52" s="86"/>
-      <c r="AJ52" s="86"/>
+      <c r="P52" s="85"/>
+      <c r="Q52" s="85"/>
+      <c r="R52" s="85"/>
+      <c r="S52" s="85"/>
+      <c r="T52" s="85"/>
+      <c r="U52" s="85"/>
+      <c r="V52" s="85"/>
+      <c r="W52" s="85"/>
+      <c r="X52" s="85"/>
+      <c r="Y52" s="85"/>
+      <c r="Z52" s="85"/>
+      <c r="AA52" s="85"/>
+      <c r="AB52" s="85"/>
+      <c r="AC52" s="85"/>
+      <c r="AD52" s="85"/>
+      <c r="AE52" s="85"/>
+      <c r="AF52" s="85"/>
+      <c r="AG52" s="85"/>
+      <c r="AH52" s="85"/>
+      <c r="AI52" s="85"/>
+      <c r="AJ52" s="85"/>
       <c r="AK52" s="88"/>
       <c r="AL52" s="90"/>
       <c r="AM52" s="39"/>
@@ -3788,7 +3761,7 @@
       <c r="AM53" s="40"/>
       <c r="AN53" s="42"/>
     </row>
-    <row r="54" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="43">
         <v>24</v>
       </c>
@@ -3800,36 +3773,36 @@
       <c r="F54" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="85"/>
-      <c r="H54" s="86"/>
-      <c r="I54" s="86"/>
-      <c r="J54" s="86"/>
+      <c r="G54" s="86"/>
+      <c r="H54" s="85"/>
+      <c r="I54" s="85"/>
+      <c r="J54" s="85"/>
       <c r="K54" s="87"/>
       <c r="L54" s="87"/>
       <c r="M54" s="87"/>
       <c r="N54" s="88"/>
       <c r="O54" s="89"/>
-      <c r="P54" s="86"/>
-      <c r="Q54" s="86"/>
-      <c r="R54" s="86"/>
-      <c r="S54" s="86"/>
-      <c r="T54" s="86"/>
-      <c r="U54" s="86"/>
-      <c r="V54" s="86"/>
-      <c r="W54" s="86"/>
-      <c r="X54" s="86"/>
-      <c r="Y54" s="86"/>
-      <c r="Z54" s="86"/>
-      <c r="AA54" s="86"/>
-      <c r="AB54" s="86"/>
-      <c r="AC54" s="86"/>
-      <c r="AD54" s="86"/>
-      <c r="AE54" s="86"/>
-      <c r="AF54" s="86"/>
-      <c r="AG54" s="86"/>
-      <c r="AH54" s="86"/>
-      <c r="AI54" s="86"/>
-      <c r="AJ54" s="86"/>
+      <c r="P54" s="85"/>
+      <c r="Q54" s="85"/>
+      <c r="R54" s="85"/>
+      <c r="S54" s="85"/>
+      <c r="T54" s="85"/>
+      <c r="U54" s="85"/>
+      <c r="V54" s="85"/>
+      <c r="W54" s="85"/>
+      <c r="X54" s="85"/>
+      <c r="Y54" s="85"/>
+      <c r="Z54" s="85"/>
+      <c r="AA54" s="85"/>
+      <c r="AB54" s="85"/>
+      <c r="AC54" s="85"/>
+      <c r="AD54" s="85"/>
+      <c r="AE54" s="85"/>
+      <c r="AF54" s="85"/>
+      <c r="AG54" s="85"/>
+      <c r="AH54" s="85"/>
+      <c r="AI54" s="85"/>
+      <c r="AJ54" s="85"/>
       <c r="AK54" s="88"/>
       <c r="AL54" s="90"/>
       <c r="AM54" s="39"/>
@@ -3880,7 +3853,7 @@
       <c r="AM55" s="40"/>
       <c r="AN55" s="42"/>
     </row>
-    <row r="56" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="33">
         <v>25</v>
       </c>
@@ -3892,36 +3865,36 @@
       <c r="F56" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="85"/>
-      <c r="H56" s="86"/>
-      <c r="I56" s="86"/>
-      <c r="J56" s="86"/>
+      <c r="G56" s="86"/>
+      <c r="H56" s="85"/>
+      <c r="I56" s="85"/>
+      <c r="J56" s="85"/>
       <c r="K56" s="87"/>
       <c r="L56" s="87"/>
       <c r="M56" s="87"/>
       <c r="N56" s="88"/>
       <c r="O56" s="89"/>
-      <c r="P56" s="86"/>
-      <c r="Q56" s="86"/>
-      <c r="R56" s="86"/>
-      <c r="S56" s="86"/>
-      <c r="T56" s="86"/>
-      <c r="U56" s="86"/>
-      <c r="V56" s="86"/>
-      <c r="W56" s="86"/>
-      <c r="X56" s="86"/>
-      <c r="Y56" s="86"/>
-      <c r="Z56" s="86"/>
-      <c r="AA56" s="86"/>
-      <c r="AB56" s="86"/>
-      <c r="AC56" s="86"/>
-      <c r="AD56" s="86"/>
-      <c r="AE56" s="86"/>
-      <c r="AF56" s="86"/>
-      <c r="AG56" s="86"/>
-      <c r="AH56" s="86"/>
-      <c r="AI56" s="86"/>
-      <c r="AJ56" s="86"/>
+      <c r="P56" s="85"/>
+      <c r="Q56" s="85"/>
+      <c r="R56" s="85"/>
+      <c r="S56" s="85"/>
+      <c r="T56" s="85"/>
+      <c r="U56" s="85"/>
+      <c r="V56" s="85"/>
+      <c r="W56" s="85"/>
+      <c r="X56" s="85"/>
+      <c r="Y56" s="85"/>
+      <c r="Z56" s="85"/>
+      <c r="AA56" s="85"/>
+      <c r="AB56" s="85"/>
+      <c r="AC56" s="85"/>
+      <c r="AD56" s="85"/>
+      <c r="AE56" s="85"/>
+      <c r="AF56" s="85"/>
+      <c r="AG56" s="85"/>
+      <c r="AH56" s="85"/>
+      <c r="AI56" s="85"/>
+      <c r="AJ56" s="85"/>
       <c r="AK56" s="88"/>
       <c r="AL56" s="90"/>
       <c r="AM56" s="39"/>
@@ -3972,7 +3945,7 @@
       <c r="AM57" s="40"/>
       <c r="AN57" s="42"/>
     </row>
-    <row r="58" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="43">
         <v>26</v>
       </c>
@@ -3984,36 +3957,36 @@
       <c r="F58" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="85"/>
-      <c r="H58" s="86"/>
-      <c r="I58" s="86"/>
-      <c r="J58" s="86"/>
+      <c r="G58" s="86"/>
+      <c r="H58" s="85"/>
+      <c r="I58" s="85"/>
+      <c r="J58" s="85"/>
       <c r="K58" s="87"/>
       <c r="L58" s="87"/>
       <c r="M58" s="87"/>
       <c r="N58" s="88"/>
       <c r="O58" s="89"/>
-      <c r="P58" s="86"/>
-      <c r="Q58" s="86"/>
-      <c r="R58" s="86"/>
-      <c r="S58" s="86"/>
-      <c r="T58" s="86"/>
-      <c r="U58" s="86"/>
-      <c r="V58" s="86"/>
-      <c r="W58" s="86"/>
-      <c r="X58" s="86"/>
-      <c r="Y58" s="86"/>
-      <c r="Z58" s="86"/>
-      <c r="AA58" s="86"/>
-      <c r="AB58" s="86"/>
-      <c r="AC58" s="86"/>
-      <c r="AD58" s="86"/>
-      <c r="AE58" s="86"/>
-      <c r="AF58" s="86"/>
-      <c r="AG58" s="86"/>
-      <c r="AH58" s="86"/>
-      <c r="AI58" s="86"/>
-      <c r="AJ58" s="86"/>
+      <c r="P58" s="85"/>
+      <c r="Q58" s="85"/>
+      <c r="R58" s="85"/>
+      <c r="S58" s="85"/>
+      <c r="T58" s="85"/>
+      <c r="U58" s="85"/>
+      <c r="V58" s="85"/>
+      <c r="W58" s="85"/>
+      <c r="X58" s="85"/>
+      <c r="Y58" s="85"/>
+      <c r="Z58" s="85"/>
+      <c r="AA58" s="85"/>
+      <c r="AB58" s="85"/>
+      <c r="AC58" s="85"/>
+      <c r="AD58" s="85"/>
+      <c r="AE58" s="85"/>
+      <c r="AF58" s="85"/>
+      <c r="AG58" s="85"/>
+      <c r="AH58" s="85"/>
+      <c r="AI58" s="85"/>
+      <c r="AJ58" s="85"/>
       <c r="AK58" s="88"/>
       <c r="AL58" s="90"/>
       <c r="AM58" s="39"/>
@@ -4064,7 +4037,7 @@
       <c r="AM59" s="40"/>
       <c r="AN59" s="42"/>
     </row>
-    <row r="60" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="33">
         <v>27</v>
       </c>
@@ -4076,36 +4049,36 @@
       <c r="F60" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="85"/>
-      <c r="H60" s="86"/>
-      <c r="I60" s="86"/>
-      <c r="J60" s="86"/>
+      <c r="G60" s="86"/>
+      <c r="H60" s="85"/>
+      <c r="I60" s="85"/>
+      <c r="J60" s="85"/>
       <c r="K60" s="87"/>
       <c r="L60" s="87"/>
       <c r="M60" s="87"/>
       <c r="N60" s="88"/>
       <c r="O60" s="89"/>
-      <c r="P60" s="86"/>
-      <c r="Q60" s="86"/>
-      <c r="R60" s="86"/>
-      <c r="S60" s="86"/>
-      <c r="T60" s="86"/>
-      <c r="U60" s="86"/>
-      <c r="V60" s="86"/>
-      <c r="W60" s="86"/>
-      <c r="X60" s="86"/>
-      <c r="Y60" s="86"/>
-      <c r="Z60" s="86"/>
-      <c r="AA60" s="86"/>
-      <c r="AB60" s="86"/>
-      <c r="AC60" s="86"/>
-      <c r="AD60" s="86"/>
-      <c r="AE60" s="86"/>
-      <c r="AF60" s="86"/>
-      <c r="AG60" s="86"/>
-      <c r="AH60" s="86"/>
-      <c r="AI60" s="86"/>
-      <c r="AJ60" s="86"/>
+      <c r="P60" s="85"/>
+      <c r="Q60" s="85"/>
+      <c r="R60" s="85"/>
+      <c r="S60" s="85"/>
+      <c r="T60" s="85"/>
+      <c r="U60" s="85"/>
+      <c r="V60" s="85"/>
+      <c r="W60" s="85"/>
+      <c r="X60" s="85"/>
+      <c r="Y60" s="85"/>
+      <c r="Z60" s="85"/>
+      <c r="AA60" s="85"/>
+      <c r="AB60" s="85"/>
+      <c r="AC60" s="85"/>
+      <c r="AD60" s="85"/>
+      <c r="AE60" s="85"/>
+      <c r="AF60" s="85"/>
+      <c r="AG60" s="85"/>
+      <c r="AH60" s="85"/>
+      <c r="AI60" s="85"/>
+      <c r="AJ60" s="85"/>
       <c r="AK60" s="88"/>
       <c r="AL60" s="90"/>
       <c r="AM60" s="39"/>
@@ -4156,7 +4129,7 @@
       <c r="AM61" s="40"/>
       <c r="AN61" s="42"/>
     </row>
-    <row r="62" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="43">
         <v>28</v>
       </c>
@@ -4168,36 +4141,36 @@
       <c r="F62" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="85"/>
-      <c r="H62" s="86"/>
-      <c r="I62" s="86"/>
-      <c r="J62" s="86"/>
+      <c r="G62" s="86"/>
+      <c r="H62" s="85"/>
+      <c r="I62" s="85"/>
+      <c r="J62" s="85"/>
       <c r="K62" s="87"/>
       <c r="L62" s="87"/>
       <c r="M62" s="87"/>
       <c r="N62" s="88"/>
       <c r="O62" s="89"/>
-      <c r="P62" s="86"/>
-      <c r="Q62" s="86"/>
-      <c r="R62" s="86"/>
-      <c r="S62" s="86"/>
-      <c r="T62" s="86"/>
-      <c r="U62" s="86"/>
-      <c r="V62" s="86"/>
-      <c r="W62" s="86"/>
-      <c r="X62" s="86"/>
-      <c r="Y62" s="86"/>
-      <c r="Z62" s="86"/>
-      <c r="AA62" s="86"/>
-      <c r="AB62" s="86"/>
-      <c r="AC62" s="86"/>
-      <c r="AD62" s="86"/>
-      <c r="AE62" s="86"/>
-      <c r="AF62" s="86"/>
-      <c r="AG62" s="86"/>
-      <c r="AH62" s="86"/>
-      <c r="AI62" s="86"/>
-      <c r="AJ62" s="86"/>
+      <c r="P62" s="85"/>
+      <c r="Q62" s="85"/>
+      <c r="R62" s="85"/>
+      <c r="S62" s="85"/>
+      <c r="T62" s="85"/>
+      <c r="U62" s="85"/>
+      <c r="V62" s="85"/>
+      <c r="W62" s="85"/>
+      <c r="X62" s="85"/>
+      <c r="Y62" s="85"/>
+      <c r="Z62" s="85"/>
+      <c r="AA62" s="85"/>
+      <c r="AB62" s="85"/>
+      <c r="AC62" s="85"/>
+      <c r="AD62" s="85"/>
+      <c r="AE62" s="85"/>
+      <c r="AF62" s="85"/>
+      <c r="AG62" s="85"/>
+      <c r="AH62" s="85"/>
+      <c r="AI62" s="85"/>
+      <c r="AJ62" s="85"/>
       <c r="AK62" s="88"/>
       <c r="AL62" s="90"/>
       <c r="AM62" s="39"/>
@@ -4248,7 +4221,7 @@
       <c r="AM63" s="40"/>
       <c r="AN63" s="42"/>
     </row>
-    <row r="64" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="33">
         <v>29</v>
       </c>
@@ -4260,36 +4233,36 @@
       <c r="F64" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="85"/>
-      <c r="H64" s="86"/>
-      <c r="I64" s="86"/>
-      <c r="J64" s="86"/>
+      <c r="G64" s="86"/>
+      <c r="H64" s="85"/>
+      <c r="I64" s="85"/>
+      <c r="J64" s="85"/>
       <c r="K64" s="87"/>
       <c r="L64" s="87"/>
       <c r="M64" s="87"/>
       <c r="N64" s="88"/>
       <c r="O64" s="89"/>
-      <c r="P64" s="86"/>
-      <c r="Q64" s="86"/>
-      <c r="R64" s="86"/>
-      <c r="S64" s="86"/>
-      <c r="T64" s="86"/>
-      <c r="U64" s="86"/>
-      <c r="V64" s="86"/>
-      <c r="W64" s="86"/>
-      <c r="X64" s="86"/>
-      <c r="Y64" s="86"/>
-      <c r="Z64" s="86"/>
-      <c r="AA64" s="86"/>
-      <c r="AB64" s="86"/>
-      <c r="AC64" s="86"/>
-      <c r="AD64" s="86"/>
-      <c r="AE64" s="86"/>
-      <c r="AF64" s="86"/>
-      <c r="AG64" s="86"/>
-      <c r="AH64" s="86"/>
-      <c r="AI64" s="86"/>
-      <c r="AJ64" s="86"/>
+      <c r="P64" s="85"/>
+      <c r="Q64" s="85"/>
+      <c r="R64" s="85"/>
+      <c r="S64" s="85"/>
+      <c r="T64" s="85"/>
+      <c r="U64" s="85"/>
+      <c r="V64" s="85"/>
+      <c r="W64" s="85"/>
+      <c r="X64" s="85"/>
+      <c r="Y64" s="85"/>
+      <c r="Z64" s="85"/>
+      <c r="AA64" s="85"/>
+      <c r="AB64" s="85"/>
+      <c r="AC64" s="85"/>
+      <c r="AD64" s="85"/>
+      <c r="AE64" s="85"/>
+      <c r="AF64" s="85"/>
+      <c r="AG64" s="85"/>
+      <c r="AH64" s="85"/>
+      <c r="AI64" s="85"/>
+      <c r="AJ64" s="85"/>
       <c r="AK64" s="88"/>
       <c r="AL64" s="90"/>
       <c r="AM64" s="39"/>
@@ -4340,7 +4313,7 @@
       <c r="AM65" s="40"/>
       <c r="AN65" s="42"/>
     </row>
-    <row r="66" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B66" s="43">
         <v>30</v>
       </c>
@@ -4352,36 +4325,36 @@
       <c r="F66" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="85"/>
-      <c r="H66" s="86"/>
-      <c r="I66" s="86"/>
-      <c r="J66" s="86"/>
+      <c r="G66" s="86"/>
+      <c r="H66" s="85"/>
+      <c r="I66" s="85"/>
+      <c r="J66" s="85"/>
       <c r="K66" s="87"/>
       <c r="L66" s="87"/>
       <c r="M66" s="87"/>
       <c r="N66" s="88"/>
       <c r="O66" s="89"/>
-      <c r="P66" s="86"/>
-      <c r="Q66" s="86"/>
-      <c r="R66" s="86"/>
-      <c r="S66" s="86"/>
-      <c r="T66" s="86"/>
-      <c r="U66" s="86"/>
-      <c r="V66" s="86"/>
-      <c r="W66" s="86"/>
-      <c r="X66" s="86"/>
-      <c r="Y66" s="86"/>
-      <c r="Z66" s="86"/>
-      <c r="AA66" s="86"/>
-      <c r="AB66" s="86"/>
-      <c r="AC66" s="86"/>
-      <c r="AD66" s="86"/>
-      <c r="AE66" s="86"/>
-      <c r="AF66" s="86"/>
-      <c r="AG66" s="86"/>
-      <c r="AH66" s="86"/>
-      <c r="AI66" s="86"/>
-      <c r="AJ66" s="86"/>
+      <c r="P66" s="85"/>
+      <c r="Q66" s="85"/>
+      <c r="R66" s="85"/>
+      <c r="S66" s="85"/>
+      <c r="T66" s="85"/>
+      <c r="U66" s="85"/>
+      <c r="V66" s="85"/>
+      <c r="W66" s="85"/>
+      <c r="X66" s="85"/>
+      <c r="Y66" s="85"/>
+      <c r="Z66" s="85"/>
+      <c r="AA66" s="85"/>
+      <c r="AB66" s="85"/>
+      <c r="AC66" s="85"/>
+      <c r="AD66" s="85"/>
+      <c r="AE66" s="85"/>
+      <c r="AF66" s="85"/>
+      <c r="AG66" s="85"/>
+      <c r="AH66" s="85"/>
+      <c r="AI66" s="85"/>
+      <c r="AJ66" s="85"/>
       <c r="AK66" s="88"/>
       <c r="AL66" s="90"/>
       <c r="AM66" s="39"/>
@@ -4432,7 +4405,7 @@
       <c r="AM67" s="40"/>
       <c r="AN67" s="42"/>
     </row>
-    <row r="68" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="33">
         <v>31</v>
       </c>
@@ -4444,36 +4417,36 @@
       <c r="F68" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="85"/>
-      <c r="H68" s="86"/>
-      <c r="I68" s="86"/>
-      <c r="J68" s="86"/>
+      <c r="G68" s="86"/>
+      <c r="H68" s="85"/>
+      <c r="I68" s="85"/>
+      <c r="J68" s="85"/>
       <c r="K68" s="87"/>
       <c r="L68" s="87"/>
       <c r="M68" s="87"/>
       <c r="N68" s="88"/>
       <c r="O68" s="89"/>
-      <c r="P68" s="86"/>
-      <c r="Q68" s="86"/>
-      <c r="R68" s="86"/>
-      <c r="S68" s="86"/>
-      <c r="T68" s="86"/>
-      <c r="U68" s="86"/>
-      <c r="V68" s="86"/>
-      <c r="W68" s="86"/>
-      <c r="X68" s="86"/>
-      <c r="Y68" s="86"/>
-      <c r="Z68" s="86"/>
-      <c r="AA68" s="86"/>
-      <c r="AB68" s="86"/>
-      <c r="AC68" s="86"/>
-      <c r="AD68" s="86"/>
-      <c r="AE68" s="86"/>
-      <c r="AF68" s="86"/>
-      <c r="AG68" s="86"/>
-      <c r="AH68" s="86"/>
-      <c r="AI68" s="86"/>
-      <c r="AJ68" s="86"/>
+      <c r="P68" s="85"/>
+      <c r="Q68" s="85"/>
+      <c r="R68" s="85"/>
+      <c r="S68" s="85"/>
+      <c r="T68" s="85"/>
+      <c r="U68" s="85"/>
+      <c r="V68" s="85"/>
+      <c r="W68" s="85"/>
+      <c r="X68" s="85"/>
+      <c r="Y68" s="85"/>
+      <c r="Z68" s="85"/>
+      <c r="AA68" s="85"/>
+      <c r="AB68" s="85"/>
+      <c r="AC68" s="85"/>
+      <c r="AD68" s="85"/>
+      <c r="AE68" s="85"/>
+      <c r="AF68" s="85"/>
+      <c r="AG68" s="85"/>
+      <c r="AH68" s="85"/>
+      <c r="AI68" s="85"/>
+      <c r="AJ68" s="85"/>
       <c r="AK68" s="88"/>
       <c r="AL68" s="90"/>
       <c r="AM68" s="39"/>
@@ -4524,7 +4497,7 @@
       <c r="AM69" s="40"/>
       <c r="AN69" s="42"/>
     </row>
-    <row r="70" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="43">
         <v>32</v>
       </c>
@@ -4536,36 +4509,36 @@
       <c r="F70" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="85"/>
-      <c r="H70" s="86"/>
-      <c r="I70" s="86"/>
-      <c r="J70" s="86"/>
+      <c r="G70" s="86"/>
+      <c r="H70" s="85"/>
+      <c r="I70" s="85"/>
+      <c r="J70" s="85"/>
       <c r="K70" s="87"/>
       <c r="L70" s="87"/>
       <c r="M70" s="87"/>
       <c r="N70" s="88"/>
       <c r="O70" s="89"/>
-      <c r="P70" s="86"/>
-      <c r="Q70" s="86"/>
-      <c r="R70" s="86"/>
-      <c r="S70" s="86"/>
-      <c r="T70" s="86"/>
-      <c r="U70" s="86"/>
-      <c r="V70" s="86"/>
-      <c r="W70" s="86"/>
-      <c r="X70" s="86"/>
-      <c r="Y70" s="86"/>
-      <c r="Z70" s="86"/>
-      <c r="AA70" s="86"/>
-      <c r="AB70" s="86"/>
-      <c r="AC70" s="86"/>
-      <c r="AD70" s="86"/>
-      <c r="AE70" s="86"/>
-      <c r="AF70" s="86"/>
-      <c r="AG70" s="86"/>
-      <c r="AH70" s="86"/>
-      <c r="AI70" s="86"/>
-      <c r="AJ70" s="86"/>
+      <c r="P70" s="85"/>
+      <c r="Q70" s="85"/>
+      <c r="R70" s="85"/>
+      <c r="S70" s="85"/>
+      <c r="T70" s="85"/>
+      <c r="U70" s="85"/>
+      <c r="V70" s="85"/>
+      <c r="W70" s="85"/>
+      <c r="X70" s="85"/>
+      <c r="Y70" s="85"/>
+      <c r="Z70" s="85"/>
+      <c r="AA70" s="85"/>
+      <c r="AB70" s="85"/>
+      <c r="AC70" s="85"/>
+      <c r="AD70" s="85"/>
+      <c r="AE70" s="85"/>
+      <c r="AF70" s="85"/>
+      <c r="AG70" s="85"/>
+      <c r="AH70" s="85"/>
+      <c r="AI70" s="85"/>
+      <c r="AJ70" s="85"/>
       <c r="AK70" s="88"/>
       <c r="AL70" s="90"/>
       <c r="AM70" s="39"/>
@@ -4616,7 +4589,7 @@
       <c r="AM71" s="40"/>
       <c r="AN71" s="42"/>
     </row>
-    <row r="72" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="33">
         <v>33</v>
       </c>
@@ -4628,36 +4601,36 @@
       <c r="F72" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="85"/>
-      <c r="H72" s="86"/>
-      <c r="I72" s="86"/>
-      <c r="J72" s="86"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="85"/>
+      <c r="I72" s="85"/>
+      <c r="J72" s="85"/>
       <c r="K72" s="87"/>
       <c r="L72" s="87"/>
       <c r="M72" s="87"/>
       <c r="N72" s="88"/>
       <c r="O72" s="89"/>
-      <c r="P72" s="86"/>
-      <c r="Q72" s="86"/>
-      <c r="R72" s="86"/>
-      <c r="S72" s="86"/>
-      <c r="T72" s="86"/>
-      <c r="U72" s="86"/>
-      <c r="V72" s="86"/>
-      <c r="W72" s="86"/>
-      <c r="X72" s="86"/>
-      <c r="Y72" s="86"/>
-      <c r="Z72" s="86"/>
-      <c r="AA72" s="86"/>
-      <c r="AB72" s="86"/>
-      <c r="AC72" s="86"/>
-      <c r="AD72" s="86"/>
-      <c r="AE72" s="86"/>
-      <c r="AF72" s="86"/>
-      <c r="AG72" s="86"/>
-      <c r="AH72" s="86"/>
-      <c r="AI72" s="86"/>
-      <c r="AJ72" s="86"/>
+      <c r="P72" s="85"/>
+      <c r="Q72" s="85"/>
+      <c r="R72" s="85"/>
+      <c r="S72" s="85"/>
+      <c r="T72" s="85"/>
+      <c r="U72" s="85"/>
+      <c r="V72" s="85"/>
+      <c r="W72" s="85"/>
+      <c r="X72" s="85"/>
+      <c r="Y72" s="85"/>
+      <c r="Z72" s="85"/>
+      <c r="AA72" s="85"/>
+      <c r="AB72" s="85"/>
+      <c r="AC72" s="85"/>
+      <c r="AD72" s="85"/>
+      <c r="AE72" s="85"/>
+      <c r="AF72" s="85"/>
+      <c r="AG72" s="85"/>
+      <c r="AH72" s="85"/>
+      <c r="AI72" s="85"/>
+      <c r="AJ72" s="85"/>
       <c r="AK72" s="88"/>
       <c r="AL72" s="90"/>
       <c r="AM72" s="39"/>
@@ -4708,7 +4681,7 @@
       <c r="AM73" s="40"/>
       <c r="AN73" s="42"/>
     </row>
-    <row r="74" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="43">
         <v>34</v>
       </c>
@@ -4720,36 +4693,36 @@
       <c r="F74" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="85"/>
-      <c r="H74" s="86"/>
-      <c r="I74" s="86"/>
-      <c r="J74" s="86"/>
+      <c r="G74" s="86"/>
+      <c r="H74" s="85"/>
+      <c r="I74" s="85"/>
+      <c r="J74" s="85"/>
       <c r="K74" s="87"/>
       <c r="L74" s="87"/>
       <c r="M74" s="87"/>
       <c r="N74" s="88"/>
       <c r="O74" s="89"/>
-      <c r="P74" s="86"/>
-      <c r="Q74" s="86"/>
-      <c r="R74" s="86"/>
-      <c r="S74" s="86"/>
-      <c r="T74" s="86"/>
-      <c r="U74" s="86"/>
-      <c r="V74" s="86"/>
-      <c r="W74" s="86"/>
-      <c r="X74" s="86"/>
-      <c r="Y74" s="86"/>
-      <c r="Z74" s="86"/>
-      <c r="AA74" s="86"/>
-      <c r="AB74" s="86"/>
-      <c r="AC74" s="86"/>
-      <c r="AD74" s="86"/>
-      <c r="AE74" s="86"/>
-      <c r="AF74" s="86"/>
-      <c r="AG74" s="86"/>
-      <c r="AH74" s="86"/>
-      <c r="AI74" s="86"/>
-      <c r="AJ74" s="86"/>
+      <c r="P74" s="85"/>
+      <c r="Q74" s="85"/>
+      <c r="R74" s="85"/>
+      <c r="S74" s="85"/>
+      <c r="T74" s="85"/>
+      <c r="U74" s="85"/>
+      <c r="V74" s="85"/>
+      <c r="W74" s="85"/>
+      <c r="X74" s="85"/>
+      <c r="Y74" s="85"/>
+      <c r="Z74" s="85"/>
+      <c r="AA74" s="85"/>
+      <c r="AB74" s="85"/>
+      <c r="AC74" s="85"/>
+      <c r="AD74" s="85"/>
+      <c r="AE74" s="85"/>
+      <c r="AF74" s="85"/>
+      <c r="AG74" s="85"/>
+      <c r="AH74" s="85"/>
+      <c r="AI74" s="85"/>
+      <c r="AJ74" s="85"/>
       <c r="AK74" s="88"/>
       <c r="AL74" s="90"/>
       <c r="AM74" s="39"/>
@@ -4800,7 +4773,7 @@
       <c r="AM75" s="40"/>
       <c r="AN75" s="42"/>
     </row>
-    <row r="76" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B76" s="33">
         <v>35</v>
       </c>
@@ -4812,36 +4785,36 @@
       <c r="F76" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="85"/>
-      <c r="H76" s="86"/>
-      <c r="I76" s="86"/>
-      <c r="J76" s="86"/>
+      <c r="G76" s="86"/>
+      <c r="H76" s="85"/>
+      <c r="I76" s="85"/>
+      <c r="J76" s="85"/>
       <c r="K76" s="87"/>
       <c r="L76" s="87"/>
       <c r="M76" s="87"/>
       <c r="N76" s="88"/>
       <c r="O76" s="89"/>
-      <c r="P76" s="86"/>
-      <c r="Q76" s="86"/>
-      <c r="R76" s="86"/>
-      <c r="S76" s="86"/>
-      <c r="T76" s="86"/>
-      <c r="U76" s="86"/>
-      <c r="V76" s="86"/>
-      <c r="W76" s="86"/>
-      <c r="X76" s="86"/>
-      <c r="Y76" s="86"/>
-      <c r="Z76" s="86"/>
-      <c r="AA76" s="86"/>
-      <c r="AB76" s="86"/>
-      <c r="AC76" s="86"/>
-      <c r="AD76" s="86"/>
-      <c r="AE76" s="86"/>
-      <c r="AF76" s="86"/>
-      <c r="AG76" s="86"/>
-      <c r="AH76" s="86"/>
-      <c r="AI76" s="86"/>
-      <c r="AJ76" s="86"/>
+      <c r="P76" s="85"/>
+      <c r="Q76" s="85"/>
+      <c r="R76" s="85"/>
+      <c r="S76" s="85"/>
+      <c r="T76" s="85"/>
+      <c r="U76" s="85"/>
+      <c r="V76" s="85"/>
+      <c r="W76" s="85"/>
+      <c r="X76" s="85"/>
+      <c r="Y76" s="85"/>
+      <c r="Z76" s="85"/>
+      <c r="AA76" s="85"/>
+      <c r="AB76" s="85"/>
+      <c r="AC76" s="85"/>
+      <c r="AD76" s="85"/>
+      <c r="AE76" s="85"/>
+      <c r="AF76" s="85"/>
+      <c r="AG76" s="85"/>
+      <c r="AH76" s="85"/>
+      <c r="AI76" s="85"/>
+      <c r="AJ76" s="85"/>
       <c r="AK76" s="88"/>
       <c r="AL76" s="90"/>
       <c r="AM76" s="39"/>
@@ -4892,7 +4865,7 @@
       <c r="AM77" s="40"/>
       <c r="AN77" s="42"/>
     </row>
-    <row r="78" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="43">
         <v>36</v>
       </c>
@@ -4904,36 +4877,36 @@
       <c r="F78" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="85"/>
-      <c r="H78" s="86"/>
-      <c r="I78" s="86"/>
-      <c r="J78" s="86"/>
+      <c r="G78" s="86"/>
+      <c r="H78" s="85"/>
+      <c r="I78" s="85"/>
+      <c r="J78" s="85"/>
       <c r="K78" s="87"/>
       <c r="L78" s="87"/>
       <c r="M78" s="87"/>
       <c r="N78" s="88"/>
       <c r="O78" s="89"/>
-      <c r="P78" s="86"/>
-      <c r="Q78" s="86"/>
-      <c r="R78" s="86"/>
-      <c r="S78" s="86"/>
-      <c r="T78" s="86"/>
-      <c r="U78" s="86"/>
-      <c r="V78" s="86"/>
-      <c r="W78" s="86"/>
-      <c r="X78" s="86"/>
-      <c r="Y78" s="86"/>
-      <c r="Z78" s="86"/>
-      <c r="AA78" s="86"/>
-      <c r="AB78" s="86"/>
-      <c r="AC78" s="86"/>
-      <c r="AD78" s="86"/>
-      <c r="AE78" s="86"/>
-      <c r="AF78" s="86"/>
-      <c r="AG78" s="86"/>
-      <c r="AH78" s="86"/>
-      <c r="AI78" s="86"/>
-      <c r="AJ78" s="86"/>
+      <c r="P78" s="85"/>
+      <c r="Q78" s="85"/>
+      <c r="R78" s="85"/>
+      <c r="S78" s="85"/>
+      <c r="T78" s="85"/>
+      <c r="U78" s="85"/>
+      <c r="V78" s="85"/>
+      <c r="W78" s="85"/>
+      <c r="X78" s="85"/>
+      <c r="Y78" s="85"/>
+      <c r="Z78" s="85"/>
+      <c r="AA78" s="85"/>
+      <c r="AB78" s="85"/>
+      <c r="AC78" s="85"/>
+      <c r="AD78" s="85"/>
+      <c r="AE78" s="85"/>
+      <c r="AF78" s="85"/>
+      <c r="AG78" s="85"/>
+      <c r="AH78" s="85"/>
+      <c r="AI78" s="85"/>
+      <c r="AJ78" s="85"/>
       <c r="AK78" s="88"/>
       <c r="AL78" s="90"/>
       <c r="AM78" s="39"/>
@@ -4984,7 +4957,7 @@
       <c r="AM79" s="40"/>
       <c r="AN79" s="42"/>
     </row>
-    <row r="80" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B80" s="33">
         <v>37</v>
       </c>
@@ -4996,36 +4969,36 @@
       <c r="F80" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="85"/>
-      <c r="H80" s="86"/>
-      <c r="I80" s="86"/>
-      <c r="J80" s="86"/>
+      <c r="G80" s="86"/>
+      <c r="H80" s="85"/>
+      <c r="I80" s="85"/>
+      <c r="J80" s="85"/>
       <c r="K80" s="87"/>
       <c r="L80" s="87"/>
       <c r="M80" s="87"/>
       <c r="N80" s="88"/>
       <c r="O80" s="89"/>
-      <c r="P80" s="86"/>
-      <c r="Q80" s="86"/>
-      <c r="R80" s="86"/>
-      <c r="S80" s="86"/>
-      <c r="T80" s="86"/>
-      <c r="U80" s="86"/>
-      <c r="V80" s="86"/>
-      <c r="W80" s="86"/>
-      <c r="X80" s="86"/>
-      <c r="Y80" s="86"/>
-      <c r="Z80" s="86"/>
-      <c r="AA80" s="86"/>
-      <c r="AB80" s="86"/>
-      <c r="AC80" s="86"/>
-      <c r="AD80" s="86"/>
-      <c r="AE80" s="86"/>
-      <c r="AF80" s="86"/>
-      <c r="AG80" s="86"/>
-      <c r="AH80" s="86"/>
-      <c r="AI80" s="86"/>
-      <c r="AJ80" s="86"/>
+      <c r="P80" s="85"/>
+      <c r="Q80" s="85"/>
+      <c r="R80" s="85"/>
+      <c r="S80" s="85"/>
+      <c r="T80" s="85"/>
+      <c r="U80" s="85"/>
+      <c r="V80" s="85"/>
+      <c r="W80" s="85"/>
+      <c r="X80" s="85"/>
+      <c r="Y80" s="85"/>
+      <c r="Z80" s="85"/>
+      <c r="AA80" s="85"/>
+      <c r="AB80" s="85"/>
+      <c r="AC80" s="85"/>
+      <c r="AD80" s="85"/>
+      <c r="AE80" s="85"/>
+      <c r="AF80" s="85"/>
+      <c r="AG80" s="85"/>
+      <c r="AH80" s="85"/>
+      <c r="AI80" s="85"/>
+      <c r="AJ80" s="85"/>
       <c r="AK80" s="88"/>
       <c r="AL80" s="90"/>
       <c r="AM80" s="39"/>
@@ -5076,7 +5049,7 @@
       <c r="AM81" s="40"/>
       <c r="AN81" s="42"/>
     </row>
-    <row r="82" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82" s="43">
         <v>38</v>
       </c>
@@ -5088,36 +5061,36 @@
       <c r="F82" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="85"/>
-      <c r="H82" s="86"/>
-      <c r="I82" s="86"/>
-      <c r="J82" s="86"/>
+      <c r="G82" s="86"/>
+      <c r="H82" s="85"/>
+      <c r="I82" s="85"/>
+      <c r="J82" s="85"/>
       <c r="K82" s="87"/>
       <c r="L82" s="87"/>
       <c r="M82" s="87"/>
       <c r="N82" s="88"/>
       <c r="O82" s="89"/>
-      <c r="P82" s="86"/>
-      <c r="Q82" s="86"/>
-      <c r="R82" s="86"/>
-      <c r="S82" s="86"/>
-      <c r="T82" s="86"/>
-      <c r="U82" s="86"/>
-      <c r="V82" s="86"/>
-      <c r="W82" s="86"/>
-      <c r="X82" s="86"/>
-      <c r="Y82" s="86"/>
-      <c r="Z82" s="86"/>
-      <c r="AA82" s="86"/>
-      <c r="AB82" s="86"/>
-      <c r="AC82" s="86"/>
-      <c r="AD82" s="86"/>
-      <c r="AE82" s="86"/>
-      <c r="AF82" s="86"/>
-      <c r="AG82" s="86"/>
-      <c r="AH82" s="86"/>
-      <c r="AI82" s="86"/>
-      <c r="AJ82" s="86"/>
+      <c r="P82" s="85"/>
+      <c r="Q82" s="85"/>
+      <c r="R82" s="85"/>
+      <c r="S82" s="85"/>
+      <c r="T82" s="85"/>
+      <c r="U82" s="85"/>
+      <c r="V82" s="85"/>
+      <c r="W82" s="85"/>
+      <c r="X82" s="85"/>
+      <c r="Y82" s="85"/>
+      <c r="Z82" s="85"/>
+      <c r="AA82" s="85"/>
+      <c r="AB82" s="85"/>
+      <c r="AC82" s="85"/>
+      <c r="AD82" s="85"/>
+      <c r="AE82" s="85"/>
+      <c r="AF82" s="85"/>
+      <c r="AG82" s="85"/>
+      <c r="AH82" s="85"/>
+      <c r="AI82" s="85"/>
+      <c r="AJ82" s="85"/>
       <c r="AK82" s="88"/>
       <c r="AL82" s="90"/>
       <c r="AM82" s="39"/>
@@ -5168,7 +5141,7 @@
       <c r="AM83" s="40"/>
       <c r="AN83" s="42"/>
     </row>
-    <row r="84" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B84" s="33">
         <v>39</v>
       </c>
@@ -5180,36 +5153,36 @@
       <c r="F84" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G84" s="85"/>
-      <c r="H84" s="86"/>
-      <c r="I84" s="86"/>
-      <c r="J84" s="86"/>
+      <c r="G84" s="86"/>
+      <c r="H84" s="85"/>
+      <c r="I84" s="85"/>
+      <c r="J84" s="85"/>
       <c r="K84" s="87"/>
       <c r="L84" s="87"/>
       <c r="M84" s="87"/>
       <c r="N84" s="88"/>
       <c r="O84" s="89"/>
-      <c r="P84" s="86"/>
-      <c r="Q84" s="86"/>
-      <c r="R84" s="86"/>
-      <c r="S84" s="86"/>
-      <c r="T84" s="86"/>
-      <c r="U84" s="86"/>
-      <c r="V84" s="86"/>
-      <c r="W84" s="86"/>
-      <c r="X84" s="86"/>
-      <c r="Y84" s="86"/>
-      <c r="Z84" s="86"/>
-      <c r="AA84" s="86"/>
-      <c r="AB84" s="86"/>
-      <c r="AC84" s="86"/>
-      <c r="AD84" s="86"/>
-      <c r="AE84" s="86"/>
-      <c r="AF84" s="86"/>
-      <c r="AG84" s="86"/>
-      <c r="AH84" s="86"/>
-      <c r="AI84" s="86"/>
-      <c r="AJ84" s="86"/>
+      <c r="P84" s="85"/>
+      <c r="Q84" s="85"/>
+      <c r="R84" s="85"/>
+      <c r="S84" s="85"/>
+      <c r="T84" s="85"/>
+      <c r="U84" s="85"/>
+      <c r="V84" s="85"/>
+      <c r="W84" s="85"/>
+      <c r="X84" s="85"/>
+      <c r="Y84" s="85"/>
+      <c r="Z84" s="85"/>
+      <c r="AA84" s="85"/>
+      <c r="AB84" s="85"/>
+      <c r="AC84" s="85"/>
+      <c r="AD84" s="85"/>
+      <c r="AE84" s="85"/>
+      <c r="AF84" s="85"/>
+      <c r="AG84" s="85"/>
+      <c r="AH84" s="85"/>
+      <c r="AI84" s="85"/>
+      <c r="AJ84" s="85"/>
       <c r="AK84" s="88"/>
       <c r="AL84" s="90"/>
       <c r="AM84" s="39"/>
@@ -5260,7 +5233,7 @@
       <c r="AM85" s="40"/>
       <c r="AN85" s="42"/>
     </row>
-    <row r="86" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="43">
         <v>40</v>
       </c>
@@ -5272,36 +5245,36 @@
       <c r="F86" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="85"/>
-      <c r="H86" s="86"/>
-      <c r="I86" s="86"/>
-      <c r="J86" s="86"/>
+      <c r="G86" s="86"/>
+      <c r="H86" s="85"/>
+      <c r="I86" s="85"/>
+      <c r="J86" s="85"/>
       <c r="K86" s="87"/>
       <c r="L86" s="87"/>
       <c r="M86" s="87"/>
       <c r="N86" s="88"/>
       <c r="O86" s="89"/>
-      <c r="P86" s="86"/>
-      <c r="Q86" s="86"/>
-      <c r="R86" s="86"/>
-      <c r="S86" s="86"/>
-      <c r="T86" s="86"/>
-      <c r="U86" s="86"/>
-      <c r="V86" s="86"/>
-      <c r="W86" s="86"/>
-      <c r="X86" s="86"/>
-      <c r="Y86" s="86"/>
-      <c r="Z86" s="86"/>
-      <c r="AA86" s="86"/>
-      <c r="AB86" s="86"/>
-      <c r="AC86" s="86"/>
-      <c r="AD86" s="86"/>
-      <c r="AE86" s="86"/>
-      <c r="AF86" s="86"/>
-      <c r="AG86" s="86"/>
-      <c r="AH86" s="86"/>
-      <c r="AI86" s="86"/>
-      <c r="AJ86" s="86"/>
+      <c r="P86" s="85"/>
+      <c r="Q86" s="85"/>
+      <c r="R86" s="85"/>
+      <c r="S86" s="85"/>
+      <c r="T86" s="85"/>
+      <c r="U86" s="85"/>
+      <c r="V86" s="85"/>
+      <c r="W86" s="85"/>
+      <c r="X86" s="85"/>
+      <c r="Y86" s="85"/>
+      <c r="Z86" s="85"/>
+      <c r="AA86" s="85"/>
+      <c r="AB86" s="85"/>
+      <c r="AC86" s="85"/>
+      <c r="AD86" s="85"/>
+      <c r="AE86" s="85"/>
+      <c r="AF86" s="85"/>
+      <c r="AG86" s="85"/>
+      <c r="AH86" s="85"/>
+      <c r="AI86" s="85"/>
+      <c r="AJ86" s="85"/>
       <c r="AK86" s="88"/>
       <c r="AL86" s="90"/>
       <c r="AM86" s="39"/>
@@ -5352,7 +5325,7 @@
       <c r="AM87" s="40"/>
       <c r="AN87" s="42"/>
     </row>
-    <row r="88" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="33">
         <v>41</v>
       </c>
@@ -5364,36 +5337,36 @@
       <c r="F88" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="85"/>
-      <c r="H88" s="86"/>
-      <c r="I88" s="86"/>
-      <c r="J88" s="86"/>
+      <c r="G88" s="86"/>
+      <c r="H88" s="85"/>
+      <c r="I88" s="85"/>
+      <c r="J88" s="85"/>
       <c r="K88" s="87"/>
       <c r="L88" s="87"/>
       <c r="M88" s="87"/>
       <c r="N88" s="88"/>
       <c r="O88" s="89"/>
-      <c r="P88" s="86"/>
-      <c r="Q88" s="86"/>
-      <c r="R88" s="86"/>
-      <c r="S88" s="86"/>
-      <c r="T88" s="86"/>
-      <c r="U88" s="86"/>
-      <c r="V88" s="86"/>
-      <c r="W88" s="86"/>
-      <c r="X88" s="86"/>
-      <c r="Y88" s="86"/>
-      <c r="Z88" s="86"/>
-      <c r="AA88" s="86"/>
-      <c r="AB88" s="86"/>
-      <c r="AC88" s="86"/>
-      <c r="AD88" s="86"/>
-      <c r="AE88" s="86"/>
-      <c r="AF88" s="86"/>
-      <c r="AG88" s="86"/>
-      <c r="AH88" s="86"/>
-      <c r="AI88" s="86"/>
-      <c r="AJ88" s="86"/>
+      <c r="P88" s="85"/>
+      <c r="Q88" s="85"/>
+      <c r="R88" s="85"/>
+      <c r="S88" s="85"/>
+      <c r="T88" s="85"/>
+      <c r="U88" s="85"/>
+      <c r="V88" s="85"/>
+      <c r="W88" s="85"/>
+      <c r="X88" s="85"/>
+      <c r="Y88" s="85"/>
+      <c r="Z88" s="85"/>
+      <c r="AA88" s="85"/>
+      <c r="AB88" s="85"/>
+      <c r="AC88" s="85"/>
+      <c r="AD88" s="85"/>
+      <c r="AE88" s="85"/>
+      <c r="AF88" s="85"/>
+      <c r="AG88" s="85"/>
+      <c r="AH88" s="85"/>
+      <c r="AI88" s="85"/>
+      <c r="AJ88" s="85"/>
       <c r="AK88" s="88"/>
       <c r="AL88" s="90"/>
       <c r="AM88" s="39"/>
@@ -5444,7 +5417,7 @@
       <c r="AM89" s="40"/>
       <c r="AN89" s="42"/>
     </row>
-    <row r="90" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="43">
         <v>42</v>
       </c>
@@ -5456,36 +5429,36 @@
       <c r="F90" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G90" s="85"/>
-      <c r="H90" s="86"/>
-      <c r="I90" s="86"/>
-      <c r="J90" s="86"/>
+      <c r="G90" s="86"/>
+      <c r="H90" s="85"/>
+      <c r="I90" s="85"/>
+      <c r="J90" s="85"/>
       <c r="K90" s="87"/>
       <c r="L90" s="87"/>
       <c r="M90" s="87"/>
       <c r="N90" s="88"/>
       <c r="O90" s="89"/>
-      <c r="P90" s="86"/>
-      <c r="Q90" s="86"/>
-      <c r="R90" s="86"/>
-      <c r="S90" s="86"/>
-      <c r="T90" s="86"/>
-      <c r="U90" s="86"/>
-      <c r="V90" s="86"/>
-      <c r="W90" s="86"/>
-      <c r="X90" s="86"/>
-      <c r="Y90" s="86"/>
-      <c r="Z90" s="86"/>
-      <c r="AA90" s="86"/>
-      <c r="AB90" s="86"/>
-      <c r="AC90" s="86"/>
-      <c r="AD90" s="86"/>
-      <c r="AE90" s="86"/>
-      <c r="AF90" s="86"/>
-      <c r="AG90" s="86"/>
-      <c r="AH90" s="86"/>
-      <c r="AI90" s="86"/>
-      <c r="AJ90" s="86"/>
+      <c r="P90" s="85"/>
+      <c r="Q90" s="85"/>
+      <c r="R90" s="85"/>
+      <c r="S90" s="85"/>
+      <c r="T90" s="85"/>
+      <c r="U90" s="85"/>
+      <c r="V90" s="85"/>
+      <c r="W90" s="85"/>
+      <c r="X90" s="85"/>
+      <c r="Y90" s="85"/>
+      <c r="Z90" s="85"/>
+      <c r="AA90" s="85"/>
+      <c r="AB90" s="85"/>
+      <c r="AC90" s="85"/>
+      <c r="AD90" s="85"/>
+      <c r="AE90" s="85"/>
+      <c r="AF90" s="85"/>
+      <c r="AG90" s="85"/>
+      <c r="AH90" s="85"/>
+      <c r="AI90" s="85"/>
+      <c r="AJ90" s="85"/>
       <c r="AK90" s="88"/>
       <c r="AL90" s="90"/>
       <c r="AM90" s="39"/>
@@ -5536,7 +5509,7 @@
       <c r="AM91" s="40"/>
       <c r="AN91" s="42"/>
     </row>
-    <row r="92" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B92" s="33">
         <v>43</v>
       </c>
@@ -5548,36 +5521,36 @@
       <c r="F92" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="85"/>
-      <c r="H92" s="86"/>
-      <c r="I92" s="86"/>
-      <c r="J92" s="86"/>
+      <c r="G92" s="86"/>
+      <c r="H92" s="85"/>
+      <c r="I92" s="85"/>
+      <c r="J92" s="85"/>
       <c r="K92" s="87"/>
       <c r="L92" s="87"/>
       <c r="M92" s="87"/>
       <c r="N92" s="88"/>
       <c r="O92" s="89"/>
-      <c r="P92" s="86"/>
-      <c r="Q92" s="86"/>
-      <c r="R92" s="86"/>
-      <c r="S92" s="86"/>
-      <c r="T92" s="86"/>
-      <c r="U92" s="86"/>
-      <c r="V92" s="86"/>
-      <c r="W92" s="86"/>
-      <c r="X92" s="86"/>
-      <c r="Y92" s="86"/>
-      <c r="Z92" s="86"/>
-      <c r="AA92" s="86"/>
-      <c r="AB92" s="86"/>
-      <c r="AC92" s="86"/>
-      <c r="AD92" s="86"/>
-      <c r="AE92" s="86"/>
-      <c r="AF92" s="86"/>
-      <c r="AG92" s="86"/>
-      <c r="AH92" s="86"/>
-      <c r="AI92" s="86"/>
-      <c r="AJ92" s="86"/>
+      <c r="P92" s="85"/>
+      <c r="Q92" s="85"/>
+      <c r="R92" s="85"/>
+      <c r="S92" s="85"/>
+      <c r="T92" s="85"/>
+      <c r="U92" s="85"/>
+      <c r="V92" s="85"/>
+      <c r="W92" s="85"/>
+      <c r="X92" s="85"/>
+      <c r="Y92" s="85"/>
+      <c r="Z92" s="85"/>
+      <c r="AA92" s="85"/>
+      <c r="AB92" s="85"/>
+      <c r="AC92" s="85"/>
+      <c r="AD92" s="85"/>
+      <c r="AE92" s="85"/>
+      <c r="AF92" s="85"/>
+      <c r="AG92" s="85"/>
+      <c r="AH92" s="85"/>
+      <c r="AI92" s="85"/>
+      <c r="AJ92" s="85"/>
       <c r="AK92" s="88"/>
       <c r="AL92" s="90"/>
       <c r="AM92" s="39"/>
@@ -5628,7 +5601,7 @@
       <c r="AM93" s="40"/>
       <c r="AN93" s="42"/>
     </row>
-    <row r="94" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="43">
         <v>44</v>
       </c>
@@ -5640,36 +5613,36 @@
       <c r="F94" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G94" s="85"/>
-      <c r="H94" s="86"/>
-      <c r="I94" s="86"/>
-      <c r="J94" s="86"/>
+      <c r="G94" s="86"/>
+      <c r="H94" s="85"/>
+      <c r="I94" s="85"/>
+      <c r="J94" s="85"/>
       <c r="K94" s="87"/>
       <c r="L94" s="87"/>
       <c r="M94" s="87"/>
       <c r="N94" s="88"/>
       <c r="O94" s="89"/>
-      <c r="P94" s="86"/>
-      <c r="Q94" s="86"/>
-      <c r="R94" s="86"/>
-      <c r="S94" s="86"/>
-      <c r="T94" s="86"/>
-      <c r="U94" s="86"/>
-      <c r="V94" s="86"/>
-      <c r="W94" s="86"/>
-      <c r="X94" s="86"/>
-      <c r="Y94" s="86"/>
-      <c r="Z94" s="86"/>
-      <c r="AA94" s="86"/>
-      <c r="AB94" s="86"/>
-      <c r="AC94" s="86"/>
-      <c r="AD94" s="86"/>
-      <c r="AE94" s="86"/>
-      <c r="AF94" s="86"/>
-      <c r="AG94" s="86"/>
-      <c r="AH94" s="86"/>
-      <c r="AI94" s="86"/>
-      <c r="AJ94" s="86"/>
+      <c r="P94" s="85"/>
+      <c r="Q94" s="85"/>
+      <c r="R94" s="85"/>
+      <c r="S94" s="85"/>
+      <c r="T94" s="85"/>
+      <c r="U94" s="85"/>
+      <c r="V94" s="85"/>
+      <c r="W94" s="85"/>
+      <c r="X94" s="85"/>
+      <c r="Y94" s="85"/>
+      <c r="Z94" s="85"/>
+      <c r="AA94" s="85"/>
+      <c r="AB94" s="85"/>
+      <c r="AC94" s="85"/>
+      <c r="AD94" s="85"/>
+      <c r="AE94" s="85"/>
+      <c r="AF94" s="85"/>
+      <c r="AG94" s="85"/>
+      <c r="AH94" s="85"/>
+      <c r="AI94" s="85"/>
+      <c r="AJ94" s="85"/>
       <c r="AK94" s="88"/>
       <c r="AL94" s="90"/>
       <c r="AM94" s="39"/>
@@ -5720,7 +5693,7 @@
       <c r="AM95" s="40"/>
       <c r="AN95" s="42"/>
     </row>
-    <row r="96" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B96" s="33">
         <v>45</v>
       </c>
@@ -5732,36 +5705,36 @@
       <c r="F96" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G96" s="85"/>
-      <c r="H96" s="86"/>
-      <c r="I96" s="86"/>
-      <c r="J96" s="86"/>
+      <c r="G96" s="86"/>
+      <c r="H96" s="85"/>
+      <c r="I96" s="85"/>
+      <c r="J96" s="85"/>
       <c r="K96" s="87"/>
       <c r="L96" s="87"/>
       <c r="M96" s="87"/>
       <c r="N96" s="88"/>
       <c r="O96" s="89"/>
-      <c r="P96" s="86"/>
-      <c r="Q96" s="86"/>
-      <c r="R96" s="86"/>
-      <c r="S96" s="86"/>
-      <c r="T96" s="86"/>
-      <c r="U96" s="86"/>
-      <c r="V96" s="86"/>
-      <c r="W96" s="86"/>
-      <c r="X96" s="86"/>
-      <c r="Y96" s="86"/>
-      <c r="Z96" s="86"/>
-      <c r="AA96" s="86"/>
-      <c r="AB96" s="86"/>
-      <c r="AC96" s="86"/>
-      <c r="AD96" s="86"/>
-      <c r="AE96" s="86"/>
-      <c r="AF96" s="86"/>
-      <c r="AG96" s="86"/>
-      <c r="AH96" s="86"/>
-      <c r="AI96" s="86"/>
-      <c r="AJ96" s="86"/>
+      <c r="P96" s="85"/>
+      <c r="Q96" s="85"/>
+      <c r="R96" s="85"/>
+      <c r="S96" s="85"/>
+      <c r="T96" s="85"/>
+      <c r="U96" s="85"/>
+      <c r="V96" s="85"/>
+      <c r="W96" s="85"/>
+      <c r="X96" s="85"/>
+      <c r="Y96" s="85"/>
+      <c r="Z96" s="85"/>
+      <c r="AA96" s="85"/>
+      <c r="AB96" s="85"/>
+      <c r="AC96" s="85"/>
+      <c r="AD96" s="85"/>
+      <c r="AE96" s="85"/>
+      <c r="AF96" s="85"/>
+      <c r="AG96" s="85"/>
+      <c r="AH96" s="85"/>
+      <c r="AI96" s="85"/>
+      <c r="AJ96" s="85"/>
       <c r="AK96" s="88"/>
       <c r="AL96" s="90"/>
       <c r="AM96" s="39"/>
@@ -5812,7 +5785,7 @@
       <c r="AM97" s="40"/>
       <c r="AN97" s="42"/>
     </row>
-    <row r="98" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B98" s="43">
         <v>46</v>
       </c>
@@ -5824,36 +5797,36 @@
       <c r="F98" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G98" s="85"/>
-      <c r="H98" s="86"/>
-      <c r="I98" s="86"/>
-      <c r="J98" s="86"/>
+      <c r="G98" s="86"/>
+      <c r="H98" s="85"/>
+      <c r="I98" s="85"/>
+      <c r="J98" s="85"/>
       <c r="K98" s="87"/>
       <c r="L98" s="87"/>
       <c r="M98" s="87"/>
       <c r="N98" s="88"/>
       <c r="O98" s="89"/>
-      <c r="P98" s="86"/>
-      <c r="Q98" s="86"/>
-      <c r="R98" s="86"/>
-      <c r="S98" s="86"/>
-      <c r="T98" s="86"/>
-      <c r="U98" s="86"/>
-      <c r="V98" s="86"/>
-      <c r="W98" s="86"/>
-      <c r="X98" s="86"/>
-      <c r="Y98" s="86"/>
-      <c r="Z98" s="86"/>
-      <c r="AA98" s="86"/>
-      <c r="AB98" s="86"/>
-      <c r="AC98" s="86"/>
-      <c r="AD98" s="86"/>
-      <c r="AE98" s="86"/>
-      <c r="AF98" s="86"/>
-      <c r="AG98" s="86"/>
-      <c r="AH98" s="86"/>
-      <c r="AI98" s="86"/>
-      <c r="AJ98" s="86"/>
+      <c r="P98" s="85"/>
+      <c r="Q98" s="85"/>
+      <c r="R98" s="85"/>
+      <c r="S98" s="85"/>
+      <c r="T98" s="85"/>
+      <c r="U98" s="85"/>
+      <c r="V98" s="85"/>
+      <c r="W98" s="85"/>
+      <c r="X98" s="85"/>
+      <c r="Y98" s="85"/>
+      <c r="Z98" s="85"/>
+      <c r="AA98" s="85"/>
+      <c r="AB98" s="85"/>
+      <c r="AC98" s="85"/>
+      <c r="AD98" s="85"/>
+      <c r="AE98" s="85"/>
+      <c r="AF98" s="85"/>
+      <c r="AG98" s="85"/>
+      <c r="AH98" s="85"/>
+      <c r="AI98" s="85"/>
+      <c r="AJ98" s="85"/>
       <c r="AK98" s="88"/>
       <c r="AL98" s="90"/>
       <c r="AM98" s="39"/>
@@ -5904,7 +5877,7 @@
       <c r="AM99" s="40"/>
       <c r="AN99" s="42"/>
     </row>
-    <row r="100" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B100" s="33">
         <v>47</v>
       </c>
@@ -5916,36 +5889,36 @@
       <c r="F100" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G100" s="85"/>
-      <c r="H100" s="86"/>
-      <c r="I100" s="86"/>
-      <c r="J100" s="86"/>
+      <c r="G100" s="86"/>
+      <c r="H100" s="85"/>
+      <c r="I100" s="85"/>
+      <c r="J100" s="85"/>
       <c r="K100" s="87"/>
       <c r="L100" s="87"/>
       <c r="M100" s="87"/>
       <c r="N100" s="88"/>
       <c r="O100" s="89"/>
-      <c r="P100" s="86"/>
-      <c r="Q100" s="86"/>
-      <c r="R100" s="86"/>
-      <c r="S100" s="86"/>
-      <c r="T100" s="86"/>
-      <c r="U100" s="86"/>
-      <c r="V100" s="86"/>
-      <c r="W100" s="86"/>
-      <c r="X100" s="86"/>
-      <c r="Y100" s="86"/>
-      <c r="Z100" s="86"/>
-      <c r="AA100" s="86"/>
-      <c r="AB100" s="86"/>
-      <c r="AC100" s="86"/>
-      <c r="AD100" s="86"/>
-      <c r="AE100" s="86"/>
-      <c r="AF100" s="86"/>
-      <c r="AG100" s="86"/>
-      <c r="AH100" s="86"/>
-      <c r="AI100" s="86"/>
-      <c r="AJ100" s="86"/>
+      <c r="P100" s="85"/>
+      <c r="Q100" s="85"/>
+      <c r="R100" s="85"/>
+      <c r="S100" s="85"/>
+      <c r="T100" s="85"/>
+      <c r="U100" s="85"/>
+      <c r="V100" s="85"/>
+      <c r="W100" s="85"/>
+      <c r="X100" s="85"/>
+      <c r="Y100" s="85"/>
+      <c r="Z100" s="85"/>
+      <c r="AA100" s="85"/>
+      <c r="AB100" s="85"/>
+      <c r="AC100" s="85"/>
+      <c r="AD100" s="85"/>
+      <c r="AE100" s="85"/>
+      <c r="AF100" s="85"/>
+      <c r="AG100" s="85"/>
+      <c r="AH100" s="85"/>
+      <c r="AI100" s="85"/>
+      <c r="AJ100" s="85"/>
       <c r="AK100" s="88"/>
       <c r="AL100" s="90"/>
       <c r="AM100" s="39"/>
@@ -5996,7 +5969,7 @@
       <c r="AM101" s="40"/>
       <c r="AN101" s="42"/>
     </row>
-    <row r="102" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B102" s="43">
         <v>48</v>
       </c>
@@ -6008,36 +5981,36 @@
       <c r="F102" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="85"/>
-      <c r="H102" s="86"/>
-      <c r="I102" s="86"/>
-      <c r="J102" s="86"/>
+      <c r="G102" s="86"/>
+      <c r="H102" s="85"/>
+      <c r="I102" s="85"/>
+      <c r="J102" s="85"/>
       <c r="K102" s="87"/>
       <c r="L102" s="87"/>
       <c r="M102" s="87"/>
       <c r="N102" s="88"/>
       <c r="O102" s="89"/>
-      <c r="P102" s="86"/>
-      <c r="Q102" s="86"/>
-      <c r="R102" s="86"/>
-      <c r="S102" s="86"/>
-      <c r="T102" s="86"/>
-      <c r="U102" s="86"/>
-      <c r="V102" s="86"/>
-      <c r="W102" s="86"/>
-      <c r="X102" s="86"/>
-      <c r="Y102" s="86"/>
-      <c r="Z102" s="86"/>
-      <c r="AA102" s="86"/>
-      <c r="AB102" s="86"/>
-      <c r="AC102" s="86"/>
-      <c r="AD102" s="86"/>
-      <c r="AE102" s="86"/>
-      <c r="AF102" s="86"/>
-      <c r="AG102" s="86"/>
-      <c r="AH102" s="86"/>
-      <c r="AI102" s="86"/>
-      <c r="AJ102" s="86"/>
+      <c r="P102" s="85"/>
+      <c r="Q102" s="85"/>
+      <c r="R102" s="85"/>
+      <c r="S102" s="85"/>
+      <c r="T102" s="85"/>
+      <c r="U102" s="85"/>
+      <c r="V102" s="85"/>
+      <c r="W102" s="85"/>
+      <c r="X102" s="85"/>
+      <c r="Y102" s="85"/>
+      <c r="Z102" s="85"/>
+      <c r="AA102" s="85"/>
+      <c r="AB102" s="85"/>
+      <c r="AC102" s="85"/>
+      <c r="AD102" s="85"/>
+      <c r="AE102" s="85"/>
+      <c r="AF102" s="85"/>
+      <c r="AG102" s="85"/>
+      <c r="AH102" s="85"/>
+      <c r="AI102" s="85"/>
+      <c r="AJ102" s="85"/>
       <c r="AK102" s="88"/>
       <c r="AL102" s="90"/>
       <c r="AM102" s="39"/>
@@ -6088,7 +6061,7 @@
       <c r="AM103" s="40"/>
       <c r="AN103" s="42"/>
     </row>
-    <row r="104" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B104" s="33">
         <v>49</v>
       </c>
@@ -6100,36 +6073,36 @@
       <c r="F104" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G104" s="85"/>
-      <c r="H104" s="86"/>
-      <c r="I104" s="86"/>
-      <c r="J104" s="86"/>
+      <c r="G104" s="86"/>
+      <c r="H104" s="85"/>
+      <c r="I104" s="85"/>
+      <c r="J104" s="85"/>
       <c r="K104" s="87"/>
       <c r="L104" s="87"/>
       <c r="M104" s="87"/>
       <c r="N104" s="88"/>
       <c r="O104" s="89"/>
-      <c r="P104" s="86"/>
-      <c r="Q104" s="86"/>
-      <c r="R104" s="86"/>
-      <c r="S104" s="86"/>
-      <c r="T104" s="86"/>
-      <c r="U104" s="86"/>
-      <c r="V104" s="86"/>
-      <c r="W104" s="86"/>
-      <c r="X104" s="86"/>
-      <c r="Y104" s="86"/>
-      <c r="Z104" s="86"/>
-      <c r="AA104" s="86"/>
-      <c r="AB104" s="86"/>
-      <c r="AC104" s="86"/>
-      <c r="AD104" s="86"/>
-      <c r="AE104" s="86"/>
-      <c r="AF104" s="86"/>
-      <c r="AG104" s="86"/>
-      <c r="AH104" s="86"/>
-      <c r="AI104" s="86"/>
-      <c r="AJ104" s="86"/>
+      <c r="P104" s="85"/>
+      <c r="Q104" s="85"/>
+      <c r="R104" s="85"/>
+      <c r="S104" s="85"/>
+      <c r="T104" s="85"/>
+      <c r="U104" s="85"/>
+      <c r="V104" s="85"/>
+      <c r="W104" s="85"/>
+      <c r="X104" s="85"/>
+      <c r="Y104" s="85"/>
+      <c r="Z104" s="85"/>
+      <c r="AA104" s="85"/>
+      <c r="AB104" s="85"/>
+      <c r="AC104" s="85"/>
+      <c r="AD104" s="85"/>
+      <c r="AE104" s="85"/>
+      <c r="AF104" s="85"/>
+      <c r="AG104" s="85"/>
+      <c r="AH104" s="85"/>
+      <c r="AI104" s="85"/>
+      <c r="AJ104" s="85"/>
       <c r="AK104" s="88"/>
       <c r="AL104" s="90"/>
       <c r="AM104" s="39"/>
@@ -6180,7 +6153,7 @@
       <c r="AM105" s="40"/>
       <c r="AN105" s="42"/>
     </row>
-    <row r="106" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B106" s="43">
         <v>50</v>
       </c>
@@ -6192,36 +6165,36 @@
       <c r="F106" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G106" s="85"/>
-      <c r="H106" s="86"/>
-      <c r="I106" s="86"/>
-      <c r="J106" s="86"/>
+      <c r="G106" s="86"/>
+      <c r="H106" s="85"/>
+      <c r="I106" s="85"/>
+      <c r="J106" s="85"/>
       <c r="K106" s="87"/>
       <c r="L106" s="87"/>
       <c r="M106" s="87"/>
       <c r="N106" s="88"/>
       <c r="O106" s="89"/>
-      <c r="P106" s="86"/>
-      <c r="Q106" s="86"/>
-      <c r="R106" s="86"/>
-      <c r="S106" s="86"/>
-      <c r="T106" s="86"/>
-      <c r="U106" s="86"/>
-      <c r="V106" s="86"/>
-      <c r="W106" s="86"/>
-      <c r="X106" s="86"/>
-      <c r="Y106" s="86"/>
-      <c r="Z106" s="86"/>
-      <c r="AA106" s="86"/>
-      <c r="AB106" s="86"/>
-      <c r="AC106" s="86"/>
-      <c r="AD106" s="86"/>
-      <c r="AE106" s="86"/>
-      <c r="AF106" s="86"/>
-      <c r="AG106" s="86"/>
-      <c r="AH106" s="86"/>
-      <c r="AI106" s="86"/>
-      <c r="AJ106" s="86"/>
+      <c r="P106" s="85"/>
+      <c r="Q106" s="85"/>
+      <c r="R106" s="85"/>
+      <c r="S106" s="85"/>
+      <c r="T106" s="85"/>
+      <c r="U106" s="85"/>
+      <c r="V106" s="85"/>
+      <c r="W106" s="85"/>
+      <c r="X106" s="85"/>
+      <c r="Y106" s="85"/>
+      <c r="Z106" s="85"/>
+      <c r="AA106" s="85"/>
+      <c r="AB106" s="85"/>
+      <c r="AC106" s="85"/>
+      <c r="AD106" s="85"/>
+      <c r="AE106" s="85"/>
+      <c r="AF106" s="85"/>
+      <c r="AG106" s="85"/>
+      <c r="AH106" s="85"/>
+      <c r="AI106" s="85"/>
+      <c r="AJ106" s="85"/>
       <c r="AK106" s="88"/>
       <c r="AL106" s="90"/>
       <c r="AM106" s="39"/>
@@ -6272,7 +6245,7 @@
       <c r="AM107" s="40"/>
       <c r="AN107" s="42"/>
     </row>
-    <row r="108" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B108" s="33">
         <v>51</v>
       </c>
@@ -6284,36 +6257,36 @@
       <c r="F108" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G108" s="85"/>
-      <c r="H108" s="86"/>
-      <c r="I108" s="86"/>
-      <c r="J108" s="86"/>
+      <c r="G108" s="86"/>
+      <c r="H108" s="85"/>
+      <c r="I108" s="85"/>
+      <c r="J108" s="85"/>
       <c r="K108" s="87"/>
       <c r="L108" s="87"/>
       <c r="M108" s="87"/>
       <c r="N108" s="88"/>
       <c r="O108" s="89"/>
-      <c r="P108" s="86"/>
-      <c r="Q108" s="86"/>
-      <c r="R108" s="86"/>
-      <c r="S108" s="86"/>
-      <c r="T108" s="86"/>
-      <c r="U108" s="86"/>
-      <c r="V108" s="86"/>
-      <c r="W108" s="86"/>
-      <c r="X108" s="86"/>
-      <c r="Y108" s="86"/>
-      <c r="Z108" s="86"/>
-      <c r="AA108" s="86"/>
-      <c r="AB108" s="86"/>
-      <c r="AC108" s="86"/>
-      <c r="AD108" s="86"/>
-      <c r="AE108" s="86"/>
-      <c r="AF108" s="86"/>
-      <c r="AG108" s="86"/>
-      <c r="AH108" s="86"/>
-      <c r="AI108" s="86"/>
-      <c r="AJ108" s="86"/>
+      <c r="P108" s="85"/>
+      <c r="Q108" s="85"/>
+      <c r="R108" s="85"/>
+      <c r="S108" s="85"/>
+      <c r="T108" s="85"/>
+      <c r="U108" s="85"/>
+      <c r="V108" s="85"/>
+      <c r="W108" s="85"/>
+      <c r="X108" s="85"/>
+      <c r="Y108" s="85"/>
+      <c r="Z108" s="85"/>
+      <c r="AA108" s="85"/>
+      <c r="AB108" s="85"/>
+      <c r="AC108" s="85"/>
+      <c r="AD108" s="85"/>
+      <c r="AE108" s="85"/>
+      <c r="AF108" s="85"/>
+      <c r="AG108" s="85"/>
+      <c r="AH108" s="85"/>
+      <c r="AI108" s="85"/>
+      <c r="AJ108" s="85"/>
       <c r="AK108" s="88"/>
       <c r="AL108" s="90"/>
       <c r="AM108" s="39"/>
@@ -6364,7 +6337,7 @@
       <c r="AM109" s="40"/>
       <c r="AN109" s="42"/>
     </row>
-    <row r="110" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B110" s="43">
         <v>52</v>
       </c>
@@ -6376,36 +6349,36 @@
       <c r="F110" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G110" s="85"/>
-      <c r="H110" s="86"/>
-      <c r="I110" s="86"/>
-      <c r="J110" s="86"/>
+      <c r="G110" s="86"/>
+      <c r="H110" s="85"/>
+      <c r="I110" s="85"/>
+      <c r="J110" s="85"/>
       <c r="K110" s="87"/>
       <c r="L110" s="87"/>
       <c r="M110" s="87"/>
       <c r="N110" s="88"/>
       <c r="O110" s="89"/>
-      <c r="P110" s="86"/>
-      <c r="Q110" s="86"/>
-      <c r="R110" s="86"/>
-      <c r="S110" s="86"/>
-      <c r="T110" s="86"/>
-      <c r="U110" s="86"/>
-      <c r="V110" s="86"/>
-      <c r="W110" s="86"/>
-      <c r="X110" s="86"/>
-      <c r="Y110" s="86"/>
-      <c r="Z110" s="86"/>
-      <c r="AA110" s="86"/>
-      <c r="AB110" s="86"/>
-      <c r="AC110" s="86"/>
-      <c r="AD110" s="86"/>
-      <c r="AE110" s="86"/>
-      <c r="AF110" s="86"/>
-      <c r="AG110" s="86"/>
-      <c r="AH110" s="86"/>
-      <c r="AI110" s="86"/>
-      <c r="AJ110" s="86"/>
+      <c r="P110" s="85"/>
+      <c r="Q110" s="85"/>
+      <c r="R110" s="85"/>
+      <c r="S110" s="85"/>
+      <c r="T110" s="85"/>
+      <c r="U110" s="85"/>
+      <c r="V110" s="85"/>
+      <c r="W110" s="85"/>
+      <c r="X110" s="85"/>
+      <c r="Y110" s="85"/>
+      <c r="Z110" s="85"/>
+      <c r="AA110" s="85"/>
+      <c r="AB110" s="85"/>
+      <c r="AC110" s="85"/>
+      <c r="AD110" s="85"/>
+      <c r="AE110" s="85"/>
+      <c r="AF110" s="85"/>
+      <c r="AG110" s="85"/>
+      <c r="AH110" s="85"/>
+      <c r="AI110" s="85"/>
+      <c r="AJ110" s="85"/>
       <c r="AK110" s="88"/>
       <c r="AL110" s="90"/>
       <c r="AM110" s="39"/>
@@ -6456,7 +6429,7 @@
       <c r="AM111" s="40"/>
       <c r="AN111" s="42"/>
     </row>
-    <row r="112" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B112" s="33">
         <v>53</v>
       </c>
@@ -6468,36 +6441,36 @@
       <c r="F112" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="85"/>
-      <c r="H112" s="86"/>
-      <c r="I112" s="86"/>
-      <c r="J112" s="86"/>
+      <c r="G112" s="86"/>
+      <c r="H112" s="85"/>
+      <c r="I112" s="85"/>
+      <c r="J112" s="85"/>
       <c r="K112" s="87"/>
       <c r="L112" s="87"/>
       <c r="M112" s="87"/>
       <c r="N112" s="88"/>
       <c r="O112" s="89"/>
-      <c r="P112" s="86"/>
-      <c r="Q112" s="86"/>
-      <c r="R112" s="86"/>
-      <c r="S112" s="86"/>
-      <c r="T112" s="86"/>
-      <c r="U112" s="86"/>
-      <c r="V112" s="86"/>
-      <c r="W112" s="86"/>
-      <c r="X112" s="86"/>
-      <c r="Y112" s="86"/>
-      <c r="Z112" s="86"/>
-      <c r="AA112" s="86"/>
-      <c r="AB112" s="86"/>
-      <c r="AC112" s="86"/>
-      <c r="AD112" s="86"/>
-      <c r="AE112" s="86"/>
-      <c r="AF112" s="86"/>
-      <c r="AG112" s="86"/>
-      <c r="AH112" s="86"/>
-      <c r="AI112" s="86"/>
-      <c r="AJ112" s="86"/>
+      <c r="P112" s="85"/>
+      <c r="Q112" s="85"/>
+      <c r="R112" s="85"/>
+      <c r="S112" s="85"/>
+      <c r="T112" s="85"/>
+      <c r="U112" s="85"/>
+      <c r="V112" s="85"/>
+      <c r="W112" s="85"/>
+      <c r="X112" s="85"/>
+      <c r="Y112" s="85"/>
+      <c r="Z112" s="85"/>
+      <c r="AA112" s="85"/>
+      <c r="AB112" s="85"/>
+      <c r="AC112" s="85"/>
+      <c r="AD112" s="85"/>
+      <c r="AE112" s="85"/>
+      <c r="AF112" s="85"/>
+      <c r="AG112" s="85"/>
+      <c r="AH112" s="85"/>
+      <c r="AI112" s="85"/>
+      <c r="AJ112" s="85"/>
       <c r="AK112" s="88"/>
       <c r="AL112" s="90"/>
       <c r="AM112" s="39"/>
@@ -6548,7 +6521,7 @@
       <c r="AM113" s="40"/>
       <c r="AN113" s="42"/>
     </row>
-    <row r="114" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B114" s="43">
         <v>54</v>
       </c>
@@ -6560,36 +6533,36 @@
       <c r="F114" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="85"/>
-      <c r="H114" s="86"/>
-      <c r="I114" s="86"/>
-      <c r="J114" s="86"/>
+      <c r="G114" s="86"/>
+      <c r="H114" s="85"/>
+      <c r="I114" s="85"/>
+      <c r="J114" s="85"/>
       <c r="K114" s="87"/>
       <c r="L114" s="87"/>
       <c r="M114" s="87"/>
       <c r="N114" s="88"/>
       <c r="O114" s="89"/>
-      <c r="P114" s="86"/>
-      <c r="Q114" s="86"/>
-      <c r="R114" s="86"/>
-      <c r="S114" s="86"/>
-      <c r="T114" s="86"/>
-      <c r="U114" s="86"/>
-      <c r="V114" s="86"/>
-      <c r="W114" s="86"/>
-      <c r="X114" s="86"/>
-      <c r="Y114" s="86"/>
-      <c r="Z114" s="86"/>
-      <c r="AA114" s="86"/>
-      <c r="AB114" s="86"/>
-      <c r="AC114" s="86"/>
-      <c r="AD114" s="86"/>
-      <c r="AE114" s="86"/>
-      <c r="AF114" s="86"/>
-      <c r="AG114" s="86"/>
-      <c r="AH114" s="86"/>
-      <c r="AI114" s="86"/>
-      <c r="AJ114" s="86"/>
+      <c r="P114" s="85"/>
+      <c r="Q114" s="85"/>
+      <c r="R114" s="85"/>
+      <c r="S114" s="85"/>
+      <c r="T114" s="85"/>
+      <c r="U114" s="85"/>
+      <c r="V114" s="85"/>
+      <c r="W114" s="85"/>
+      <c r="X114" s="85"/>
+      <c r="Y114" s="85"/>
+      <c r="Z114" s="85"/>
+      <c r="AA114" s="85"/>
+      <c r="AB114" s="85"/>
+      <c r="AC114" s="85"/>
+      <c r="AD114" s="85"/>
+      <c r="AE114" s="85"/>
+      <c r="AF114" s="85"/>
+      <c r="AG114" s="85"/>
+      <c r="AH114" s="85"/>
+      <c r="AI114" s="85"/>
+      <c r="AJ114" s="85"/>
       <c r="AK114" s="88"/>
       <c r="AL114" s="90"/>
       <c r="AM114" s="39"/>
@@ -6636,11 +6609,11 @@
       <c r="AI115" s="98"/>
       <c r="AJ115" s="98"/>
       <c r="AK115" s="100"/>
-      <c r="AL115" s="102"/>
+      <c r="AL115" s="96"/>
       <c r="AM115" s="53"/>
       <c r="AN115" s="54"/>
     </row>
-    <row r="116" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B116" s="33">
         <v>55</v>
       </c>
@@ -6652,36 +6625,36 @@
       <c r="F116" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G116" s="85"/>
-      <c r="H116" s="86"/>
-      <c r="I116" s="86"/>
-      <c r="J116" s="86"/>
+      <c r="G116" s="86"/>
+      <c r="H116" s="85"/>
+      <c r="I116" s="85"/>
+      <c r="J116" s="85"/>
       <c r="K116" s="87"/>
       <c r="L116" s="87"/>
       <c r="M116" s="87"/>
       <c r="N116" s="88"/>
       <c r="O116" s="89"/>
-      <c r="P116" s="86"/>
-      <c r="Q116" s="86"/>
-      <c r="R116" s="86"/>
-      <c r="S116" s="86"/>
-      <c r="T116" s="86"/>
-      <c r="U116" s="86"/>
-      <c r="V116" s="86"/>
-      <c r="W116" s="86"/>
-      <c r="X116" s="86"/>
-      <c r="Y116" s="103"/>
-      <c r="Z116" s="86"/>
-      <c r="AA116" s="86"/>
-      <c r="AB116" s="86"/>
-      <c r="AC116" s="86"/>
-      <c r="AD116" s="86"/>
-      <c r="AE116" s="86"/>
-      <c r="AF116" s="86"/>
-      <c r="AG116" s="86"/>
-      <c r="AH116" s="86"/>
-      <c r="AI116" s="86"/>
-      <c r="AJ116" s="86"/>
+      <c r="P116" s="85"/>
+      <c r="Q116" s="85"/>
+      <c r="R116" s="85"/>
+      <c r="S116" s="85"/>
+      <c r="T116" s="85"/>
+      <c r="U116" s="85"/>
+      <c r="V116" s="85"/>
+      <c r="W116" s="85"/>
+      <c r="X116" s="85"/>
+      <c r="Y116" s="102"/>
+      <c r="Z116" s="85"/>
+      <c r="AA116" s="85"/>
+      <c r="AB116" s="85"/>
+      <c r="AC116" s="85"/>
+      <c r="AD116" s="85"/>
+      <c r="AE116" s="85"/>
+      <c r="AF116" s="85"/>
+      <c r="AG116" s="85"/>
+      <c r="AH116" s="85"/>
+      <c r="AI116" s="85"/>
+      <c r="AJ116" s="85"/>
       <c r="AK116" s="88"/>
       <c r="AL116" s="90"/>
       <c r="AM116" s="39"/>
@@ -6715,7 +6688,7 @@
       <c r="V117" s="92"/>
       <c r="W117" s="92"/>
       <c r="X117" s="92"/>
-      <c r="Y117" s="104"/>
+      <c r="Y117" s="103"/>
       <c r="Z117" s="92"/>
       <c r="AA117" s="92"/>
       <c r="AB117" s="92"/>
@@ -6732,7 +6705,7 @@
       <c r="AM117" s="40"/>
       <c r="AN117" s="42"/>
     </row>
-    <row r="118" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B118" s="43">
         <v>56</v>
       </c>
@@ -6744,36 +6717,36 @@
       <c r="F118" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G118" s="85"/>
-      <c r="H118" s="86"/>
-      <c r="I118" s="86"/>
-      <c r="J118" s="86"/>
+      <c r="G118" s="86"/>
+      <c r="H118" s="85"/>
+      <c r="I118" s="85"/>
+      <c r="J118" s="85"/>
       <c r="K118" s="87"/>
       <c r="L118" s="87"/>
       <c r="M118" s="87"/>
       <c r="N118" s="88"/>
       <c r="O118" s="89"/>
-      <c r="P118" s="86"/>
-      <c r="Q118" s="86"/>
-      <c r="R118" s="86"/>
-      <c r="S118" s="86"/>
-      <c r="T118" s="86"/>
-      <c r="U118" s="86"/>
-      <c r="V118" s="86"/>
-      <c r="W118" s="86"/>
-      <c r="X118" s="86"/>
-      <c r="Y118" s="86"/>
-      <c r="Z118" s="86"/>
-      <c r="AA118" s="86"/>
-      <c r="AB118" s="86"/>
-      <c r="AC118" s="86"/>
-      <c r="AD118" s="86"/>
-      <c r="AE118" s="86"/>
-      <c r="AF118" s="86"/>
-      <c r="AG118" s="86"/>
-      <c r="AH118" s="86"/>
-      <c r="AI118" s="86"/>
-      <c r="AJ118" s="86"/>
+      <c r="P118" s="85"/>
+      <c r="Q118" s="85"/>
+      <c r="R118" s="85"/>
+      <c r="S118" s="85"/>
+      <c r="T118" s="85"/>
+      <c r="U118" s="85"/>
+      <c r="V118" s="85"/>
+      <c r="W118" s="85"/>
+      <c r="X118" s="85"/>
+      <c r="Y118" s="85"/>
+      <c r="Z118" s="85"/>
+      <c r="AA118" s="85"/>
+      <c r="AB118" s="85"/>
+      <c r="AC118" s="85"/>
+      <c r="AD118" s="85"/>
+      <c r="AE118" s="85"/>
+      <c r="AF118" s="85"/>
+      <c r="AG118" s="85"/>
+      <c r="AH118" s="85"/>
+      <c r="AI118" s="85"/>
+      <c r="AJ118" s="85"/>
       <c r="AK118" s="88"/>
       <c r="AL118" s="90"/>
       <c r="AM118" s="39"/>
@@ -6824,7 +6797,7 @@
       <c r="AM119" s="40"/>
       <c r="AN119" s="42"/>
     </row>
-    <row r="120" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B120" s="33">
         <v>57</v>
       </c>
@@ -6836,36 +6809,36 @@
       <c r="F120" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G120" s="85"/>
-      <c r="H120" s="86"/>
-      <c r="I120" s="86"/>
-      <c r="J120" s="86"/>
+      <c r="G120" s="86"/>
+      <c r="H120" s="85"/>
+      <c r="I120" s="85"/>
+      <c r="J120" s="85"/>
       <c r="K120" s="87"/>
       <c r="L120" s="87"/>
       <c r="M120" s="87"/>
       <c r="N120" s="88"/>
       <c r="O120" s="89"/>
-      <c r="P120" s="86"/>
-      <c r="Q120" s="86"/>
-      <c r="R120" s="86"/>
-      <c r="S120" s="86"/>
-      <c r="T120" s="86"/>
-      <c r="U120" s="86"/>
-      <c r="V120" s="86"/>
-      <c r="W120" s="86"/>
-      <c r="X120" s="86"/>
-      <c r="Y120" s="86"/>
-      <c r="Z120" s="86"/>
-      <c r="AA120" s="86"/>
-      <c r="AB120" s="86"/>
-      <c r="AC120" s="86"/>
-      <c r="AD120" s="86"/>
-      <c r="AE120" s="86"/>
-      <c r="AF120" s="86"/>
-      <c r="AG120" s="86"/>
-      <c r="AH120" s="86"/>
-      <c r="AI120" s="86"/>
-      <c r="AJ120" s="86"/>
+      <c r="P120" s="85"/>
+      <c r="Q120" s="85"/>
+      <c r="R120" s="85"/>
+      <c r="S120" s="85"/>
+      <c r="T120" s="85"/>
+      <c r="U120" s="85"/>
+      <c r="V120" s="85"/>
+      <c r="W120" s="85"/>
+      <c r="X120" s="85"/>
+      <c r="Y120" s="85"/>
+      <c r="Z120" s="85"/>
+      <c r="AA120" s="85"/>
+      <c r="AB120" s="85"/>
+      <c r="AC120" s="85"/>
+      <c r="AD120" s="85"/>
+      <c r="AE120" s="85"/>
+      <c r="AF120" s="85"/>
+      <c r="AG120" s="85"/>
+      <c r="AH120" s="85"/>
+      <c r="AI120" s="85"/>
+      <c r="AJ120" s="85"/>
       <c r="AK120" s="88"/>
       <c r="AL120" s="90"/>
       <c r="AM120" s="39"/>
@@ -6916,7 +6889,7 @@
       <c r="AM121" s="40"/>
       <c r="AN121" s="42"/>
     </row>
-    <row r="122" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B122" s="43">
         <v>58</v>
       </c>
@@ -6928,36 +6901,36 @@
       <c r="F122" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="85"/>
-      <c r="H122" s="86"/>
-      <c r="I122" s="86"/>
-      <c r="J122" s="86"/>
+      <c r="G122" s="86"/>
+      <c r="H122" s="85"/>
+      <c r="I122" s="85"/>
+      <c r="J122" s="85"/>
       <c r="K122" s="87"/>
       <c r="L122" s="87"/>
       <c r="M122" s="87"/>
       <c r="N122" s="88"/>
       <c r="O122" s="89"/>
-      <c r="P122" s="86"/>
-      <c r="Q122" s="86"/>
-      <c r="R122" s="86"/>
-      <c r="S122" s="86"/>
-      <c r="T122" s="86"/>
-      <c r="U122" s="86"/>
-      <c r="V122" s="86"/>
-      <c r="W122" s="86"/>
-      <c r="X122" s="86"/>
-      <c r="Y122" s="86"/>
-      <c r="Z122" s="86"/>
-      <c r="AA122" s="86"/>
-      <c r="AB122" s="86"/>
-      <c r="AC122" s="86"/>
-      <c r="AD122" s="86"/>
-      <c r="AE122" s="86"/>
-      <c r="AF122" s="86"/>
-      <c r="AG122" s="86"/>
-      <c r="AH122" s="86"/>
-      <c r="AI122" s="86"/>
-      <c r="AJ122" s="86"/>
+      <c r="P122" s="85"/>
+      <c r="Q122" s="85"/>
+      <c r="R122" s="85"/>
+      <c r="S122" s="85"/>
+      <c r="T122" s="85"/>
+      <c r="U122" s="85"/>
+      <c r="V122" s="85"/>
+      <c r="W122" s="85"/>
+      <c r="X122" s="85"/>
+      <c r="Y122" s="85"/>
+      <c r="Z122" s="85"/>
+      <c r="AA122" s="85"/>
+      <c r="AB122" s="85"/>
+      <c r="AC122" s="85"/>
+      <c r="AD122" s="85"/>
+      <c r="AE122" s="85"/>
+      <c r="AF122" s="85"/>
+      <c r="AG122" s="85"/>
+      <c r="AH122" s="85"/>
+      <c r="AI122" s="85"/>
+      <c r="AJ122" s="85"/>
       <c r="AK122" s="88"/>
       <c r="AL122" s="90"/>
       <c r="AM122" s="39"/>
@@ -7008,7 +6981,7 @@
       <c r="AM123" s="40"/>
       <c r="AN123" s="42"/>
     </row>
-    <row r="124" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="33">
         <v>59</v>
       </c>
@@ -7020,36 +6993,36 @@
       <c r="F124" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="85"/>
-      <c r="H124" s="86"/>
-      <c r="I124" s="86"/>
-      <c r="J124" s="86"/>
+      <c r="G124" s="86"/>
+      <c r="H124" s="85"/>
+      <c r="I124" s="85"/>
+      <c r="J124" s="85"/>
       <c r="K124" s="87"/>
       <c r="L124" s="87"/>
       <c r="M124" s="87"/>
       <c r="N124" s="88"/>
       <c r="O124" s="89"/>
-      <c r="P124" s="86"/>
-      <c r="Q124" s="86"/>
-      <c r="R124" s="86"/>
-      <c r="S124" s="86"/>
-      <c r="T124" s="86"/>
-      <c r="U124" s="86"/>
-      <c r="V124" s="86"/>
-      <c r="W124" s="86"/>
-      <c r="X124" s="86"/>
-      <c r="Y124" s="86"/>
-      <c r="Z124" s="86"/>
-      <c r="AA124" s="86"/>
-      <c r="AB124" s="86"/>
-      <c r="AC124" s="86"/>
-      <c r="AD124" s="86"/>
-      <c r="AE124" s="86"/>
-      <c r="AF124" s="86"/>
-      <c r="AG124" s="86"/>
-      <c r="AH124" s="86"/>
-      <c r="AI124" s="86"/>
-      <c r="AJ124" s="86"/>
+      <c r="P124" s="85"/>
+      <c r="Q124" s="85"/>
+      <c r="R124" s="85"/>
+      <c r="S124" s="85"/>
+      <c r="T124" s="85"/>
+      <c r="U124" s="85"/>
+      <c r="V124" s="85"/>
+      <c r="W124" s="85"/>
+      <c r="X124" s="85"/>
+      <c r="Y124" s="85"/>
+      <c r="Z124" s="85"/>
+      <c r="AA124" s="85"/>
+      <c r="AB124" s="85"/>
+      <c r="AC124" s="85"/>
+      <c r="AD124" s="85"/>
+      <c r="AE124" s="85"/>
+      <c r="AF124" s="85"/>
+      <c r="AG124" s="85"/>
+      <c r="AH124" s="85"/>
+      <c r="AI124" s="85"/>
+      <c r="AJ124" s="85"/>
       <c r="AK124" s="88"/>
       <c r="AL124" s="90"/>
       <c r="AM124" s="39"/>
@@ -7100,7 +7073,7 @@
       <c r="AM125" s="40"/>
       <c r="AN125" s="42"/>
     </row>
-    <row r="126" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B126" s="43">
         <v>60</v>
       </c>
@@ -7112,36 +7085,36 @@
       <c r="F126" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G126" s="85"/>
-      <c r="H126" s="86"/>
-      <c r="I126" s="86"/>
-      <c r="J126" s="86"/>
+      <c r="G126" s="86"/>
+      <c r="H126" s="85"/>
+      <c r="I126" s="85"/>
+      <c r="J126" s="85"/>
       <c r="K126" s="87"/>
       <c r="L126" s="87"/>
       <c r="M126" s="87"/>
       <c r="N126" s="88"/>
       <c r="O126" s="89"/>
-      <c r="P126" s="86"/>
-      <c r="Q126" s="86"/>
-      <c r="R126" s="86"/>
-      <c r="S126" s="86"/>
-      <c r="T126" s="86"/>
-      <c r="U126" s="86"/>
-      <c r="V126" s="86"/>
-      <c r="W126" s="86"/>
-      <c r="X126" s="86"/>
-      <c r="Y126" s="86"/>
-      <c r="Z126" s="86"/>
-      <c r="AA126" s="86"/>
-      <c r="AB126" s="86"/>
-      <c r="AC126" s="86"/>
-      <c r="AD126" s="86"/>
-      <c r="AE126" s="86"/>
-      <c r="AF126" s="86"/>
-      <c r="AG126" s="86"/>
-      <c r="AH126" s="86"/>
-      <c r="AI126" s="86"/>
-      <c r="AJ126" s="86"/>
+      <c r="P126" s="85"/>
+      <c r="Q126" s="85"/>
+      <c r="R126" s="85"/>
+      <c r="S126" s="85"/>
+      <c r="T126" s="85"/>
+      <c r="U126" s="85"/>
+      <c r="V126" s="85"/>
+      <c r="W126" s="85"/>
+      <c r="X126" s="85"/>
+      <c r="Y126" s="85"/>
+      <c r="Z126" s="85"/>
+      <c r="AA126" s="85"/>
+      <c r="AB126" s="85"/>
+      <c r="AC126" s="85"/>
+      <c r="AD126" s="85"/>
+      <c r="AE126" s="85"/>
+      <c r="AF126" s="85"/>
+      <c r="AG126" s="85"/>
+      <c r="AH126" s="85"/>
+      <c r="AI126" s="85"/>
+      <c r="AJ126" s="85"/>
       <c r="AK126" s="88"/>
       <c r="AL126" s="90"/>
       <c r="AM126" s="39"/>
@@ -7192,7 +7165,7 @@
       <c r="AM127" s="40"/>
       <c r="AN127" s="42"/>
     </row>
-    <row r="128" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="33">
         <v>61</v>
       </c>
@@ -7204,36 +7177,36 @@
       <c r="F128" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="85"/>
-      <c r="H128" s="86"/>
-      <c r="I128" s="86"/>
-      <c r="J128" s="86"/>
+      <c r="G128" s="86"/>
+      <c r="H128" s="85"/>
+      <c r="I128" s="85"/>
+      <c r="J128" s="85"/>
       <c r="K128" s="87"/>
       <c r="L128" s="87"/>
       <c r="M128" s="87"/>
       <c r="N128" s="88"/>
       <c r="O128" s="89"/>
-      <c r="P128" s="86"/>
-      <c r="Q128" s="86"/>
-      <c r="R128" s="86"/>
-      <c r="S128" s="86"/>
-      <c r="T128" s="86"/>
-      <c r="U128" s="86"/>
-      <c r="V128" s="86"/>
-      <c r="W128" s="86"/>
-      <c r="X128" s="86"/>
-      <c r="Y128" s="86"/>
-      <c r="Z128" s="86"/>
-      <c r="AA128" s="86"/>
-      <c r="AB128" s="86"/>
-      <c r="AC128" s="86"/>
-      <c r="AD128" s="86"/>
-      <c r="AE128" s="86"/>
-      <c r="AF128" s="86"/>
-      <c r="AG128" s="86"/>
-      <c r="AH128" s="86"/>
-      <c r="AI128" s="86"/>
-      <c r="AJ128" s="86"/>
+      <c r="P128" s="85"/>
+      <c r="Q128" s="85"/>
+      <c r="R128" s="85"/>
+      <c r="S128" s="85"/>
+      <c r="T128" s="85"/>
+      <c r="U128" s="85"/>
+      <c r="V128" s="85"/>
+      <c r="W128" s="85"/>
+      <c r="X128" s="85"/>
+      <c r="Y128" s="85"/>
+      <c r="Z128" s="85"/>
+      <c r="AA128" s="85"/>
+      <c r="AB128" s="85"/>
+      <c r="AC128" s="85"/>
+      <c r="AD128" s="85"/>
+      <c r="AE128" s="85"/>
+      <c r="AF128" s="85"/>
+      <c r="AG128" s="85"/>
+      <c r="AH128" s="85"/>
+      <c r="AI128" s="85"/>
+      <c r="AJ128" s="85"/>
       <c r="AK128" s="88"/>
       <c r="AL128" s="90"/>
       <c r="AM128" s="39"/>
@@ -7284,7 +7257,7 @@
       <c r="AM129" s="40"/>
       <c r="AN129" s="42"/>
     </row>
-    <row r="130" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B130" s="43">
         <v>62</v>
       </c>
@@ -7296,36 +7269,36 @@
       <c r="F130" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G130" s="85"/>
-      <c r="H130" s="86"/>
-      <c r="I130" s="86"/>
-      <c r="J130" s="86"/>
+      <c r="G130" s="86"/>
+      <c r="H130" s="85"/>
+      <c r="I130" s="85"/>
+      <c r="J130" s="85"/>
       <c r="K130" s="87"/>
       <c r="L130" s="87"/>
       <c r="M130" s="87"/>
       <c r="N130" s="88"/>
       <c r="O130" s="89"/>
-      <c r="P130" s="86"/>
-      <c r="Q130" s="86"/>
-      <c r="R130" s="86"/>
-      <c r="S130" s="86"/>
-      <c r="T130" s="86"/>
-      <c r="U130" s="86"/>
-      <c r="V130" s="86"/>
-      <c r="W130" s="86"/>
-      <c r="X130" s="86"/>
-      <c r="Y130" s="86"/>
-      <c r="Z130" s="86"/>
-      <c r="AA130" s="86"/>
-      <c r="AB130" s="86"/>
-      <c r="AC130" s="86"/>
-      <c r="AD130" s="86"/>
-      <c r="AE130" s="86"/>
-      <c r="AF130" s="86"/>
-      <c r="AG130" s="86"/>
-      <c r="AH130" s="86"/>
-      <c r="AI130" s="86"/>
-      <c r="AJ130" s="86"/>
+      <c r="P130" s="85"/>
+      <c r="Q130" s="85"/>
+      <c r="R130" s="85"/>
+      <c r="S130" s="85"/>
+      <c r="T130" s="85"/>
+      <c r="U130" s="85"/>
+      <c r="V130" s="85"/>
+      <c r="W130" s="85"/>
+      <c r="X130" s="85"/>
+      <c r="Y130" s="85"/>
+      <c r="Z130" s="85"/>
+      <c r="AA130" s="85"/>
+      <c r="AB130" s="85"/>
+      <c r="AC130" s="85"/>
+      <c r="AD130" s="85"/>
+      <c r="AE130" s="85"/>
+      <c r="AF130" s="85"/>
+      <c r="AG130" s="85"/>
+      <c r="AH130" s="85"/>
+      <c r="AI130" s="85"/>
+      <c r="AJ130" s="85"/>
       <c r="AK130" s="88"/>
       <c r="AL130" s="90"/>
       <c r="AM130" s="39"/>
@@ -7372,11 +7345,11 @@
       <c r="AI131" s="98"/>
       <c r="AJ131" s="98"/>
       <c r="AK131" s="100"/>
-      <c r="AL131" s="102"/>
+      <c r="AL131" s="96"/>
       <c r="AM131" s="53"/>
       <c r="AN131" s="54"/>
     </row>
-    <row r="132" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B132" s="33">
         <v>63</v>
       </c>
@@ -7388,36 +7361,36 @@
       <c r="F132" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G132" s="85"/>
-      <c r="H132" s="86"/>
-      <c r="I132" s="86"/>
-      <c r="J132" s="86"/>
+      <c r="G132" s="86"/>
+      <c r="H132" s="85"/>
+      <c r="I132" s="85"/>
+      <c r="J132" s="85"/>
       <c r="K132" s="87"/>
       <c r="L132" s="87"/>
       <c r="M132" s="87"/>
       <c r="N132" s="88"/>
       <c r="O132" s="89"/>
-      <c r="P132" s="86"/>
-      <c r="Q132" s="86"/>
-      <c r="R132" s="86"/>
-      <c r="S132" s="86"/>
-      <c r="T132" s="86"/>
-      <c r="U132" s="86"/>
-      <c r="V132" s="86"/>
-      <c r="W132" s="86"/>
-      <c r="X132" s="86"/>
-      <c r="Y132" s="86"/>
-      <c r="Z132" s="86"/>
-      <c r="AA132" s="86"/>
-      <c r="AB132" s="86"/>
-      <c r="AC132" s="86"/>
-      <c r="AD132" s="86"/>
-      <c r="AE132" s="86"/>
-      <c r="AF132" s="86"/>
-      <c r="AG132" s="86"/>
-      <c r="AH132" s="86"/>
-      <c r="AI132" s="86"/>
-      <c r="AJ132" s="86"/>
+      <c r="P132" s="85"/>
+      <c r="Q132" s="85"/>
+      <c r="R132" s="85"/>
+      <c r="S132" s="85"/>
+      <c r="T132" s="85"/>
+      <c r="U132" s="85"/>
+      <c r="V132" s="85"/>
+      <c r="W132" s="85"/>
+      <c r="X132" s="85"/>
+      <c r="Y132" s="85"/>
+      <c r="Z132" s="85"/>
+      <c r="AA132" s="85"/>
+      <c r="AB132" s="85"/>
+      <c r="AC132" s="85"/>
+      <c r="AD132" s="85"/>
+      <c r="AE132" s="85"/>
+      <c r="AF132" s="85"/>
+      <c r="AG132" s="85"/>
+      <c r="AH132" s="85"/>
+      <c r="AI132" s="85"/>
+      <c r="AJ132" s="85"/>
       <c r="AK132" s="88"/>
       <c r="AL132" s="90"/>
       <c r="AM132" s="39"/>
@@ -7468,7 +7441,7 @@
       <c r="AM133" s="40"/>
       <c r="AN133" s="42"/>
     </row>
-    <row r="134" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B134" s="43">
         <v>64</v>
       </c>
@@ -7480,36 +7453,36 @@
       <c r="F134" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G134" s="85"/>
-      <c r="H134" s="86"/>
-      <c r="I134" s="86"/>
-      <c r="J134" s="86"/>
+      <c r="G134" s="86"/>
+      <c r="H134" s="85"/>
+      <c r="I134" s="85"/>
+      <c r="J134" s="85"/>
       <c r="K134" s="87"/>
       <c r="L134" s="87"/>
       <c r="M134" s="87"/>
       <c r="N134" s="88"/>
       <c r="O134" s="89"/>
-      <c r="P134" s="86"/>
-      <c r="Q134" s="86"/>
-      <c r="R134" s="86"/>
-      <c r="S134" s="86"/>
-      <c r="T134" s="86"/>
-      <c r="U134" s="86"/>
-      <c r="V134" s="86"/>
-      <c r="W134" s="86"/>
-      <c r="X134" s="86"/>
-      <c r="Y134" s="86"/>
-      <c r="Z134" s="86"/>
-      <c r="AA134" s="86"/>
-      <c r="AB134" s="86"/>
-      <c r="AC134" s="86"/>
-      <c r="AD134" s="86"/>
-      <c r="AE134" s="86"/>
-      <c r="AF134" s="86"/>
-      <c r="AG134" s="86"/>
-      <c r="AH134" s="86"/>
-      <c r="AI134" s="86"/>
-      <c r="AJ134" s="86"/>
+      <c r="P134" s="85"/>
+      <c r="Q134" s="85"/>
+      <c r="R134" s="85"/>
+      <c r="S134" s="85"/>
+      <c r="T134" s="85"/>
+      <c r="U134" s="85"/>
+      <c r="V134" s="85"/>
+      <c r="W134" s="85"/>
+      <c r="X134" s="85"/>
+      <c r="Y134" s="85"/>
+      <c r="Z134" s="85"/>
+      <c r="AA134" s="85"/>
+      <c r="AB134" s="85"/>
+      <c r="AC134" s="85"/>
+      <c r="AD134" s="85"/>
+      <c r="AE134" s="85"/>
+      <c r="AF134" s="85"/>
+      <c r="AG134" s="85"/>
+      <c r="AH134" s="85"/>
+      <c r="AI134" s="85"/>
+      <c r="AJ134" s="85"/>
       <c r="AK134" s="88"/>
       <c r="AL134" s="90"/>
       <c r="AM134" s="39"/>
@@ -7560,7 +7533,7 @@
       <c r="AM135" s="40"/>
       <c r="AN135" s="42"/>
     </row>
-    <row r="136" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B136" s="33">
         <v>65</v>
       </c>
@@ -7572,36 +7545,36 @@
       <c r="F136" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G136" s="85"/>
-      <c r="H136" s="86"/>
-      <c r="I136" s="86"/>
-      <c r="J136" s="86"/>
+      <c r="G136" s="86"/>
+      <c r="H136" s="85"/>
+      <c r="I136" s="85"/>
+      <c r="J136" s="85"/>
       <c r="K136" s="87"/>
       <c r="L136" s="87"/>
       <c r="M136" s="87"/>
       <c r="N136" s="88"/>
       <c r="O136" s="89"/>
-      <c r="P136" s="86"/>
-      <c r="Q136" s="86"/>
-      <c r="R136" s="86"/>
-      <c r="S136" s="86"/>
-      <c r="T136" s="86"/>
-      <c r="U136" s="86"/>
-      <c r="V136" s="86"/>
-      <c r="W136" s="86"/>
-      <c r="X136" s="86"/>
-      <c r="Y136" s="86"/>
-      <c r="Z136" s="86"/>
-      <c r="AA136" s="86"/>
-      <c r="AB136" s="86"/>
-      <c r="AC136" s="86"/>
-      <c r="AD136" s="86"/>
-      <c r="AE136" s="86"/>
-      <c r="AF136" s="86"/>
-      <c r="AG136" s="86"/>
-      <c r="AH136" s="86"/>
-      <c r="AI136" s="86"/>
-      <c r="AJ136" s="86"/>
+      <c r="P136" s="85"/>
+      <c r="Q136" s="85"/>
+      <c r="R136" s="85"/>
+      <c r="S136" s="85"/>
+      <c r="T136" s="85"/>
+      <c r="U136" s="85"/>
+      <c r="V136" s="85"/>
+      <c r="W136" s="85"/>
+      <c r="X136" s="85"/>
+      <c r="Y136" s="85"/>
+      <c r="Z136" s="85"/>
+      <c r="AA136" s="85"/>
+      <c r="AB136" s="85"/>
+      <c r="AC136" s="85"/>
+      <c r="AD136" s="85"/>
+      <c r="AE136" s="85"/>
+      <c r="AF136" s="85"/>
+      <c r="AG136" s="85"/>
+      <c r="AH136" s="85"/>
+      <c r="AI136" s="85"/>
+      <c r="AJ136" s="85"/>
       <c r="AK136" s="88"/>
       <c r="AL136" s="90"/>
       <c r="AM136" s="39"/>
@@ -7652,7 +7625,7 @@
       <c r="AM137" s="40"/>
       <c r="AN137" s="42"/>
     </row>
-    <row r="138" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B138" s="43">
         <v>66</v>
       </c>
@@ -7664,36 +7637,36 @@
       <c r="F138" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G138" s="85"/>
-      <c r="H138" s="86"/>
-      <c r="I138" s="86"/>
-      <c r="J138" s="86"/>
+      <c r="G138" s="86"/>
+      <c r="H138" s="85"/>
+      <c r="I138" s="85"/>
+      <c r="J138" s="85"/>
       <c r="K138" s="87"/>
       <c r="L138" s="87"/>
       <c r="M138" s="87"/>
       <c r="N138" s="88"/>
       <c r="O138" s="89"/>
-      <c r="P138" s="86"/>
-      <c r="Q138" s="86"/>
-      <c r="R138" s="86"/>
-      <c r="S138" s="86"/>
-      <c r="T138" s="86"/>
-      <c r="U138" s="86"/>
-      <c r="V138" s="86"/>
-      <c r="W138" s="86"/>
-      <c r="X138" s="86"/>
-      <c r="Y138" s="86"/>
-      <c r="Z138" s="86"/>
-      <c r="AA138" s="86"/>
-      <c r="AB138" s="86"/>
-      <c r="AC138" s="86"/>
-      <c r="AD138" s="86"/>
-      <c r="AE138" s="86"/>
-      <c r="AF138" s="86"/>
-      <c r="AG138" s="86"/>
-      <c r="AH138" s="86"/>
-      <c r="AI138" s="86"/>
-      <c r="AJ138" s="86"/>
+      <c r="P138" s="85"/>
+      <c r="Q138" s="85"/>
+      <c r="R138" s="85"/>
+      <c r="S138" s="85"/>
+      <c r="T138" s="85"/>
+      <c r="U138" s="85"/>
+      <c r="V138" s="85"/>
+      <c r="W138" s="85"/>
+      <c r="X138" s="85"/>
+      <c r="Y138" s="85"/>
+      <c r="Z138" s="85"/>
+      <c r="AA138" s="85"/>
+      <c r="AB138" s="85"/>
+      <c r="AC138" s="85"/>
+      <c r="AD138" s="85"/>
+      <c r="AE138" s="85"/>
+      <c r="AF138" s="85"/>
+      <c r="AG138" s="85"/>
+      <c r="AH138" s="85"/>
+      <c r="AI138" s="85"/>
+      <c r="AJ138" s="85"/>
       <c r="AK138" s="88"/>
       <c r="AL138" s="90"/>
       <c r="AM138" s="39"/>
@@ -7744,7 +7717,7 @@
       <c r="AM139" s="40"/>
       <c r="AN139" s="42"/>
     </row>
-    <row r="140" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B140" s="33">
         <v>67</v>
       </c>
@@ -7756,36 +7729,36 @@
       <c r="F140" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G140" s="85"/>
-      <c r="H140" s="86"/>
-      <c r="I140" s="86"/>
-      <c r="J140" s="86"/>
+      <c r="G140" s="86"/>
+      <c r="H140" s="85"/>
+      <c r="I140" s="85"/>
+      <c r="J140" s="85"/>
       <c r="K140" s="87"/>
       <c r="L140" s="87"/>
       <c r="M140" s="87"/>
       <c r="N140" s="88"/>
       <c r="O140" s="89"/>
-      <c r="P140" s="86"/>
-      <c r="Q140" s="86"/>
-      <c r="R140" s="86"/>
-      <c r="S140" s="86"/>
-      <c r="T140" s="86"/>
-      <c r="U140" s="86"/>
-      <c r="V140" s="86"/>
-      <c r="W140" s="86"/>
-      <c r="X140" s="86"/>
-      <c r="Y140" s="86"/>
-      <c r="Z140" s="86"/>
-      <c r="AA140" s="86"/>
-      <c r="AB140" s="86"/>
-      <c r="AC140" s="86"/>
-      <c r="AD140" s="86"/>
-      <c r="AE140" s="86"/>
-      <c r="AF140" s="86"/>
-      <c r="AG140" s="86"/>
-      <c r="AH140" s="86"/>
-      <c r="AI140" s="86"/>
-      <c r="AJ140" s="86"/>
+      <c r="P140" s="85"/>
+      <c r="Q140" s="85"/>
+      <c r="R140" s="85"/>
+      <c r="S140" s="85"/>
+      <c r="T140" s="85"/>
+      <c r="U140" s="85"/>
+      <c r="V140" s="85"/>
+      <c r="W140" s="85"/>
+      <c r="X140" s="85"/>
+      <c r="Y140" s="85"/>
+      <c r="Z140" s="85"/>
+      <c r="AA140" s="85"/>
+      <c r="AB140" s="85"/>
+      <c r="AC140" s="85"/>
+      <c r="AD140" s="85"/>
+      <c r="AE140" s="85"/>
+      <c r="AF140" s="85"/>
+      <c r="AG140" s="85"/>
+      <c r="AH140" s="85"/>
+      <c r="AI140" s="85"/>
+      <c r="AJ140" s="85"/>
       <c r="AK140" s="88"/>
       <c r="AL140" s="90"/>
       <c r="AM140" s="39"/>
@@ -7836,7 +7809,7 @@
       <c r="AM141" s="40"/>
       <c r="AN141" s="42"/>
     </row>
-    <row r="142" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B142" s="43">
         <v>68</v>
       </c>
@@ -7848,36 +7821,36 @@
       <c r="F142" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G142" s="85"/>
-      <c r="H142" s="86"/>
-      <c r="I142" s="86"/>
-      <c r="J142" s="86"/>
+      <c r="G142" s="86"/>
+      <c r="H142" s="85"/>
+      <c r="I142" s="85"/>
+      <c r="J142" s="85"/>
       <c r="K142" s="87"/>
       <c r="L142" s="87"/>
       <c r="M142" s="87"/>
       <c r="N142" s="88"/>
       <c r="O142" s="89"/>
-      <c r="P142" s="86"/>
-      <c r="Q142" s="86"/>
-      <c r="R142" s="86"/>
-      <c r="S142" s="86"/>
-      <c r="T142" s="86"/>
-      <c r="U142" s="86"/>
-      <c r="V142" s="86"/>
-      <c r="W142" s="86"/>
-      <c r="X142" s="86"/>
-      <c r="Y142" s="86"/>
-      <c r="Z142" s="86"/>
-      <c r="AA142" s="86"/>
-      <c r="AB142" s="86"/>
-      <c r="AC142" s="86"/>
-      <c r="AD142" s="86"/>
-      <c r="AE142" s="86"/>
-      <c r="AF142" s="86"/>
-      <c r="AG142" s="86"/>
-      <c r="AH142" s="86"/>
-      <c r="AI142" s="86"/>
-      <c r="AJ142" s="86"/>
+      <c r="P142" s="85"/>
+      <c r="Q142" s="85"/>
+      <c r="R142" s="85"/>
+      <c r="S142" s="85"/>
+      <c r="T142" s="85"/>
+      <c r="U142" s="85"/>
+      <c r="V142" s="85"/>
+      <c r="W142" s="85"/>
+      <c r="X142" s="85"/>
+      <c r="Y142" s="85"/>
+      <c r="Z142" s="85"/>
+      <c r="AA142" s="85"/>
+      <c r="AB142" s="85"/>
+      <c r="AC142" s="85"/>
+      <c r="AD142" s="85"/>
+      <c r="AE142" s="85"/>
+      <c r="AF142" s="85"/>
+      <c r="AG142" s="85"/>
+      <c r="AH142" s="85"/>
+      <c r="AI142" s="85"/>
+      <c r="AJ142" s="85"/>
       <c r="AK142" s="88"/>
       <c r="AL142" s="90"/>
       <c r="AM142" s="39"/>
@@ -7928,7 +7901,7 @@
       <c r="AM143" s="40"/>
       <c r="AN143" s="42"/>
     </row>
-    <row r="144" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B144" s="33">
         <v>69</v>
       </c>
@@ -7940,36 +7913,36 @@
       <c r="F144" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G144" s="85"/>
-      <c r="H144" s="86"/>
-      <c r="I144" s="86"/>
-      <c r="J144" s="86"/>
+      <c r="G144" s="86"/>
+      <c r="H144" s="85"/>
+      <c r="I144" s="85"/>
+      <c r="J144" s="85"/>
       <c r="K144" s="87"/>
       <c r="L144" s="87"/>
       <c r="M144" s="87"/>
       <c r="N144" s="88"/>
       <c r="O144" s="89"/>
-      <c r="P144" s="86"/>
-      <c r="Q144" s="86"/>
-      <c r="R144" s="86"/>
-      <c r="S144" s="86"/>
-      <c r="T144" s="86"/>
-      <c r="U144" s="86"/>
-      <c r="V144" s="86"/>
-      <c r="W144" s="86"/>
-      <c r="X144" s="86"/>
-      <c r="Y144" s="86"/>
-      <c r="Z144" s="86"/>
-      <c r="AA144" s="86"/>
-      <c r="AB144" s="86"/>
-      <c r="AC144" s="86"/>
-      <c r="AD144" s="86"/>
-      <c r="AE144" s="86"/>
-      <c r="AF144" s="86"/>
-      <c r="AG144" s="86"/>
-      <c r="AH144" s="86"/>
-      <c r="AI144" s="86"/>
-      <c r="AJ144" s="86"/>
+      <c r="P144" s="85"/>
+      <c r="Q144" s="85"/>
+      <c r="R144" s="85"/>
+      <c r="S144" s="85"/>
+      <c r="T144" s="85"/>
+      <c r="U144" s="85"/>
+      <c r="V144" s="85"/>
+      <c r="W144" s="85"/>
+      <c r="X144" s="85"/>
+      <c r="Y144" s="85"/>
+      <c r="Z144" s="85"/>
+      <c r="AA144" s="85"/>
+      <c r="AB144" s="85"/>
+      <c r="AC144" s="85"/>
+      <c r="AD144" s="85"/>
+      <c r="AE144" s="85"/>
+      <c r="AF144" s="85"/>
+      <c r="AG144" s="85"/>
+      <c r="AH144" s="85"/>
+      <c r="AI144" s="85"/>
+      <c r="AJ144" s="85"/>
       <c r="AK144" s="88"/>
       <c r="AL144" s="90"/>
       <c r="AM144" s="39"/>
@@ -8020,7 +7993,7 @@
       <c r="AM145" s="40"/>
       <c r="AN145" s="42"/>
     </row>
-    <row r="146" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B146" s="43">
         <v>70</v>
       </c>
@@ -8032,36 +8005,36 @@
       <c r="F146" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G146" s="85"/>
-      <c r="H146" s="86"/>
-      <c r="I146" s="86"/>
-      <c r="J146" s="86"/>
+      <c r="G146" s="86"/>
+      <c r="H146" s="85"/>
+      <c r="I146" s="85"/>
+      <c r="J146" s="85"/>
       <c r="K146" s="87"/>
       <c r="L146" s="87"/>
       <c r="M146" s="87"/>
       <c r="N146" s="88"/>
       <c r="O146" s="89"/>
-      <c r="P146" s="86"/>
-      <c r="Q146" s="86"/>
-      <c r="R146" s="86"/>
-      <c r="S146" s="86"/>
-      <c r="T146" s="86"/>
-      <c r="U146" s="86"/>
-      <c r="V146" s="86"/>
-      <c r="W146" s="86"/>
-      <c r="X146" s="86"/>
-      <c r="Y146" s="86"/>
-      <c r="Z146" s="86"/>
-      <c r="AA146" s="86"/>
-      <c r="AB146" s="86"/>
-      <c r="AC146" s="86"/>
-      <c r="AD146" s="86"/>
-      <c r="AE146" s="86"/>
-      <c r="AF146" s="86"/>
-      <c r="AG146" s="86"/>
-      <c r="AH146" s="86"/>
-      <c r="AI146" s="86"/>
-      <c r="AJ146" s="86"/>
+      <c r="P146" s="85"/>
+      <c r="Q146" s="85"/>
+      <c r="R146" s="85"/>
+      <c r="S146" s="85"/>
+      <c r="T146" s="85"/>
+      <c r="U146" s="85"/>
+      <c r="V146" s="85"/>
+      <c r="W146" s="85"/>
+      <c r="X146" s="85"/>
+      <c r="Y146" s="85"/>
+      <c r="Z146" s="85"/>
+      <c r="AA146" s="85"/>
+      <c r="AB146" s="85"/>
+      <c r="AC146" s="85"/>
+      <c r="AD146" s="85"/>
+      <c r="AE146" s="85"/>
+      <c r="AF146" s="85"/>
+      <c r="AG146" s="85"/>
+      <c r="AH146" s="85"/>
+      <c r="AI146" s="85"/>
+      <c r="AJ146" s="85"/>
       <c r="AK146" s="88"/>
       <c r="AL146" s="90"/>
       <c r="AM146" s="39"/>
@@ -8112,7 +8085,7 @@
       <c r="AM147" s="40"/>
       <c r="AN147" s="42"/>
     </row>
-    <row r="148" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B148" s="33">
         <v>71</v>
       </c>
@@ -8124,36 +8097,36 @@
       <c r="F148" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G148" s="85"/>
-      <c r="H148" s="86"/>
-      <c r="I148" s="86"/>
-      <c r="J148" s="86"/>
+      <c r="G148" s="86"/>
+      <c r="H148" s="85"/>
+      <c r="I148" s="85"/>
+      <c r="J148" s="85"/>
       <c r="K148" s="87"/>
       <c r="L148" s="87"/>
       <c r="M148" s="87"/>
       <c r="N148" s="88"/>
       <c r="O148" s="89"/>
-      <c r="P148" s="86"/>
-      <c r="Q148" s="86"/>
-      <c r="R148" s="86"/>
-      <c r="S148" s="86"/>
-      <c r="T148" s="86"/>
-      <c r="U148" s="86"/>
-      <c r="V148" s="86"/>
-      <c r="W148" s="86"/>
-      <c r="X148" s="86"/>
-      <c r="Y148" s="86"/>
-      <c r="Z148" s="86"/>
-      <c r="AA148" s="86"/>
-      <c r="AB148" s="86"/>
-      <c r="AC148" s="86"/>
-      <c r="AD148" s="86"/>
-      <c r="AE148" s="86"/>
-      <c r="AF148" s="86"/>
-      <c r="AG148" s="86"/>
-      <c r="AH148" s="86"/>
-      <c r="AI148" s="86"/>
-      <c r="AJ148" s="86"/>
+      <c r="P148" s="85"/>
+      <c r="Q148" s="85"/>
+      <c r="R148" s="85"/>
+      <c r="S148" s="85"/>
+      <c r="T148" s="85"/>
+      <c r="U148" s="85"/>
+      <c r="V148" s="85"/>
+      <c r="W148" s="85"/>
+      <c r="X148" s="85"/>
+      <c r="Y148" s="85"/>
+      <c r="Z148" s="85"/>
+      <c r="AA148" s="85"/>
+      <c r="AB148" s="85"/>
+      <c r="AC148" s="85"/>
+      <c r="AD148" s="85"/>
+      <c r="AE148" s="85"/>
+      <c r="AF148" s="85"/>
+      <c r="AG148" s="85"/>
+      <c r="AH148" s="85"/>
+      <c r="AI148" s="85"/>
+      <c r="AJ148" s="85"/>
       <c r="AK148" s="88"/>
       <c r="AL148" s="90"/>
       <c r="AM148" s="39"/>
@@ -8204,7 +8177,7 @@
       <c r="AM149" s="40"/>
       <c r="AN149" s="42"/>
     </row>
-    <row r="150" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B150" s="43">
         <v>72</v>
       </c>
@@ -8216,36 +8189,36 @@
       <c r="F150" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G150" s="85"/>
-      <c r="H150" s="86"/>
-      <c r="I150" s="86"/>
-      <c r="J150" s="86"/>
+      <c r="G150" s="86"/>
+      <c r="H150" s="85"/>
+      <c r="I150" s="85"/>
+      <c r="J150" s="85"/>
       <c r="K150" s="87"/>
       <c r="L150" s="87"/>
       <c r="M150" s="87"/>
       <c r="N150" s="88"/>
       <c r="O150" s="89"/>
-      <c r="P150" s="86"/>
-      <c r="Q150" s="86"/>
-      <c r="R150" s="86"/>
-      <c r="S150" s="86"/>
-      <c r="T150" s="86"/>
-      <c r="U150" s="86"/>
-      <c r="V150" s="86"/>
-      <c r="W150" s="86"/>
-      <c r="X150" s="86"/>
-      <c r="Y150" s="86"/>
-      <c r="Z150" s="86"/>
-      <c r="AA150" s="86"/>
-      <c r="AB150" s="86"/>
-      <c r="AC150" s="86"/>
-      <c r="AD150" s="86"/>
-      <c r="AE150" s="86"/>
-      <c r="AF150" s="86"/>
-      <c r="AG150" s="86"/>
-      <c r="AH150" s="86"/>
-      <c r="AI150" s="86"/>
-      <c r="AJ150" s="86"/>
+      <c r="P150" s="85"/>
+      <c r="Q150" s="85"/>
+      <c r="R150" s="85"/>
+      <c r="S150" s="85"/>
+      <c r="T150" s="85"/>
+      <c r="U150" s="85"/>
+      <c r="V150" s="85"/>
+      <c r="W150" s="85"/>
+      <c r="X150" s="85"/>
+      <c r="Y150" s="85"/>
+      <c r="Z150" s="85"/>
+      <c r="AA150" s="85"/>
+      <c r="AB150" s="85"/>
+      <c r="AC150" s="85"/>
+      <c r="AD150" s="85"/>
+      <c r="AE150" s="85"/>
+      <c r="AF150" s="85"/>
+      <c r="AG150" s="85"/>
+      <c r="AH150" s="85"/>
+      <c r="AI150" s="85"/>
+      <c r="AJ150" s="85"/>
       <c r="AK150" s="88"/>
       <c r="AL150" s="90"/>
       <c r="AM150" s="39"/>
@@ -8292,11 +8265,11 @@
       <c r="AI151" s="98"/>
       <c r="AJ151" s="98"/>
       <c r="AK151" s="100"/>
-      <c r="AL151" s="102"/>
+      <c r="AL151" s="96"/>
       <c r="AM151" s="53"/>
       <c r="AN151" s="54"/>
     </row>
-    <row r="152" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B152" s="33">
         <v>73</v>
       </c>
@@ -8308,36 +8281,36 @@
       <c r="F152" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G152" s="85"/>
-      <c r="H152" s="86"/>
-      <c r="I152" s="86"/>
-      <c r="J152" s="86"/>
+      <c r="G152" s="86"/>
+      <c r="H152" s="85"/>
+      <c r="I152" s="85"/>
+      <c r="J152" s="85"/>
       <c r="K152" s="87"/>
       <c r="L152" s="87"/>
       <c r="M152" s="87"/>
       <c r="N152" s="88"/>
       <c r="O152" s="89"/>
-      <c r="P152" s="86"/>
-      <c r="Q152" s="86"/>
-      <c r="R152" s="86"/>
-      <c r="S152" s="86"/>
-      <c r="T152" s="86"/>
-      <c r="U152" s="86"/>
-      <c r="V152" s="86"/>
-      <c r="W152" s="86"/>
-      <c r="X152" s="86"/>
-      <c r="Y152" s="86"/>
-      <c r="Z152" s="86"/>
-      <c r="AA152" s="86"/>
-      <c r="AB152" s="86"/>
-      <c r="AC152" s="86"/>
-      <c r="AD152" s="86"/>
-      <c r="AE152" s="86"/>
-      <c r="AF152" s="86"/>
-      <c r="AG152" s="86"/>
-      <c r="AH152" s="86"/>
-      <c r="AI152" s="86"/>
-      <c r="AJ152" s="86"/>
+      <c r="P152" s="85"/>
+      <c r="Q152" s="85"/>
+      <c r="R152" s="85"/>
+      <c r="S152" s="85"/>
+      <c r="T152" s="85"/>
+      <c r="U152" s="85"/>
+      <c r="V152" s="85"/>
+      <c r="W152" s="85"/>
+      <c r="X152" s="85"/>
+      <c r="Y152" s="85"/>
+      <c r="Z152" s="85"/>
+      <c r="AA152" s="85"/>
+      <c r="AB152" s="85"/>
+      <c r="AC152" s="85"/>
+      <c r="AD152" s="85"/>
+      <c r="AE152" s="85"/>
+      <c r="AF152" s="85"/>
+      <c r="AG152" s="85"/>
+      <c r="AH152" s="85"/>
+      <c r="AI152" s="85"/>
+      <c r="AJ152" s="85"/>
       <c r="AK152" s="88"/>
       <c r="AL152" s="90"/>
       <c r="AM152" s="39"/>
@@ -8388,7 +8361,7 @@
       <c r="AM153" s="40"/>
       <c r="AN153" s="42"/>
     </row>
-    <row r="154" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B154" s="43">
         <v>74</v>
       </c>
@@ -8400,36 +8373,36 @@
       <c r="F154" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G154" s="85"/>
-      <c r="H154" s="86"/>
-      <c r="I154" s="86"/>
-      <c r="J154" s="86"/>
+      <c r="G154" s="86"/>
+      <c r="H154" s="85"/>
+      <c r="I154" s="85"/>
+      <c r="J154" s="85"/>
       <c r="K154" s="87"/>
       <c r="L154" s="87"/>
       <c r="M154" s="87"/>
       <c r="N154" s="88"/>
       <c r="O154" s="89"/>
-      <c r="P154" s="86"/>
-      <c r="Q154" s="86"/>
-      <c r="R154" s="86"/>
-      <c r="S154" s="86"/>
-      <c r="T154" s="86"/>
-      <c r="U154" s="86"/>
-      <c r="V154" s="86"/>
-      <c r="W154" s="86"/>
-      <c r="X154" s="86"/>
-      <c r="Y154" s="86"/>
-      <c r="Z154" s="86"/>
-      <c r="AA154" s="86"/>
-      <c r="AB154" s="86"/>
-      <c r="AC154" s="86"/>
-      <c r="AD154" s="86"/>
-      <c r="AE154" s="86"/>
-      <c r="AF154" s="86"/>
-      <c r="AG154" s="86"/>
-      <c r="AH154" s="86"/>
-      <c r="AI154" s="86"/>
-      <c r="AJ154" s="86"/>
+      <c r="P154" s="85"/>
+      <c r="Q154" s="85"/>
+      <c r="R154" s="85"/>
+      <c r="S154" s="85"/>
+      <c r="T154" s="85"/>
+      <c r="U154" s="85"/>
+      <c r="V154" s="85"/>
+      <c r="W154" s="85"/>
+      <c r="X154" s="85"/>
+      <c r="Y154" s="85"/>
+      <c r="Z154" s="85"/>
+      <c r="AA154" s="85"/>
+      <c r="AB154" s="85"/>
+      <c r="AC154" s="85"/>
+      <c r="AD154" s="85"/>
+      <c r="AE154" s="85"/>
+      <c r="AF154" s="85"/>
+      <c r="AG154" s="85"/>
+      <c r="AH154" s="85"/>
+      <c r="AI154" s="85"/>
+      <c r="AJ154" s="85"/>
       <c r="AK154" s="88"/>
       <c r="AL154" s="90"/>
       <c r="AM154" s="39"/>
@@ -8480,7 +8453,7 @@
       <c r="AM155" s="40"/>
       <c r="AN155" s="42"/>
     </row>
-    <row r="156" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B156" s="33">
         <v>75</v>
       </c>
@@ -8492,36 +8465,36 @@
       <c r="F156" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G156" s="85"/>
-      <c r="H156" s="86"/>
-      <c r="I156" s="86"/>
-      <c r="J156" s="86"/>
+      <c r="G156" s="86"/>
+      <c r="H156" s="85"/>
+      <c r="I156" s="85"/>
+      <c r="J156" s="85"/>
       <c r="K156" s="87"/>
       <c r="L156" s="87"/>
       <c r="M156" s="87"/>
       <c r="N156" s="88"/>
       <c r="O156" s="89"/>
-      <c r="P156" s="86"/>
-      <c r="Q156" s="86"/>
-      <c r="R156" s="86"/>
-      <c r="S156" s="86"/>
-      <c r="T156" s="86"/>
-      <c r="U156" s="86"/>
-      <c r="V156" s="86"/>
-      <c r="W156" s="86"/>
-      <c r="X156" s="86"/>
-      <c r="Y156" s="86"/>
-      <c r="Z156" s="86"/>
-      <c r="AA156" s="86"/>
-      <c r="AB156" s="86"/>
-      <c r="AC156" s="86"/>
-      <c r="AD156" s="86"/>
-      <c r="AE156" s="86"/>
-      <c r="AF156" s="86"/>
-      <c r="AG156" s="86"/>
-      <c r="AH156" s="86"/>
-      <c r="AI156" s="86"/>
-      <c r="AJ156" s="86"/>
+      <c r="P156" s="85"/>
+      <c r="Q156" s="85"/>
+      <c r="R156" s="85"/>
+      <c r="S156" s="85"/>
+      <c r="T156" s="85"/>
+      <c r="U156" s="85"/>
+      <c r="V156" s="85"/>
+      <c r="W156" s="85"/>
+      <c r="X156" s="85"/>
+      <c r="Y156" s="85"/>
+      <c r="Z156" s="85"/>
+      <c r="AA156" s="85"/>
+      <c r="AB156" s="85"/>
+      <c r="AC156" s="85"/>
+      <c r="AD156" s="85"/>
+      <c r="AE156" s="85"/>
+      <c r="AF156" s="85"/>
+      <c r="AG156" s="85"/>
+      <c r="AH156" s="85"/>
+      <c r="AI156" s="85"/>
+      <c r="AJ156" s="85"/>
       <c r="AK156" s="88"/>
       <c r="AL156" s="90"/>
       <c r="AM156" s="39"/>
@@ -8572,7 +8545,7 @@
       <c r="AM157" s="40"/>
       <c r="AN157" s="42"/>
     </row>
-    <row r="158" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="43">
         <v>76</v>
       </c>
@@ -8584,36 +8557,36 @@
       <c r="F158" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G158" s="85"/>
-      <c r="H158" s="86"/>
-      <c r="I158" s="86"/>
-      <c r="J158" s="86"/>
+      <c r="G158" s="86"/>
+      <c r="H158" s="85"/>
+      <c r="I158" s="85"/>
+      <c r="J158" s="85"/>
       <c r="K158" s="87"/>
       <c r="L158" s="87"/>
       <c r="M158" s="87"/>
       <c r="N158" s="88"/>
       <c r="O158" s="89"/>
-      <c r="P158" s="86"/>
-      <c r="Q158" s="86"/>
-      <c r="R158" s="86"/>
-      <c r="S158" s="86"/>
-      <c r="T158" s="86"/>
-      <c r="U158" s="86"/>
-      <c r="V158" s="86"/>
-      <c r="W158" s="86"/>
-      <c r="X158" s="86"/>
-      <c r="Y158" s="86"/>
-      <c r="Z158" s="86"/>
-      <c r="AA158" s="86"/>
-      <c r="AB158" s="86"/>
-      <c r="AC158" s="86"/>
-      <c r="AD158" s="86"/>
-      <c r="AE158" s="86"/>
-      <c r="AF158" s="86"/>
-      <c r="AG158" s="86"/>
-      <c r="AH158" s="86"/>
-      <c r="AI158" s="86"/>
-      <c r="AJ158" s="86"/>
+      <c r="P158" s="85"/>
+      <c r="Q158" s="85"/>
+      <c r="R158" s="85"/>
+      <c r="S158" s="85"/>
+      <c r="T158" s="85"/>
+      <c r="U158" s="85"/>
+      <c r="V158" s="85"/>
+      <c r="W158" s="85"/>
+      <c r="X158" s="85"/>
+      <c r="Y158" s="85"/>
+      <c r="Z158" s="85"/>
+      <c r="AA158" s="85"/>
+      <c r="AB158" s="85"/>
+      <c r="AC158" s="85"/>
+      <c r="AD158" s="85"/>
+      <c r="AE158" s="85"/>
+      <c r="AF158" s="85"/>
+      <c r="AG158" s="85"/>
+      <c r="AH158" s="85"/>
+      <c r="AI158" s="85"/>
+      <c r="AJ158" s="85"/>
       <c r="AK158" s="88"/>
       <c r="AL158" s="90"/>
       <c r="AM158" s="39"/>
@@ -8664,7 +8637,7 @@
       <c r="AM159" s="40"/>
       <c r="AN159" s="42"/>
     </row>
-    <row r="160" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B160" s="33">
         <v>77</v>
       </c>
@@ -8676,36 +8649,36 @@
       <c r="F160" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G160" s="85"/>
-      <c r="H160" s="86"/>
-      <c r="I160" s="86"/>
-      <c r="J160" s="86"/>
+      <c r="G160" s="86"/>
+      <c r="H160" s="85"/>
+      <c r="I160" s="85"/>
+      <c r="J160" s="85"/>
       <c r="K160" s="87"/>
       <c r="L160" s="87"/>
       <c r="M160" s="87"/>
       <c r="N160" s="88"/>
       <c r="O160" s="89"/>
-      <c r="P160" s="86"/>
-      <c r="Q160" s="86"/>
-      <c r="R160" s="86"/>
-      <c r="S160" s="86"/>
-      <c r="T160" s="86"/>
-      <c r="U160" s="86"/>
-      <c r="V160" s="86"/>
-      <c r="W160" s="86"/>
-      <c r="X160" s="86"/>
-      <c r="Y160" s="86"/>
-      <c r="Z160" s="86"/>
-      <c r="AA160" s="86"/>
-      <c r="AB160" s="86"/>
-      <c r="AC160" s="86"/>
-      <c r="AD160" s="86"/>
-      <c r="AE160" s="86"/>
-      <c r="AF160" s="86"/>
-      <c r="AG160" s="86"/>
-      <c r="AH160" s="86"/>
-      <c r="AI160" s="86"/>
-      <c r="AJ160" s="86"/>
+      <c r="P160" s="85"/>
+      <c r="Q160" s="85"/>
+      <c r="R160" s="85"/>
+      <c r="S160" s="85"/>
+      <c r="T160" s="85"/>
+      <c r="U160" s="85"/>
+      <c r="V160" s="85"/>
+      <c r="W160" s="85"/>
+      <c r="X160" s="85"/>
+      <c r="Y160" s="85"/>
+      <c r="Z160" s="85"/>
+      <c r="AA160" s="85"/>
+      <c r="AB160" s="85"/>
+      <c r="AC160" s="85"/>
+      <c r="AD160" s="85"/>
+      <c r="AE160" s="85"/>
+      <c r="AF160" s="85"/>
+      <c r="AG160" s="85"/>
+      <c r="AH160" s="85"/>
+      <c r="AI160" s="85"/>
+      <c r="AJ160" s="85"/>
       <c r="AK160" s="88"/>
       <c r="AL160" s="90"/>
       <c r="AM160" s="39"/>
@@ -8756,7 +8729,7 @@
       <c r="AM161" s="40"/>
       <c r="AN161" s="42"/>
     </row>
-    <row r="162" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B162" s="43">
         <v>78</v>
       </c>
@@ -8768,36 +8741,36 @@
       <c r="F162" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G162" s="85"/>
-      <c r="H162" s="86"/>
-      <c r="I162" s="86"/>
-      <c r="J162" s="86"/>
+      <c r="G162" s="86"/>
+      <c r="H162" s="85"/>
+      <c r="I162" s="85"/>
+      <c r="J162" s="85"/>
       <c r="K162" s="87"/>
       <c r="L162" s="87"/>
       <c r="M162" s="87"/>
       <c r="N162" s="88"/>
       <c r="O162" s="89"/>
-      <c r="P162" s="86"/>
-      <c r="Q162" s="86"/>
-      <c r="R162" s="86"/>
-      <c r="S162" s="86"/>
-      <c r="T162" s="86"/>
-      <c r="U162" s="86"/>
-      <c r="V162" s="86"/>
-      <c r="W162" s="86"/>
-      <c r="X162" s="86"/>
-      <c r="Y162" s="86"/>
-      <c r="Z162" s="86"/>
-      <c r="AA162" s="86"/>
-      <c r="AB162" s="86"/>
-      <c r="AC162" s="86"/>
-      <c r="AD162" s="86"/>
-      <c r="AE162" s="86"/>
-      <c r="AF162" s="86"/>
-      <c r="AG162" s="86"/>
-      <c r="AH162" s="86"/>
-      <c r="AI162" s="86"/>
-      <c r="AJ162" s="86"/>
+      <c r="P162" s="85"/>
+      <c r="Q162" s="85"/>
+      <c r="R162" s="85"/>
+      <c r="S162" s="85"/>
+      <c r="T162" s="85"/>
+      <c r="U162" s="85"/>
+      <c r="V162" s="85"/>
+      <c r="W162" s="85"/>
+      <c r="X162" s="85"/>
+      <c r="Y162" s="85"/>
+      <c r="Z162" s="85"/>
+      <c r="AA162" s="85"/>
+      <c r="AB162" s="85"/>
+      <c r="AC162" s="85"/>
+      <c r="AD162" s="85"/>
+      <c r="AE162" s="85"/>
+      <c r="AF162" s="85"/>
+      <c r="AG162" s="85"/>
+      <c r="AH162" s="85"/>
+      <c r="AI162" s="85"/>
+      <c r="AJ162" s="85"/>
       <c r="AK162" s="88"/>
       <c r="AL162" s="90"/>
       <c r="AM162" s="39"/>
@@ -8848,7 +8821,7 @@
       <c r="AM163" s="40"/>
       <c r="AN163" s="42"/>
     </row>
-    <row r="164" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B164" s="33">
         <v>79</v>
       </c>
@@ -8860,36 +8833,36 @@
       <c r="F164" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G164" s="85"/>
-      <c r="H164" s="86"/>
-      <c r="I164" s="86"/>
-      <c r="J164" s="86"/>
+      <c r="G164" s="86"/>
+      <c r="H164" s="85"/>
+      <c r="I164" s="85"/>
+      <c r="J164" s="85"/>
       <c r="K164" s="87"/>
       <c r="L164" s="87"/>
       <c r="M164" s="87"/>
       <c r="N164" s="88"/>
       <c r="O164" s="89"/>
-      <c r="P164" s="86"/>
-      <c r="Q164" s="86"/>
-      <c r="R164" s="86"/>
-      <c r="S164" s="86"/>
-      <c r="T164" s="86"/>
-      <c r="U164" s="86"/>
-      <c r="V164" s="86"/>
-      <c r="W164" s="86"/>
-      <c r="X164" s="86"/>
-      <c r="Y164" s="86"/>
-      <c r="Z164" s="86"/>
-      <c r="AA164" s="86"/>
-      <c r="AB164" s="86"/>
-      <c r="AC164" s="86"/>
-      <c r="AD164" s="86"/>
-      <c r="AE164" s="86"/>
-      <c r="AF164" s="86"/>
-      <c r="AG164" s="86"/>
-      <c r="AH164" s="86"/>
-      <c r="AI164" s="86"/>
-      <c r="AJ164" s="86"/>
+      <c r="P164" s="85"/>
+      <c r="Q164" s="85"/>
+      <c r="R164" s="85"/>
+      <c r="S164" s="85"/>
+      <c r="T164" s="85"/>
+      <c r="U164" s="85"/>
+      <c r="V164" s="85"/>
+      <c r="W164" s="85"/>
+      <c r="X164" s="85"/>
+      <c r="Y164" s="85"/>
+      <c r="Z164" s="85"/>
+      <c r="AA164" s="85"/>
+      <c r="AB164" s="85"/>
+      <c r="AC164" s="85"/>
+      <c r="AD164" s="85"/>
+      <c r="AE164" s="85"/>
+      <c r="AF164" s="85"/>
+      <c r="AG164" s="85"/>
+      <c r="AH164" s="85"/>
+      <c r="AI164" s="85"/>
+      <c r="AJ164" s="85"/>
       <c r="AK164" s="88"/>
       <c r="AL164" s="90"/>
       <c r="AM164" s="39"/>
@@ -8940,7 +8913,7 @@
       <c r="AM165" s="40"/>
       <c r="AN165" s="42"/>
     </row>
-    <row r="166" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B166" s="43">
         <v>80</v>
       </c>
@@ -8952,36 +8925,36 @@
       <c r="F166" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G166" s="85"/>
-      <c r="H166" s="86"/>
-      <c r="I166" s="86"/>
-      <c r="J166" s="86"/>
+      <c r="G166" s="86"/>
+      <c r="H166" s="85"/>
+      <c r="I166" s="85"/>
+      <c r="J166" s="85"/>
       <c r="K166" s="87"/>
       <c r="L166" s="87"/>
       <c r="M166" s="87"/>
       <c r="N166" s="88"/>
       <c r="O166" s="89"/>
-      <c r="P166" s="86"/>
-      <c r="Q166" s="86"/>
-      <c r="R166" s="86"/>
-      <c r="S166" s="86"/>
-      <c r="T166" s="86"/>
-      <c r="U166" s="86"/>
-      <c r="V166" s="86"/>
-      <c r="W166" s="86"/>
-      <c r="X166" s="86"/>
-      <c r="Y166" s="86"/>
-      <c r="Z166" s="86"/>
-      <c r="AA166" s="86"/>
-      <c r="AB166" s="86"/>
-      <c r="AC166" s="86"/>
-      <c r="AD166" s="86"/>
-      <c r="AE166" s="86"/>
-      <c r="AF166" s="86"/>
-      <c r="AG166" s="86"/>
-      <c r="AH166" s="86"/>
-      <c r="AI166" s="86"/>
-      <c r="AJ166" s="86"/>
+      <c r="P166" s="85"/>
+      <c r="Q166" s="85"/>
+      <c r="R166" s="85"/>
+      <c r="S166" s="85"/>
+      <c r="T166" s="85"/>
+      <c r="U166" s="85"/>
+      <c r="V166" s="85"/>
+      <c r="W166" s="85"/>
+      <c r="X166" s="85"/>
+      <c r="Y166" s="85"/>
+      <c r="Z166" s="85"/>
+      <c r="AA166" s="85"/>
+      <c r="AB166" s="85"/>
+      <c r="AC166" s="85"/>
+      <c r="AD166" s="85"/>
+      <c r="AE166" s="85"/>
+      <c r="AF166" s="85"/>
+      <c r="AG166" s="85"/>
+      <c r="AH166" s="85"/>
+      <c r="AI166" s="85"/>
+      <c r="AJ166" s="85"/>
       <c r="AK166" s="88"/>
       <c r="AL166" s="90"/>
       <c r="AM166" s="39"/>
@@ -9032,7 +9005,7 @@
       <c r="AM167" s="40"/>
       <c r="AN167" s="42"/>
     </row>
-    <row r="168" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B168" s="33">
         <v>81</v>
       </c>
@@ -9044,36 +9017,36 @@
       <c r="F168" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G168" s="85"/>
-      <c r="H168" s="86"/>
-      <c r="I168" s="86"/>
-      <c r="J168" s="86"/>
+      <c r="G168" s="86"/>
+      <c r="H168" s="85"/>
+      <c r="I168" s="85"/>
+      <c r="J168" s="85"/>
       <c r="K168" s="87"/>
       <c r="L168" s="87"/>
       <c r="M168" s="87"/>
       <c r="N168" s="88"/>
       <c r="O168" s="89"/>
-      <c r="P168" s="86"/>
-      <c r="Q168" s="86"/>
-      <c r="R168" s="86"/>
-      <c r="S168" s="86"/>
-      <c r="T168" s="86"/>
-      <c r="U168" s="86"/>
-      <c r="V168" s="86"/>
-      <c r="W168" s="86"/>
-      <c r="X168" s="86"/>
-      <c r="Y168" s="86"/>
-      <c r="Z168" s="86"/>
-      <c r="AA168" s="86"/>
-      <c r="AB168" s="86"/>
-      <c r="AC168" s="86"/>
-      <c r="AD168" s="86"/>
-      <c r="AE168" s="86"/>
-      <c r="AF168" s="86"/>
-      <c r="AG168" s="86"/>
-      <c r="AH168" s="86"/>
-      <c r="AI168" s="86"/>
-      <c r="AJ168" s="86"/>
+      <c r="P168" s="85"/>
+      <c r="Q168" s="85"/>
+      <c r="R168" s="85"/>
+      <c r="S168" s="85"/>
+      <c r="T168" s="85"/>
+      <c r="U168" s="85"/>
+      <c r="V168" s="85"/>
+      <c r="W168" s="85"/>
+      <c r="X168" s="85"/>
+      <c r="Y168" s="85"/>
+      <c r="Z168" s="85"/>
+      <c r="AA168" s="85"/>
+      <c r="AB168" s="85"/>
+      <c r="AC168" s="85"/>
+      <c r="AD168" s="85"/>
+      <c r="AE168" s="85"/>
+      <c r="AF168" s="85"/>
+      <c r="AG168" s="85"/>
+      <c r="AH168" s="85"/>
+      <c r="AI168" s="85"/>
+      <c r="AJ168" s="85"/>
       <c r="AK168" s="88"/>
       <c r="AL168" s="90"/>
       <c r="AM168" s="39"/>
@@ -9124,7 +9097,7 @@
       <c r="AM169" s="40"/>
       <c r="AN169" s="42"/>
     </row>
-    <row r="170" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B170" s="43">
         <v>82</v>
       </c>
@@ -9136,36 +9109,36 @@
       <c r="F170" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G170" s="85"/>
-      <c r="H170" s="86"/>
-      <c r="I170" s="86"/>
-      <c r="J170" s="86"/>
+      <c r="G170" s="86"/>
+      <c r="H170" s="85"/>
+      <c r="I170" s="85"/>
+      <c r="J170" s="85"/>
       <c r="K170" s="87"/>
       <c r="L170" s="87"/>
       <c r="M170" s="87"/>
       <c r="N170" s="88"/>
       <c r="O170" s="89"/>
-      <c r="P170" s="86"/>
-      <c r="Q170" s="86"/>
-      <c r="R170" s="86"/>
-      <c r="S170" s="86"/>
-      <c r="T170" s="86"/>
-      <c r="U170" s="86"/>
-      <c r="V170" s="86"/>
-      <c r="W170" s="86"/>
-      <c r="X170" s="86"/>
-      <c r="Y170" s="86"/>
-      <c r="Z170" s="86"/>
-      <c r="AA170" s="86"/>
-      <c r="AB170" s="86"/>
-      <c r="AC170" s="86"/>
-      <c r="AD170" s="86"/>
-      <c r="AE170" s="86"/>
-      <c r="AF170" s="86"/>
-      <c r="AG170" s="86"/>
-      <c r="AH170" s="86"/>
-      <c r="AI170" s="86"/>
-      <c r="AJ170" s="86"/>
+      <c r="P170" s="85"/>
+      <c r="Q170" s="85"/>
+      <c r="R170" s="85"/>
+      <c r="S170" s="85"/>
+      <c r="T170" s="85"/>
+      <c r="U170" s="85"/>
+      <c r="V170" s="85"/>
+      <c r="W170" s="85"/>
+      <c r="X170" s="85"/>
+      <c r="Y170" s="85"/>
+      <c r="Z170" s="85"/>
+      <c r="AA170" s="85"/>
+      <c r="AB170" s="85"/>
+      <c r="AC170" s="85"/>
+      <c r="AD170" s="85"/>
+      <c r="AE170" s="85"/>
+      <c r="AF170" s="85"/>
+      <c r="AG170" s="85"/>
+      <c r="AH170" s="85"/>
+      <c r="AI170" s="85"/>
+      <c r="AJ170" s="85"/>
       <c r="AK170" s="88"/>
       <c r="AL170" s="90"/>
       <c r="AM170" s="39"/>
@@ -9216,7 +9189,7 @@
       <c r="AM171" s="40"/>
       <c r="AN171" s="42"/>
     </row>
-    <row r="172" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B172" s="33">
         <v>83</v>
       </c>
@@ -9228,36 +9201,36 @@
       <c r="F172" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G172" s="85"/>
-      <c r="H172" s="86"/>
-      <c r="I172" s="86"/>
-      <c r="J172" s="86"/>
+      <c r="G172" s="86"/>
+      <c r="H172" s="85"/>
+      <c r="I172" s="85"/>
+      <c r="J172" s="85"/>
       <c r="K172" s="87"/>
       <c r="L172" s="87"/>
       <c r="M172" s="87"/>
       <c r="N172" s="88"/>
       <c r="O172" s="89"/>
-      <c r="P172" s="86"/>
-      <c r="Q172" s="86"/>
-      <c r="R172" s="86"/>
-      <c r="S172" s="86"/>
-      <c r="T172" s="86"/>
-      <c r="U172" s="86"/>
-      <c r="V172" s="86"/>
-      <c r="W172" s="86"/>
-      <c r="X172" s="86"/>
-      <c r="Y172" s="86"/>
-      <c r="Z172" s="86"/>
-      <c r="AA172" s="86"/>
-      <c r="AB172" s="86"/>
-      <c r="AC172" s="86"/>
-      <c r="AD172" s="86"/>
-      <c r="AE172" s="86"/>
-      <c r="AF172" s="86"/>
-      <c r="AG172" s="86"/>
-      <c r="AH172" s="86"/>
-      <c r="AI172" s="86"/>
-      <c r="AJ172" s="86"/>
+      <c r="P172" s="85"/>
+      <c r="Q172" s="85"/>
+      <c r="R172" s="85"/>
+      <c r="S172" s="85"/>
+      <c r="T172" s="85"/>
+      <c r="U172" s="85"/>
+      <c r="V172" s="85"/>
+      <c r="W172" s="85"/>
+      <c r="X172" s="85"/>
+      <c r="Y172" s="85"/>
+      <c r="Z172" s="85"/>
+      <c r="AA172" s="85"/>
+      <c r="AB172" s="85"/>
+      <c r="AC172" s="85"/>
+      <c r="AD172" s="85"/>
+      <c r="AE172" s="85"/>
+      <c r="AF172" s="85"/>
+      <c r="AG172" s="85"/>
+      <c r="AH172" s="85"/>
+      <c r="AI172" s="85"/>
+      <c r="AJ172" s="85"/>
       <c r="AK172" s="88"/>
       <c r="AL172" s="90"/>
       <c r="AM172" s="39"/>
@@ -9308,7 +9281,7 @@
       <c r="AM173" s="40"/>
       <c r="AN173" s="42"/>
     </row>
-    <row r="174" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B174" s="43">
         <v>84</v>
       </c>
@@ -9320,36 +9293,36 @@
       <c r="F174" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G174" s="85"/>
-      <c r="H174" s="86"/>
-      <c r="I174" s="86"/>
-      <c r="J174" s="86"/>
+      <c r="G174" s="86"/>
+      <c r="H174" s="85"/>
+      <c r="I174" s="85"/>
+      <c r="J174" s="85"/>
       <c r="K174" s="87"/>
       <c r="L174" s="87"/>
       <c r="M174" s="87"/>
       <c r="N174" s="88"/>
       <c r="O174" s="89"/>
-      <c r="P174" s="86"/>
-      <c r="Q174" s="86"/>
-      <c r="R174" s="86"/>
-      <c r="S174" s="86"/>
-      <c r="T174" s="86"/>
-      <c r="U174" s="86"/>
-      <c r="V174" s="86"/>
-      <c r="W174" s="86"/>
-      <c r="X174" s="86"/>
-      <c r="Y174" s="86"/>
-      <c r="Z174" s="86"/>
-      <c r="AA174" s="86"/>
-      <c r="AB174" s="86"/>
-      <c r="AC174" s="86"/>
-      <c r="AD174" s="86"/>
-      <c r="AE174" s="86"/>
-      <c r="AF174" s="86"/>
-      <c r="AG174" s="86"/>
-      <c r="AH174" s="86"/>
-      <c r="AI174" s="86"/>
-      <c r="AJ174" s="86"/>
+      <c r="P174" s="85"/>
+      <c r="Q174" s="85"/>
+      <c r="R174" s="85"/>
+      <c r="S174" s="85"/>
+      <c r="T174" s="85"/>
+      <c r="U174" s="85"/>
+      <c r="V174" s="85"/>
+      <c r="W174" s="85"/>
+      <c r="X174" s="85"/>
+      <c r="Y174" s="85"/>
+      <c r="Z174" s="85"/>
+      <c r="AA174" s="85"/>
+      <c r="AB174" s="85"/>
+      <c r="AC174" s="85"/>
+      <c r="AD174" s="85"/>
+      <c r="AE174" s="85"/>
+      <c r="AF174" s="85"/>
+      <c r="AG174" s="85"/>
+      <c r="AH174" s="85"/>
+      <c r="AI174" s="85"/>
+      <c r="AJ174" s="85"/>
       <c r="AK174" s="88"/>
       <c r="AL174" s="90"/>
       <c r="AM174" s="39"/>
@@ -9400,7 +9373,7 @@
       <c r="AM175" s="40"/>
       <c r="AN175" s="42"/>
     </row>
-    <row r="176" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B176" s="33">
         <v>85</v>
       </c>
@@ -9412,36 +9385,36 @@
       <c r="F176" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G176" s="85"/>
-      <c r="H176" s="86"/>
-      <c r="I176" s="86"/>
-      <c r="J176" s="86"/>
+      <c r="G176" s="86"/>
+      <c r="H176" s="85"/>
+      <c r="I176" s="85"/>
+      <c r="J176" s="85"/>
       <c r="K176" s="87"/>
       <c r="L176" s="87"/>
       <c r="M176" s="87"/>
       <c r="N176" s="88"/>
       <c r="O176" s="89"/>
-      <c r="P176" s="86"/>
-      <c r="Q176" s="86"/>
-      <c r="R176" s="86"/>
-      <c r="S176" s="86"/>
-      <c r="T176" s="86"/>
-      <c r="U176" s="86"/>
-      <c r="V176" s="86"/>
-      <c r="W176" s="86"/>
-      <c r="X176" s="86"/>
-      <c r="Y176" s="86"/>
-      <c r="Z176" s="86"/>
-      <c r="AA176" s="86"/>
-      <c r="AB176" s="86"/>
-      <c r="AC176" s="86"/>
-      <c r="AD176" s="86"/>
-      <c r="AE176" s="86"/>
-      <c r="AF176" s="86"/>
-      <c r="AG176" s="86"/>
-      <c r="AH176" s="86"/>
-      <c r="AI176" s="86"/>
-      <c r="AJ176" s="86"/>
+      <c r="P176" s="85"/>
+      <c r="Q176" s="85"/>
+      <c r="R176" s="85"/>
+      <c r="S176" s="85"/>
+      <c r="T176" s="85"/>
+      <c r="U176" s="85"/>
+      <c r="V176" s="85"/>
+      <c r="W176" s="85"/>
+      <c r="X176" s="85"/>
+      <c r="Y176" s="85"/>
+      <c r="Z176" s="85"/>
+      <c r="AA176" s="85"/>
+      <c r="AB176" s="85"/>
+      <c r="AC176" s="85"/>
+      <c r="AD176" s="85"/>
+      <c r="AE176" s="85"/>
+      <c r="AF176" s="85"/>
+      <c r="AG176" s="85"/>
+      <c r="AH176" s="85"/>
+      <c r="AI176" s="85"/>
+      <c r="AJ176" s="85"/>
       <c r="AK176" s="88"/>
       <c r="AL176" s="90"/>
       <c r="AM176" s="39"/>
@@ -9492,7 +9465,7 @@
       <c r="AM177" s="40"/>
       <c r="AN177" s="42"/>
     </row>
-    <row r="178" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B178" s="43">
         <v>86</v>
       </c>
@@ -9504,36 +9477,36 @@
       <c r="F178" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G178" s="85"/>
-      <c r="H178" s="86"/>
-      <c r="I178" s="86"/>
-      <c r="J178" s="86"/>
+      <c r="G178" s="86"/>
+      <c r="H178" s="85"/>
+      <c r="I178" s="85"/>
+      <c r="J178" s="85"/>
       <c r="K178" s="87"/>
       <c r="L178" s="87"/>
       <c r="M178" s="87"/>
       <c r="N178" s="88"/>
       <c r="O178" s="89"/>
-      <c r="P178" s="86"/>
-      <c r="Q178" s="86"/>
-      <c r="R178" s="86"/>
-      <c r="S178" s="86"/>
-      <c r="T178" s="86"/>
-      <c r="U178" s="86"/>
-      <c r="V178" s="86"/>
-      <c r="W178" s="86"/>
-      <c r="X178" s="86"/>
-      <c r="Y178" s="86"/>
-      <c r="Z178" s="86"/>
-      <c r="AA178" s="86"/>
-      <c r="AB178" s="86"/>
-      <c r="AC178" s="86"/>
-      <c r="AD178" s="86"/>
-      <c r="AE178" s="86"/>
-      <c r="AF178" s="86"/>
-      <c r="AG178" s="86"/>
-      <c r="AH178" s="86"/>
-      <c r="AI178" s="86"/>
-      <c r="AJ178" s="86"/>
+      <c r="P178" s="85"/>
+      <c r="Q178" s="85"/>
+      <c r="R178" s="85"/>
+      <c r="S178" s="85"/>
+      <c r="T178" s="85"/>
+      <c r="U178" s="85"/>
+      <c r="V178" s="85"/>
+      <c r="W178" s="85"/>
+      <c r="X178" s="85"/>
+      <c r="Y178" s="85"/>
+      <c r="Z178" s="85"/>
+      <c r="AA178" s="85"/>
+      <c r="AB178" s="85"/>
+      <c r="AC178" s="85"/>
+      <c r="AD178" s="85"/>
+      <c r="AE178" s="85"/>
+      <c r="AF178" s="85"/>
+      <c r="AG178" s="85"/>
+      <c r="AH178" s="85"/>
+      <c r="AI178" s="85"/>
+      <c r="AJ178" s="85"/>
       <c r="AK178" s="88"/>
       <c r="AL178" s="90"/>
       <c r="AM178" s="39"/>
@@ -9584,7 +9557,7 @@
       <c r="AM179" s="40"/>
       <c r="AN179" s="42"/>
     </row>
-    <row r="180" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B180" s="33">
         <v>87</v>
       </c>
@@ -9596,36 +9569,36 @@
       <c r="F180" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G180" s="85"/>
-      <c r="H180" s="86"/>
-      <c r="I180" s="86"/>
-      <c r="J180" s="86"/>
+      <c r="G180" s="86"/>
+      <c r="H180" s="85"/>
+      <c r="I180" s="85"/>
+      <c r="J180" s="85"/>
       <c r="K180" s="87"/>
       <c r="L180" s="87"/>
       <c r="M180" s="87"/>
       <c r="N180" s="88"/>
       <c r="O180" s="89"/>
-      <c r="P180" s="86"/>
-      <c r="Q180" s="86"/>
-      <c r="R180" s="86"/>
-      <c r="S180" s="86"/>
-      <c r="T180" s="86"/>
-      <c r="U180" s="86"/>
-      <c r="V180" s="86"/>
-      <c r="W180" s="86"/>
-      <c r="X180" s="86"/>
-      <c r="Y180" s="86"/>
-      <c r="Z180" s="86"/>
-      <c r="AA180" s="86"/>
-      <c r="AB180" s="86"/>
-      <c r="AC180" s="86"/>
-      <c r="AD180" s="86"/>
-      <c r="AE180" s="86"/>
-      <c r="AF180" s="86"/>
-      <c r="AG180" s="86"/>
-      <c r="AH180" s="86"/>
-      <c r="AI180" s="86"/>
-      <c r="AJ180" s="86"/>
+      <c r="P180" s="85"/>
+      <c r="Q180" s="85"/>
+      <c r="R180" s="85"/>
+      <c r="S180" s="85"/>
+      <c r="T180" s="85"/>
+      <c r="U180" s="85"/>
+      <c r="V180" s="85"/>
+      <c r="W180" s="85"/>
+      <c r="X180" s="85"/>
+      <c r="Y180" s="85"/>
+      <c r="Z180" s="85"/>
+      <c r="AA180" s="85"/>
+      <c r="AB180" s="85"/>
+      <c r="AC180" s="85"/>
+      <c r="AD180" s="85"/>
+      <c r="AE180" s="85"/>
+      <c r="AF180" s="85"/>
+      <c r="AG180" s="85"/>
+      <c r="AH180" s="85"/>
+      <c r="AI180" s="85"/>
+      <c r="AJ180" s="85"/>
       <c r="AK180" s="88"/>
       <c r="AL180" s="90"/>
       <c r="AM180" s="39"/>
@@ -9676,7 +9649,7 @@
       <c r="AM181" s="40"/>
       <c r="AN181" s="42"/>
     </row>
-    <row r="182" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B182" s="43">
         <v>88</v>
       </c>
@@ -9688,36 +9661,36 @@
       <c r="F182" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G182" s="85"/>
-      <c r="H182" s="86"/>
-      <c r="I182" s="86"/>
-      <c r="J182" s="86"/>
+      <c r="G182" s="86"/>
+      <c r="H182" s="85"/>
+      <c r="I182" s="85"/>
+      <c r="J182" s="85"/>
       <c r="K182" s="87"/>
       <c r="L182" s="87"/>
       <c r="M182" s="87"/>
       <c r="N182" s="88"/>
       <c r="O182" s="89"/>
-      <c r="P182" s="86"/>
-      <c r="Q182" s="86"/>
-      <c r="R182" s="86"/>
-      <c r="S182" s="86"/>
-      <c r="T182" s="86"/>
-      <c r="U182" s="86"/>
-      <c r="V182" s="86"/>
-      <c r="W182" s="86"/>
-      <c r="X182" s="86"/>
-      <c r="Y182" s="86"/>
-      <c r="Z182" s="86"/>
-      <c r="AA182" s="86"/>
-      <c r="AB182" s="86"/>
-      <c r="AC182" s="86"/>
-      <c r="AD182" s="86"/>
-      <c r="AE182" s="86"/>
-      <c r="AF182" s="86"/>
-      <c r="AG182" s="86"/>
-      <c r="AH182" s="86"/>
-      <c r="AI182" s="86"/>
-      <c r="AJ182" s="86"/>
+      <c r="P182" s="85"/>
+      <c r="Q182" s="85"/>
+      <c r="R182" s="85"/>
+      <c r="S182" s="85"/>
+      <c r="T182" s="85"/>
+      <c r="U182" s="85"/>
+      <c r="V182" s="85"/>
+      <c r="W182" s="85"/>
+      <c r="X182" s="85"/>
+      <c r="Y182" s="85"/>
+      <c r="Z182" s="85"/>
+      <c r="AA182" s="85"/>
+      <c r="AB182" s="85"/>
+      <c r="AC182" s="85"/>
+      <c r="AD182" s="85"/>
+      <c r="AE182" s="85"/>
+      <c r="AF182" s="85"/>
+      <c r="AG182" s="85"/>
+      <c r="AH182" s="85"/>
+      <c r="AI182" s="85"/>
+      <c r="AJ182" s="85"/>
       <c r="AK182" s="88"/>
       <c r="AL182" s="90"/>
       <c r="AM182" s="39"/>
@@ -9768,7 +9741,7 @@
       <c r="AM183" s="40"/>
       <c r="AN183" s="42"/>
     </row>
-    <row r="184" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B184" s="33">
         <v>89</v>
       </c>
@@ -9780,36 +9753,36 @@
       <c r="F184" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G184" s="85"/>
-      <c r="H184" s="86"/>
-      <c r="I184" s="86"/>
-      <c r="J184" s="86"/>
+      <c r="G184" s="86"/>
+      <c r="H184" s="85"/>
+      <c r="I184" s="85"/>
+      <c r="J184" s="85"/>
       <c r="K184" s="87"/>
       <c r="L184" s="87"/>
       <c r="M184" s="87"/>
       <c r="N184" s="88"/>
       <c r="O184" s="89"/>
-      <c r="P184" s="86"/>
-      <c r="Q184" s="86"/>
-      <c r="R184" s="86"/>
-      <c r="S184" s="86"/>
-      <c r="T184" s="86"/>
-      <c r="U184" s="86"/>
-      <c r="V184" s="86"/>
-      <c r="W184" s="86"/>
-      <c r="X184" s="86"/>
-      <c r="Y184" s="86"/>
-      <c r="Z184" s="86"/>
-      <c r="AA184" s="86"/>
-      <c r="AB184" s="86"/>
-      <c r="AC184" s="86"/>
-      <c r="AD184" s="86"/>
-      <c r="AE184" s="86"/>
-      <c r="AF184" s="86"/>
-      <c r="AG184" s="86"/>
-      <c r="AH184" s="86"/>
-      <c r="AI184" s="86"/>
-      <c r="AJ184" s="86"/>
+      <c r="P184" s="85"/>
+      <c r="Q184" s="85"/>
+      <c r="R184" s="85"/>
+      <c r="S184" s="85"/>
+      <c r="T184" s="85"/>
+      <c r="U184" s="85"/>
+      <c r="V184" s="85"/>
+      <c r="W184" s="85"/>
+      <c r="X184" s="85"/>
+      <c r="Y184" s="85"/>
+      <c r="Z184" s="85"/>
+      <c r="AA184" s="85"/>
+      <c r="AB184" s="85"/>
+      <c r="AC184" s="85"/>
+      <c r="AD184" s="85"/>
+      <c r="AE184" s="85"/>
+      <c r="AF184" s="85"/>
+      <c r="AG184" s="85"/>
+      <c r="AH184" s="85"/>
+      <c r="AI184" s="85"/>
+      <c r="AJ184" s="85"/>
       <c r="AK184" s="88"/>
       <c r="AL184" s="90"/>
       <c r="AM184" s="39"/>
@@ -9860,7 +9833,7 @@
       <c r="AM185" s="40"/>
       <c r="AN185" s="42"/>
     </row>
-    <row r="186" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B186" s="43">
         <v>90</v>
       </c>
@@ -9872,36 +9845,36 @@
       <c r="F186" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G186" s="85"/>
-      <c r="H186" s="86"/>
-      <c r="I186" s="86"/>
-      <c r="J186" s="86"/>
+      <c r="G186" s="86"/>
+      <c r="H186" s="85"/>
+      <c r="I186" s="85"/>
+      <c r="J186" s="85"/>
       <c r="K186" s="87"/>
       <c r="L186" s="87"/>
       <c r="M186" s="87"/>
       <c r="N186" s="88"/>
       <c r="O186" s="89"/>
-      <c r="P186" s="86"/>
-      <c r="Q186" s="86"/>
-      <c r="R186" s="86"/>
-      <c r="S186" s="86"/>
-      <c r="T186" s="86"/>
-      <c r="U186" s="86"/>
-      <c r="V186" s="86"/>
-      <c r="W186" s="86"/>
-      <c r="X186" s="86"/>
-      <c r="Y186" s="86"/>
-      <c r="Z186" s="86"/>
-      <c r="AA186" s="86"/>
-      <c r="AB186" s="86"/>
-      <c r="AC186" s="86"/>
-      <c r="AD186" s="86"/>
-      <c r="AE186" s="86"/>
-      <c r="AF186" s="86"/>
-      <c r="AG186" s="86"/>
-      <c r="AH186" s="86"/>
-      <c r="AI186" s="86"/>
-      <c r="AJ186" s="86"/>
+      <c r="P186" s="85"/>
+      <c r="Q186" s="85"/>
+      <c r="R186" s="85"/>
+      <c r="S186" s="85"/>
+      <c r="T186" s="85"/>
+      <c r="U186" s="85"/>
+      <c r="V186" s="85"/>
+      <c r="W186" s="85"/>
+      <c r="X186" s="85"/>
+      <c r="Y186" s="85"/>
+      <c r="Z186" s="85"/>
+      <c r="AA186" s="85"/>
+      <c r="AB186" s="85"/>
+      <c r="AC186" s="85"/>
+      <c r="AD186" s="85"/>
+      <c r="AE186" s="85"/>
+      <c r="AF186" s="85"/>
+      <c r="AG186" s="85"/>
+      <c r="AH186" s="85"/>
+      <c r="AI186" s="85"/>
+      <c r="AJ186" s="85"/>
       <c r="AK186" s="88"/>
       <c r="AL186" s="90"/>
       <c r="AM186" s="39"/>
@@ -9952,7 +9925,7 @@
       <c r="AM187" s="40"/>
       <c r="AN187" s="42"/>
     </row>
-    <row r="188" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B188" s="33">
         <v>91</v>
       </c>
@@ -9964,36 +9937,36 @@
       <c r="F188" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G188" s="85"/>
-      <c r="H188" s="86"/>
-      <c r="I188" s="86"/>
-      <c r="J188" s="86"/>
+      <c r="G188" s="86"/>
+      <c r="H188" s="85"/>
+      <c r="I188" s="85"/>
+      <c r="J188" s="85"/>
       <c r="K188" s="87"/>
       <c r="L188" s="87"/>
       <c r="M188" s="87"/>
       <c r="N188" s="88"/>
       <c r="O188" s="89"/>
-      <c r="P188" s="86"/>
-      <c r="Q188" s="86"/>
-      <c r="R188" s="86"/>
-      <c r="S188" s="86"/>
-      <c r="T188" s="86"/>
-      <c r="U188" s="86"/>
-      <c r="V188" s="86"/>
-      <c r="W188" s="86"/>
-      <c r="X188" s="86"/>
-      <c r="Y188" s="86"/>
-      <c r="Z188" s="86"/>
-      <c r="AA188" s="86"/>
-      <c r="AB188" s="86"/>
-      <c r="AC188" s="86"/>
-      <c r="AD188" s="86"/>
-      <c r="AE188" s="86"/>
-      <c r="AF188" s="86"/>
-      <c r="AG188" s="86"/>
-      <c r="AH188" s="86"/>
-      <c r="AI188" s="86"/>
-      <c r="AJ188" s="86"/>
+      <c r="P188" s="85"/>
+      <c r="Q188" s="85"/>
+      <c r="R188" s="85"/>
+      <c r="S188" s="85"/>
+      <c r="T188" s="85"/>
+      <c r="U188" s="85"/>
+      <c r="V188" s="85"/>
+      <c r="W188" s="85"/>
+      <c r="X188" s="85"/>
+      <c r="Y188" s="85"/>
+      <c r="Z188" s="85"/>
+      <c r="AA188" s="85"/>
+      <c r="AB188" s="85"/>
+      <c r="AC188" s="85"/>
+      <c r="AD188" s="85"/>
+      <c r="AE188" s="85"/>
+      <c r="AF188" s="85"/>
+      <c r="AG188" s="85"/>
+      <c r="AH188" s="85"/>
+      <c r="AI188" s="85"/>
+      <c r="AJ188" s="85"/>
       <c r="AK188" s="88"/>
       <c r="AL188" s="90"/>
       <c r="AM188" s="39"/>
@@ -10044,7 +10017,7 @@
       <c r="AM189" s="40"/>
       <c r="AN189" s="42"/>
     </row>
-    <row r="190" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B190" s="43">
         <v>92</v>
       </c>
@@ -10056,36 +10029,36 @@
       <c r="F190" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G190" s="85"/>
-      <c r="H190" s="86"/>
-      <c r="I190" s="86"/>
-      <c r="J190" s="86"/>
+      <c r="G190" s="86"/>
+      <c r="H190" s="85"/>
+      <c r="I190" s="85"/>
+      <c r="J190" s="85"/>
       <c r="K190" s="87"/>
       <c r="L190" s="87"/>
       <c r="M190" s="87"/>
       <c r="N190" s="88"/>
       <c r="O190" s="89"/>
-      <c r="P190" s="86"/>
-      <c r="Q190" s="86"/>
-      <c r="R190" s="86"/>
-      <c r="S190" s="86"/>
-      <c r="T190" s="86"/>
-      <c r="U190" s="86"/>
-      <c r="V190" s="86"/>
-      <c r="W190" s="86"/>
-      <c r="X190" s="86"/>
-      <c r="Y190" s="86"/>
-      <c r="Z190" s="86"/>
-      <c r="AA190" s="86"/>
-      <c r="AB190" s="86"/>
-      <c r="AC190" s="86"/>
-      <c r="AD190" s="86"/>
-      <c r="AE190" s="86"/>
-      <c r="AF190" s="86"/>
-      <c r="AG190" s="86"/>
-      <c r="AH190" s="86"/>
-      <c r="AI190" s="86"/>
-      <c r="AJ190" s="86"/>
+      <c r="P190" s="85"/>
+      <c r="Q190" s="85"/>
+      <c r="R190" s="85"/>
+      <c r="S190" s="85"/>
+      <c r="T190" s="85"/>
+      <c r="U190" s="85"/>
+      <c r="V190" s="85"/>
+      <c r="W190" s="85"/>
+      <c r="X190" s="85"/>
+      <c r="Y190" s="85"/>
+      <c r="Z190" s="85"/>
+      <c r="AA190" s="85"/>
+      <c r="AB190" s="85"/>
+      <c r="AC190" s="85"/>
+      <c r="AD190" s="85"/>
+      <c r="AE190" s="85"/>
+      <c r="AF190" s="85"/>
+      <c r="AG190" s="85"/>
+      <c r="AH190" s="85"/>
+      <c r="AI190" s="85"/>
+      <c r="AJ190" s="85"/>
       <c r="AK190" s="88"/>
       <c r="AL190" s="90"/>
       <c r="AM190" s="39"/>
@@ -10136,7 +10109,7 @@
       <c r="AM191" s="40"/>
       <c r="AN191" s="42"/>
     </row>
-    <row r="192" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B192" s="33">
         <v>93</v>
       </c>
@@ -10148,36 +10121,36 @@
       <c r="F192" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G192" s="85"/>
-      <c r="H192" s="86"/>
-      <c r="I192" s="86"/>
-      <c r="J192" s="86"/>
+      <c r="G192" s="86"/>
+      <c r="H192" s="85"/>
+      <c r="I192" s="85"/>
+      <c r="J192" s="85"/>
       <c r="K192" s="87"/>
       <c r="L192" s="87"/>
       <c r="M192" s="87"/>
       <c r="N192" s="88"/>
       <c r="O192" s="89"/>
-      <c r="P192" s="86"/>
-      <c r="Q192" s="86"/>
-      <c r="R192" s="86"/>
-      <c r="S192" s="86"/>
-      <c r="T192" s="86"/>
-      <c r="U192" s="86"/>
-      <c r="V192" s="86"/>
-      <c r="W192" s="86"/>
-      <c r="X192" s="86"/>
-      <c r="Y192" s="86"/>
-      <c r="Z192" s="86"/>
-      <c r="AA192" s="86"/>
-      <c r="AB192" s="86"/>
-      <c r="AC192" s="86"/>
-      <c r="AD192" s="86"/>
-      <c r="AE192" s="86"/>
-      <c r="AF192" s="86"/>
-      <c r="AG192" s="86"/>
-      <c r="AH192" s="86"/>
-      <c r="AI192" s="86"/>
-      <c r="AJ192" s="86"/>
+      <c r="P192" s="85"/>
+      <c r="Q192" s="85"/>
+      <c r="R192" s="85"/>
+      <c r="S192" s="85"/>
+      <c r="T192" s="85"/>
+      <c r="U192" s="85"/>
+      <c r="V192" s="85"/>
+      <c r="W192" s="85"/>
+      <c r="X192" s="85"/>
+      <c r="Y192" s="85"/>
+      <c r="Z192" s="85"/>
+      <c r="AA192" s="85"/>
+      <c r="AB192" s="85"/>
+      <c r="AC192" s="85"/>
+      <c r="AD192" s="85"/>
+      <c r="AE192" s="85"/>
+      <c r="AF192" s="85"/>
+      <c r="AG192" s="85"/>
+      <c r="AH192" s="85"/>
+      <c r="AI192" s="85"/>
+      <c r="AJ192" s="85"/>
       <c r="AK192" s="88"/>
       <c r="AL192" s="90"/>
       <c r="AM192" s="39"/>
@@ -10228,7 +10201,7 @@
       <c r="AM193" s="40"/>
       <c r="AN193" s="42"/>
     </row>
-    <row r="194" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B194" s="43">
         <v>94</v>
       </c>
@@ -10240,36 +10213,36 @@
       <c r="F194" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G194" s="85"/>
-      <c r="H194" s="86"/>
-      <c r="I194" s="86"/>
-      <c r="J194" s="86"/>
+      <c r="G194" s="86"/>
+      <c r="H194" s="85"/>
+      <c r="I194" s="85"/>
+      <c r="J194" s="85"/>
       <c r="K194" s="87"/>
       <c r="L194" s="87"/>
       <c r="M194" s="87"/>
       <c r="N194" s="88"/>
       <c r="O194" s="89"/>
-      <c r="P194" s="86"/>
-      <c r="Q194" s="86"/>
-      <c r="R194" s="86"/>
-      <c r="S194" s="86"/>
-      <c r="T194" s="86"/>
-      <c r="U194" s="86"/>
-      <c r="V194" s="86"/>
-      <c r="W194" s="86"/>
-      <c r="X194" s="86"/>
-      <c r="Y194" s="86"/>
-      <c r="Z194" s="86"/>
-      <c r="AA194" s="86"/>
-      <c r="AB194" s="86"/>
-      <c r="AC194" s="86"/>
-      <c r="AD194" s="86"/>
-      <c r="AE194" s="86"/>
-      <c r="AF194" s="86"/>
-      <c r="AG194" s="86"/>
-      <c r="AH194" s="86"/>
-      <c r="AI194" s="86"/>
-      <c r="AJ194" s="86"/>
+      <c r="P194" s="85"/>
+      <c r="Q194" s="85"/>
+      <c r="R194" s="85"/>
+      <c r="S194" s="85"/>
+      <c r="T194" s="85"/>
+      <c r="U194" s="85"/>
+      <c r="V194" s="85"/>
+      <c r="W194" s="85"/>
+      <c r="X194" s="85"/>
+      <c r="Y194" s="85"/>
+      <c r="Z194" s="85"/>
+      <c r="AA194" s="85"/>
+      <c r="AB194" s="85"/>
+      <c r="AC194" s="85"/>
+      <c r="AD194" s="85"/>
+      <c r="AE194" s="85"/>
+      <c r="AF194" s="85"/>
+      <c r="AG194" s="85"/>
+      <c r="AH194" s="85"/>
+      <c r="AI194" s="85"/>
+      <c r="AJ194" s="85"/>
       <c r="AK194" s="88"/>
       <c r="AL194" s="90"/>
       <c r="AM194" s="39"/>
@@ -10320,7 +10293,7 @@
       <c r="AM195" s="40"/>
       <c r="AN195" s="42"/>
     </row>
-    <row r="196" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B196" s="33">
         <v>95</v>
       </c>
@@ -10332,36 +10305,36 @@
       <c r="F196" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G196" s="85"/>
-      <c r="H196" s="86"/>
-      <c r="I196" s="86"/>
-      <c r="J196" s="86"/>
+      <c r="G196" s="86"/>
+      <c r="H196" s="85"/>
+      <c r="I196" s="85"/>
+      <c r="J196" s="85"/>
       <c r="K196" s="87"/>
       <c r="L196" s="87"/>
       <c r="M196" s="87"/>
       <c r="N196" s="88"/>
       <c r="O196" s="89"/>
-      <c r="P196" s="86"/>
-      <c r="Q196" s="86"/>
-      <c r="R196" s="86"/>
-      <c r="S196" s="86"/>
-      <c r="T196" s="86"/>
-      <c r="U196" s="86"/>
-      <c r="V196" s="86"/>
-      <c r="W196" s="86"/>
-      <c r="X196" s="86"/>
-      <c r="Y196" s="86"/>
-      <c r="Z196" s="86"/>
-      <c r="AA196" s="86"/>
-      <c r="AB196" s="86"/>
-      <c r="AC196" s="86"/>
-      <c r="AD196" s="86"/>
-      <c r="AE196" s="86"/>
-      <c r="AF196" s="86"/>
-      <c r="AG196" s="86"/>
-      <c r="AH196" s="86"/>
-      <c r="AI196" s="86"/>
-      <c r="AJ196" s="86"/>
+      <c r="P196" s="85"/>
+      <c r="Q196" s="85"/>
+      <c r="R196" s="85"/>
+      <c r="S196" s="85"/>
+      <c r="T196" s="85"/>
+      <c r="U196" s="85"/>
+      <c r="V196" s="85"/>
+      <c r="W196" s="85"/>
+      <c r="X196" s="85"/>
+      <c r="Y196" s="85"/>
+      <c r="Z196" s="85"/>
+      <c r="AA196" s="85"/>
+      <c r="AB196" s="85"/>
+      <c r="AC196" s="85"/>
+      <c r="AD196" s="85"/>
+      <c r="AE196" s="85"/>
+      <c r="AF196" s="85"/>
+      <c r="AG196" s="85"/>
+      <c r="AH196" s="85"/>
+      <c r="AI196" s="85"/>
+      <c r="AJ196" s="85"/>
       <c r="AK196" s="88"/>
       <c r="AL196" s="90"/>
       <c r="AM196" s="39"/>
@@ -10412,7 +10385,7 @@
       <c r="AM197" s="40"/>
       <c r="AN197" s="42"/>
     </row>
-    <row r="198" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B198" s="43">
         <v>96</v>
       </c>
@@ -10424,36 +10397,36 @@
       <c r="F198" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G198" s="85"/>
-      <c r="H198" s="86"/>
-      <c r="I198" s="86"/>
-      <c r="J198" s="86"/>
+      <c r="G198" s="86"/>
+      <c r="H198" s="85"/>
+      <c r="I198" s="85"/>
+      <c r="J198" s="85"/>
       <c r="K198" s="87"/>
       <c r="L198" s="87"/>
       <c r="M198" s="87"/>
       <c r="N198" s="88"/>
       <c r="O198" s="89"/>
-      <c r="P198" s="86"/>
-      <c r="Q198" s="86"/>
-      <c r="R198" s="86"/>
-      <c r="S198" s="86"/>
-      <c r="T198" s="86"/>
-      <c r="U198" s="86"/>
-      <c r="V198" s="86"/>
-      <c r="W198" s="86"/>
-      <c r="X198" s="86"/>
-      <c r="Y198" s="86"/>
-      <c r="Z198" s="86"/>
-      <c r="AA198" s="86"/>
-      <c r="AB198" s="86"/>
-      <c r="AC198" s="86"/>
-      <c r="AD198" s="86"/>
-      <c r="AE198" s="86"/>
-      <c r="AF198" s="86"/>
-      <c r="AG198" s="86"/>
-      <c r="AH198" s="86"/>
-      <c r="AI198" s="86"/>
-      <c r="AJ198" s="86"/>
+      <c r="P198" s="85"/>
+      <c r="Q198" s="85"/>
+      <c r="R198" s="85"/>
+      <c r="S198" s="85"/>
+      <c r="T198" s="85"/>
+      <c r="U198" s="85"/>
+      <c r="V198" s="85"/>
+      <c r="W198" s="85"/>
+      <c r="X198" s="85"/>
+      <c r="Y198" s="85"/>
+      <c r="Z198" s="85"/>
+      <c r="AA198" s="85"/>
+      <c r="AB198" s="85"/>
+      <c r="AC198" s="85"/>
+      <c r="AD198" s="85"/>
+      <c r="AE198" s="85"/>
+      <c r="AF198" s="85"/>
+      <c r="AG198" s="85"/>
+      <c r="AH198" s="85"/>
+      <c r="AI198" s="85"/>
+      <c r="AJ198" s="85"/>
       <c r="AK198" s="88"/>
       <c r="AL198" s="90"/>
       <c r="AM198" s="39"/>
@@ -10504,7 +10477,7 @@
       <c r="AM199" s="40"/>
       <c r="AN199" s="42"/>
     </row>
-    <row r="200" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B200" s="33">
         <v>97</v>
       </c>
@@ -10516,36 +10489,36 @@
       <c r="F200" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G200" s="85"/>
-      <c r="H200" s="86"/>
-      <c r="I200" s="86"/>
-      <c r="J200" s="86"/>
+      <c r="G200" s="86"/>
+      <c r="H200" s="85"/>
+      <c r="I200" s="85"/>
+      <c r="J200" s="85"/>
       <c r="K200" s="87"/>
       <c r="L200" s="87"/>
       <c r="M200" s="87"/>
       <c r="N200" s="88"/>
       <c r="O200" s="89"/>
-      <c r="P200" s="86"/>
-      <c r="Q200" s="86"/>
-      <c r="R200" s="86"/>
-      <c r="S200" s="86"/>
-      <c r="T200" s="86"/>
-      <c r="U200" s="86"/>
-      <c r="V200" s="86"/>
-      <c r="W200" s="86"/>
-      <c r="X200" s="86"/>
-      <c r="Y200" s="86"/>
-      <c r="Z200" s="86"/>
-      <c r="AA200" s="86"/>
-      <c r="AB200" s="86"/>
-      <c r="AC200" s="86"/>
-      <c r="AD200" s="86"/>
-      <c r="AE200" s="86"/>
-      <c r="AF200" s="86"/>
-      <c r="AG200" s="86"/>
-      <c r="AH200" s="86"/>
-      <c r="AI200" s="86"/>
-      <c r="AJ200" s="86"/>
+      <c r="P200" s="85"/>
+      <c r="Q200" s="85"/>
+      <c r="R200" s="85"/>
+      <c r="S200" s="85"/>
+      <c r="T200" s="85"/>
+      <c r="U200" s="85"/>
+      <c r="V200" s="85"/>
+      <c r="W200" s="85"/>
+      <c r="X200" s="85"/>
+      <c r="Y200" s="85"/>
+      <c r="Z200" s="85"/>
+      <c r="AA200" s="85"/>
+      <c r="AB200" s="85"/>
+      <c r="AC200" s="85"/>
+      <c r="AD200" s="85"/>
+      <c r="AE200" s="85"/>
+      <c r="AF200" s="85"/>
+      <c r="AG200" s="85"/>
+      <c r="AH200" s="85"/>
+      <c r="AI200" s="85"/>
+      <c r="AJ200" s="85"/>
       <c r="AK200" s="88"/>
       <c r="AL200" s="90"/>
       <c r="AM200" s="39"/>
@@ -10596,7 +10569,7 @@
       <c r="AM201" s="40"/>
       <c r="AN201" s="42"/>
     </row>
-    <row r="202" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B202" s="43">
         <v>98</v>
       </c>
@@ -10608,36 +10581,36 @@
       <c r="F202" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G202" s="85"/>
-      <c r="H202" s="86"/>
-      <c r="I202" s="86"/>
-      <c r="J202" s="86"/>
+      <c r="G202" s="86"/>
+      <c r="H202" s="85"/>
+      <c r="I202" s="85"/>
+      <c r="J202" s="85"/>
       <c r="K202" s="87"/>
       <c r="L202" s="87"/>
       <c r="M202" s="87"/>
       <c r="N202" s="88"/>
       <c r="O202" s="89"/>
-      <c r="P202" s="86"/>
-      <c r="Q202" s="86"/>
-      <c r="R202" s="86"/>
-      <c r="S202" s="86"/>
-      <c r="T202" s="86"/>
-      <c r="U202" s="86"/>
-      <c r="V202" s="86"/>
-      <c r="W202" s="86"/>
-      <c r="X202" s="86"/>
-      <c r="Y202" s="86"/>
-      <c r="Z202" s="86"/>
-      <c r="AA202" s="86"/>
-      <c r="AB202" s="86"/>
-      <c r="AC202" s="86"/>
-      <c r="AD202" s="86"/>
-      <c r="AE202" s="86"/>
-      <c r="AF202" s="86"/>
-      <c r="AG202" s="86"/>
-      <c r="AH202" s="86"/>
-      <c r="AI202" s="86"/>
-      <c r="AJ202" s="86"/>
+      <c r="P202" s="85"/>
+      <c r="Q202" s="85"/>
+      <c r="R202" s="85"/>
+      <c r="S202" s="85"/>
+      <c r="T202" s="85"/>
+      <c r="U202" s="85"/>
+      <c r="V202" s="85"/>
+      <c r="W202" s="85"/>
+      <c r="X202" s="85"/>
+      <c r="Y202" s="85"/>
+      <c r="Z202" s="85"/>
+      <c r="AA202" s="85"/>
+      <c r="AB202" s="85"/>
+      <c r="AC202" s="85"/>
+      <c r="AD202" s="85"/>
+      <c r="AE202" s="85"/>
+      <c r="AF202" s="85"/>
+      <c r="AG202" s="85"/>
+      <c r="AH202" s="85"/>
+      <c r="AI202" s="85"/>
+      <c r="AJ202" s="85"/>
       <c r="AK202" s="88"/>
       <c r="AL202" s="90"/>
       <c r="AM202" s="39"/>
@@ -10688,7 +10661,7 @@
       <c r="AM203" s="40"/>
       <c r="AN203" s="42"/>
     </row>
-    <row r="204" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="33">
         <v>99</v>
       </c>
@@ -10700,36 +10673,36 @@
       <c r="F204" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G204" s="85"/>
-      <c r="H204" s="86"/>
-      <c r="I204" s="86"/>
-      <c r="J204" s="86"/>
+      <c r="G204" s="86"/>
+      <c r="H204" s="85"/>
+      <c r="I204" s="85"/>
+      <c r="J204" s="85"/>
       <c r="K204" s="87"/>
       <c r="L204" s="87"/>
       <c r="M204" s="87"/>
       <c r="N204" s="88"/>
       <c r="O204" s="89"/>
-      <c r="P204" s="86"/>
-      <c r="Q204" s="86"/>
-      <c r="R204" s="86"/>
-      <c r="S204" s="86"/>
-      <c r="T204" s="86"/>
-      <c r="U204" s="86"/>
-      <c r="V204" s="86"/>
-      <c r="W204" s="86"/>
-      <c r="X204" s="86"/>
-      <c r="Y204" s="86"/>
-      <c r="Z204" s="86"/>
-      <c r="AA204" s="86"/>
-      <c r="AB204" s="86"/>
-      <c r="AC204" s="86"/>
-      <c r="AD204" s="86"/>
-      <c r="AE204" s="86"/>
-      <c r="AF204" s="86"/>
-      <c r="AG204" s="86"/>
-      <c r="AH204" s="86"/>
-      <c r="AI204" s="86"/>
-      <c r="AJ204" s="86"/>
+      <c r="P204" s="85"/>
+      <c r="Q204" s="85"/>
+      <c r="R204" s="85"/>
+      <c r="S204" s="85"/>
+      <c r="T204" s="85"/>
+      <c r="U204" s="85"/>
+      <c r="V204" s="85"/>
+      <c r="W204" s="85"/>
+      <c r="X204" s="85"/>
+      <c r="Y204" s="85"/>
+      <c r="Z204" s="85"/>
+      <c r="AA204" s="85"/>
+      <c r="AB204" s="85"/>
+      <c r="AC204" s="85"/>
+      <c r="AD204" s="85"/>
+      <c r="AE204" s="85"/>
+      <c r="AF204" s="85"/>
+      <c r="AG204" s="85"/>
+      <c r="AH204" s="85"/>
+      <c r="AI204" s="85"/>
+      <c r="AJ204" s="85"/>
       <c r="AK204" s="88"/>
       <c r="AL204" s="90"/>
       <c r="AM204" s="39"/>
@@ -10780,7 +10753,7 @@
       <c r="AM205" s="40"/>
       <c r="AN205" s="42"/>
     </row>
-    <row r="206" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B206" s="43">
         <v>100</v>
       </c>
@@ -10792,36 +10765,36 @@
       <c r="F206" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G206" s="85"/>
-      <c r="H206" s="86"/>
-      <c r="I206" s="86"/>
-      <c r="J206" s="86"/>
+      <c r="G206" s="86"/>
+      <c r="H206" s="85"/>
+      <c r="I206" s="85"/>
+      <c r="J206" s="85"/>
       <c r="K206" s="87"/>
       <c r="L206" s="87"/>
       <c r="M206" s="87"/>
       <c r="N206" s="88"/>
       <c r="O206" s="89"/>
-      <c r="P206" s="86"/>
-      <c r="Q206" s="86"/>
-      <c r="R206" s="86"/>
-      <c r="S206" s="86"/>
-      <c r="T206" s="86"/>
-      <c r="U206" s="86"/>
-      <c r="V206" s="86"/>
-      <c r="W206" s="86"/>
-      <c r="X206" s="86"/>
-      <c r="Y206" s="86"/>
-      <c r="Z206" s="86"/>
-      <c r="AA206" s="86"/>
-      <c r="AB206" s="86"/>
-      <c r="AC206" s="86"/>
-      <c r="AD206" s="86"/>
-      <c r="AE206" s="86"/>
-      <c r="AF206" s="86"/>
-      <c r="AG206" s="86"/>
-      <c r="AH206" s="86"/>
-      <c r="AI206" s="86"/>
-      <c r="AJ206" s="86"/>
+      <c r="P206" s="85"/>
+      <c r="Q206" s="85"/>
+      <c r="R206" s="85"/>
+      <c r="S206" s="85"/>
+      <c r="T206" s="85"/>
+      <c r="U206" s="85"/>
+      <c r="V206" s="85"/>
+      <c r="W206" s="85"/>
+      <c r="X206" s="85"/>
+      <c r="Y206" s="85"/>
+      <c r="Z206" s="85"/>
+      <c r="AA206" s="85"/>
+      <c r="AB206" s="85"/>
+      <c r="AC206" s="85"/>
+      <c r="AD206" s="85"/>
+      <c r="AE206" s="85"/>
+      <c r="AF206" s="85"/>
+      <c r="AG206" s="85"/>
+      <c r="AH206" s="85"/>
+      <c r="AI206" s="85"/>
+      <c r="AJ206" s="85"/>
       <c r="AK206" s="88"/>
       <c r="AL206" s="90"/>
       <c r="AM206" s="39"/>
@@ -11136,6 +11109,20 @@
     </row>
   </sheetData>
   <mergeCells count="552">
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="B1:AN1"/>
     <mergeCell ref="B2:AN2"/>
     <mergeCell ref="B3:AN3"/>
@@ -11153,22 +11140,6 @@
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
@@ -11191,6 +11162,8 @@
     <mergeCell ref="V6:V7"/>
     <mergeCell ref="W6:W7"/>
     <mergeCell ref="X6:X7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="P6:P7"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D13"/>

--- a/Toplu_Mesai_Sablon.xlsx
+++ b/Toplu_Mesai_Sablon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E667AEB0-60E2-491D-A726-E103217AA593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9A97EE-4EDF-48AF-953F-6069E66665A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2DF94309-6D47-4284-9046-50F652E00677}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>ADI SOYADI</t>
   </si>
   <si>
-    <t>Mes.</t>
-  </si>
-  <si>
     <t>Türü</t>
   </si>
   <si>
@@ -81,6 +78,9 @@
   </si>
   <si>
     <t>15</t>
+  </si>
+  <si>
+    <t>Mesai</t>
   </si>
 </sst>
 </file>
@@ -745,17 +745,29 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -769,19 +781,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -791,9 +863,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -808,85 +877,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -895,10 +889,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1228,133 +1228,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-      <c r="AD1" s="58"/>
-      <c r="AE1" s="58"/>
-      <c r="AF1" s="58"/>
-      <c r="AG1" s="58"/>
-      <c r="AH1" s="58"/>
-      <c r="AI1" s="58"/>
-      <c r="AJ1" s="58"/>
-      <c r="AK1" s="58"/>
-      <c r="AL1" s="58"/>
-      <c r="AM1" s="58"/>
-      <c r="AN1" s="58"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+      <c r="AI1" s="82"/>
+      <c r="AJ1" s="82"/>
+      <c r="AK1" s="82"/>
+      <c r="AL1" s="82"/>
+      <c r="AM1" s="82"/>
+      <c r="AN1" s="82"/>
     </row>
     <row r="2" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="58"/>
-      <c r="AB2" s="58"/>
-      <c r="AC2" s="58"/>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="58"/>
-      <c r="AH2" s="58"/>
-      <c r="AI2" s="58"/>
-      <c r="AJ2" s="58"/>
-      <c r="AK2" s="58"/>
-      <c r="AL2" s="58"/>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="58"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="82"/>
+      <c r="U2" s="82"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="82"/>
+      <c r="X2" s="82"/>
+      <c r="Y2" s="82"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
+      <c r="AB2" s="82"/>
+      <c r="AC2" s="82"/>
+      <c r="AD2" s="82"/>
+      <c r="AE2" s="82"/>
+      <c r="AF2" s="82"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="82"/>
+      <c r="AI2" s="82"/>
+      <c r="AJ2" s="82"/>
+      <c r="AK2" s="82"/>
+      <c r="AL2" s="82"/>
+      <c r="AM2" s="82"/>
+      <c r="AN2" s="82"/>
     </row>
     <row r="3" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="58"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="58"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="58"/>
-      <c r="AD3" s="58"/>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="58"/>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="58"/>
-      <c r="AJ3" s="58"/>
-      <c r="AK3" s="58"/>
-      <c r="AL3" s="58"/>
-      <c r="AM3" s="58"/>
-      <c r="AN3" s="58"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="82"/>
+      <c r="AJ3" s="82"/>
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="82"/>
+      <c r="AM3" s="82"/>
+      <c r="AN3" s="82"/>
     </row>
     <row r="4" spans="2:40" s="5" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
@@ -1394,217 +1394,217 @@
       <c r="AJ4" s="4"/>
     </row>
     <row r="5" spans="2:40" s="6" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="95"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="52"/>
-      <c r="Z5" s="52"/>
-      <c r="AA5" s="52"/>
-      <c r="AB5" s="52"/>
-      <c r="AC5" s="52"/>
-      <c r="AD5" s="52"/>
-      <c r="AE5" s="52"/>
-      <c r="AF5" s="52"/>
-      <c r="AG5" s="52"/>
-      <c r="AH5" s="52"/>
-      <c r="AI5" s="52"/>
-      <c r="AJ5" s="52"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="67" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="54"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="54"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="54"/>
+      <c r="AC5" s="54"/>
+      <c r="AD5" s="54"/>
+      <c r="AE5" s="54"/>
+      <c r="AF5" s="54"/>
+      <c r="AG5" s="54"/>
+      <c r="AH5" s="54"/>
+      <c r="AI5" s="54"/>
+      <c r="AJ5" s="54"/>
+      <c r="AK5" s="78"/>
+      <c r="AL5" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="AM5" s="56" t="s">
+      <c r="AM5" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="AN5" s="56" t="s">
+      <c r="AN5" s="60" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:40" s="6" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="99"/>
+      <c r="G6" s="100">
+        <v>24</v>
+      </c>
+      <c r="H6" s="54">
+        <v>25</v>
+      </c>
+      <c r="I6" s="54">
+        <v>26</v>
+      </c>
+      <c r="J6" s="54">
+        <v>27</v>
+      </c>
+      <c r="K6" s="66">
+        <v>28</v>
+      </c>
+      <c r="L6" s="66">
+        <v>29</v>
+      </c>
+      <c r="M6" s="66">
+        <v>30</v>
+      </c>
+      <c r="N6" s="88">
+        <v>31</v>
+      </c>
+      <c r="O6" s="89">
+        <v>1</v>
+      </c>
+      <c r="P6" s="54">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="54">
+        <v>3</v>
+      </c>
+      <c r="R6" s="54">
+        <v>4</v>
+      </c>
+      <c r="S6" s="54">
+        <v>5</v>
+      </c>
+      <c r="T6" s="54">
+        <v>6</v>
+      </c>
+      <c r="U6" s="54">
+        <v>7</v>
+      </c>
+      <c r="V6" s="54">
+        <v>8</v>
+      </c>
+      <c r="W6" s="54">
         <v>9</v>
       </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="50">
-        <v>24</v>
-      </c>
-      <c r="H6" s="52">
-        <v>25</v>
-      </c>
-      <c r="I6" s="52">
-        <v>26</v>
-      </c>
-      <c r="J6" s="52">
-        <v>27</v>
-      </c>
-      <c r="K6" s="62">
-        <v>28</v>
-      </c>
-      <c r="L6" s="62">
-        <v>29</v>
-      </c>
-      <c r="M6" s="62">
-        <v>30</v>
-      </c>
-      <c r="N6" s="64">
-        <v>31</v>
-      </c>
-      <c r="O6" s="65">
+      <c r="X6" s="54">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="54">
+        <v>11</v>
+      </c>
+      <c r="Z6" s="54">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="54">
+        <v>13</v>
+      </c>
+      <c r="AB6" s="54">
+        <v>14</v>
+      </c>
+      <c r="AC6" s="54">
+        <v>15</v>
+      </c>
+      <c r="AD6" s="54">
+        <v>16</v>
+      </c>
+      <c r="AE6" s="54">
+        <v>17</v>
+      </c>
+      <c r="AF6" s="54">
+        <v>18</v>
+      </c>
+      <c r="AG6" s="54">
+        <v>19</v>
+      </c>
+      <c r="AH6" s="54">
+        <v>20</v>
+      </c>
+      <c r="AI6" s="54">
+        <v>21</v>
+      </c>
+      <c r="AJ6" s="54">
+        <v>22</v>
+      </c>
+      <c r="AK6" s="78">
+        <v>23</v>
+      </c>
+      <c r="AL6" s="91"/>
+      <c r="AM6" s="93"/>
+      <c r="AN6" s="93"/>
+    </row>
+    <row r="7" spans="2:40" s="6" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="81"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="70"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="70"/>
+      <c r="W7" s="70"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="70"/>
+      <c r="Z7" s="70"/>
+      <c r="AA7" s="70"/>
+      <c r="AB7" s="70"/>
+      <c r="AC7" s="70"/>
+      <c r="AD7" s="70"/>
+      <c r="AE7" s="70"/>
+      <c r="AF7" s="70"/>
+      <c r="AG7" s="70"/>
+      <c r="AH7" s="70"/>
+      <c r="AI7" s="70"/>
+      <c r="AJ7" s="70"/>
+      <c r="AK7" s="79"/>
+      <c r="AL7" s="92"/>
+      <c r="AM7" s="73"/>
+      <c r="AN7" s="73"/>
+    </row>
+    <row r="8" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="52">
         <v>1</v>
       </c>
-      <c r="P6" s="52">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="52">
-        <v>3</v>
-      </c>
-      <c r="R6" s="52">
-        <v>4</v>
-      </c>
-      <c r="S6" s="52">
-        <v>5</v>
-      </c>
-      <c r="T6" s="52">
-        <v>6</v>
-      </c>
-      <c r="U6" s="52">
-        <v>7</v>
-      </c>
-      <c r="V6" s="52">
-        <v>8</v>
-      </c>
-      <c r="W6" s="52">
-        <v>9</v>
-      </c>
-      <c r="X6" s="52">
+      <c r="C8" s="54"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="Y6" s="52">
-        <v>11</v>
-      </c>
-      <c r="Z6" s="52">
-        <v>12</v>
-      </c>
-      <c r="AA6" s="52">
-        <v>13</v>
-      </c>
-      <c r="AB6" s="52">
-        <v>14</v>
-      </c>
-      <c r="AC6" s="52">
-        <v>15</v>
-      </c>
-      <c r="AD6" s="52">
-        <v>16</v>
-      </c>
-      <c r="AE6" s="52">
-        <v>17</v>
-      </c>
-      <c r="AF6" s="52">
-        <v>18</v>
-      </c>
-      <c r="AG6" s="52">
-        <v>19</v>
-      </c>
-      <c r="AH6" s="52">
-        <v>20</v>
-      </c>
-      <c r="AI6" s="52">
-        <v>21</v>
-      </c>
-      <c r="AJ6" s="52">
-        <v>22</v>
-      </c>
-      <c r="AK6" s="66">
-        <v>23</v>
-      </c>
-      <c r="AL6" s="68"/>
-      <c r="AM6" s="70"/>
-      <c r="AN6" s="70"/>
-    </row>
-    <row r="7" spans="2:40" s="6" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="82"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="101"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="53"/>
-      <c r="U7" s="53"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="53"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="53"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="53"/>
-      <c r="AB7" s="53"/>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="53"/>
-      <c r="AH7" s="53"/>
-      <c r="AI7" s="53"/>
-      <c r="AJ7" s="53"/>
-      <c r="AK7" s="80"/>
-      <c r="AL7" s="69"/>
-      <c r="AM7" s="71"/>
-      <c r="AN7" s="71"/>
-    </row>
-    <row r="8" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="81">
-        <v>1</v>
-      </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="40"/>
       <c r="H8" s="31"/>
@@ -1638,18 +1638,18 @@
       <c r="AJ8" s="31"/>
       <c r="AK8" s="36"/>
       <c r="AL8" s="33"/>
-      <c r="AM8" s="54"/>
-      <c r="AN8" s="56"/>
+      <c r="AM8" s="58"/>
+      <c r="AN8" s="60"/>
     </row>
     <row r="9" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="82"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="85"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="57"/>
       <c r="E9" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="43"/>
       <c r="H9" s="32"/>
@@ -1683,20 +1683,20 @@
       <c r="AJ9" s="32"/>
       <c r="AK9" s="45"/>
       <c r="AL9" s="34"/>
-      <c r="AM9" s="55"/>
-      <c r="AN9" s="57"/>
+      <c r="AM9" s="59"/>
+      <c r="AN9" s="61"/>
     </row>
     <row r="10" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="75">
+      <c r="B10" s="62">
         <v>2</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="77"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="75"/>
       <c r="E10" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="40"/>
       <c r="H10" s="31"/>
@@ -1730,18 +1730,18 @@
       <c r="AJ10" s="31"/>
       <c r="AK10" s="36"/>
       <c r="AL10" s="33"/>
-      <c r="AM10" s="54"/>
-      <c r="AN10" s="56"/>
+      <c r="AM10" s="58"/>
+      <c r="AN10" s="60"/>
     </row>
     <row r="11" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="76"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="78"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="76"/>
       <c r="E11" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="41"/>
       <c r="H11" s="35"/>
@@ -1775,20 +1775,20 @@
       <c r="AJ11" s="35"/>
       <c r="AK11" s="37"/>
       <c r="AL11" s="34"/>
-      <c r="AM11" s="79"/>
-      <c r="AN11" s="71"/>
+      <c r="AM11" s="72"/>
+      <c r="AN11" s="73"/>
     </row>
     <row r="12" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="81">
+      <c r="B12" s="52">
         <v>3</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="84"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="56"/>
       <c r="E12" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" s="40"/>
       <c r="H12" s="31"/>
@@ -1822,18 +1822,18 @@
       <c r="AJ12" s="31"/>
       <c r="AK12" s="36"/>
       <c r="AL12" s="33"/>
-      <c r="AM12" s="54"/>
-      <c r="AN12" s="56"/>
+      <c r="AM12" s="58"/>
+      <c r="AN12" s="60"/>
     </row>
     <row r="13" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="82"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="85"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="57"/>
       <c r="E13" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="43"/>
       <c r="H13" s="32"/>
@@ -1867,20 +1867,20 @@
       <c r="AJ13" s="32"/>
       <c r="AK13" s="45"/>
       <c r="AL13" s="34"/>
-      <c r="AM13" s="55"/>
-      <c r="AN13" s="57"/>
+      <c r="AM13" s="59"/>
+      <c r="AN13" s="61"/>
     </row>
     <row r="14" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="75">
+      <c r="B14" s="62">
         <v>4</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="84"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="40"/>
       <c r="H14" s="31"/>
@@ -1914,18 +1914,18 @@
       <c r="AJ14" s="31"/>
       <c r="AK14" s="36"/>
       <c r="AL14" s="33"/>
-      <c r="AM14" s="54"/>
-      <c r="AN14" s="56"/>
+      <c r="AM14" s="58"/>
+      <c r="AN14" s="60"/>
     </row>
     <row r="15" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="86"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="85"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="57"/>
       <c r="E15" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="43"/>
       <c r="H15" s="32"/>
@@ -1959,20 +1959,20 @@
       <c r="AJ15" s="32"/>
       <c r="AK15" s="45"/>
       <c r="AL15" s="34"/>
-      <c r="AM15" s="55"/>
-      <c r="AN15" s="57"/>
+      <c r="AM15" s="59"/>
+      <c r="AN15" s="61"/>
     </row>
     <row r="16" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="81">
+      <c r="B16" s="52">
         <v>5</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="87"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="64"/>
       <c r="E16" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="40"/>
       <c r="H16" s="31"/>
@@ -2006,18 +2006,18 @@
       <c r="AJ16" s="31"/>
       <c r="AK16" s="36"/>
       <c r="AL16" s="33"/>
-      <c r="AM16" s="54"/>
-      <c r="AN16" s="56"/>
+      <c r="AM16" s="58"/>
+      <c r="AN16" s="60"/>
     </row>
     <row r="17" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="82"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="88"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="65"/>
       <c r="E17" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="43"/>
       <c r="H17" s="32"/>
@@ -2051,20 +2051,20 @@
       <c r="AJ17" s="32"/>
       <c r="AK17" s="45"/>
       <c r="AL17" s="34"/>
-      <c r="AM17" s="55"/>
-      <c r="AN17" s="57"/>
+      <c r="AM17" s="59"/>
+      <c r="AN17" s="61"/>
     </row>
     <row r="18" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="75">
+      <c r="B18" s="62">
         <v>6</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="87"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="64"/>
       <c r="E18" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="40"/>
       <c r="H18" s="31"/>
@@ -2098,18 +2098,18 @@
       <c r="AJ18" s="31"/>
       <c r="AK18" s="36"/>
       <c r="AL18" s="33"/>
-      <c r="AM18" s="54"/>
-      <c r="AN18" s="56"/>
+      <c r="AM18" s="58"/>
+      <c r="AN18" s="60"/>
     </row>
     <row r="19" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="86"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="88"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="65"/>
       <c r="E19" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" s="43"/>
       <c r="H19" s="32"/>
@@ -2143,20 +2143,20 @@
       <c r="AJ19" s="32"/>
       <c r="AK19" s="45"/>
       <c r="AL19" s="34"/>
-      <c r="AM19" s="55"/>
-      <c r="AN19" s="57"/>
+      <c r="AM19" s="59"/>
+      <c r="AN19" s="61"/>
     </row>
     <row r="20" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="81">
+      <c r="B20" s="52">
         <v>7</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="87"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="64"/>
       <c r="E20" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="40"/>
       <c r="H20" s="31"/>
@@ -2190,18 +2190,18 @@
       <c r="AJ20" s="31"/>
       <c r="AK20" s="36"/>
       <c r="AL20" s="33"/>
-      <c r="AM20" s="54"/>
-      <c r="AN20" s="56"/>
+      <c r="AM20" s="58"/>
+      <c r="AN20" s="60"/>
     </row>
     <row r="21" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="82"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="88"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="43"/>
       <c r="H21" s="32"/>
@@ -2235,20 +2235,20 @@
       <c r="AJ21" s="32"/>
       <c r="AK21" s="45"/>
       <c r="AL21" s="34"/>
-      <c r="AM21" s="55"/>
-      <c r="AN21" s="57"/>
+      <c r="AM21" s="59"/>
+      <c r="AN21" s="61"/>
     </row>
     <row r="22" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="75">
+      <c r="B22" s="62">
         <v>8</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="84"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="56"/>
       <c r="E22" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" s="40"/>
       <c r="H22" s="31"/>
@@ -2282,18 +2282,18 @@
       <c r="AJ22" s="31"/>
       <c r="AK22" s="36"/>
       <c r="AL22" s="33"/>
-      <c r="AM22" s="54"/>
-      <c r="AN22" s="56"/>
+      <c r="AM22" s="58"/>
+      <c r="AN22" s="60"/>
     </row>
     <row r="23" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="86"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="85"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="57"/>
       <c r="E23" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="43"/>
       <c r="H23" s="32"/>
@@ -2327,20 +2327,20 @@
       <c r="AJ23" s="32"/>
       <c r="AK23" s="45"/>
       <c r="AL23" s="34"/>
-      <c r="AM23" s="55"/>
-      <c r="AN23" s="57"/>
+      <c r="AM23" s="59"/>
+      <c r="AN23" s="61"/>
     </row>
     <row r="24" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="81">
+      <c r="B24" s="52">
         <v>9</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="87"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="64"/>
       <c r="E24" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" s="40"/>
       <c r="H24" s="31"/>
@@ -2374,18 +2374,18 @@
       <c r="AJ24" s="31"/>
       <c r="AK24" s="36"/>
       <c r="AL24" s="33"/>
-      <c r="AM24" s="54"/>
-      <c r="AN24" s="56"/>
+      <c r="AM24" s="58"/>
+      <c r="AN24" s="60"/>
     </row>
     <row r="25" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="82"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="88"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="65"/>
       <c r="E25" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="43"/>
       <c r="H25" s="32"/>
@@ -2419,20 +2419,20 @@
       <c r="AJ25" s="32"/>
       <c r="AK25" s="45"/>
       <c r="AL25" s="34"/>
-      <c r="AM25" s="55"/>
-      <c r="AN25" s="57"/>
+      <c r="AM25" s="59"/>
+      <c r="AN25" s="61"/>
     </row>
     <row r="26" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="75">
+      <c r="B26" s="62">
         <v>10</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="84"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26" s="40"/>
       <c r="H26" s="31"/>
@@ -2466,18 +2466,18 @@
       <c r="AJ26" s="31"/>
       <c r="AK26" s="36"/>
       <c r="AL26" s="33"/>
-      <c r="AM26" s="54"/>
-      <c r="AN26" s="56"/>
+      <c r="AM26" s="58"/>
+      <c r="AN26" s="60"/>
     </row>
     <row r="27" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="76"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="89"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="71"/>
       <c r="E27" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27" s="41"/>
       <c r="H27" s="35"/>
@@ -2511,20 +2511,20 @@
       <c r="AJ27" s="35"/>
       <c r="AK27" s="37"/>
       <c r="AL27" s="34"/>
-      <c r="AM27" s="79"/>
-      <c r="AN27" s="71"/>
+      <c r="AM27" s="72"/>
+      <c r="AN27" s="73"/>
     </row>
     <row r="28" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="81">
-        <v>11</v>
-      </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="84"/>
+      <c r="B28" s="52">
+        <v>11</v>
+      </c>
+      <c r="C28" s="54"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="31"/>
@@ -2558,18 +2558,18 @@
       <c r="AJ28" s="31"/>
       <c r="AK28" s="36"/>
       <c r="AL28" s="33"/>
-      <c r="AM28" s="54"/>
-      <c r="AN28" s="56"/>
+      <c r="AM28" s="58"/>
+      <c r="AN28" s="60"/>
     </row>
     <row r="29" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="82"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="85"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="57"/>
       <c r="E29" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G29" s="43"/>
       <c r="H29" s="32"/>
@@ -2603,20 +2603,20 @@
       <c r="AJ29" s="32"/>
       <c r="AK29" s="45"/>
       <c r="AL29" s="34"/>
-      <c r="AM29" s="55"/>
-      <c r="AN29" s="57"/>
+      <c r="AM29" s="59"/>
+      <c r="AN29" s="61"/>
     </row>
     <row r="30" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="75">
+      <c r="B30" s="62">
         <v>12</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="84"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="31"/>
@@ -2650,18 +2650,18 @@
       <c r="AJ30" s="31"/>
       <c r="AK30" s="36"/>
       <c r="AL30" s="33"/>
-      <c r="AM30" s="54"/>
-      <c r="AN30" s="56"/>
+      <c r="AM30" s="58"/>
+      <c r="AN30" s="60"/>
     </row>
     <row r="31" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="86"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="85"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G31" s="43"/>
       <c r="H31" s="32"/>
@@ -2695,20 +2695,20 @@
       <c r="AJ31" s="32"/>
       <c r="AK31" s="45"/>
       <c r="AL31" s="34"/>
-      <c r="AM31" s="55"/>
-      <c r="AN31" s="57"/>
+      <c r="AM31" s="59"/>
+      <c r="AN31" s="61"/>
     </row>
     <row r="32" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="81">
+      <c r="B32" s="52">
         <v>13</v>
       </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="84"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G32" s="40"/>
       <c r="H32" s="31"/>
@@ -2742,18 +2742,18 @@
       <c r="AJ32" s="31"/>
       <c r="AK32" s="36"/>
       <c r="AL32" s="33"/>
-      <c r="AM32" s="54"/>
-      <c r="AN32" s="56"/>
+      <c r="AM32" s="58"/>
+      <c r="AN32" s="60"/>
     </row>
     <row r="33" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="82"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="85"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="57"/>
       <c r="E33" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G33" s="43"/>
       <c r="H33" s="32"/>
@@ -2787,20 +2787,20 @@
       <c r="AJ33" s="32"/>
       <c r="AK33" s="45"/>
       <c r="AL33" s="34"/>
-      <c r="AM33" s="55"/>
-      <c r="AN33" s="57"/>
+      <c r="AM33" s="59"/>
+      <c r="AN33" s="61"/>
     </row>
     <row r="34" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="75">
+      <c r="B34" s="62">
         <v>14</v>
       </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="84"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34" s="40"/>
       <c r="H34" s="31"/>
@@ -2834,18 +2834,18 @@
       <c r="AJ34" s="31"/>
       <c r="AK34" s="36"/>
       <c r="AL34" s="33"/>
-      <c r="AM34" s="54"/>
-      <c r="AN34" s="56"/>
+      <c r="AM34" s="58"/>
+      <c r="AN34" s="60"/>
     </row>
     <row r="35" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="86"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="85"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="57"/>
       <c r="E35" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G35" s="43"/>
       <c r="H35" s="32"/>
@@ -2879,20 +2879,20 @@
       <c r="AJ35" s="32"/>
       <c r="AK35" s="45"/>
       <c r="AL35" s="34"/>
-      <c r="AM35" s="55"/>
-      <c r="AN35" s="57"/>
+      <c r="AM35" s="59"/>
+      <c r="AN35" s="61"/>
     </row>
     <row r="36" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="81">
+      <c r="B36" s="52">
         <v>15</v>
       </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="84"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="56"/>
       <c r="E36" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36" s="40"/>
       <c r="H36" s="31"/>
@@ -2926,18 +2926,18 @@
       <c r="AJ36" s="31"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="33"/>
-      <c r="AM36" s="54"/>
-      <c r="AN36" s="56"/>
+      <c r="AM36" s="58"/>
+      <c r="AN36" s="60"/>
     </row>
     <row r="37" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="82"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="85"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="57"/>
       <c r="E37" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G37" s="43"/>
       <c r="H37" s="32"/>
@@ -2971,20 +2971,20 @@
       <c r="AJ37" s="32"/>
       <c r="AK37" s="45"/>
       <c r="AL37" s="34"/>
-      <c r="AM37" s="55"/>
-      <c r="AN37" s="57"/>
+      <c r="AM37" s="59"/>
+      <c r="AN37" s="61"/>
     </row>
     <row r="38" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="75">
+      <c r="B38" s="62">
         <v>16</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="84"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="56"/>
       <c r="E38" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G38" s="40"/>
       <c r="H38" s="31"/>
@@ -3018,18 +3018,18 @@
       <c r="AJ38" s="31"/>
       <c r="AK38" s="36"/>
       <c r="AL38" s="33"/>
-      <c r="AM38" s="54"/>
-      <c r="AN38" s="56"/>
+      <c r="AM38" s="58"/>
+      <c r="AN38" s="60"/>
     </row>
     <row r="39" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="86"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="85"/>
+      <c r="B39" s="63"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="57"/>
       <c r="E39" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G39" s="43"/>
       <c r="H39" s="32"/>
@@ -3063,20 +3063,20 @@
       <c r="AJ39" s="32"/>
       <c r="AK39" s="45"/>
       <c r="AL39" s="34"/>
-      <c r="AM39" s="55"/>
-      <c r="AN39" s="57"/>
+      <c r="AM39" s="59"/>
+      <c r="AN39" s="61"/>
     </row>
     <row r="40" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="81">
+      <c r="B40" s="52">
         <v>17</v>
       </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="84"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="56"/>
       <c r="E40" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="31"/>
@@ -3110,18 +3110,18 @@
       <c r="AJ40" s="31"/>
       <c r="AK40" s="36"/>
       <c r="AL40" s="33"/>
-      <c r="AM40" s="54"/>
-      <c r="AN40" s="56"/>
+      <c r="AM40" s="58"/>
+      <c r="AN40" s="60"/>
     </row>
     <row r="41" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="82"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="85"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="57"/>
       <c r="E41" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41" s="43"/>
       <c r="H41" s="32"/>
@@ -3155,20 +3155,20 @@
       <c r="AJ41" s="32"/>
       <c r="AK41" s="45"/>
       <c r="AL41" s="34"/>
-      <c r="AM41" s="55"/>
-      <c r="AN41" s="57"/>
+      <c r="AM41" s="59"/>
+      <c r="AN41" s="61"/>
     </row>
     <row r="42" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="75">
+      <c r="B42" s="62">
         <v>18</v>
       </c>
-      <c r="C42" s="52"/>
-      <c r="D42" s="84"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="56"/>
       <c r="E42" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="31"/>
@@ -3202,18 +3202,18 @@
       <c r="AJ42" s="31"/>
       <c r="AK42" s="36"/>
       <c r="AL42" s="33"/>
-      <c r="AM42" s="54"/>
-      <c r="AN42" s="56"/>
+      <c r="AM42" s="58"/>
+      <c r="AN42" s="60"/>
     </row>
     <row r="43" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="86"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="85"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="57"/>
       <c r="E43" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G43" s="43"/>
       <c r="H43" s="32"/>
@@ -3247,20 +3247,20 @@
       <c r="AJ43" s="32"/>
       <c r="AK43" s="45"/>
       <c r="AL43" s="34"/>
-      <c r="AM43" s="55"/>
-      <c r="AN43" s="57"/>
+      <c r="AM43" s="59"/>
+      <c r="AN43" s="61"/>
     </row>
     <row r="44" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="81">
+      <c r="B44" s="52">
         <v>19</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="84"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="56"/>
       <c r="E44" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G44" s="40"/>
       <c r="H44" s="31"/>
@@ -3294,18 +3294,18 @@
       <c r="AJ44" s="31"/>
       <c r="AK44" s="36"/>
       <c r="AL44" s="33"/>
-      <c r="AM44" s="54"/>
-      <c r="AN44" s="56"/>
+      <c r="AM44" s="58"/>
+      <c r="AN44" s="60"/>
     </row>
     <row r="45" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="82"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="85"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="57"/>
       <c r="E45" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G45" s="43"/>
       <c r="H45" s="32"/>
@@ -3339,20 +3339,20 @@
       <c r="AJ45" s="32"/>
       <c r="AK45" s="45"/>
       <c r="AL45" s="34"/>
-      <c r="AM45" s="55"/>
-      <c r="AN45" s="57"/>
+      <c r="AM45" s="59"/>
+      <c r="AN45" s="61"/>
     </row>
     <row r="46" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="75">
+      <c r="B46" s="62">
         <v>20</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="84"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="56"/>
       <c r="E46" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G46" s="40"/>
       <c r="H46" s="31"/>
@@ -3386,18 +3386,18 @@
       <c r="AJ46" s="31"/>
       <c r="AK46" s="36"/>
       <c r="AL46" s="33"/>
-      <c r="AM46" s="54"/>
-      <c r="AN46" s="56"/>
+      <c r="AM46" s="58"/>
+      <c r="AN46" s="60"/>
     </row>
     <row r="47" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="76"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="89"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="71"/>
       <c r="E47" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G47" s="41"/>
       <c r="H47" s="35"/>
@@ -3431,20 +3431,20 @@
       <c r="AJ47" s="35"/>
       <c r="AK47" s="37"/>
       <c r="AL47" s="34"/>
-      <c r="AM47" s="79"/>
-      <c r="AN47" s="71"/>
+      <c r="AM47" s="72"/>
+      <c r="AN47" s="73"/>
     </row>
     <row r="48" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="81">
+      <c r="B48" s="52">
         <v>21</v>
       </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="87"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="64"/>
       <c r="E48" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G48" s="40"/>
       <c r="H48" s="31"/>
@@ -3478,18 +3478,18 @@
       <c r="AJ48" s="31"/>
       <c r="AK48" s="36"/>
       <c r="AL48" s="33"/>
-      <c r="AM48" s="54"/>
-      <c r="AN48" s="56"/>
+      <c r="AM48" s="58"/>
+      <c r="AN48" s="60"/>
     </row>
     <row r="49" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="82"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="88"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="65"/>
       <c r="E49" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G49" s="43"/>
       <c r="H49" s="32"/>
@@ -3523,20 +3523,20 @@
       <c r="AJ49" s="32"/>
       <c r="AK49" s="45"/>
       <c r="AL49" s="34"/>
-      <c r="AM49" s="55"/>
-      <c r="AN49" s="57"/>
+      <c r="AM49" s="59"/>
+      <c r="AN49" s="61"/>
     </row>
     <row r="50" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="75">
+      <c r="B50" s="62">
         <v>22</v>
       </c>
-      <c r="C50" s="52"/>
-      <c r="D50" s="87"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="64"/>
       <c r="E50" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G50" s="40"/>
       <c r="H50" s="31"/>
@@ -3570,18 +3570,18 @@
       <c r="AJ50" s="31"/>
       <c r="AK50" s="36"/>
       <c r="AL50" s="33"/>
-      <c r="AM50" s="54"/>
-      <c r="AN50" s="56"/>
+      <c r="AM50" s="58"/>
+      <c r="AN50" s="60"/>
     </row>
     <row r="51" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="86"/>
-      <c r="C51" s="83"/>
-      <c r="D51" s="88"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="65"/>
       <c r="E51" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G51" s="43"/>
       <c r="H51" s="32"/>
@@ -3615,20 +3615,20 @@
       <c r="AJ51" s="32"/>
       <c r="AK51" s="45"/>
       <c r="AL51" s="34"/>
-      <c r="AM51" s="55"/>
-      <c r="AN51" s="57"/>
+      <c r="AM51" s="59"/>
+      <c r="AN51" s="61"/>
     </row>
     <row r="52" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="81">
+      <c r="B52" s="52">
         <v>23</v>
       </c>
-      <c r="C52" s="52"/>
-      <c r="D52" s="87"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="64"/>
       <c r="E52" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G52" s="40"/>
       <c r="H52" s="31"/>
@@ -3662,18 +3662,18 @@
       <c r="AJ52" s="31"/>
       <c r="AK52" s="36"/>
       <c r="AL52" s="33"/>
-      <c r="AM52" s="54"/>
-      <c r="AN52" s="56"/>
+      <c r="AM52" s="58"/>
+      <c r="AN52" s="60"/>
     </row>
     <row r="53" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="82"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="88"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="65"/>
       <c r="E53" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G53" s="43"/>
       <c r="H53" s="32"/>
@@ -3707,20 +3707,20 @@
       <c r="AJ53" s="32"/>
       <c r="AK53" s="45"/>
       <c r="AL53" s="34"/>
-      <c r="AM53" s="55"/>
-      <c r="AN53" s="57"/>
+      <c r="AM53" s="59"/>
+      <c r="AN53" s="61"/>
     </row>
     <row r="54" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="75">
+      <c r="B54" s="62">
         <v>24</v>
       </c>
-      <c r="C54" s="52"/>
-      <c r="D54" s="87"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="64"/>
       <c r="E54" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G54" s="40"/>
       <c r="H54" s="31"/>
@@ -3754,18 +3754,18 @@
       <c r="AJ54" s="31"/>
       <c r="AK54" s="36"/>
       <c r="AL54" s="33"/>
-      <c r="AM54" s="54"/>
-      <c r="AN54" s="56"/>
+      <c r="AM54" s="58"/>
+      <c r="AN54" s="60"/>
     </row>
     <row r="55" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="86"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="88"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="55"/>
+      <c r="D55" s="65"/>
       <c r="E55" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G55" s="43"/>
       <c r="H55" s="32"/>
@@ -3799,20 +3799,20 @@
       <c r="AJ55" s="32"/>
       <c r="AK55" s="45"/>
       <c r="AL55" s="34"/>
-      <c r="AM55" s="55"/>
-      <c r="AN55" s="57"/>
+      <c r="AM55" s="59"/>
+      <c r="AN55" s="61"/>
     </row>
     <row r="56" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="81">
+      <c r="B56" s="52">
         <v>25</v>
       </c>
-      <c r="C56" s="52"/>
-      <c r="D56" s="84"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="56"/>
       <c r="E56" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G56" s="40"/>
       <c r="H56" s="31"/>
@@ -3846,18 +3846,18 @@
       <c r="AJ56" s="31"/>
       <c r="AK56" s="36"/>
       <c r="AL56" s="33"/>
-      <c r="AM56" s="54"/>
-      <c r="AN56" s="56"/>
+      <c r="AM56" s="58"/>
+      <c r="AN56" s="60"/>
     </row>
     <row r="57" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="82"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="85"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="55"/>
+      <c r="D57" s="57"/>
       <c r="E57" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G57" s="43"/>
       <c r="H57" s="32"/>
@@ -3891,20 +3891,20 @@
       <c r="AJ57" s="32"/>
       <c r="AK57" s="45"/>
       <c r="AL57" s="34"/>
-      <c r="AM57" s="55"/>
-      <c r="AN57" s="57"/>
+      <c r="AM57" s="59"/>
+      <c r="AN57" s="61"/>
     </row>
     <row r="58" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="75">
+      <c r="B58" s="62">
         <v>26</v>
       </c>
-      <c r="C58" s="52"/>
-      <c r="D58" s="84"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="56"/>
       <c r="E58" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G58" s="40"/>
       <c r="H58" s="31"/>
@@ -3938,18 +3938,18 @@
       <c r="AJ58" s="31"/>
       <c r="AK58" s="36"/>
       <c r="AL58" s="33"/>
-      <c r="AM58" s="54"/>
-      <c r="AN58" s="56"/>
+      <c r="AM58" s="58"/>
+      <c r="AN58" s="60"/>
     </row>
     <row r="59" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="86"/>
-      <c r="C59" s="83"/>
-      <c r="D59" s="85"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="55"/>
+      <c r="D59" s="57"/>
       <c r="E59" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G59" s="43"/>
       <c r="H59" s="32"/>
@@ -3983,20 +3983,20 @@
       <c r="AJ59" s="32"/>
       <c r="AK59" s="45"/>
       <c r="AL59" s="34"/>
-      <c r="AM59" s="55"/>
-      <c r="AN59" s="57"/>
+      <c r="AM59" s="59"/>
+      <c r="AN59" s="61"/>
     </row>
     <row r="60" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="81">
+      <c r="B60" s="52">
         <v>27</v>
       </c>
-      <c r="C60" s="52"/>
-      <c r="D60" s="84"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="56"/>
       <c r="E60" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G60" s="40"/>
       <c r="H60" s="31"/>
@@ -4030,18 +4030,18 @@
       <c r="AJ60" s="31"/>
       <c r="AK60" s="36"/>
       <c r="AL60" s="33"/>
-      <c r="AM60" s="54"/>
-      <c r="AN60" s="56"/>
+      <c r="AM60" s="58"/>
+      <c r="AN60" s="60"/>
     </row>
     <row r="61" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="82"/>
-      <c r="C61" s="83"/>
-      <c r="D61" s="85"/>
+      <c r="B61" s="53"/>
+      <c r="C61" s="55"/>
+      <c r="D61" s="57"/>
       <c r="E61" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G61" s="43"/>
       <c r="H61" s="32"/>
@@ -4075,20 +4075,20 @@
       <c r="AJ61" s="32"/>
       <c r="AK61" s="45"/>
       <c r="AL61" s="34"/>
-      <c r="AM61" s="55"/>
-      <c r="AN61" s="57"/>
+      <c r="AM61" s="59"/>
+      <c r="AN61" s="61"/>
     </row>
     <row r="62" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="75">
+      <c r="B62" s="62">
         <v>28</v>
       </c>
-      <c r="C62" s="52"/>
-      <c r="D62" s="84"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="56"/>
       <c r="E62" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G62" s="40"/>
       <c r="H62" s="31"/>
@@ -4122,18 +4122,18 @@
       <c r="AJ62" s="31"/>
       <c r="AK62" s="36"/>
       <c r="AL62" s="33"/>
-      <c r="AM62" s="54"/>
-      <c r="AN62" s="56"/>
+      <c r="AM62" s="58"/>
+      <c r="AN62" s="60"/>
     </row>
     <row r="63" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="86"/>
-      <c r="C63" s="83"/>
-      <c r="D63" s="85"/>
+      <c r="B63" s="63"/>
+      <c r="C63" s="55"/>
+      <c r="D63" s="57"/>
       <c r="E63" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G63" s="43"/>
       <c r="H63" s="32"/>
@@ -4167,20 +4167,20 @@
       <c r="AJ63" s="32"/>
       <c r="AK63" s="45"/>
       <c r="AL63" s="34"/>
-      <c r="AM63" s="55"/>
-      <c r="AN63" s="57"/>
+      <c r="AM63" s="59"/>
+      <c r="AN63" s="61"/>
     </row>
     <row r="64" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="81">
+      <c r="B64" s="52">
         <v>29</v>
       </c>
-      <c r="C64" s="52"/>
-      <c r="D64" s="84"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="56"/>
       <c r="E64" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G64" s="40"/>
       <c r="H64" s="31"/>
@@ -4214,18 +4214,18 @@
       <c r="AJ64" s="31"/>
       <c r="AK64" s="36"/>
       <c r="AL64" s="33"/>
-      <c r="AM64" s="54"/>
-      <c r="AN64" s="56"/>
+      <c r="AM64" s="58"/>
+      <c r="AN64" s="60"/>
     </row>
     <row r="65" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="82"/>
-      <c r="C65" s="83"/>
-      <c r="D65" s="85"/>
+      <c r="B65" s="53"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="57"/>
       <c r="E65" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G65" s="43"/>
       <c r="H65" s="32"/>
@@ -4259,20 +4259,20 @@
       <c r="AJ65" s="32"/>
       <c r="AK65" s="45"/>
       <c r="AL65" s="34"/>
-      <c r="AM65" s="55"/>
-      <c r="AN65" s="57"/>
+      <c r="AM65" s="59"/>
+      <c r="AN65" s="61"/>
     </row>
     <row r="66" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="75">
+      <c r="B66" s="62">
         <v>30</v>
       </c>
-      <c r="C66" s="52"/>
-      <c r="D66" s="84"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="56"/>
       <c r="E66" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G66" s="40"/>
       <c r="H66" s="31"/>
@@ -4306,18 +4306,18 @@
       <c r="AJ66" s="31"/>
       <c r="AK66" s="36"/>
       <c r="AL66" s="33"/>
-      <c r="AM66" s="54"/>
-      <c r="AN66" s="56"/>
+      <c r="AM66" s="58"/>
+      <c r="AN66" s="60"/>
     </row>
     <row r="67" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="86"/>
-      <c r="C67" s="83"/>
-      <c r="D67" s="85"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="55"/>
+      <c r="D67" s="57"/>
       <c r="E67" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G67" s="43"/>
       <c r="H67" s="32"/>
@@ -4351,20 +4351,20 @@
       <c r="AJ67" s="32"/>
       <c r="AK67" s="45"/>
       <c r="AL67" s="34"/>
-      <c r="AM67" s="55"/>
-      <c r="AN67" s="57"/>
+      <c r="AM67" s="59"/>
+      <c r="AN67" s="61"/>
     </row>
     <row r="68" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="81">
+      <c r="B68" s="52">
         <v>31</v>
       </c>
-      <c r="C68" s="52"/>
-      <c r="D68" s="84"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="56"/>
       <c r="E68" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G68" s="40"/>
       <c r="H68" s="31"/>
@@ -4398,18 +4398,18 @@
       <c r="AJ68" s="31"/>
       <c r="AK68" s="36"/>
       <c r="AL68" s="33"/>
-      <c r="AM68" s="54"/>
-      <c r="AN68" s="56"/>
+      <c r="AM68" s="58"/>
+      <c r="AN68" s="60"/>
     </row>
     <row r="69" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="82"/>
-      <c r="C69" s="83"/>
-      <c r="D69" s="85"/>
+      <c r="B69" s="53"/>
+      <c r="C69" s="55"/>
+      <c r="D69" s="57"/>
       <c r="E69" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G69" s="43"/>
       <c r="H69" s="32"/>
@@ -4443,20 +4443,20 @@
       <c r="AJ69" s="32"/>
       <c r="AK69" s="45"/>
       <c r="AL69" s="34"/>
-      <c r="AM69" s="55"/>
-      <c r="AN69" s="57"/>
+      <c r="AM69" s="59"/>
+      <c r="AN69" s="61"/>
     </row>
     <row r="70" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="75">
+      <c r="B70" s="62">
         <v>32</v>
       </c>
-      <c r="C70" s="52"/>
-      <c r="D70" s="84"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="56"/>
       <c r="E70" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G70" s="40"/>
       <c r="H70" s="31"/>
@@ -4490,18 +4490,18 @@
       <c r="AJ70" s="31"/>
       <c r="AK70" s="36"/>
       <c r="AL70" s="33"/>
-      <c r="AM70" s="54"/>
-      <c r="AN70" s="56"/>
+      <c r="AM70" s="58"/>
+      <c r="AN70" s="60"/>
     </row>
     <row r="71" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="86"/>
-      <c r="C71" s="83"/>
-      <c r="D71" s="85"/>
+      <c r="B71" s="63"/>
+      <c r="C71" s="55"/>
+      <c r="D71" s="57"/>
       <c r="E71" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G71" s="43"/>
       <c r="H71" s="32"/>
@@ -4535,20 +4535,20 @@
       <c r="AJ71" s="32"/>
       <c r="AK71" s="45"/>
       <c r="AL71" s="34"/>
-      <c r="AM71" s="55"/>
-      <c r="AN71" s="57"/>
+      <c r="AM71" s="59"/>
+      <c r="AN71" s="61"/>
     </row>
     <row r="72" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="81">
+      <c r="B72" s="52">
         <v>33</v>
       </c>
-      <c r="C72" s="52"/>
-      <c r="D72" s="84"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="56"/>
       <c r="E72" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G72" s="40"/>
       <c r="H72" s="31"/>
@@ -4582,18 +4582,18 @@
       <c r="AJ72" s="31"/>
       <c r="AK72" s="36"/>
       <c r="AL72" s="33"/>
-      <c r="AM72" s="54"/>
-      <c r="AN72" s="56"/>
+      <c r="AM72" s="58"/>
+      <c r="AN72" s="60"/>
     </row>
     <row r="73" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="82"/>
-      <c r="C73" s="83"/>
-      <c r="D73" s="85"/>
+      <c r="B73" s="53"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="57"/>
       <c r="E73" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G73" s="43"/>
       <c r="H73" s="32"/>
@@ -4627,20 +4627,20 @@
       <c r="AJ73" s="32"/>
       <c r="AK73" s="45"/>
       <c r="AL73" s="34"/>
-      <c r="AM73" s="55"/>
-      <c r="AN73" s="57"/>
+      <c r="AM73" s="59"/>
+      <c r="AN73" s="61"/>
     </row>
     <row r="74" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="75">
+      <c r="B74" s="62">
         <v>34</v>
       </c>
-      <c r="C74" s="52"/>
-      <c r="D74" s="87"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="64"/>
       <c r="E74" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G74" s="40"/>
       <c r="H74" s="31"/>
@@ -4674,18 +4674,18 @@
       <c r="AJ74" s="31"/>
       <c r="AK74" s="36"/>
       <c r="AL74" s="33"/>
-      <c r="AM74" s="54"/>
-      <c r="AN74" s="56"/>
+      <c r="AM74" s="58"/>
+      <c r="AN74" s="60"/>
     </row>
     <row r="75" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="86"/>
-      <c r="C75" s="83"/>
-      <c r="D75" s="88"/>
+      <c r="B75" s="63"/>
+      <c r="C75" s="55"/>
+      <c r="D75" s="65"/>
       <c r="E75" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G75" s="43"/>
       <c r="H75" s="32"/>
@@ -4719,20 +4719,20 @@
       <c r="AJ75" s="32"/>
       <c r="AK75" s="45"/>
       <c r="AL75" s="34"/>
-      <c r="AM75" s="55"/>
-      <c r="AN75" s="57"/>
+      <c r="AM75" s="59"/>
+      <c r="AN75" s="61"/>
     </row>
     <row r="76" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="81">
+      <c r="B76" s="52">
         <v>35</v>
       </c>
-      <c r="C76" s="52"/>
-      <c r="D76" s="87"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="64"/>
       <c r="E76" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G76" s="40"/>
       <c r="H76" s="31"/>
@@ -4766,18 +4766,18 @@
       <c r="AJ76" s="31"/>
       <c r="AK76" s="36"/>
       <c r="AL76" s="33"/>
-      <c r="AM76" s="54"/>
-      <c r="AN76" s="56"/>
+      <c r="AM76" s="58"/>
+      <c r="AN76" s="60"/>
     </row>
     <row r="77" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="82"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="88"/>
+      <c r="B77" s="53"/>
+      <c r="C77" s="55"/>
+      <c r="D77" s="65"/>
       <c r="E77" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G77" s="43"/>
       <c r="H77" s="32"/>
@@ -4811,20 +4811,20 @@
       <c r="AJ77" s="32"/>
       <c r="AK77" s="45"/>
       <c r="AL77" s="34"/>
-      <c r="AM77" s="55"/>
-      <c r="AN77" s="57"/>
+      <c r="AM77" s="59"/>
+      <c r="AN77" s="61"/>
     </row>
     <row r="78" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="75">
+      <c r="B78" s="62">
         <v>36</v>
       </c>
-      <c r="C78" s="62"/>
-      <c r="D78" s="91"/>
+      <c r="C78" s="66"/>
+      <c r="D78" s="68"/>
       <c r="E78" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G78" s="40"/>
       <c r="H78" s="31"/>
@@ -4858,18 +4858,18 @@
       <c r="AJ78" s="31"/>
       <c r="AK78" s="36"/>
       <c r="AL78" s="33"/>
-      <c r="AM78" s="54"/>
-      <c r="AN78" s="56"/>
+      <c r="AM78" s="58"/>
+      <c r="AN78" s="60"/>
     </row>
     <row r="79" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="86"/>
-      <c r="C79" s="90"/>
-      <c r="D79" s="92"/>
+      <c r="B79" s="63"/>
+      <c r="C79" s="67"/>
+      <c r="D79" s="69"/>
       <c r="E79" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G79" s="43"/>
       <c r="H79" s="32"/>
@@ -4903,20 +4903,20 @@
       <c r="AJ79" s="32"/>
       <c r="AK79" s="45"/>
       <c r="AL79" s="34"/>
-      <c r="AM79" s="55"/>
-      <c r="AN79" s="57"/>
+      <c r="AM79" s="59"/>
+      <c r="AN79" s="61"/>
     </row>
     <row r="80" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="81">
+      <c r="B80" s="52">
         <v>37</v>
       </c>
-      <c r="C80" s="52"/>
-      <c r="D80" s="87"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="64"/>
       <c r="E80" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G80" s="40"/>
       <c r="H80" s="31"/>
@@ -4950,18 +4950,18 @@
       <c r="AJ80" s="31"/>
       <c r="AK80" s="36"/>
       <c r="AL80" s="33"/>
-      <c r="AM80" s="54"/>
-      <c r="AN80" s="56"/>
+      <c r="AM80" s="58"/>
+      <c r="AN80" s="60"/>
     </row>
     <row r="81" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="82"/>
-      <c r="C81" s="83"/>
-      <c r="D81" s="88"/>
+      <c r="B81" s="53"/>
+      <c r="C81" s="55"/>
+      <c r="D81" s="65"/>
       <c r="E81" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G81" s="43"/>
       <c r="H81" s="32"/>
@@ -4995,20 +4995,20 @@
       <c r="AJ81" s="32"/>
       <c r="AK81" s="45"/>
       <c r="AL81" s="34"/>
-      <c r="AM81" s="55"/>
-      <c r="AN81" s="57"/>
+      <c r="AM81" s="59"/>
+      <c r="AN81" s="61"/>
     </row>
     <row r="82" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="75">
+      <c r="B82" s="62">
         <v>38</v>
       </c>
-      <c r="C82" s="52"/>
-      <c r="D82" s="87"/>
+      <c r="C82" s="54"/>
+      <c r="D82" s="64"/>
       <c r="E82" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G82" s="40"/>
       <c r="H82" s="31"/>
@@ -5042,18 +5042,18 @@
       <c r="AJ82" s="31"/>
       <c r="AK82" s="36"/>
       <c r="AL82" s="33"/>
-      <c r="AM82" s="54"/>
-      <c r="AN82" s="56"/>
+      <c r="AM82" s="58"/>
+      <c r="AN82" s="60"/>
     </row>
     <row r="83" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="86"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="88"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="55"/>
+      <c r="D83" s="65"/>
       <c r="E83" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G83" s="43"/>
       <c r="H83" s="32"/>
@@ -5087,20 +5087,20 @@
       <c r="AJ83" s="32"/>
       <c r="AK83" s="45"/>
       <c r="AL83" s="34"/>
-      <c r="AM83" s="55"/>
-      <c r="AN83" s="57"/>
+      <c r="AM83" s="59"/>
+      <c r="AN83" s="61"/>
     </row>
     <row r="84" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="81">
+      <c r="B84" s="52">
         <v>39</v>
       </c>
-      <c r="C84" s="52"/>
-      <c r="D84" s="87"/>
+      <c r="C84" s="54"/>
+      <c r="D84" s="64"/>
       <c r="E84" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G84" s="40"/>
       <c r="H84" s="31"/>
@@ -5134,18 +5134,18 @@
       <c r="AJ84" s="31"/>
       <c r="AK84" s="36"/>
       <c r="AL84" s="33"/>
-      <c r="AM84" s="54"/>
-      <c r="AN84" s="56"/>
+      <c r="AM84" s="58"/>
+      <c r="AN84" s="60"/>
     </row>
     <row r="85" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="82"/>
-      <c r="C85" s="83"/>
-      <c r="D85" s="88"/>
+      <c r="B85" s="53"/>
+      <c r="C85" s="55"/>
+      <c r="D85" s="65"/>
       <c r="E85" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G85" s="43"/>
       <c r="H85" s="32"/>
@@ -5179,20 +5179,20 @@
       <c r="AJ85" s="32"/>
       <c r="AK85" s="45"/>
       <c r="AL85" s="34"/>
-      <c r="AM85" s="55"/>
-      <c r="AN85" s="57"/>
+      <c r="AM85" s="59"/>
+      <c r="AN85" s="61"/>
     </row>
     <row r="86" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="75">
+      <c r="B86" s="62">
         <v>40</v>
       </c>
-      <c r="C86" s="52"/>
-      <c r="D86" s="87"/>
+      <c r="C86" s="54"/>
+      <c r="D86" s="64"/>
       <c r="E86" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G86" s="40"/>
       <c r="H86" s="31"/>
@@ -5226,18 +5226,18 @@
       <c r="AJ86" s="31"/>
       <c r="AK86" s="36"/>
       <c r="AL86" s="33"/>
-      <c r="AM86" s="54"/>
-      <c r="AN86" s="56"/>
+      <c r="AM86" s="58"/>
+      <c r="AN86" s="60"/>
     </row>
     <row r="87" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="86"/>
-      <c r="C87" s="83"/>
-      <c r="D87" s="88"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="55"/>
+      <c r="D87" s="65"/>
       <c r="E87" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G87" s="43"/>
       <c r="H87" s="32"/>
@@ -5271,20 +5271,20 @@
       <c r="AJ87" s="32"/>
       <c r="AK87" s="45"/>
       <c r="AL87" s="34"/>
-      <c r="AM87" s="55"/>
-      <c r="AN87" s="57"/>
+      <c r="AM87" s="59"/>
+      <c r="AN87" s="61"/>
     </row>
     <row r="88" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="81">
+      <c r="B88" s="52">
         <v>41</v>
       </c>
-      <c r="C88" s="52"/>
-      <c r="D88" s="84"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="56"/>
       <c r="E88" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G88" s="40"/>
       <c r="H88" s="31"/>
@@ -5318,18 +5318,18 @@
       <c r="AJ88" s="31"/>
       <c r="AK88" s="36"/>
       <c r="AL88" s="33"/>
-      <c r="AM88" s="54"/>
-      <c r="AN88" s="56"/>
+      <c r="AM88" s="58"/>
+      <c r="AN88" s="60"/>
     </row>
     <row r="89" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="82"/>
-      <c r="C89" s="83"/>
-      <c r="D89" s="85"/>
+      <c r="B89" s="53"/>
+      <c r="C89" s="55"/>
+      <c r="D89" s="57"/>
       <c r="E89" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G89" s="43"/>
       <c r="H89" s="32"/>
@@ -5363,20 +5363,20 @@
       <c r="AJ89" s="32"/>
       <c r="AK89" s="45"/>
       <c r="AL89" s="34"/>
-      <c r="AM89" s="55"/>
-      <c r="AN89" s="57"/>
+      <c r="AM89" s="59"/>
+      <c r="AN89" s="61"/>
     </row>
     <row r="90" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="75">
+      <c r="B90" s="62">
         <v>42</v>
       </c>
-      <c r="C90" s="52"/>
-      <c r="D90" s="84"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="56"/>
       <c r="E90" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G90" s="40"/>
       <c r="H90" s="31"/>
@@ -5410,18 +5410,18 @@
       <c r="AJ90" s="31"/>
       <c r="AK90" s="36"/>
       <c r="AL90" s="33"/>
-      <c r="AM90" s="54"/>
-      <c r="AN90" s="56"/>
+      <c r="AM90" s="58"/>
+      <c r="AN90" s="60"/>
     </row>
     <row r="91" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="86"/>
-      <c r="C91" s="83"/>
-      <c r="D91" s="85"/>
+      <c r="B91" s="63"/>
+      <c r="C91" s="55"/>
+      <c r="D91" s="57"/>
       <c r="E91" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G91" s="43"/>
       <c r="H91" s="32"/>
@@ -5455,20 +5455,20 @@
       <c r="AJ91" s="32"/>
       <c r="AK91" s="45"/>
       <c r="AL91" s="34"/>
-      <c r="AM91" s="55"/>
-      <c r="AN91" s="57"/>
+      <c r="AM91" s="59"/>
+      <c r="AN91" s="61"/>
     </row>
     <row r="92" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="81">
+      <c r="B92" s="52">
         <v>43</v>
       </c>
-      <c r="C92" s="52"/>
-      <c r="D92" s="84"/>
+      <c r="C92" s="54"/>
+      <c r="D92" s="56"/>
       <c r="E92" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G92" s="40"/>
       <c r="H92" s="31"/>
@@ -5502,18 +5502,18 @@
       <c r="AJ92" s="31"/>
       <c r="AK92" s="36"/>
       <c r="AL92" s="33"/>
-      <c r="AM92" s="54"/>
-      <c r="AN92" s="56"/>
+      <c r="AM92" s="58"/>
+      <c r="AN92" s="60"/>
     </row>
     <row r="93" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="82"/>
-      <c r="C93" s="83"/>
-      <c r="D93" s="85"/>
+      <c r="B93" s="53"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="57"/>
       <c r="E93" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G93" s="43"/>
       <c r="H93" s="32"/>
@@ -5547,20 +5547,20 @@
       <c r="AJ93" s="32"/>
       <c r="AK93" s="45"/>
       <c r="AL93" s="34"/>
-      <c r="AM93" s="55"/>
-      <c r="AN93" s="57"/>
+      <c r="AM93" s="59"/>
+      <c r="AN93" s="61"/>
     </row>
     <row r="94" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="75">
+      <c r="B94" s="62">
         <v>44</v>
       </c>
-      <c r="C94" s="52"/>
-      <c r="D94" s="84"/>
+      <c r="C94" s="54"/>
+      <c r="D94" s="56"/>
       <c r="E94" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G94" s="40"/>
       <c r="H94" s="31"/>
@@ -5594,18 +5594,18 @@
       <c r="AJ94" s="31"/>
       <c r="AK94" s="36"/>
       <c r="AL94" s="33"/>
-      <c r="AM94" s="54"/>
-      <c r="AN94" s="56"/>
+      <c r="AM94" s="58"/>
+      <c r="AN94" s="60"/>
     </row>
     <row r="95" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="86"/>
-      <c r="C95" s="83"/>
-      <c r="D95" s="85"/>
+      <c r="B95" s="63"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="57"/>
       <c r="E95" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G95" s="43"/>
       <c r="H95" s="32"/>
@@ -5639,20 +5639,20 @@
       <c r="AJ95" s="32"/>
       <c r="AK95" s="45"/>
       <c r="AL95" s="34"/>
-      <c r="AM95" s="55"/>
-      <c r="AN95" s="57"/>
+      <c r="AM95" s="59"/>
+      <c r="AN95" s="61"/>
     </row>
     <row r="96" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="81">
+      <c r="B96" s="52">
         <v>45</v>
       </c>
-      <c r="C96" s="52"/>
-      <c r="D96" s="84"/>
+      <c r="C96" s="54"/>
+      <c r="D96" s="56"/>
       <c r="E96" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G96" s="40"/>
       <c r="H96" s="31"/>
@@ -5686,18 +5686,18 @@
       <c r="AJ96" s="31"/>
       <c r="AK96" s="36"/>
       <c r="AL96" s="33"/>
-      <c r="AM96" s="54"/>
-      <c r="AN96" s="56"/>
+      <c r="AM96" s="58"/>
+      <c r="AN96" s="60"/>
     </row>
     <row r="97" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="82"/>
-      <c r="C97" s="83"/>
-      <c r="D97" s="85"/>
+      <c r="B97" s="53"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G97" s="43"/>
       <c r="H97" s="32"/>
@@ -5731,20 +5731,20 @@
       <c r="AJ97" s="32"/>
       <c r="AK97" s="45"/>
       <c r="AL97" s="34"/>
-      <c r="AM97" s="55"/>
-      <c r="AN97" s="57"/>
+      <c r="AM97" s="59"/>
+      <c r="AN97" s="61"/>
     </row>
     <row r="98" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="75">
+      <c r="B98" s="62">
         <v>46</v>
       </c>
-      <c r="C98" s="52"/>
-      <c r="D98" s="84"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="56"/>
       <c r="E98" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G98" s="40"/>
       <c r="H98" s="31"/>
@@ -5778,18 +5778,18 @@
       <c r="AJ98" s="31"/>
       <c r="AK98" s="36"/>
       <c r="AL98" s="33"/>
-      <c r="AM98" s="54"/>
-      <c r="AN98" s="56"/>
+      <c r="AM98" s="58"/>
+      <c r="AN98" s="60"/>
     </row>
     <row r="99" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="86"/>
-      <c r="C99" s="83"/>
-      <c r="D99" s="85"/>
+      <c r="B99" s="63"/>
+      <c r="C99" s="55"/>
+      <c r="D99" s="57"/>
       <c r="E99" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G99" s="43"/>
       <c r="H99" s="32"/>
@@ -5823,20 +5823,20 @@
       <c r="AJ99" s="32"/>
       <c r="AK99" s="45"/>
       <c r="AL99" s="34"/>
-      <c r="AM99" s="55"/>
-      <c r="AN99" s="57"/>
+      <c r="AM99" s="59"/>
+      <c r="AN99" s="61"/>
     </row>
     <row r="100" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="81">
+      <c r="B100" s="52">
         <v>47</v>
       </c>
-      <c r="C100" s="52"/>
-      <c r="D100" s="84"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
       <c r="E100" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G100" s="40"/>
       <c r="H100" s="31"/>
@@ -5870,18 +5870,18 @@
       <c r="AJ100" s="31"/>
       <c r="AK100" s="36"/>
       <c r="AL100" s="33"/>
-      <c r="AM100" s="54"/>
-      <c r="AN100" s="56"/>
+      <c r="AM100" s="58"/>
+      <c r="AN100" s="60"/>
     </row>
     <row r="101" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="82"/>
-      <c r="C101" s="83"/>
-      <c r="D101" s="85"/>
+      <c r="B101" s="53"/>
+      <c r="C101" s="55"/>
+      <c r="D101" s="57"/>
       <c r="E101" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G101" s="43"/>
       <c r="H101" s="32"/>
@@ -5915,20 +5915,20 @@
       <c r="AJ101" s="32"/>
       <c r="AK101" s="45"/>
       <c r="AL101" s="34"/>
-      <c r="AM101" s="55"/>
-      <c r="AN101" s="57"/>
+      <c r="AM101" s="59"/>
+      <c r="AN101" s="61"/>
     </row>
     <row r="102" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="75">
+      <c r="B102" s="62">
         <v>48</v>
       </c>
-      <c r="C102" s="52"/>
-      <c r="D102" s="84"/>
+      <c r="C102" s="54"/>
+      <c r="D102" s="56"/>
       <c r="E102" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G102" s="40"/>
       <c r="H102" s="31"/>
@@ -5962,18 +5962,18 @@
       <c r="AJ102" s="31"/>
       <c r="AK102" s="36"/>
       <c r="AL102" s="33"/>
-      <c r="AM102" s="54"/>
-      <c r="AN102" s="56"/>
+      <c r="AM102" s="58"/>
+      <c r="AN102" s="60"/>
     </row>
     <row r="103" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="86"/>
-      <c r="C103" s="83"/>
-      <c r="D103" s="85"/>
+      <c r="B103" s="63"/>
+      <c r="C103" s="55"/>
+      <c r="D103" s="57"/>
       <c r="E103" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G103" s="43"/>
       <c r="H103" s="32"/>
@@ -6007,20 +6007,20 @@
       <c r="AJ103" s="32"/>
       <c r="AK103" s="45"/>
       <c r="AL103" s="34"/>
-      <c r="AM103" s="55"/>
-      <c r="AN103" s="57"/>
+      <c r="AM103" s="59"/>
+      <c r="AN103" s="61"/>
     </row>
     <row r="104" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="81">
+      <c r="B104" s="52">
         <v>49</v>
       </c>
-      <c r="C104" s="52"/>
-      <c r="D104" s="84"/>
+      <c r="C104" s="54"/>
+      <c r="D104" s="56"/>
       <c r="E104" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G104" s="40"/>
       <c r="H104" s="31"/>
@@ -6054,18 +6054,18 @@
       <c r="AJ104" s="31"/>
       <c r="AK104" s="36"/>
       <c r="AL104" s="33"/>
-      <c r="AM104" s="54"/>
-      <c r="AN104" s="56"/>
+      <c r="AM104" s="58"/>
+      <c r="AN104" s="60"/>
     </row>
     <row r="105" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="82"/>
-      <c r="C105" s="83"/>
-      <c r="D105" s="85"/>
+      <c r="B105" s="53"/>
+      <c r="C105" s="55"/>
+      <c r="D105" s="57"/>
       <c r="E105" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G105" s="43"/>
       <c r="H105" s="32"/>
@@ -6099,20 +6099,20 @@
       <c r="AJ105" s="32"/>
       <c r="AK105" s="45"/>
       <c r="AL105" s="34"/>
-      <c r="AM105" s="55"/>
-      <c r="AN105" s="57"/>
+      <c r="AM105" s="59"/>
+      <c r="AN105" s="61"/>
     </row>
     <row r="106" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="75">
+      <c r="B106" s="62">
         <v>50</v>
       </c>
-      <c r="C106" s="52"/>
-      <c r="D106" s="84"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="56"/>
       <c r="E106" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G106" s="40"/>
       <c r="H106" s="31"/>
@@ -6146,18 +6146,18 @@
       <c r="AJ106" s="31"/>
       <c r="AK106" s="36"/>
       <c r="AL106" s="33"/>
-      <c r="AM106" s="54"/>
-      <c r="AN106" s="56"/>
+      <c r="AM106" s="58"/>
+      <c r="AN106" s="60"/>
     </row>
     <row r="107" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="86"/>
-      <c r="C107" s="83"/>
-      <c r="D107" s="85"/>
+      <c r="B107" s="63"/>
+      <c r="C107" s="55"/>
+      <c r="D107" s="57"/>
       <c r="E107" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G107" s="43"/>
       <c r="H107" s="32"/>
@@ -6191,20 +6191,20 @@
       <c r="AJ107" s="32"/>
       <c r="AK107" s="45"/>
       <c r="AL107" s="34"/>
-      <c r="AM107" s="55"/>
-      <c r="AN107" s="57"/>
+      <c r="AM107" s="59"/>
+      <c r="AN107" s="61"/>
     </row>
     <row r="108" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="81">
+      <c r="B108" s="52">
         <v>51</v>
       </c>
-      <c r="C108" s="52"/>
-      <c r="D108" s="84"/>
+      <c r="C108" s="54"/>
+      <c r="D108" s="56"/>
       <c r="E108" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G108" s="40"/>
       <c r="H108" s="31"/>
@@ -6238,18 +6238,18 @@
       <c r="AJ108" s="31"/>
       <c r="AK108" s="36"/>
       <c r="AL108" s="33"/>
-      <c r="AM108" s="54"/>
-      <c r="AN108" s="56"/>
+      <c r="AM108" s="58"/>
+      <c r="AN108" s="60"/>
     </row>
     <row r="109" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="82"/>
-      <c r="C109" s="83"/>
-      <c r="D109" s="85"/>
+      <c r="B109" s="53"/>
+      <c r="C109" s="55"/>
+      <c r="D109" s="57"/>
       <c r="E109" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G109" s="43"/>
       <c r="H109" s="32"/>
@@ -6283,20 +6283,20 @@
       <c r="AJ109" s="32"/>
       <c r="AK109" s="45"/>
       <c r="AL109" s="34"/>
-      <c r="AM109" s="55"/>
-      <c r="AN109" s="57"/>
+      <c r="AM109" s="59"/>
+      <c r="AN109" s="61"/>
     </row>
     <row r="110" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B110" s="75">
+      <c r="B110" s="62">
         <v>52</v>
       </c>
-      <c r="C110" s="52"/>
-      <c r="D110" s="84"/>
+      <c r="C110" s="54"/>
+      <c r="D110" s="56"/>
       <c r="E110" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G110" s="40"/>
       <c r="H110" s="31"/>
@@ -6330,18 +6330,18 @@
       <c r="AJ110" s="31"/>
       <c r="AK110" s="36"/>
       <c r="AL110" s="33"/>
-      <c r="AM110" s="54"/>
-      <c r="AN110" s="56"/>
+      <c r="AM110" s="58"/>
+      <c r="AN110" s="60"/>
     </row>
     <row r="111" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="86"/>
-      <c r="C111" s="83"/>
-      <c r="D111" s="85"/>
+      <c r="B111" s="63"/>
+      <c r="C111" s="55"/>
+      <c r="D111" s="57"/>
       <c r="E111" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G111" s="43"/>
       <c r="H111" s="32"/>
@@ -6375,20 +6375,20 @@
       <c r="AJ111" s="32"/>
       <c r="AK111" s="45"/>
       <c r="AL111" s="34"/>
-      <c r="AM111" s="55"/>
-      <c r="AN111" s="57"/>
+      <c r="AM111" s="59"/>
+      <c r="AN111" s="61"/>
     </row>
     <row r="112" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="81">
+      <c r="B112" s="52">
         <v>53</v>
       </c>
-      <c r="C112" s="52"/>
-      <c r="D112" s="84"/>
+      <c r="C112" s="54"/>
+      <c r="D112" s="56"/>
       <c r="E112" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G112" s="40"/>
       <c r="H112" s="31"/>
@@ -6422,18 +6422,18 @@
       <c r="AJ112" s="31"/>
       <c r="AK112" s="36"/>
       <c r="AL112" s="33"/>
-      <c r="AM112" s="54"/>
-      <c r="AN112" s="56"/>
+      <c r="AM112" s="58"/>
+      <c r="AN112" s="60"/>
     </row>
     <row r="113" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="82"/>
-      <c r="C113" s="83"/>
-      <c r="D113" s="85"/>
+      <c r="B113" s="53"/>
+      <c r="C113" s="55"/>
+      <c r="D113" s="57"/>
       <c r="E113" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G113" s="43"/>
       <c r="H113" s="32"/>
@@ -6467,20 +6467,20 @@
       <c r="AJ113" s="32"/>
       <c r="AK113" s="45"/>
       <c r="AL113" s="34"/>
-      <c r="AM113" s="55"/>
-      <c r="AN113" s="57"/>
+      <c r="AM113" s="59"/>
+      <c r="AN113" s="61"/>
     </row>
     <row r="114" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="75">
+      <c r="B114" s="62">
         <v>54</v>
       </c>
-      <c r="C114" s="62"/>
-      <c r="D114" s="77"/>
+      <c r="C114" s="66"/>
+      <c r="D114" s="75"/>
       <c r="E114" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G114" s="40"/>
       <c r="H114" s="31"/>
@@ -6514,18 +6514,18 @@
       <c r="AJ114" s="31"/>
       <c r="AK114" s="36"/>
       <c r="AL114" s="33"/>
-      <c r="AM114" s="54"/>
-      <c r="AN114" s="56"/>
+      <c r="AM114" s="58"/>
+      <c r="AN114" s="60"/>
     </row>
     <row r="115" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="86"/>
-      <c r="C115" s="72"/>
-      <c r="D115" s="78"/>
+      <c r="B115" s="63"/>
+      <c r="C115" s="74"/>
+      <c r="D115" s="76"/>
       <c r="E115" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G115" s="41"/>
       <c r="H115" s="35"/>
@@ -6559,20 +6559,20 @@
       <c r="AJ115" s="35"/>
       <c r="AK115" s="37"/>
       <c r="AL115" s="34"/>
-      <c r="AM115" s="79"/>
-      <c r="AN115" s="71"/>
+      <c r="AM115" s="72"/>
+      <c r="AN115" s="73"/>
     </row>
     <row r="116" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B116" s="81">
+      <c r="B116" s="52">
         <v>55</v>
       </c>
-      <c r="C116" s="52"/>
-      <c r="D116" s="84"/>
+      <c r="C116" s="54"/>
+      <c r="D116" s="56"/>
       <c r="E116" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G116" s="40"/>
       <c r="H116" s="31"/>
@@ -6606,18 +6606,18 @@
       <c r="AJ116" s="31"/>
       <c r="AK116" s="36"/>
       <c r="AL116" s="33"/>
-      <c r="AM116" s="54"/>
-      <c r="AN116" s="56"/>
+      <c r="AM116" s="58"/>
+      <c r="AN116" s="60"/>
     </row>
     <row r="117" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="82"/>
-      <c r="C117" s="83"/>
-      <c r="D117" s="85"/>
+      <c r="B117" s="53"/>
+      <c r="C117" s="55"/>
+      <c r="D117" s="57"/>
       <c r="E117" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G117" s="43"/>
       <c r="H117" s="32"/>
@@ -6651,20 +6651,20 @@
       <c r="AJ117" s="32"/>
       <c r="AK117" s="45"/>
       <c r="AL117" s="34"/>
-      <c r="AM117" s="55"/>
-      <c r="AN117" s="57"/>
+      <c r="AM117" s="59"/>
+      <c r="AN117" s="61"/>
     </row>
     <row r="118" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="75">
+      <c r="B118" s="62">
         <v>56</v>
       </c>
-      <c r="C118" s="52"/>
-      <c r="D118" s="84"/>
+      <c r="C118" s="54"/>
+      <c r="D118" s="56"/>
       <c r="E118" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G118" s="40"/>
       <c r="H118" s="31"/>
@@ -6698,18 +6698,18 @@
       <c r="AJ118" s="31"/>
       <c r="AK118" s="36"/>
       <c r="AL118" s="33"/>
-      <c r="AM118" s="54"/>
-      <c r="AN118" s="56"/>
+      <c r="AM118" s="58"/>
+      <c r="AN118" s="60"/>
     </row>
     <row r="119" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="86"/>
-      <c r="C119" s="83"/>
-      <c r="D119" s="85"/>
+      <c r="B119" s="63"/>
+      <c r="C119" s="55"/>
+      <c r="D119" s="57"/>
       <c r="E119" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G119" s="43"/>
       <c r="H119" s="32"/>
@@ -6743,20 +6743,20 @@
       <c r="AJ119" s="32"/>
       <c r="AK119" s="45"/>
       <c r="AL119" s="34"/>
-      <c r="AM119" s="55"/>
-      <c r="AN119" s="57"/>
+      <c r="AM119" s="59"/>
+      <c r="AN119" s="61"/>
     </row>
     <row r="120" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="81">
+      <c r="B120" s="52">
         <v>57</v>
       </c>
-      <c r="C120" s="52"/>
-      <c r="D120" s="87"/>
+      <c r="C120" s="54"/>
+      <c r="D120" s="64"/>
       <c r="E120" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G120" s="40"/>
       <c r="H120" s="31"/>
@@ -6790,18 +6790,18 @@
       <c r="AJ120" s="31"/>
       <c r="AK120" s="36"/>
       <c r="AL120" s="33"/>
-      <c r="AM120" s="54"/>
-      <c r="AN120" s="56"/>
+      <c r="AM120" s="58"/>
+      <c r="AN120" s="60"/>
     </row>
     <row r="121" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="82"/>
-      <c r="C121" s="83"/>
-      <c r="D121" s="88"/>
+      <c r="B121" s="53"/>
+      <c r="C121" s="55"/>
+      <c r="D121" s="65"/>
       <c r="E121" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G121" s="43"/>
       <c r="H121" s="32"/>
@@ -6835,20 +6835,20 @@
       <c r="AJ121" s="32"/>
       <c r="AK121" s="45"/>
       <c r="AL121" s="34"/>
-      <c r="AM121" s="55"/>
-      <c r="AN121" s="57"/>
+      <c r="AM121" s="59"/>
+      <c r="AN121" s="61"/>
     </row>
     <row r="122" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="75">
+      <c r="B122" s="62">
         <v>58</v>
       </c>
-      <c r="C122" s="52"/>
-      <c r="D122" s="87"/>
+      <c r="C122" s="54"/>
+      <c r="D122" s="64"/>
       <c r="E122" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G122" s="40"/>
       <c r="H122" s="31"/>
@@ -6882,18 +6882,18 @@
       <c r="AJ122" s="31"/>
       <c r="AK122" s="36"/>
       <c r="AL122" s="33"/>
-      <c r="AM122" s="54"/>
-      <c r="AN122" s="56"/>
+      <c r="AM122" s="58"/>
+      <c r="AN122" s="60"/>
     </row>
     <row r="123" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="86"/>
-      <c r="C123" s="83"/>
-      <c r="D123" s="88"/>
+      <c r="B123" s="63"/>
+      <c r="C123" s="55"/>
+      <c r="D123" s="65"/>
       <c r="E123" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G123" s="43"/>
       <c r="H123" s="32"/>
@@ -6927,20 +6927,20 @@
       <c r="AJ123" s="32"/>
       <c r="AK123" s="45"/>
       <c r="AL123" s="34"/>
-      <c r="AM123" s="55"/>
-      <c r="AN123" s="57"/>
+      <c r="AM123" s="59"/>
+      <c r="AN123" s="61"/>
     </row>
     <row r="124" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="81">
+      <c r="B124" s="52">
         <v>59</v>
       </c>
-      <c r="C124" s="52"/>
-      <c r="D124" s="87"/>
+      <c r="C124" s="54"/>
+      <c r="D124" s="64"/>
       <c r="E124" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G124" s="40"/>
       <c r="H124" s="31"/>
@@ -6974,18 +6974,18 @@
       <c r="AJ124" s="31"/>
       <c r="AK124" s="36"/>
       <c r="AL124" s="33"/>
-      <c r="AM124" s="54"/>
-      <c r="AN124" s="56"/>
+      <c r="AM124" s="58"/>
+      <c r="AN124" s="60"/>
     </row>
     <row r="125" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="82"/>
-      <c r="C125" s="83"/>
-      <c r="D125" s="88"/>
+      <c r="B125" s="53"/>
+      <c r="C125" s="55"/>
+      <c r="D125" s="65"/>
       <c r="E125" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G125" s="43"/>
       <c r="H125" s="32"/>
@@ -7019,20 +7019,20 @@
       <c r="AJ125" s="32"/>
       <c r="AK125" s="45"/>
       <c r="AL125" s="34"/>
-      <c r="AM125" s="55"/>
-      <c r="AN125" s="57"/>
+      <c r="AM125" s="59"/>
+      <c r="AN125" s="61"/>
     </row>
     <row r="126" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="75">
+      <c r="B126" s="62">
         <v>60</v>
       </c>
-      <c r="C126" s="52"/>
-      <c r="D126" s="84"/>
+      <c r="C126" s="54"/>
+      <c r="D126" s="56"/>
       <c r="E126" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G126" s="40"/>
       <c r="H126" s="31"/>
@@ -7066,18 +7066,18 @@
       <c r="AJ126" s="31"/>
       <c r="AK126" s="36"/>
       <c r="AL126" s="33"/>
-      <c r="AM126" s="54"/>
-      <c r="AN126" s="56"/>
+      <c r="AM126" s="58"/>
+      <c r="AN126" s="60"/>
     </row>
     <row r="127" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="86"/>
-      <c r="C127" s="83"/>
-      <c r="D127" s="85"/>
+      <c r="B127" s="63"/>
+      <c r="C127" s="55"/>
+      <c r="D127" s="57"/>
       <c r="E127" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G127" s="43"/>
       <c r="H127" s="32"/>
@@ -7111,20 +7111,20 @@
       <c r="AJ127" s="32"/>
       <c r="AK127" s="45"/>
       <c r="AL127" s="34"/>
-      <c r="AM127" s="55"/>
-      <c r="AN127" s="57"/>
+      <c r="AM127" s="59"/>
+      <c r="AN127" s="61"/>
     </row>
     <row r="128" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="81">
+      <c r="B128" s="52">
         <v>61</v>
       </c>
-      <c r="C128" s="52"/>
-      <c r="D128" s="87"/>
+      <c r="C128" s="54"/>
+      <c r="D128" s="64"/>
       <c r="E128" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G128" s="40"/>
       <c r="H128" s="31"/>
@@ -7158,18 +7158,18 @@
       <c r="AJ128" s="31"/>
       <c r="AK128" s="36"/>
       <c r="AL128" s="33"/>
-      <c r="AM128" s="54"/>
-      <c r="AN128" s="56"/>
+      <c r="AM128" s="58"/>
+      <c r="AN128" s="60"/>
     </row>
     <row r="129" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="82"/>
-      <c r="C129" s="83"/>
-      <c r="D129" s="88"/>
+      <c r="B129" s="53"/>
+      <c r="C129" s="55"/>
+      <c r="D129" s="65"/>
       <c r="E129" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G129" s="43"/>
       <c r="H129" s="32"/>
@@ -7203,20 +7203,20 @@
       <c r="AJ129" s="32"/>
       <c r="AK129" s="45"/>
       <c r="AL129" s="34"/>
-      <c r="AM129" s="55"/>
-      <c r="AN129" s="57"/>
+      <c r="AM129" s="59"/>
+      <c r="AN129" s="61"/>
     </row>
     <row r="130" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="75">
+      <c r="B130" s="62">
         <v>62</v>
       </c>
-      <c r="C130" s="52"/>
-      <c r="D130" s="84"/>
+      <c r="C130" s="54"/>
+      <c r="D130" s="56"/>
       <c r="E130" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G130" s="40"/>
       <c r="H130" s="31"/>
@@ -7250,18 +7250,18 @@
       <c r="AJ130" s="31"/>
       <c r="AK130" s="36"/>
       <c r="AL130" s="33"/>
-      <c r="AM130" s="54"/>
-      <c r="AN130" s="56"/>
+      <c r="AM130" s="58"/>
+      <c r="AN130" s="60"/>
     </row>
     <row r="131" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="86"/>
-      <c r="C131" s="53"/>
-      <c r="D131" s="89"/>
+      <c r="B131" s="63"/>
+      <c r="C131" s="70"/>
+      <c r="D131" s="71"/>
       <c r="E131" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G131" s="41"/>
       <c r="H131" s="35"/>
@@ -7295,20 +7295,20 @@
       <c r="AJ131" s="35"/>
       <c r="AK131" s="37"/>
       <c r="AL131" s="34"/>
-      <c r="AM131" s="79"/>
-      <c r="AN131" s="71"/>
+      <c r="AM131" s="72"/>
+      <c r="AN131" s="73"/>
     </row>
     <row r="132" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="81">
+      <c r="B132" s="52">
         <v>63</v>
       </c>
-      <c r="C132" s="52"/>
-      <c r="D132" s="84"/>
+      <c r="C132" s="54"/>
+      <c r="D132" s="56"/>
       <c r="E132" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G132" s="40"/>
       <c r="H132" s="31"/>
@@ -7342,18 +7342,18 @@
       <c r="AJ132" s="31"/>
       <c r="AK132" s="36"/>
       <c r="AL132" s="33"/>
-      <c r="AM132" s="54"/>
-      <c r="AN132" s="56"/>
+      <c r="AM132" s="58"/>
+      <c r="AN132" s="60"/>
     </row>
     <row r="133" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="82"/>
-      <c r="C133" s="83"/>
-      <c r="D133" s="85"/>
+      <c r="B133" s="53"/>
+      <c r="C133" s="55"/>
+      <c r="D133" s="57"/>
       <c r="E133" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G133" s="43"/>
       <c r="H133" s="32"/>
@@ -7387,20 +7387,20 @@
       <c r="AJ133" s="32"/>
       <c r="AK133" s="45"/>
       <c r="AL133" s="34"/>
-      <c r="AM133" s="55"/>
-      <c r="AN133" s="57"/>
+      <c r="AM133" s="59"/>
+      <c r="AN133" s="61"/>
     </row>
     <row r="134" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B134" s="75">
+      <c r="B134" s="62">
         <v>64</v>
       </c>
-      <c r="C134" s="52"/>
-      <c r="D134" s="84"/>
+      <c r="C134" s="54"/>
+      <c r="D134" s="56"/>
       <c r="E134" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G134" s="40"/>
       <c r="H134" s="31"/>
@@ -7434,18 +7434,18 @@
       <c r="AJ134" s="31"/>
       <c r="AK134" s="36"/>
       <c r="AL134" s="33"/>
-      <c r="AM134" s="54"/>
-      <c r="AN134" s="56"/>
+      <c r="AM134" s="58"/>
+      <c r="AN134" s="60"/>
     </row>
     <row r="135" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="86"/>
-      <c r="C135" s="83"/>
-      <c r="D135" s="85"/>
+      <c r="B135" s="63"/>
+      <c r="C135" s="55"/>
+      <c r="D135" s="57"/>
       <c r="E135" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G135" s="43"/>
       <c r="H135" s="32"/>
@@ -7479,20 +7479,20 @@
       <c r="AJ135" s="32"/>
       <c r="AK135" s="45"/>
       <c r="AL135" s="34"/>
-      <c r="AM135" s="55"/>
-      <c r="AN135" s="57"/>
+      <c r="AM135" s="59"/>
+      <c r="AN135" s="61"/>
     </row>
     <row r="136" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" s="81">
+      <c r="B136" s="52">
         <v>65</v>
       </c>
-      <c r="C136" s="52"/>
-      <c r="D136" s="84"/>
+      <c r="C136" s="54"/>
+      <c r="D136" s="56"/>
       <c r="E136" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G136" s="40"/>
       <c r="H136" s="31"/>
@@ -7526,18 +7526,18 @@
       <c r="AJ136" s="31"/>
       <c r="AK136" s="36"/>
       <c r="AL136" s="33"/>
-      <c r="AM136" s="54"/>
-      <c r="AN136" s="56"/>
+      <c r="AM136" s="58"/>
+      <c r="AN136" s="60"/>
     </row>
     <row r="137" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="82"/>
-      <c r="C137" s="83"/>
-      <c r="D137" s="85"/>
+      <c r="B137" s="53"/>
+      <c r="C137" s="55"/>
+      <c r="D137" s="57"/>
       <c r="E137" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G137" s="43"/>
       <c r="H137" s="32"/>
@@ -7571,20 +7571,20 @@
       <c r="AJ137" s="32"/>
       <c r="AK137" s="45"/>
       <c r="AL137" s="34"/>
-      <c r="AM137" s="55"/>
-      <c r="AN137" s="57"/>
+      <c r="AM137" s="59"/>
+      <c r="AN137" s="61"/>
     </row>
     <row r="138" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="75">
+      <c r="B138" s="62">
         <v>66</v>
       </c>
-      <c r="C138" s="52"/>
-      <c r="D138" s="84"/>
+      <c r="C138" s="54"/>
+      <c r="D138" s="56"/>
       <c r="E138" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G138" s="40"/>
       <c r="H138" s="31"/>
@@ -7618,18 +7618,18 @@
       <c r="AJ138" s="31"/>
       <c r="AK138" s="36"/>
       <c r="AL138" s="33"/>
-      <c r="AM138" s="54"/>
-      <c r="AN138" s="56"/>
+      <c r="AM138" s="58"/>
+      <c r="AN138" s="60"/>
     </row>
     <row r="139" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="86"/>
-      <c r="C139" s="83"/>
-      <c r="D139" s="85"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="55"/>
+      <c r="D139" s="57"/>
       <c r="E139" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G139" s="43"/>
       <c r="H139" s="32"/>
@@ -7663,20 +7663,20 @@
       <c r="AJ139" s="32"/>
       <c r="AK139" s="45"/>
       <c r="AL139" s="34"/>
-      <c r="AM139" s="55"/>
-      <c r="AN139" s="57"/>
+      <c r="AM139" s="59"/>
+      <c r="AN139" s="61"/>
     </row>
     <row r="140" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="81">
+      <c r="B140" s="52">
         <v>67</v>
       </c>
-      <c r="C140" s="52"/>
-      <c r="D140" s="84"/>
+      <c r="C140" s="54"/>
+      <c r="D140" s="56"/>
       <c r="E140" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G140" s="40"/>
       <c r="H140" s="31"/>
@@ -7710,18 +7710,18 @@
       <c r="AJ140" s="31"/>
       <c r="AK140" s="36"/>
       <c r="AL140" s="33"/>
-      <c r="AM140" s="54"/>
-      <c r="AN140" s="56"/>
+      <c r="AM140" s="58"/>
+      <c r="AN140" s="60"/>
     </row>
     <row r="141" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="82"/>
-      <c r="C141" s="83"/>
-      <c r="D141" s="85"/>
+      <c r="B141" s="53"/>
+      <c r="C141" s="55"/>
+      <c r="D141" s="57"/>
       <c r="E141" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G141" s="43"/>
       <c r="H141" s="32"/>
@@ -7755,20 +7755,20 @@
       <c r="AJ141" s="32"/>
       <c r="AK141" s="45"/>
       <c r="AL141" s="34"/>
-      <c r="AM141" s="55"/>
-      <c r="AN141" s="57"/>
+      <c r="AM141" s="59"/>
+      <c r="AN141" s="61"/>
     </row>
     <row r="142" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="75">
+      <c r="B142" s="62">
         <v>68</v>
       </c>
-      <c r="C142" s="52"/>
-      <c r="D142" s="84"/>
+      <c r="C142" s="54"/>
+      <c r="D142" s="56"/>
       <c r="E142" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G142" s="40"/>
       <c r="H142" s="31"/>
@@ -7802,18 +7802,18 @@
       <c r="AJ142" s="31"/>
       <c r="AK142" s="36"/>
       <c r="AL142" s="33"/>
-      <c r="AM142" s="54"/>
-      <c r="AN142" s="56"/>
+      <c r="AM142" s="58"/>
+      <c r="AN142" s="60"/>
     </row>
     <row r="143" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="86"/>
-      <c r="C143" s="83"/>
-      <c r="D143" s="85"/>
+      <c r="B143" s="63"/>
+      <c r="C143" s="55"/>
+      <c r="D143" s="57"/>
       <c r="E143" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G143" s="43"/>
       <c r="H143" s="32"/>
@@ -7847,20 +7847,20 @@
       <c r="AJ143" s="32"/>
       <c r="AK143" s="45"/>
       <c r="AL143" s="34"/>
-      <c r="AM143" s="55"/>
-      <c r="AN143" s="57"/>
+      <c r="AM143" s="59"/>
+      <c r="AN143" s="61"/>
     </row>
     <row r="144" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B144" s="81">
+      <c r="B144" s="52">
         <v>69</v>
       </c>
-      <c r="C144" s="52"/>
-      <c r="D144" s="84"/>
+      <c r="C144" s="54"/>
+      <c r="D144" s="56"/>
       <c r="E144" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G144" s="40"/>
       <c r="H144" s="31"/>
@@ -7894,18 +7894,18 @@
       <c r="AJ144" s="31"/>
       <c r="AK144" s="36"/>
       <c r="AL144" s="33"/>
-      <c r="AM144" s="54"/>
-      <c r="AN144" s="56"/>
+      <c r="AM144" s="58"/>
+      <c r="AN144" s="60"/>
     </row>
     <row r="145" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="82"/>
-      <c r="C145" s="83"/>
-      <c r="D145" s="85"/>
+      <c r="B145" s="53"/>
+      <c r="C145" s="55"/>
+      <c r="D145" s="57"/>
       <c r="E145" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G145" s="43"/>
       <c r="H145" s="32"/>
@@ -7939,20 +7939,20 @@
       <c r="AJ145" s="32"/>
       <c r="AK145" s="45"/>
       <c r="AL145" s="34"/>
-      <c r="AM145" s="55"/>
-      <c r="AN145" s="57"/>
+      <c r="AM145" s="59"/>
+      <c r="AN145" s="61"/>
     </row>
     <row r="146" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B146" s="75">
+      <c r="B146" s="62">
         <v>70</v>
       </c>
-      <c r="C146" s="52"/>
-      <c r="D146" s="84"/>
+      <c r="C146" s="54"/>
+      <c r="D146" s="56"/>
       <c r="E146" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G146" s="40"/>
       <c r="H146" s="31"/>
@@ -7986,18 +7986,18 @@
       <c r="AJ146" s="31"/>
       <c r="AK146" s="36"/>
       <c r="AL146" s="33"/>
-      <c r="AM146" s="54"/>
-      <c r="AN146" s="56"/>
+      <c r="AM146" s="58"/>
+      <c r="AN146" s="60"/>
     </row>
     <row r="147" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="86"/>
-      <c r="C147" s="83"/>
-      <c r="D147" s="85"/>
+      <c r="B147" s="63"/>
+      <c r="C147" s="55"/>
+      <c r="D147" s="57"/>
       <c r="E147" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G147" s="43"/>
       <c r="H147" s="32"/>
@@ -8031,20 +8031,20 @@
       <c r="AJ147" s="32"/>
       <c r="AK147" s="45"/>
       <c r="AL147" s="34"/>
-      <c r="AM147" s="55"/>
-      <c r="AN147" s="57"/>
+      <c r="AM147" s="59"/>
+      <c r="AN147" s="61"/>
     </row>
     <row r="148" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B148" s="81">
+      <c r="B148" s="52">
         <v>71</v>
       </c>
-      <c r="C148" s="52"/>
-      <c r="D148" s="84"/>
+      <c r="C148" s="54"/>
+      <c r="D148" s="56"/>
       <c r="E148" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G148" s="40"/>
       <c r="H148" s="31"/>
@@ -8078,18 +8078,18 @@
       <c r="AJ148" s="31"/>
       <c r="AK148" s="36"/>
       <c r="AL148" s="33"/>
-      <c r="AM148" s="54"/>
-      <c r="AN148" s="56"/>
+      <c r="AM148" s="58"/>
+      <c r="AN148" s="60"/>
     </row>
     <row r="149" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="82"/>
-      <c r="C149" s="83"/>
-      <c r="D149" s="85"/>
+      <c r="B149" s="53"/>
+      <c r="C149" s="55"/>
+      <c r="D149" s="57"/>
       <c r="E149" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G149" s="43"/>
       <c r="H149" s="32"/>
@@ -8123,20 +8123,20 @@
       <c r="AJ149" s="32"/>
       <c r="AK149" s="45"/>
       <c r="AL149" s="34"/>
-      <c r="AM149" s="55"/>
-      <c r="AN149" s="57"/>
+      <c r="AM149" s="59"/>
+      <c r="AN149" s="61"/>
     </row>
     <row r="150" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="75">
+      <c r="B150" s="62">
         <v>72</v>
       </c>
-      <c r="C150" s="52"/>
-      <c r="D150" s="84"/>
+      <c r="C150" s="54"/>
+      <c r="D150" s="56"/>
       <c r="E150" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G150" s="40"/>
       <c r="H150" s="31"/>
@@ -8170,18 +8170,18 @@
       <c r="AJ150" s="31"/>
       <c r="AK150" s="36"/>
       <c r="AL150" s="33"/>
-      <c r="AM150" s="54"/>
-      <c r="AN150" s="56"/>
+      <c r="AM150" s="58"/>
+      <c r="AN150" s="60"/>
     </row>
     <row r="151" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="86"/>
-      <c r="C151" s="53"/>
-      <c r="D151" s="89"/>
+      <c r="B151" s="63"/>
+      <c r="C151" s="70"/>
+      <c r="D151" s="71"/>
       <c r="E151" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F151" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G151" s="41"/>
       <c r="H151" s="35"/>
@@ -8215,20 +8215,20 @@
       <c r="AJ151" s="35"/>
       <c r="AK151" s="37"/>
       <c r="AL151" s="34"/>
-      <c r="AM151" s="79"/>
-      <c r="AN151" s="71"/>
+      <c r="AM151" s="72"/>
+      <c r="AN151" s="73"/>
     </row>
     <row r="152" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="81">
+      <c r="B152" s="52">
         <v>73</v>
       </c>
-      <c r="C152" s="52"/>
-      <c r="D152" s="87"/>
+      <c r="C152" s="54"/>
+      <c r="D152" s="64"/>
       <c r="E152" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G152" s="40"/>
       <c r="H152" s="31"/>
@@ -8262,18 +8262,18 @@
       <c r="AJ152" s="31"/>
       <c r="AK152" s="36"/>
       <c r="AL152" s="33"/>
-      <c r="AM152" s="54"/>
-      <c r="AN152" s="56"/>
+      <c r="AM152" s="58"/>
+      <c r="AN152" s="60"/>
     </row>
     <row r="153" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="82"/>
-      <c r="C153" s="83"/>
-      <c r="D153" s="88"/>
+      <c r="B153" s="53"/>
+      <c r="C153" s="55"/>
+      <c r="D153" s="65"/>
       <c r="E153" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G153" s="43"/>
       <c r="H153" s="32"/>
@@ -8307,20 +8307,20 @@
       <c r="AJ153" s="32"/>
       <c r="AK153" s="45"/>
       <c r="AL153" s="34"/>
-      <c r="AM153" s="55"/>
-      <c r="AN153" s="57"/>
+      <c r="AM153" s="59"/>
+      <c r="AN153" s="61"/>
     </row>
     <row r="154" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B154" s="75">
+      <c r="B154" s="62">
         <v>74</v>
       </c>
-      <c r="C154" s="52"/>
-      <c r="D154" s="87"/>
+      <c r="C154" s="54"/>
+      <c r="D154" s="64"/>
       <c r="E154" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G154" s="40"/>
       <c r="H154" s="31"/>
@@ -8354,18 +8354,18 @@
       <c r="AJ154" s="31"/>
       <c r="AK154" s="36"/>
       <c r="AL154" s="33"/>
-      <c r="AM154" s="54"/>
-      <c r="AN154" s="56"/>
+      <c r="AM154" s="58"/>
+      <c r="AN154" s="60"/>
     </row>
     <row r="155" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="86"/>
-      <c r="C155" s="83"/>
-      <c r="D155" s="88"/>
+      <c r="B155" s="63"/>
+      <c r="C155" s="55"/>
+      <c r="D155" s="65"/>
       <c r="E155" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G155" s="43"/>
       <c r="H155" s="32"/>
@@ -8399,20 +8399,20 @@
       <c r="AJ155" s="32"/>
       <c r="AK155" s="45"/>
       <c r="AL155" s="34"/>
-      <c r="AM155" s="55"/>
-      <c r="AN155" s="57"/>
+      <c r="AM155" s="59"/>
+      <c r="AN155" s="61"/>
     </row>
     <row r="156" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B156" s="81">
+      <c r="B156" s="52">
         <v>75</v>
       </c>
-      <c r="C156" s="52"/>
-      <c r="D156" s="87"/>
+      <c r="C156" s="54"/>
+      <c r="D156" s="64"/>
       <c r="E156" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G156" s="40"/>
       <c r="H156" s="31"/>
@@ -8446,18 +8446,18 @@
       <c r="AJ156" s="31"/>
       <c r="AK156" s="36"/>
       <c r="AL156" s="33"/>
-      <c r="AM156" s="54"/>
-      <c r="AN156" s="56"/>
+      <c r="AM156" s="58"/>
+      <c r="AN156" s="60"/>
     </row>
     <row r="157" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="82"/>
-      <c r="C157" s="83"/>
-      <c r="D157" s="88"/>
+      <c r="B157" s="53"/>
+      <c r="C157" s="55"/>
+      <c r="D157" s="65"/>
       <c r="E157" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G157" s="43"/>
       <c r="H157" s="32"/>
@@ -8491,20 +8491,20 @@
       <c r="AJ157" s="32"/>
       <c r="AK157" s="45"/>
       <c r="AL157" s="34"/>
-      <c r="AM157" s="55"/>
-      <c r="AN157" s="57"/>
+      <c r="AM157" s="59"/>
+      <c r="AN157" s="61"/>
     </row>
     <row r="158" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="75">
+      <c r="B158" s="62">
         <v>76</v>
       </c>
-      <c r="C158" s="52"/>
-      <c r="D158" s="87"/>
+      <c r="C158" s="54"/>
+      <c r="D158" s="64"/>
       <c r="E158" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G158" s="40"/>
       <c r="H158" s="31"/>
@@ -8538,18 +8538,18 @@
       <c r="AJ158" s="31"/>
       <c r="AK158" s="36"/>
       <c r="AL158" s="33"/>
-      <c r="AM158" s="54"/>
-      <c r="AN158" s="56"/>
+      <c r="AM158" s="58"/>
+      <c r="AN158" s="60"/>
     </row>
     <row r="159" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="86"/>
-      <c r="C159" s="83"/>
-      <c r="D159" s="88"/>
+      <c r="B159" s="63"/>
+      <c r="C159" s="55"/>
+      <c r="D159" s="65"/>
       <c r="E159" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G159" s="43"/>
       <c r="H159" s="32"/>
@@ -8583,20 +8583,20 @@
       <c r="AJ159" s="32"/>
       <c r="AK159" s="45"/>
       <c r="AL159" s="34"/>
-      <c r="AM159" s="55"/>
-      <c r="AN159" s="57"/>
+      <c r="AM159" s="59"/>
+      <c r="AN159" s="61"/>
     </row>
     <row r="160" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="81">
+      <c r="B160" s="52">
         <v>77</v>
       </c>
-      <c r="C160" s="52"/>
-      <c r="D160" s="84"/>
+      <c r="C160" s="54"/>
+      <c r="D160" s="56"/>
       <c r="E160" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G160" s="40"/>
       <c r="H160" s="31"/>
@@ -8630,18 +8630,18 @@
       <c r="AJ160" s="31"/>
       <c r="AK160" s="36"/>
       <c r="AL160" s="33"/>
-      <c r="AM160" s="54"/>
-      <c r="AN160" s="56"/>
+      <c r="AM160" s="58"/>
+      <c r="AN160" s="60"/>
     </row>
     <row r="161" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="82"/>
-      <c r="C161" s="83"/>
-      <c r="D161" s="85"/>
+      <c r="B161" s="53"/>
+      <c r="C161" s="55"/>
+      <c r="D161" s="57"/>
       <c r="E161" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G161" s="43"/>
       <c r="H161" s="32"/>
@@ -8675,20 +8675,20 @@
       <c r="AJ161" s="32"/>
       <c r="AK161" s="45"/>
       <c r="AL161" s="34"/>
-      <c r="AM161" s="55"/>
-      <c r="AN161" s="57"/>
+      <c r="AM161" s="59"/>
+      <c r="AN161" s="61"/>
     </row>
     <row r="162" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B162" s="75">
+      <c r="B162" s="62">
         <v>78</v>
       </c>
-      <c r="C162" s="52"/>
-      <c r="D162" s="84"/>
+      <c r="C162" s="54"/>
+      <c r="D162" s="56"/>
       <c r="E162" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G162" s="40"/>
       <c r="H162" s="31"/>
@@ -8722,18 +8722,18 @@
       <c r="AJ162" s="31"/>
       <c r="AK162" s="36"/>
       <c r="AL162" s="33"/>
-      <c r="AM162" s="54"/>
-      <c r="AN162" s="56"/>
+      <c r="AM162" s="58"/>
+      <c r="AN162" s="60"/>
     </row>
     <row r="163" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="86"/>
-      <c r="C163" s="83"/>
-      <c r="D163" s="85"/>
+      <c r="B163" s="63"/>
+      <c r="C163" s="55"/>
+      <c r="D163" s="57"/>
       <c r="E163" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G163" s="43"/>
       <c r="H163" s="32"/>
@@ -8767,20 +8767,20 @@
       <c r="AJ163" s="32"/>
       <c r="AK163" s="45"/>
       <c r="AL163" s="34"/>
-      <c r="AM163" s="55"/>
-      <c r="AN163" s="57"/>
+      <c r="AM163" s="59"/>
+      <c r="AN163" s="61"/>
     </row>
     <row r="164" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B164" s="81">
+      <c r="B164" s="52">
         <v>79</v>
       </c>
-      <c r="C164" s="52"/>
-      <c r="D164" s="84"/>
+      <c r="C164" s="54"/>
+      <c r="D164" s="56"/>
       <c r="E164" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G164" s="40"/>
       <c r="H164" s="31"/>
@@ -8814,18 +8814,18 @@
       <c r="AJ164" s="31"/>
       <c r="AK164" s="36"/>
       <c r="AL164" s="33"/>
-      <c r="AM164" s="54"/>
-      <c r="AN164" s="56"/>
+      <c r="AM164" s="58"/>
+      <c r="AN164" s="60"/>
     </row>
     <row r="165" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="82"/>
-      <c r="C165" s="83"/>
-      <c r="D165" s="85"/>
+      <c r="B165" s="53"/>
+      <c r="C165" s="55"/>
+      <c r="D165" s="57"/>
       <c r="E165" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G165" s="43"/>
       <c r="H165" s="32"/>
@@ -8859,20 +8859,20 @@
       <c r="AJ165" s="32"/>
       <c r="AK165" s="45"/>
       <c r="AL165" s="34"/>
-      <c r="AM165" s="55"/>
-      <c r="AN165" s="57"/>
+      <c r="AM165" s="59"/>
+      <c r="AN165" s="61"/>
     </row>
     <row r="166" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B166" s="75">
+      <c r="B166" s="62">
         <v>80</v>
       </c>
-      <c r="C166" s="52"/>
-      <c r="D166" s="84"/>
+      <c r="C166" s="54"/>
+      <c r="D166" s="56"/>
       <c r="E166" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G166" s="40"/>
       <c r="H166" s="31"/>
@@ -8906,18 +8906,18 @@
       <c r="AJ166" s="31"/>
       <c r="AK166" s="36"/>
       <c r="AL166" s="33"/>
-      <c r="AM166" s="54"/>
-      <c r="AN166" s="56"/>
+      <c r="AM166" s="58"/>
+      <c r="AN166" s="60"/>
     </row>
     <row r="167" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="86"/>
-      <c r="C167" s="83"/>
-      <c r="D167" s="85"/>
+      <c r="B167" s="63"/>
+      <c r="C167" s="55"/>
+      <c r="D167" s="57"/>
       <c r="E167" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G167" s="43"/>
       <c r="H167" s="32"/>
@@ -8951,20 +8951,20 @@
       <c r="AJ167" s="32"/>
       <c r="AK167" s="45"/>
       <c r="AL167" s="34"/>
-      <c r="AM167" s="55"/>
-      <c r="AN167" s="57"/>
+      <c r="AM167" s="59"/>
+      <c r="AN167" s="61"/>
     </row>
     <row r="168" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="81">
+      <c r="B168" s="52">
         <v>81</v>
       </c>
-      <c r="C168" s="52"/>
-      <c r="D168" s="84"/>
+      <c r="C168" s="54"/>
+      <c r="D168" s="56"/>
       <c r="E168" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G168" s="40"/>
       <c r="H168" s="31"/>
@@ -8998,18 +8998,18 @@
       <c r="AJ168" s="31"/>
       <c r="AK168" s="36"/>
       <c r="AL168" s="33"/>
-      <c r="AM168" s="54"/>
-      <c r="AN168" s="56"/>
+      <c r="AM168" s="58"/>
+      <c r="AN168" s="60"/>
     </row>
     <row r="169" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="82"/>
-      <c r="C169" s="83"/>
-      <c r="D169" s="85"/>
+      <c r="B169" s="53"/>
+      <c r="C169" s="55"/>
+      <c r="D169" s="57"/>
       <c r="E169" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G169" s="43"/>
       <c r="H169" s="32"/>
@@ -9043,20 +9043,20 @@
       <c r="AJ169" s="32"/>
       <c r="AK169" s="45"/>
       <c r="AL169" s="34"/>
-      <c r="AM169" s="55"/>
-      <c r="AN169" s="57"/>
+      <c r="AM169" s="59"/>
+      <c r="AN169" s="61"/>
     </row>
     <row r="170" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B170" s="75">
+      <c r="B170" s="62">
         <v>82</v>
       </c>
-      <c r="C170" s="52"/>
-      <c r="D170" s="84"/>
+      <c r="C170" s="54"/>
+      <c r="D170" s="56"/>
       <c r="E170" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G170" s="40"/>
       <c r="H170" s="31"/>
@@ -9090,18 +9090,18 @@
       <c r="AJ170" s="31"/>
       <c r="AK170" s="36"/>
       <c r="AL170" s="33"/>
-      <c r="AM170" s="54"/>
-      <c r="AN170" s="56"/>
+      <c r="AM170" s="58"/>
+      <c r="AN170" s="60"/>
     </row>
     <row r="171" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="86"/>
-      <c r="C171" s="83"/>
-      <c r="D171" s="85"/>
+      <c r="B171" s="63"/>
+      <c r="C171" s="55"/>
+      <c r="D171" s="57"/>
       <c r="E171" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G171" s="43"/>
       <c r="H171" s="32"/>
@@ -9135,20 +9135,20 @@
       <c r="AJ171" s="32"/>
       <c r="AK171" s="45"/>
       <c r="AL171" s="34"/>
-      <c r="AM171" s="55"/>
-      <c r="AN171" s="57"/>
+      <c r="AM171" s="59"/>
+      <c r="AN171" s="61"/>
     </row>
     <row r="172" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B172" s="81">
+      <c r="B172" s="52">
         <v>83</v>
       </c>
-      <c r="C172" s="52"/>
-      <c r="D172" s="84"/>
+      <c r="C172" s="54"/>
+      <c r="D172" s="56"/>
       <c r="E172" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G172" s="40"/>
       <c r="H172" s="31"/>
@@ -9182,18 +9182,18 @@
       <c r="AJ172" s="31"/>
       <c r="AK172" s="36"/>
       <c r="AL172" s="33"/>
-      <c r="AM172" s="54"/>
-      <c r="AN172" s="56"/>
+      <c r="AM172" s="58"/>
+      <c r="AN172" s="60"/>
     </row>
     <row r="173" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="82"/>
-      <c r="C173" s="83"/>
-      <c r="D173" s="85"/>
+      <c r="B173" s="53"/>
+      <c r="C173" s="55"/>
+      <c r="D173" s="57"/>
       <c r="E173" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G173" s="43"/>
       <c r="H173" s="32"/>
@@ -9227,20 +9227,20 @@
       <c r="AJ173" s="32"/>
       <c r="AK173" s="45"/>
       <c r="AL173" s="34"/>
-      <c r="AM173" s="55"/>
-      <c r="AN173" s="57"/>
+      <c r="AM173" s="59"/>
+      <c r="AN173" s="61"/>
     </row>
     <row r="174" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B174" s="75">
+      <c r="B174" s="62">
         <v>84</v>
       </c>
-      <c r="C174" s="52"/>
-      <c r="D174" s="84"/>
+      <c r="C174" s="54"/>
+      <c r="D174" s="56"/>
       <c r="E174" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G174" s="40"/>
       <c r="H174" s="31"/>
@@ -9274,18 +9274,18 @@
       <c r="AJ174" s="31"/>
       <c r="AK174" s="36"/>
       <c r="AL174" s="33"/>
-      <c r="AM174" s="54"/>
-      <c r="AN174" s="56"/>
+      <c r="AM174" s="58"/>
+      <c r="AN174" s="60"/>
     </row>
     <row r="175" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="86"/>
-      <c r="C175" s="83"/>
-      <c r="D175" s="85"/>
+      <c r="B175" s="63"/>
+      <c r="C175" s="55"/>
+      <c r="D175" s="57"/>
       <c r="E175" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G175" s="43"/>
       <c r="H175" s="32"/>
@@ -9319,20 +9319,20 @@
       <c r="AJ175" s="32"/>
       <c r="AK175" s="45"/>
       <c r="AL175" s="34"/>
-      <c r="AM175" s="55"/>
-      <c r="AN175" s="57"/>
+      <c r="AM175" s="59"/>
+      <c r="AN175" s="61"/>
     </row>
     <row r="176" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B176" s="81">
+      <c r="B176" s="52">
         <v>85</v>
       </c>
-      <c r="C176" s="52"/>
-      <c r="D176" s="84"/>
+      <c r="C176" s="54"/>
+      <c r="D176" s="56"/>
       <c r="E176" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G176" s="40"/>
       <c r="H176" s="31"/>
@@ -9366,18 +9366,18 @@
       <c r="AJ176" s="31"/>
       <c r="AK176" s="36"/>
       <c r="AL176" s="33"/>
-      <c r="AM176" s="54"/>
-      <c r="AN176" s="56"/>
+      <c r="AM176" s="58"/>
+      <c r="AN176" s="60"/>
     </row>
     <row r="177" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="82"/>
-      <c r="C177" s="83"/>
-      <c r="D177" s="85"/>
+      <c r="B177" s="53"/>
+      <c r="C177" s="55"/>
+      <c r="D177" s="57"/>
       <c r="E177" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F177" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G177" s="43"/>
       <c r="H177" s="32"/>
@@ -9411,20 +9411,20 @@
       <c r="AJ177" s="32"/>
       <c r="AK177" s="45"/>
       <c r="AL177" s="34"/>
-      <c r="AM177" s="55"/>
-      <c r="AN177" s="57"/>
+      <c r="AM177" s="59"/>
+      <c r="AN177" s="61"/>
     </row>
     <row r="178" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="75">
+      <c r="B178" s="62">
         <v>86</v>
       </c>
-      <c r="C178" s="52"/>
-      <c r="D178" s="87"/>
+      <c r="C178" s="54"/>
+      <c r="D178" s="64"/>
       <c r="E178" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G178" s="40"/>
       <c r="H178" s="31"/>
@@ -9458,18 +9458,18 @@
       <c r="AJ178" s="31"/>
       <c r="AK178" s="36"/>
       <c r="AL178" s="33"/>
-      <c r="AM178" s="54"/>
-      <c r="AN178" s="56"/>
+      <c r="AM178" s="58"/>
+      <c r="AN178" s="60"/>
     </row>
     <row r="179" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="86"/>
-      <c r="C179" s="83"/>
-      <c r="D179" s="88"/>
+      <c r="B179" s="63"/>
+      <c r="C179" s="55"/>
+      <c r="D179" s="65"/>
       <c r="E179" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G179" s="43"/>
       <c r="H179" s="32"/>
@@ -9503,20 +9503,20 @@
       <c r="AJ179" s="32"/>
       <c r="AK179" s="45"/>
       <c r="AL179" s="34"/>
-      <c r="AM179" s="55"/>
-      <c r="AN179" s="57"/>
+      <c r="AM179" s="59"/>
+      <c r="AN179" s="61"/>
     </row>
     <row r="180" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B180" s="81">
+      <c r="B180" s="52">
         <v>87</v>
       </c>
-      <c r="C180" s="52"/>
-      <c r="D180" s="87"/>
+      <c r="C180" s="54"/>
+      <c r="D180" s="64"/>
       <c r="E180" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G180" s="40"/>
       <c r="H180" s="31"/>
@@ -9550,18 +9550,18 @@
       <c r="AJ180" s="31"/>
       <c r="AK180" s="36"/>
       <c r="AL180" s="33"/>
-      <c r="AM180" s="54"/>
-      <c r="AN180" s="56"/>
+      <c r="AM180" s="58"/>
+      <c r="AN180" s="60"/>
     </row>
     <row r="181" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="82"/>
-      <c r="C181" s="83"/>
-      <c r="D181" s="88"/>
+      <c r="B181" s="53"/>
+      <c r="C181" s="55"/>
+      <c r="D181" s="65"/>
       <c r="E181" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F181" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G181" s="43"/>
       <c r="H181" s="32"/>
@@ -9595,20 +9595,20 @@
       <c r="AJ181" s="32"/>
       <c r="AK181" s="45"/>
       <c r="AL181" s="34"/>
-      <c r="AM181" s="55"/>
-      <c r="AN181" s="57"/>
+      <c r="AM181" s="59"/>
+      <c r="AN181" s="61"/>
     </row>
     <row r="182" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="75">
+      <c r="B182" s="62">
         <v>88</v>
       </c>
-      <c r="C182" s="62"/>
-      <c r="D182" s="91"/>
+      <c r="C182" s="66"/>
+      <c r="D182" s="68"/>
       <c r="E182" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G182" s="40"/>
       <c r="H182" s="31"/>
@@ -9642,18 +9642,18 @@
       <c r="AJ182" s="31"/>
       <c r="AK182" s="36"/>
       <c r="AL182" s="33"/>
-      <c r="AM182" s="54"/>
-      <c r="AN182" s="56"/>
+      <c r="AM182" s="58"/>
+      <c r="AN182" s="60"/>
     </row>
     <row r="183" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="86"/>
-      <c r="C183" s="90"/>
-      <c r="D183" s="92"/>
+      <c r="B183" s="63"/>
+      <c r="C183" s="67"/>
+      <c r="D183" s="69"/>
       <c r="E183" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F183" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G183" s="43"/>
       <c r="H183" s="32"/>
@@ -9687,20 +9687,20 @@
       <c r="AJ183" s="32"/>
       <c r="AK183" s="45"/>
       <c r="AL183" s="34"/>
-      <c r="AM183" s="55"/>
-      <c r="AN183" s="57"/>
+      <c r="AM183" s="59"/>
+      <c r="AN183" s="61"/>
     </row>
     <row r="184" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B184" s="81">
+      <c r="B184" s="52">
         <v>89</v>
       </c>
-      <c r="C184" s="52"/>
-      <c r="D184" s="87"/>
+      <c r="C184" s="54"/>
+      <c r="D184" s="64"/>
       <c r="E184" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F184" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G184" s="40"/>
       <c r="H184" s="31"/>
@@ -9734,18 +9734,18 @@
       <c r="AJ184" s="31"/>
       <c r="AK184" s="36"/>
       <c r="AL184" s="33"/>
-      <c r="AM184" s="54"/>
-      <c r="AN184" s="56"/>
+      <c r="AM184" s="58"/>
+      <c r="AN184" s="60"/>
     </row>
     <row r="185" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="82"/>
-      <c r="C185" s="83"/>
-      <c r="D185" s="88"/>
+      <c r="B185" s="53"/>
+      <c r="C185" s="55"/>
+      <c r="D185" s="65"/>
       <c r="E185" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G185" s="43"/>
       <c r="H185" s="32"/>
@@ -9779,20 +9779,20 @@
       <c r="AJ185" s="32"/>
       <c r="AK185" s="45"/>
       <c r="AL185" s="34"/>
-      <c r="AM185" s="55"/>
-      <c r="AN185" s="57"/>
+      <c r="AM185" s="59"/>
+      <c r="AN185" s="61"/>
     </row>
     <row r="186" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B186" s="75">
+      <c r="B186" s="62">
         <v>90</v>
       </c>
-      <c r="C186" s="52"/>
-      <c r="D186" s="87"/>
+      <c r="C186" s="54"/>
+      <c r="D186" s="64"/>
       <c r="E186" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F186" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G186" s="40"/>
       <c r="H186" s="31"/>
@@ -9826,18 +9826,18 @@
       <c r="AJ186" s="31"/>
       <c r="AK186" s="36"/>
       <c r="AL186" s="33"/>
-      <c r="AM186" s="54"/>
-      <c r="AN186" s="56"/>
+      <c r="AM186" s="58"/>
+      <c r="AN186" s="60"/>
     </row>
     <row r="187" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="86"/>
-      <c r="C187" s="83"/>
-      <c r="D187" s="88"/>
+      <c r="B187" s="63"/>
+      <c r="C187" s="55"/>
+      <c r="D187" s="65"/>
       <c r="E187" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G187" s="43"/>
       <c r="H187" s="32"/>
@@ -9871,20 +9871,20 @@
       <c r="AJ187" s="32"/>
       <c r="AK187" s="45"/>
       <c r="AL187" s="34"/>
-      <c r="AM187" s="55"/>
-      <c r="AN187" s="57"/>
+      <c r="AM187" s="59"/>
+      <c r="AN187" s="61"/>
     </row>
     <row r="188" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B188" s="81">
+      <c r="B188" s="52">
         <v>91</v>
       </c>
-      <c r="C188" s="52"/>
-      <c r="D188" s="87"/>
+      <c r="C188" s="54"/>
+      <c r="D188" s="64"/>
       <c r="E188" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G188" s="40"/>
       <c r="H188" s="31"/>
@@ -9918,18 +9918,18 @@
       <c r="AJ188" s="31"/>
       <c r="AK188" s="36"/>
       <c r="AL188" s="33"/>
-      <c r="AM188" s="54"/>
-      <c r="AN188" s="56"/>
+      <c r="AM188" s="58"/>
+      <c r="AN188" s="60"/>
     </row>
     <row r="189" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="82"/>
-      <c r="C189" s="83"/>
-      <c r="D189" s="88"/>
+      <c r="B189" s="53"/>
+      <c r="C189" s="55"/>
+      <c r="D189" s="65"/>
       <c r="E189" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G189" s="43"/>
       <c r="H189" s="32"/>
@@ -9963,20 +9963,20 @@
       <c r="AJ189" s="32"/>
       <c r="AK189" s="45"/>
       <c r="AL189" s="34"/>
-      <c r="AM189" s="55"/>
-      <c r="AN189" s="57"/>
+      <c r="AM189" s="59"/>
+      <c r="AN189" s="61"/>
     </row>
     <row r="190" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B190" s="75">
+      <c r="B190" s="62">
         <v>92</v>
       </c>
-      <c r="C190" s="52"/>
-      <c r="D190" s="87"/>
+      <c r="C190" s="54"/>
+      <c r="D190" s="64"/>
       <c r="E190" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G190" s="40"/>
       <c r="H190" s="31"/>
@@ -10010,18 +10010,18 @@
       <c r="AJ190" s="31"/>
       <c r="AK190" s="36"/>
       <c r="AL190" s="33"/>
-      <c r="AM190" s="54"/>
-      <c r="AN190" s="56"/>
+      <c r="AM190" s="58"/>
+      <c r="AN190" s="60"/>
     </row>
     <row r="191" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="86"/>
-      <c r="C191" s="83"/>
-      <c r="D191" s="88"/>
+      <c r="B191" s="63"/>
+      <c r="C191" s="55"/>
+      <c r="D191" s="65"/>
       <c r="E191" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G191" s="43"/>
       <c r="H191" s="32"/>
@@ -10055,20 +10055,20 @@
       <c r="AJ191" s="32"/>
       <c r="AK191" s="45"/>
       <c r="AL191" s="34"/>
-      <c r="AM191" s="55"/>
-      <c r="AN191" s="57"/>
+      <c r="AM191" s="59"/>
+      <c r="AN191" s="61"/>
     </row>
     <row r="192" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B192" s="81">
+      <c r="B192" s="52">
         <v>93</v>
       </c>
-      <c r="C192" s="52"/>
-      <c r="D192" s="84"/>
+      <c r="C192" s="54"/>
+      <c r="D192" s="56"/>
       <c r="E192" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G192" s="40"/>
       <c r="H192" s="31"/>
@@ -10102,18 +10102,18 @@
       <c r="AJ192" s="31"/>
       <c r="AK192" s="36"/>
       <c r="AL192" s="33"/>
-      <c r="AM192" s="54"/>
-      <c r="AN192" s="56"/>
+      <c r="AM192" s="58"/>
+      <c r="AN192" s="60"/>
     </row>
     <row r="193" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="82"/>
-      <c r="C193" s="83"/>
-      <c r="D193" s="85"/>
+      <c r="B193" s="53"/>
+      <c r="C193" s="55"/>
+      <c r="D193" s="57"/>
       <c r="E193" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G193" s="43"/>
       <c r="H193" s="32"/>
@@ -10147,20 +10147,20 @@
       <c r="AJ193" s="32"/>
       <c r="AK193" s="45"/>
       <c r="AL193" s="34"/>
-      <c r="AM193" s="55"/>
-      <c r="AN193" s="57"/>
+      <c r="AM193" s="59"/>
+      <c r="AN193" s="61"/>
     </row>
     <row r="194" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="75">
+      <c r="B194" s="62">
         <v>94</v>
       </c>
-      <c r="C194" s="52"/>
-      <c r="D194" s="84"/>
+      <c r="C194" s="54"/>
+      <c r="D194" s="56"/>
       <c r="E194" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G194" s="40"/>
       <c r="H194" s="31"/>
@@ -10194,18 +10194,18 @@
       <c r="AJ194" s="31"/>
       <c r="AK194" s="36"/>
       <c r="AL194" s="33"/>
-      <c r="AM194" s="54"/>
-      <c r="AN194" s="56"/>
+      <c r="AM194" s="58"/>
+      <c r="AN194" s="60"/>
     </row>
     <row r="195" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="86"/>
-      <c r="C195" s="83"/>
-      <c r="D195" s="85"/>
+      <c r="B195" s="63"/>
+      <c r="C195" s="55"/>
+      <c r="D195" s="57"/>
       <c r="E195" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G195" s="43"/>
       <c r="H195" s="32"/>
@@ -10239,20 +10239,20 @@
       <c r="AJ195" s="32"/>
       <c r="AK195" s="45"/>
       <c r="AL195" s="34"/>
-      <c r="AM195" s="55"/>
-      <c r="AN195" s="57"/>
+      <c r="AM195" s="59"/>
+      <c r="AN195" s="61"/>
     </row>
     <row r="196" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B196" s="81">
+      <c r="B196" s="52">
         <v>95</v>
       </c>
-      <c r="C196" s="52"/>
-      <c r="D196" s="84"/>
+      <c r="C196" s="54"/>
+      <c r="D196" s="56"/>
       <c r="E196" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G196" s="40"/>
       <c r="H196" s="31"/>
@@ -10286,18 +10286,18 @@
       <c r="AJ196" s="31"/>
       <c r="AK196" s="36"/>
       <c r="AL196" s="33"/>
-      <c r="AM196" s="54"/>
-      <c r="AN196" s="56"/>
+      <c r="AM196" s="58"/>
+      <c r="AN196" s="60"/>
     </row>
     <row r="197" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B197" s="82"/>
-      <c r="C197" s="83"/>
-      <c r="D197" s="85"/>
+      <c r="B197" s="53"/>
+      <c r="C197" s="55"/>
+      <c r="D197" s="57"/>
       <c r="E197" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G197" s="43"/>
       <c r="H197" s="32"/>
@@ -10331,20 +10331,20 @@
       <c r="AJ197" s="32"/>
       <c r="AK197" s="45"/>
       <c r="AL197" s="34"/>
-      <c r="AM197" s="55"/>
-      <c r="AN197" s="57"/>
+      <c r="AM197" s="59"/>
+      <c r="AN197" s="61"/>
     </row>
     <row r="198" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B198" s="75">
+      <c r="B198" s="62">
         <v>96</v>
       </c>
-      <c r="C198" s="52"/>
-      <c r="D198" s="84"/>
+      <c r="C198" s="54"/>
+      <c r="D198" s="56"/>
       <c r="E198" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G198" s="40"/>
       <c r="H198" s="31"/>
@@ -10378,18 +10378,18 @@
       <c r="AJ198" s="31"/>
       <c r="AK198" s="36"/>
       <c r="AL198" s="33"/>
-      <c r="AM198" s="54"/>
-      <c r="AN198" s="56"/>
+      <c r="AM198" s="58"/>
+      <c r="AN198" s="60"/>
     </row>
     <row r="199" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="86"/>
-      <c r="C199" s="83"/>
-      <c r="D199" s="85"/>
+      <c r="B199" s="63"/>
+      <c r="C199" s="55"/>
+      <c r="D199" s="57"/>
       <c r="E199" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G199" s="43"/>
       <c r="H199" s="32"/>
@@ -10423,20 +10423,20 @@
       <c r="AJ199" s="32"/>
       <c r="AK199" s="45"/>
       <c r="AL199" s="34"/>
-      <c r="AM199" s="55"/>
-      <c r="AN199" s="57"/>
+      <c r="AM199" s="59"/>
+      <c r="AN199" s="61"/>
     </row>
     <row r="200" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B200" s="81">
+      <c r="B200" s="52">
         <v>97</v>
       </c>
-      <c r="C200" s="52"/>
-      <c r="D200" s="84"/>
+      <c r="C200" s="54"/>
+      <c r="D200" s="56"/>
       <c r="E200" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G200" s="40"/>
       <c r="H200" s="31"/>
@@ -10470,18 +10470,18 @@
       <c r="AJ200" s="31"/>
       <c r="AK200" s="36"/>
       <c r="AL200" s="33"/>
-      <c r="AM200" s="54"/>
-      <c r="AN200" s="56"/>
+      <c r="AM200" s="58"/>
+      <c r="AN200" s="60"/>
     </row>
     <row r="201" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="82"/>
-      <c r="C201" s="83"/>
-      <c r="D201" s="85"/>
+      <c r="B201" s="53"/>
+      <c r="C201" s="55"/>
+      <c r="D201" s="57"/>
       <c r="E201" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G201" s="43"/>
       <c r="H201" s="32"/>
@@ -10515,20 +10515,20 @@
       <c r="AJ201" s="32"/>
       <c r="AK201" s="45"/>
       <c r="AL201" s="34"/>
-      <c r="AM201" s="55"/>
-      <c r="AN201" s="57"/>
+      <c r="AM201" s="59"/>
+      <c r="AN201" s="61"/>
     </row>
     <row r="202" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B202" s="75">
+      <c r="B202" s="62">
         <v>98</v>
       </c>
-      <c r="C202" s="52"/>
-      <c r="D202" s="84"/>
+      <c r="C202" s="54"/>
+      <c r="D202" s="56"/>
       <c r="E202" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F202" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G202" s="40"/>
       <c r="H202" s="31"/>
@@ -10562,18 +10562,18 @@
       <c r="AJ202" s="31"/>
       <c r="AK202" s="36"/>
       <c r="AL202" s="33"/>
-      <c r="AM202" s="54"/>
-      <c r="AN202" s="56"/>
+      <c r="AM202" s="58"/>
+      <c r="AN202" s="60"/>
     </row>
     <row r="203" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="86"/>
-      <c r="C203" s="83"/>
-      <c r="D203" s="85"/>
+      <c r="B203" s="63"/>
+      <c r="C203" s="55"/>
+      <c r="D203" s="57"/>
       <c r="E203" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F203" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G203" s="43"/>
       <c r="H203" s="32"/>
@@ -10607,20 +10607,20 @@
       <c r="AJ203" s="32"/>
       <c r="AK203" s="45"/>
       <c r="AL203" s="34"/>
-      <c r="AM203" s="55"/>
-      <c r="AN203" s="57"/>
+      <c r="AM203" s="59"/>
+      <c r="AN203" s="61"/>
     </row>
     <row r="204" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B204" s="81">
+      <c r="B204" s="52">
         <v>99</v>
       </c>
-      <c r="C204" s="52"/>
-      <c r="D204" s="84"/>
+      <c r="C204" s="54"/>
+      <c r="D204" s="56"/>
       <c r="E204" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F204" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G204" s="40"/>
       <c r="H204" s="31"/>
@@ -10654,18 +10654,18 @@
       <c r="AJ204" s="31"/>
       <c r="AK204" s="36"/>
       <c r="AL204" s="33"/>
-      <c r="AM204" s="54"/>
-      <c r="AN204" s="56"/>
+      <c r="AM204" s="58"/>
+      <c r="AN204" s="60"/>
     </row>
     <row r="205" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="82"/>
-      <c r="C205" s="83"/>
-      <c r="D205" s="85"/>
+      <c r="B205" s="53"/>
+      <c r="C205" s="55"/>
+      <c r="D205" s="57"/>
       <c r="E205" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F205" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G205" s="43"/>
       <c r="H205" s="32"/>
@@ -10699,20 +10699,20 @@
       <c r="AJ205" s="32"/>
       <c r="AK205" s="45"/>
       <c r="AL205" s="34"/>
-      <c r="AM205" s="55"/>
-      <c r="AN205" s="57"/>
+      <c r="AM205" s="59"/>
+      <c r="AN205" s="61"/>
     </row>
     <row r="206" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="75">
+      <c r="B206" s="62">
         <v>100</v>
       </c>
-      <c r="C206" s="52"/>
-      <c r="D206" s="84"/>
+      <c r="C206" s="54"/>
+      <c r="D206" s="56"/>
       <c r="E206" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F206" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G206" s="40"/>
       <c r="H206" s="31"/>
@@ -10746,18 +10746,18 @@
       <c r="AJ206" s="31"/>
       <c r="AK206" s="36"/>
       <c r="AL206" s="33"/>
-      <c r="AM206" s="54"/>
-      <c r="AN206" s="56"/>
+      <c r="AM206" s="58"/>
+      <c r="AN206" s="60"/>
     </row>
     <row r="207" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B207" s="86"/>
-      <c r="C207" s="83"/>
-      <c r="D207" s="85"/>
+      <c r="B207" s="63"/>
+      <c r="C207" s="55"/>
+      <c r="D207" s="57"/>
       <c r="E207" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F207" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G207" s="43"/>
       <c r="H207" s="32"/>
@@ -10791,8 +10791,8 @@
       <c r="AJ207" s="32"/>
       <c r="AK207" s="45"/>
       <c r="AL207" s="34"/>
-      <c r="AM207" s="55"/>
-      <c r="AN207" s="57"/>
+      <c r="AM207" s="59"/>
+      <c r="AN207" s="61"/>
     </row>
     <row r="208" spans="2:40" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="14"/>
@@ -10833,43 +10833,43 @@
     <row r="209" spans="2:41" s="13" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
-      <c r="D209" s="93"/>
-      <c r="E209" s="93"/>
-      <c r="F209" s="93"/>
-      <c r="G209" s="93"/>
-      <c r="H209" s="93"/>
-      <c r="I209" s="93"/>
-      <c r="J209" s="93"/>
-      <c r="K209" s="93"/>
-      <c r="L209" s="93"/>
-      <c r="M209" s="93"/>
-      <c r="N209" s="93"/>
-      <c r="O209" s="93"/>
-      <c r="P209" s="93"/>
-      <c r="Q209" s="93"/>
-      <c r="R209" s="93"/>
-      <c r="S209" s="93"/>
-      <c r="T209" s="93"/>
-      <c r="U209" s="93"/>
-      <c r="V209" s="93"/>
-      <c r="W209" s="93"/>
-      <c r="X209" s="93"/>
-      <c r="Y209" s="93"/>
-      <c r="Z209" s="93"/>
-      <c r="AA209" s="93"/>
-      <c r="AB209" s="93"/>
-      <c r="AC209" s="93"/>
-      <c r="AD209" s="93"/>
-      <c r="AE209" s="93"/>
-      <c r="AF209" s="93"/>
-      <c r="AG209" s="93"/>
-      <c r="AH209" s="93"/>
-      <c r="AI209" s="93"/>
-      <c r="AJ209" s="93"/>
-      <c r="AK209" s="93"/>
-      <c r="AL209" s="93"/>
-      <c r="AM209" s="93"/>
-      <c r="AN209" s="93"/>
+      <c r="D209" s="50"/>
+      <c r="E209" s="50"/>
+      <c r="F209" s="50"/>
+      <c r="G209" s="50"/>
+      <c r="H209" s="50"/>
+      <c r="I209" s="50"/>
+      <c r="J209" s="50"/>
+      <c r="K209" s="50"/>
+      <c r="L209" s="50"/>
+      <c r="M209" s="50"/>
+      <c r="N209" s="50"/>
+      <c r="O209" s="50"/>
+      <c r="P209" s="50"/>
+      <c r="Q209" s="50"/>
+      <c r="R209" s="50"/>
+      <c r="S209" s="50"/>
+      <c r="T209" s="50"/>
+      <c r="U209" s="50"/>
+      <c r="V209" s="50"/>
+      <c r="W209" s="50"/>
+      <c r="X209" s="50"/>
+      <c r="Y209" s="50"/>
+      <c r="Z209" s="50"/>
+      <c r="AA209" s="50"/>
+      <c r="AB209" s="50"/>
+      <c r="AC209" s="50"/>
+      <c r="AD209" s="50"/>
+      <c r="AE209" s="50"/>
+      <c r="AF209" s="50"/>
+      <c r="AG209" s="50"/>
+      <c r="AH209" s="50"/>
+      <c r="AI209" s="50"/>
+      <c r="AJ209" s="50"/>
+      <c r="AK209" s="50"/>
+      <c r="AL209" s="50"/>
+      <c r="AM209" s="50"/>
+      <c r="AN209" s="50"/>
     </row>
     <row r="210" spans="2:41" s="21" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B210" s="18"/>
@@ -10988,573 +10988,107 @@
     </row>
     <row r="213" spans="2:41" s="24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C213" s="25"/>
-      <c r="D213" s="94"/>
-      <c r="E213" s="94"/>
-      <c r="F213" s="94"/>
-      <c r="G213" s="94"/>
-      <c r="H213" s="94"/>
-      <c r="I213" s="94"/>
+      <c r="D213" s="51"/>
+      <c r="E213" s="51"/>
+      <c r="F213" s="51"/>
+      <c r="G213" s="51"/>
+      <c r="H213" s="51"/>
+      <c r="I213" s="51"/>
       <c r="J213" s="26"/>
       <c r="K213" s="26"/>
       <c r="L213" s="26"/>
       <c r="M213" s="26"/>
       <c r="N213" s="26"/>
-      <c r="O213" s="94"/>
-      <c r="P213" s="94"/>
-      <c r="Q213" s="94"/>
-      <c r="R213" s="94"/>
-      <c r="S213" s="94"/>
-      <c r="T213" s="94"/>
-      <c r="U213" s="94"/>
-      <c r="V213" s="94"/>
-      <c r="W213" s="94"/>
-      <c r="X213" s="94"/>
+      <c r="O213" s="51"/>
+      <c r="P213" s="51"/>
+      <c r="Q213" s="51"/>
+      <c r="R213" s="51"/>
+      <c r="S213" s="51"/>
+      <c r="T213" s="51"/>
+      <c r="U213" s="51"/>
+      <c r="V213" s="51"/>
+      <c r="W213" s="51"/>
+      <c r="X213" s="51"/>
       <c r="Y213" s="26"/>
       <c r="Z213" s="26"/>
       <c r="AA213" s="26"/>
       <c r="AB213" s="26"/>
-      <c r="AC213" s="94"/>
-      <c r="AD213" s="94"/>
-      <c r="AE213" s="94"/>
-      <c r="AF213" s="94"/>
-      <c r="AG213" s="94"/>
-      <c r="AH213" s="94"/>
-      <c r="AI213" s="94"/>
-      <c r="AJ213" s="94"/>
-      <c r="AK213" s="94"/>
-      <c r="AL213" s="94"/>
+      <c r="AC213" s="51"/>
+      <c r="AD213" s="51"/>
+      <c r="AE213" s="51"/>
+      <c r="AF213" s="51"/>
+      <c r="AG213" s="51"/>
+      <c r="AH213" s="51"/>
+      <c r="AI213" s="51"/>
+      <c r="AJ213" s="51"/>
+      <c r="AK213" s="51"/>
+      <c r="AL213" s="51"/>
       <c r="AM213" s="26"/>
       <c r="AN213" s="26"/>
       <c r="AO213" s="26"/>
     </row>
     <row r="214" spans="2:41" s="26" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="25"/>
-      <c r="D214" s="94"/>
-      <c r="E214" s="94"/>
-      <c r="F214" s="94"/>
-      <c r="G214" s="94"/>
-      <c r="H214" s="94"/>
-      <c r="I214" s="94"/>
-      <c r="O214" s="94"/>
-      <c r="P214" s="94"/>
-      <c r="Q214" s="94"/>
-      <c r="R214" s="94"/>
-      <c r="S214" s="94"/>
-      <c r="T214" s="94"/>
-      <c r="U214" s="94"/>
-      <c r="V214" s="94"/>
-      <c r="W214" s="94"/>
-      <c r="X214" s="94"/>
-      <c r="AC214" s="94"/>
-      <c r="AD214" s="94"/>
-      <c r="AE214" s="94"/>
-      <c r="AF214" s="94"/>
-      <c r="AG214" s="94"/>
-      <c r="AH214" s="94"/>
-      <c r="AI214" s="94"/>
-      <c r="AJ214" s="94"/>
-      <c r="AK214" s="94"/>
-      <c r="AL214" s="94"/>
+      <c r="D214" s="51"/>
+      <c r="E214" s="51"/>
+      <c r="F214" s="51"/>
+      <c r="G214" s="51"/>
+      <c r="H214" s="51"/>
+      <c r="I214" s="51"/>
+      <c r="O214" s="51"/>
+      <c r="P214" s="51"/>
+      <c r="Q214" s="51"/>
+      <c r="R214" s="51"/>
+      <c r="S214" s="51"/>
+      <c r="T214" s="51"/>
+      <c r="U214" s="51"/>
+      <c r="V214" s="51"/>
+      <c r="W214" s="51"/>
+      <c r="X214" s="51"/>
+      <c r="AC214" s="51"/>
+      <c r="AD214" s="51"/>
+      <c r="AE214" s="51"/>
+      <c r="AF214" s="51"/>
+      <c r="AG214" s="51"/>
+      <c r="AH214" s="51"/>
+      <c r="AI214" s="51"/>
+      <c r="AJ214" s="51"/>
+      <c r="AK214" s="51"/>
+      <c r="AL214" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="552">
-    <mergeCell ref="D209:AN209"/>
-    <mergeCell ref="D213:I213"/>
-    <mergeCell ref="O213:X213"/>
-    <mergeCell ref="AC213:AL213"/>
-    <mergeCell ref="D214:I214"/>
-    <mergeCell ref="O214:X214"/>
-    <mergeCell ref="AC214:AL214"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="D204:D205"/>
-    <mergeCell ref="AM204:AM205"/>
-    <mergeCell ref="AN204:AN205"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="AM206:AM207"/>
-    <mergeCell ref="AN206:AN207"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="D200:D201"/>
-    <mergeCell ref="AM200:AM201"/>
-    <mergeCell ref="AN200:AN201"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="AM202:AM203"/>
-    <mergeCell ref="AN202:AN203"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="AM196:AM197"/>
-    <mergeCell ref="AN196:AN197"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="AM198:AM199"/>
-    <mergeCell ref="AN198:AN199"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="D192:D193"/>
-    <mergeCell ref="AM192:AM193"/>
-    <mergeCell ref="AN192:AN193"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="C194:C195"/>
-    <mergeCell ref="D194:D195"/>
-    <mergeCell ref="AM194:AM195"/>
-    <mergeCell ref="AN194:AN195"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="D188:D189"/>
-    <mergeCell ref="AM188:AM189"/>
-    <mergeCell ref="AN188:AN189"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="D190:D191"/>
-    <mergeCell ref="AM190:AM191"/>
-    <mergeCell ref="AN190:AN191"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="AM184:AM185"/>
-    <mergeCell ref="AN184:AN185"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="AM186:AM187"/>
-    <mergeCell ref="AN186:AN187"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="D180:D181"/>
-    <mergeCell ref="AM180:AM181"/>
-    <mergeCell ref="AN180:AN181"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="D182:D183"/>
-    <mergeCell ref="AM182:AM183"/>
-    <mergeCell ref="AN182:AN183"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="D176:D177"/>
-    <mergeCell ref="AM176:AM177"/>
-    <mergeCell ref="AN176:AN177"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="D178:D179"/>
-    <mergeCell ref="AM178:AM179"/>
-    <mergeCell ref="AN178:AN179"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="AM172:AM173"/>
-    <mergeCell ref="AN172:AN173"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="AM174:AM175"/>
-    <mergeCell ref="AN174:AN175"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="D168:D169"/>
-    <mergeCell ref="AM168:AM169"/>
-    <mergeCell ref="AN168:AN169"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="AM170:AM171"/>
-    <mergeCell ref="AN170:AN171"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="AM164:AM165"/>
-    <mergeCell ref="AN164:AN165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="AM166:AM167"/>
-    <mergeCell ref="AN166:AN167"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="AM160:AM161"/>
-    <mergeCell ref="AN160:AN161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="D162:D163"/>
-    <mergeCell ref="AM162:AM163"/>
-    <mergeCell ref="AN162:AN163"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="D156:D157"/>
-    <mergeCell ref="AM156:AM157"/>
-    <mergeCell ref="AN156:AN157"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="AM158:AM159"/>
-    <mergeCell ref="AN158:AN159"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="AM152:AM153"/>
-    <mergeCell ref="AN152:AN153"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="AM154:AM155"/>
-    <mergeCell ref="AN154:AN155"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="AM148:AM149"/>
-    <mergeCell ref="AN148:AN149"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="AM150:AM151"/>
-    <mergeCell ref="AN150:AN151"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="AM144:AM145"/>
-    <mergeCell ref="AN144:AN145"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="AM146:AM147"/>
-    <mergeCell ref="AN146:AN147"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="AM140:AM141"/>
-    <mergeCell ref="AN140:AN141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="AM142:AM143"/>
-    <mergeCell ref="AN142:AN143"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="AM136:AM137"/>
-    <mergeCell ref="AN136:AN137"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="AM138:AM139"/>
-    <mergeCell ref="AN138:AN139"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:D133"/>
-    <mergeCell ref="AM132:AM133"/>
-    <mergeCell ref="AN132:AN133"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:D135"/>
-    <mergeCell ref="AM134:AM135"/>
-    <mergeCell ref="AN134:AN135"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="AM128:AM129"/>
-    <mergeCell ref="AN128:AN129"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="AM130:AM131"/>
-    <mergeCell ref="AN130:AN131"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="AM124:AM125"/>
-    <mergeCell ref="AN124:AN125"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="AM126:AM127"/>
-    <mergeCell ref="AN126:AN127"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="AM120:AM121"/>
-    <mergeCell ref="AN120:AN121"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="D122:D123"/>
-    <mergeCell ref="AM122:AM123"/>
-    <mergeCell ref="AN122:AN123"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="AM116:AM117"/>
-    <mergeCell ref="AN116:AN117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="AM118:AM119"/>
-    <mergeCell ref="AN118:AN119"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="AM112:AM113"/>
-    <mergeCell ref="AN112:AN113"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="AM114:AM115"/>
-    <mergeCell ref="AN114:AN115"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="AM108:AM109"/>
-    <mergeCell ref="AN108:AN109"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="D110:D111"/>
-    <mergeCell ref="AM110:AM111"/>
-    <mergeCell ref="AN110:AN111"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="AM104:AM105"/>
-    <mergeCell ref="AN104:AN105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="AM106:AM107"/>
-    <mergeCell ref="AN106:AN107"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="AM100:AM101"/>
-    <mergeCell ref="AN100:AN101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="AM102:AM103"/>
-    <mergeCell ref="AN102:AN103"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="AM96:AM97"/>
-    <mergeCell ref="AN96:AN97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="AM98:AM99"/>
-    <mergeCell ref="AN98:AN99"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="AM92:AM93"/>
-    <mergeCell ref="AN92:AN93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="AM94:AM95"/>
-    <mergeCell ref="AN94:AN95"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="AM88:AM89"/>
-    <mergeCell ref="AN88:AN89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="AM90:AM91"/>
-    <mergeCell ref="AN90:AN91"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="AM84:AM85"/>
-    <mergeCell ref="AN84:AN85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="AM86:AM87"/>
-    <mergeCell ref="AN86:AN87"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="AM80:AM81"/>
-    <mergeCell ref="AN80:AN81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="AM82:AM83"/>
-    <mergeCell ref="AN82:AN83"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="AM76:AM77"/>
-    <mergeCell ref="AN76:AN77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="AM78:AM79"/>
-    <mergeCell ref="AN78:AN79"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="AM72:AM73"/>
-    <mergeCell ref="AN72:AN73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="AM74:AM75"/>
-    <mergeCell ref="AN74:AN75"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="AM68:AM69"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="AM70:AM71"/>
-    <mergeCell ref="AN70:AN71"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="AM64:AM65"/>
-    <mergeCell ref="AN64:AN65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="AM66:AM67"/>
-    <mergeCell ref="AN66:AN67"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="AM60:AM61"/>
-    <mergeCell ref="AN60:AN61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="AM62:AM63"/>
-    <mergeCell ref="AN62:AN63"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="AM56:AM57"/>
-    <mergeCell ref="AN56:AN57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="AM58:AM59"/>
-    <mergeCell ref="AN58:AN59"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="AM52:AM53"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="AM54:AM55"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="AM48:AM49"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="AM50:AM51"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="AM44:AM45"/>
-    <mergeCell ref="AN44:AN45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="AM46:AM47"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="AM40:AM41"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="AM42:AM43"/>
-    <mergeCell ref="AN42:AN43"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="AM36:AM37"/>
-    <mergeCell ref="AN36:AN37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="AM38:AM39"/>
-    <mergeCell ref="AN38:AN39"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="AM32:AM33"/>
-    <mergeCell ref="AN32:AN33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="AM34:AM35"/>
-    <mergeCell ref="AN34:AN35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="AM28:AM29"/>
-    <mergeCell ref="AN28:AN29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="AM30:AM31"/>
-    <mergeCell ref="AN30:AN31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="AM24:AM25"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="AM26:AM27"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="AM20:AM21"/>
-    <mergeCell ref="AN20:AN21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="AM22:AM23"/>
-    <mergeCell ref="AN22:AN23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="AM16:AM17"/>
-    <mergeCell ref="AN16:AN17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="AM18:AM19"/>
-    <mergeCell ref="AN18:AN19"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="AM12:AM13"/>
-    <mergeCell ref="AN12:AN13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="AM14:AM15"/>
-    <mergeCell ref="AN14:AN15"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="B1:AN1"/>
+    <mergeCell ref="B2:AN2"/>
+    <mergeCell ref="B3:AN3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="O5:AK5"/>
+    <mergeCell ref="AL5:AL7"/>
+    <mergeCell ref="AM5:AM7"/>
+    <mergeCell ref="AN5:AN7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
@@ -11579,37 +11113,503 @@
     <mergeCell ref="X6:X7"/>
     <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="P6:P7"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="B1:AN1"/>
-    <mergeCell ref="B2:AN2"/>
-    <mergeCell ref="B3:AN3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="O5:AK5"/>
-    <mergeCell ref="AL5:AL7"/>
-    <mergeCell ref="AM5:AM7"/>
-    <mergeCell ref="AN5:AN7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="AM12:AM13"/>
+    <mergeCell ref="AN12:AN13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="AM14:AM15"/>
+    <mergeCell ref="AN14:AN15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="AM16:AM17"/>
+    <mergeCell ref="AN16:AN17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="AM18:AM19"/>
+    <mergeCell ref="AN18:AN19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="AM20:AM21"/>
+    <mergeCell ref="AN20:AN21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="AM22:AM23"/>
+    <mergeCell ref="AN22:AN23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="AM24:AM25"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="AM26:AM27"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="AM28:AM29"/>
+    <mergeCell ref="AN28:AN29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="AM30:AM31"/>
+    <mergeCell ref="AN30:AN31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="AM32:AM33"/>
+    <mergeCell ref="AN32:AN33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="AM34:AM35"/>
+    <mergeCell ref="AN34:AN35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="AM36:AM37"/>
+    <mergeCell ref="AN36:AN37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="AM38:AM39"/>
+    <mergeCell ref="AN38:AN39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="AM40:AM41"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="AM42:AM43"/>
+    <mergeCell ref="AN42:AN43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="AM44:AM45"/>
+    <mergeCell ref="AN44:AN45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="AM46:AM47"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="AM48:AM49"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="AM50:AM51"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="AM52:AM53"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="AM54:AM55"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="AM56:AM57"/>
+    <mergeCell ref="AN56:AN57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="AM58:AM59"/>
+    <mergeCell ref="AN58:AN59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="AM60:AM61"/>
+    <mergeCell ref="AN60:AN61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="AM62:AM63"/>
+    <mergeCell ref="AN62:AN63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="AM64:AM65"/>
+    <mergeCell ref="AN64:AN65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="AM66:AM67"/>
+    <mergeCell ref="AN66:AN67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="AM68:AM69"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="AM70:AM71"/>
+    <mergeCell ref="AN70:AN71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="AM72:AM73"/>
+    <mergeCell ref="AN72:AN73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="AM74:AM75"/>
+    <mergeCell ref="AN74:AN75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="AM76:AM77"/>
+    <mergeCell ref="AN76:AN77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="AM78:AM79"/>
+    <mergeCell ref="AN78:AN79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="AM80:AM81"/>
+    <mergeCell ref="AN80:AN81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="AM82:AM83"/>
+    <mergeCell ref="AN82:AN83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="AM84:AM85"/>
+    <mergeCell ref="AN84:AN85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="AM86:AM87"/>
+    <mergeCell ref="AN86:AN87"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="AM88:AM89"/>
+    <mergeCell ref="AN88:AN89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="AM90:AM91"/>
+    <mergeCell ref="AN90:AN91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="AM92:AM93"/>
+    <mergeCell ref="AN92:AN93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="AM94:AM95"/>
+    <mergeCell ref="AN94:AN95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="AM96:AM97"/>
+    <mergeCell ref="AN96:AN97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="AM98:AM99"/>
+    <mergeCell ref="AN98:AN99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="AM100:AM101"/>
+    <mergeCell ref="AN100:AN101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="AM102:AM103"/>
+    <mergeCell ref="AN102:AN103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="AM104:AM105"/>
+    <mergeCell ref="AN104:AN105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="AM106:AM107"/>
+    <mergeCell ref="AN106:AN107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="AM108:AM109"/>
+    <mergeCell ref="AN108:AN109"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="AM110:AM111"/>
+    <mergeCell ref="AN110:AN111"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="AM112:AM113"/>
+    <mergeCell ref="AN112:AN113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="AM114:AM115"/>
+    <mergeCell ref="AN114:AN115"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="AM116:AM117"/>
+    <mergeCell ref="AN116:AN117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="AM118:AM119"/>
+    <mergeCell ref="AN118:AN119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="AM120:AM121"/>
+    <mergeCell ref="AN120:AN121"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="D122:D123"/>
+    <mergeCell ref="AM122:AM123"/>
+    <mergeCell ref="AN122:AN123"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="AM124:AM125"/>
+    <mergeCell ref="AN124:AN125"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="AM126:AM127"/>
+    <mergeCell ref="AN126:AN127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="AM128:AM129"/>
+    <mergeCell ref="AN128:AN129"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="AM130:AM131"/>
+    <mergeCell ref="AN130:AN131"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="AM132:AM133"/>
+    <mergeCell ref="AN132:AN133"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="AM134:AM135"/>
+    <mergeCell ref="AN134:AN135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="AM136:AM137"/>
+    <mergeCell ref="AN136:AN137"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="AM138:AM139"/>
+    <mergeCell ref="AN138:AN139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="AM140:AM141"/>
+    <mergeCell ref="AN140:AN141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="AM142:AM143"/>
+    <mergeCell ref="AN142:AN143"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="AM144:AM145"/>
+    <mergeCell ref="AN144:AN145"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="AM146:AM147"/>
+    <mergeCell ref="AN146:AN147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="AM148:AM149"/>
+    <mergeCell ref="AN148:AN149"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="AM150:AM151"/>
+    <mergeCell ref="AN150:AN151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="AM152:AM153"/>
+    <mergeCell ref="AN152:AN153"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="AM154:AM155"/>
+    <mergeCell ref="AN154:AN155"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="D156:D157"/>
+    <mergeCell ref="AM156:AM157"/>
+    <mergeCell ref="AN156:AN157"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="AM158:AM159"/>
+    <mergeCell ref="AN158:AN159"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="AM160:AM161"/>
+    <mergeCell ref="AN160:AN161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="AM162:AM163"/>
+    <mergeCell ref="AN162:AN163"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="AM164:AM165"/>
+    <mergeCell ref="AN164:AN165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="AM166:AM167"/>
+    <mergeCell ref="AN166:AN167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="D168:D169"/>
+    <mergeCell ref="AM168:AM169"/>
+    <mergeCell ref="AN168:AN169"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="D170:D171"/>
+    <mergeCell ref="AM170:AM171"/>
+    <mergeCell ref="AN170:AN171"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="AM172:AM173"/>
+    <mergeCell ref="AN172:AN173"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="AM174:AM175"/>
+    <mergeCell ref="AN174:AN175"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="D176:D177"/>
+    <mergeCell ref="AM176:AM177"/>
+    <mergeCell ref="AN176:AN177"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="D178:D179"/>
+    <mergeCell ref="AM178:AM179"/>
+    <mergeCell ref="AN178:AN179"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="D180:D181"/>
+    <mergeCell ref="AM180:AM181"/>
+    <mergeCell ref="AN180:AN181"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="D182:D183"/>
+    <mergeCell ref="AM182:AM183"/>
+    <mergeCell ref="AN182:AN183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="AM184:AM185"/>
+    <mergeCell ref="AN184:AN185"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="AM186:AM187"/>
+    <mergeCell ref="AN186:AN187"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="D188:D189"/>
+    <mergeCell ref="AM188:AM189"/>
+    <mergeCell ref="AN188:AN189"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="AM190:AM191"/>
+    <mergeCell ref="AN190:AN191"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="D192:D193"/>
+    <mergeCell ref="AM192:AM193"/>
+    <mergeCell ref="AN192:AN193"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="C194:C195"/>
+    <mergeCell ref="D194:D195"/>
+    <mergeCell ref="AM194:AM195"/>
+    <mergeCell ref="AN194:AN195"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="AM196:AM197"/>
+    <mergeCell ref="AN196:AN197"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="AM198:AM199"/>
+    <mergeCell ref="AN198:AN199"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="D200:D201"/>
+    <mergeCell ref="AM200:AM201"/>
+    <mergeCell ref="AN200:AN201"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="AM202:AM203"/>
+    <mergeCell ref="AN202:AN203"/>
+    <mergeCell ref="D209:AN209"/>
+    <mergeCell ref="D213:I213"/>
+    <mergeCell ref="O213:X213"/>
+    <mergeCell ref="AC213:AL213"/>
+    <mergeCell ref="D214:I214"/>
+    <mergeCell ref="O214:X214"/>
+    <mergeCell ref="AC214:AL214"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
+    <mergeCell ref="AM204:AM205"/>
+    <mergeCell ref="AN204:AN205"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="AM206:AM207"/>
+    <mergeCell ref="AN206:AN207"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="76" orientation="landscape" r:id="rId1"/>

--- a/Toplu_Mesai_Sablon.xlsx
+++ b/Toplu_Mesai_Sablon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mehmet.tuzner\Documents\Mesai Programı APK\web-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAAC15E-4E3F-4AF2-B36D-80E1C44FC38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7685422-AD76-45F2-AC20-8C61DCEED7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2DF94309-6D47-4284-9046-50F652E00677}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2DF94309-6D47-4284-9046-50F652E00677}"/>
   </bookViews>
   <sheets>
     <sheet name="MESAİ ÇİZLG" sheetId="1" r:id="rId1"/>
@@ -699,11 +699,29 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -715,6 +733,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -732,16 +810,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -756,19 +831,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -780,73 +846,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1165,8 +1165,7 @@
     <col min="7" max="7" width="4.28515625" style="28" customWidth="1"/>
     <col min="8" max="9" width="4.28515625" style="29" customWidth="1"/>
     <col min="10" max="14" width="4.28515625" style="28" customWidth="1"/>
-    <col min="15" max="15" width="5" style="29" customWidth="1"/>
-    <col min="16" max="19" width="4.28515625" style="29" customWidth="1"/>
+    <col min="15" max="19" width="4.28515625" style="29" customWidth="1"/>
     <col min="20" max="35" width="4.28515625" style="28" customWidth="1"/>
     <col min="36" max="37" width="4.28515625" style="30" customWidth="1"/>
     <col min="38" max="38" width="9.85546875" style="30" customWidth="1"/>
@@ -1176,133 +1175,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
-      <c r="AC1" s="53"/>
-      <c r="AD1" s="53"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
+      <c r="Z1" s="79"/>
+      <c r="AA1" s="79"/>
+      <c r="AB1" s="79"/>
+      <c r="AC1" s="79"/>
+      <c r="AD1" s="79"/>
+      <c r="AE1" s="79"/>
+      <c r="AF1" s="79"/>
+      <c r="AG1" s="79"/>
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="79"/>
     </row>
     <row r="2" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
-      <c r="AL2" s="53"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="53"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="79"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="79"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
+      <c r="AF2" s="79"/>
+      <c r="AG2" s="79"/>
+      <c r="AH2" s="79"/>
+      <c r="AI2" s="79"/>
+      <c r="AJ2" s="79"/>
+      <c r="AK2" s="79"/>
+      <c r="AL2" s="79"/>
+      <c r="AM2" s="79"/>
+      <c r="AN2" s="79"/>
     </row>
     <row r="3" spans="2:40" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53"/>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="53"/>
-      <c r="AN3" s="53"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="79"/>
+      <c r="Y3" s="79"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="79"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="79"/>
+      <c r="AF3" s="79"/>
+      <c r="AG3" s="79"/>
+      <c r="AH3" s="79"/>
+      <c r="AI3" s="79"/>
+      <c r="AJ3" s="79"/>
+      <c r="AK3" s="79"/>
+      <c r="AL3" s="79"/>
+      <c r="AM3" s="79"/>
+      <c r="AN3" s="79"/>
     </row>
     <row r="4" spans="2:40" s="5" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
@@ -1342,212 +1341,212 @@
       <c r="AJ4" s="4"/>
     </row>
     <row r="5" spans="2:40" s="6" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="61"/>
-      <c r="AL5" s="62" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="51"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="51"/>
+      <c r="AB5" s="51"/>
+      <c r="AC5" s="51"/>
+      <c r="AD5" s="51"/>
+      <c r="AE5" s="51"/>
+      <c r="AF5" s="51"/>
+      <c r="AG5" s="51"/>
+      <c r="AH5" s="51"/>
+      <c r="AI5" s="51"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="75"/>
+      <c r="AL5" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="AM5" s="51" t="s">
+      <c r="AM5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="AN5" s="51" t="s">
+      <c r="AN5" s="57" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:40" s="6" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="75"/>
-      <c r="G6" s="76">
+      <c r="F6" s="96"/>
+      <c r="G6" s="86">
         <v>24</v>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="51">
         <v>25</v>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="51">
         <v>26</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="51">
         <v>27</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="63">
         <v>28</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="63">
         <v>29</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="63">
         <v>30</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="85">
         <v>31</v>
       </c>
-      <c r="O6" s="76">
+      <c r="O6" s="86">
         <v>1</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="51">
         <v>2</v>
       </c>
-      <c r="Q6" s="47">
+      <c r="Q6" s="51">
         <v>3</v>
       </c>
-      <c r="R6" s="47">
+      <c r="R6" s="51">
         <v>4</v>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="51">
         <v>5</v>
       </c>
-      <c r="T6" s="47">
+      <c r="T6" s="51">
         <v>6</v>
       </c>
-      <c r="U6" s="47">
+      <c r="U6" s="51">
         <v>7</v>
       </c>
-      <c r="V6" s="47">
+      <c r="V6" s="51">
         <v>8</v>
       </c>
-      <c r="W6" s="47">
+      <c r="W6" s="51">
         <v>9</v>
       </c>
-      <c r="X6" s="47">
+      <c r="X6" s="51">
         <v>10</v>
       </c>
-      <c r="Y6" s="47">
-        <v>11</v>
-      </c>
-      <c r="Z6" s="47">
+      <c r="Y6" s="51">
+        <v>11</v>
+      </c>
+      <c r="Z6" s="51">
         <v>12</v>
       </c>
-      <c r="AA6" s="47">
+      <c r="AA6" s="51">
         <v>13</v>
       </c>
-      <c r="AB6" s="47">
+      <c r="AB6" s="51">
         <v>14</v>
       </c>
-      <c r="AC6" s="47">
+      <c r="AC6" s="51">
         <v>15</v>
       </c>
-      <c r="AD6" s="47">
+      <c r="AD6" s="51">
         <v>16</v>
       </c>
-      <c r="AE6" s="47">
+      <c r="AE6" s="51">
         <v>17</v>
       </c>
-      <c r="AF6" s="47">
+      <c r="AF6" s="51">
         <v>18</v>
       </c>
-      <c r="AG6" s="47">
+      <c r="AG6" s="51">
         <v>19</v>
       </c>
-      <c r="AH6" s="47">
+      <c r="AH6" s="51">
         <v>20</v>
       </c>
-      <c r="AI6" s="47">
+      <c r="AI6" s="51">
         <v>21</v>
       </c>
-      <c r="AJ6" s="47">
+      <c r="AJ6" s="51">
         <v>22</v>
       </c>
-      <c r="AK6" s="61">
+      <c r="AK6" s="75">
         <v>23</v>
       </c>
-      <c r="AL6" s="63"/>
-      <c r="AM6" s="65"/>
-      <c r="AN6" s="65"/>
+      <c r="AL6" s="88"/>
+      <c r="AM6" s="90"/>
+      <c r="AN6" s="90"/>
     </row>
     <row r="7" spans="2:40" s="6" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="68"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="84"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="48"/>
-      <c r="X7" s="48"/>
-      <c r="Y7" s="48"/>
-      <c r="Z7" s="48"/>
-      <c r="AA7" s="48"/>
-      <c r="AB7" s="48"/>
-      <c r="AC7" s="48"/>
-      <c r="AD7" s="48"/>
-      <c r="AE7" s="48"/>
-      <c r="AF7" s="48"/>
-      <c r="AG7" s="48"/>
-      <c r="AH7" s="48"/>
-      <c r="AI7" s="48"/>
-      <c r="AJ7" s="48"/>
-      <c r="AK7" s="83"/>
-      <c r="AL7" s="64"/>
-      <c r="AM7" s="66"/>
-      <c r="AN7" s="66"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="67"/>
+      <c r="Z7" s="67"/>
+      <c r="AA7" s="67"/>
+      <c r="AB7" s="67"/>
+      <c r="AC7" s="67"/>
+      <c r="AD7" s="67"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="76"/>
+      <c r="AL7" s="89"/>
+      <c r="AM7" s="70"/>
+      <c r="AN7" s="70"/>
     </row>
     <row r="8" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="67">
+      <c r="B8" s="49">
         <v>1</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="86"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="53"/>
       <c r="E8" s="7" t="s">
         <v>10</v>
       </c>
@@ -1586,13 +1585,13 @@
       <c r="AJ8" s="31"/>
       <c r="AK8" s="36"/>
       <c r="AL8" s="33"/>
-      <c r="AM8" s="49"/>
-      <c r="AN8" s="51"/>
+      <c r="AM8" s="55"/>
+      <c r="AN8" s="57"/>
     </row>
     <row r="9" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="68"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="87"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="9" t="s">
         <v>12</v>
       </c>
@@ -1631,15 +1630,15 @@
       <c r="AJ9" s="32"/>
       <c r="AK9" s="43"/>
       <c r="AL9" s="34"/>
-      <c r="AM9" s="50"/>
-      <c r="AN9" s="52"/>
+      <c r="AM9" s="56"/>
+      <c r="AN9" s="58"/>
     </row>
     <row r="10" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="78">
+      <c r="B10" s="59">
         <v>2</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="80"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="72"/>
       <c r="E10" s="7" t="s">
         <v>10</v>
       </c>
@@ -1678,13 +1677,13 @@
       <c r="AJ10" s="31"/>
       <c r="AK10" s="36"/>
       <c r="AL10" s="33"/>
-      <c r="AM10" s="49"/>
-      <c r="AN10" s="51"/>
+      <c r="AM10" s="55"/>
+      <c r="AN10" s="57"/>
     </row>
     <row r="11" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="79"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="81"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="73"/>
       <c r="E11" s="11" t="s">
         <v>12</v>
       </c>
@@ -1723,15 +1722,15 @@
       <c r="AJ11" s="35"/>
       <c r="AK11" s="37"/>
       <c r="AL11" s="34"/>
-      <c r="AM11" s="82"/>
-      <c r="AN11" s="66"/>
+      <c r="AM11" s="69"/>
+      <c r="AN11" s="70"/>
     </row>
     <row r="12" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="67">
+      <c r="B12" s="49">
         <v>3</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="86"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
@@ -1770,13 +1769,13 @@
       <c r="AJ12" s="31"/>
       <c r="AK12" s="36"/>
       <c r="AL12" s="33"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="51"/>
+      <c r="AM12" s="55"/>
+      <c r="AN12" s="57"/>
     </row>
     <row r="13" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="68"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="87"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="54"/>
       <c r="E13" s="9" t="s">
         <v>12</v>
       </c>
@@ -1815,15 +1814,15 @@
       <c r="AJ13" s="32"/>
       <c r="AK13" s="43"/>
       <c r="AL13" s="34"/>
-      <c r="AM13" s="50"/>
-      <c r="AN13" s="52"/>
+      <c r="AM13" s="56"/>
+      <c r="AN13" s="58"/>
     </row>
     <row r="14" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="78">
+      <c r="B14" s="59">
         <v>4</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="86"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="7" t="s">
         <v>10</v>
       </c>
@@ -1862,13 +1861,13 @@
       <c r="AJ14" s="31"/>
       <c r="AK14" s="36"/>
       <c r="AL14" s="33"/>
-      <c r="AM14" s="49"/>
-      <c r="AN14" s="51"/>
+      <c r="AM14" s="55"/>
+      <c r="AN14" s="57"/>
     </row>
     <row r="15" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="88"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="87"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="54"/>
       <c r="E15" s="9" t="s">
         <v>12</v>
       </c>
@@ -1907,15 +1906,15 @@
       <c r="AJ15" s="32"/>
       <c r="AK15" s="43"/>
       <c r="AL15" s="34"/>
-      <c r="AM15" s="50"/>
-      <c r="AN15" s="52"/>
+      <c r="AM15" s="56"/>
+      <c r="AN15" s="58"/>
     </row>
     <row r="16" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="67">
+      <c r="B16" s="49">
         <v>5</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="89"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="7" t="s">
         <v>10</v>
       </c>
@@ -1954,13 +1953,13 @@
       <c r="AJ16" s="31"/>
       <c r="AK16" s="36"/>
       <c r="AL16" s="33"/>
-      <c r="AM16" s="49"/>
-      <c r="AN16" s="51"/>
+      <c r="AM16" s="55"/>
+      <c r="AN16" s="57"/>
     </row>
     <row r="17" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="68"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="90"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="9" t="s">
         <v>12</v>
       </c>
@@ -1999,15 +1998,15 @@
       <c r="AJ17" s="32"/>
       <c r="AK17" s="43"/>
       <c r="AL17" s="34"/>
-      <c r="AM17" s="50"/>
-      <c r="AN17" s="52"/>
+      <c r="AM17" s="56"/>
+      <c r="AN17" s="58"/>
     </row>
     <row r="18" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="78">
+      <c r="B18" s="59">
         <v>6</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="89"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="61"/>
       <c r="E18" s="7" t="s">
         <v>10</v>
       </c>
@@ -2046,13 +2045,13 @@
       <c r="AJ18" s="31"/>
       <c r="AK18" s="36"/>
       <c r="AL18" s="33"/>
-      <c r="AM18" s="49"/>
-      <c r="AN18" s="51"/>
+      <c r="AM18" s="55"/>
+      <c r="AN18" s="57"/>
     </row>
     <row r="19" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="88"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="90"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="9" t="s">
         <v>12</v>
       </c>
@@ -2091,15 +2090,15 @@
       <c r="AJ19" s="32"/>
       <c r="AK19" s="43"/>
       <c r="AL19" s="34"/>
-      <c r="AM19" s="50"/>
-      <c r="AN19" s="52"/>
+      <c r="AM19" s="56"/>
+      <c r="AN19" s="58"/>
     </row>
     <row r="20" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="67">
+      <c r="B20" s="49">
         <v>7</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="89"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="61"/>
       <c r="E20" s="7" t="s">
         <v>10</v>
       </c>
@@ -2138,13 +2137,13 @@
       <c r="AJ20" s="31"/>
       <c r="AK20" s="36"/>
       <c r="AL20" s="33"/>
-      <c r="AM20" s="49"/>
-      <c r="AN20" s="51"/>
+      <c r="AM20" s="55"/>
+      <c r="AN20" s="57"/>
     </row>
     <row r="21" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="68"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="90"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="9" t="s">
         <v>12</v>
       </c>
@@ -2183,15 +2182,15 @@
       <c r="AJ21" s="32"/>
       <c r="AK21" s="43"/>
       <c r="AL21" s="34"/>
-      <c r="AM21" s="50"/>
-      <c r="AN21" s="52"/>
+      <c r="AM21" s="56"/>
+      <c r="AN21" s="58"/>
     </row>
     <row r="22" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="78">
+      <c r="B22" s="59">
         <v>8</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="86"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="53"/>
       <c r="E22" s="7" t="s">
         <v>10</v>
       </c>
@@ -2230,13 +2229,13 @@
       <c r="AJ22" s="31"/>
       <c r="AK22" s="36"/>
       <c r="AL22" s="33"/>
-      <c r="AM22" s="49"/>
-      <c r="AN22" s="51"/>
+      <c r="AM22" s="55"/>
+      <c r="AN22" s="57"/>
     </row>
     <row r="23" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="88"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="87"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="54"/>
       <c r="E23" s="9" t="s">
         <v>12</v>
       </c>
@@ -2275,15 +2274,15 @@
       <c r="AJ23" s="32"/>
       <c r="AK23" s="43"/>
       <c r="AL23" s="34"/>
-      <c r="AM23" s="50"/>
-      <c r="AN23" s="52"/>
+      <c r="AM23" s="56"/>
+      <c r="AN23" s="58"/>
     </row>
     <row r="24" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="67">
+      <c r="B24" s="49">
         <v>9</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="89"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="7" t="s">
         <v>10</v>
       </c>
@@ -2322,13 +2321,13 @@
       <c r="AJ24" s="31"/>
       <c r="AK24" s="36"/>
       <c r="AL24" s="33"/>
-      <c r="AM24" s="49"/>
-      <c r="AN24" s="51"/>
+      <c r="AM24" s="55"/>
+      <c r="AN24" s="57"/>
     </row>
     <row r="25" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="68"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="90"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="9" t="s">
         <v>12</v>
       </c>
@@ -2367,15 +2366,15 @@
       <c r="AJ25" s="32"/>
       <c r="AK25" s="43"/>
       <c r="AL25" s="34"/>
-      <c r="AM25" s="50"/>
-      <c r="AN25" s="52"/>
+      <c r="AM25" s="56"/>
+      <c r="AN25" s="58"/>
     </row>
     <row r="26" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="78">
+      <c r="B26" s="59">
         <v>10</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="86"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="53"/>
       <c r="E26" s="7" t="s">
         <v>10</v>
       </c>
@@ -2414,13 +2413,13 @@
       <c r="AJ26" s="31"/>
       <c r="AK26" s="36"/>
       <c r="AL26" s="33"/>
-      <c r="AM26" s="49"/>
-      <c r="AN26" s="51"/>
+      <c r="AM26" s="55"/>
+      <c r="AN26" s="57"/>
     </row>
     <row r="27" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="79"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="91"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="68"/>
       <c r="E27" s="11" t="s">
         <v>12</v>
       </c>
@@ -2459,15 +2458,15 @@
       <c r="AJ27" s="35"/>
       <c r="AK27" s="37"/>
       <c r="AL27" s="34"/>
-      <c r="AM27" s="82"/>
-      <c r="AN27" s="66"/>
+      <c r="AM27" s="69"/>
+      <c r="AN27" s="70"/>
     </row>
     <row r="28" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="67">
-        <v>11</v>
-      </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="86"/>
+      <c r="B28" s="49">
+        <v>11</v>
+      </c>
+      <c r="C28" s="51"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="7" t="s">
         <v>10</v>
       </c>
@@ -2506,13 +2505,13 @@
       <c r="AJ28" s="31"/>
       <c r="AK28" s="36"/>
       <c r="AL28" s="33"/>
-      <c r="AM28" s="49"/>
-      <c r="AN28" s="51"/>
+      <c r="AM28" s="55"/>
+      <c r="AN28" s="57"/>
     </row>
     <row r="29" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="68"/>
-      <c r="C29" s="85"/>
-      <c r="D29" s="87"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="54"/>
       <c r="E29" s="9" t="s">
         <v>12</v>
       </c>
@@ -2551,15 +2550,15 @@
       <c r="AJ29" s="32"/>
       <c r="AK29" s="43"/>
       <c r="AL29" s="34"/>
-      <c r="AM29" s="50"/>
-      <c r="AN29" s="52"/>
+      <c r="AM29" s="56"/>
+      <c r="AN29" s="58"/>
     </row>
     <row r="30" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="78">
+      <c r="B30" s="59">
         <v>12</v>
       </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="86"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="7" t="s">
         <v>10</v>
       </c>
@@ -2598,13 +2597,13 @@
       <c r="AJ30" s="31"/>
       <c r="AK30" s="36"/>
       <c r="AL30" s="33"/>
-      <c r="AM30" s="49"/>
-      <c r="AN30" s="51"/>
+      <c r="AM30" s="55"/>
+      <c r="AN30" s="57"/>
     </row>
     <row r="31" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="88"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="87"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="54"/>
       <c r="E31" s="9" t="s">
         <v>12</v>
       </c>
@@ -2643,15 +2642,15 @@
       <c r="AJ31" s="32"/>
       <c r="AK31" s="43"/>
       <c r="AL31" s="34"/>
-      <c r="AM31" s="50"/>
-      <c r="AN31" s="52"/>
+      <c r="AM31" s="56"/>
+      <c r="AN31" s="58"/>
     </row>
     <row r="32" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="67">
+      <c r="B32" s="49">
         <v>13</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="86"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="53"/>
       <c r="E32" s="7" t="s">
         <v>10</v>
       </c>
@@ -2690,13 +2689,13 @@
       <c r="AJ32" s="31"/>
       <c r="AK32" s="36"/>
       <c r="AL32" s="33"/>
-      <c r="AM32" s="49"/>
-      <c r="AN32" s="51"/>
+      <c r="AM32" s="55"/>
+      <c r="AN32" s="57"/>
     </row>
     <row r="33" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="68"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="87"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="54"/>
       <c r="E33" s="9" t="s">
         <v>12</v>
       </c>
@@ -2735,15 +2734,15 @@
       <c r="AJ33" s="32"/>
       <c r="AK33" s="43"/>
       <c r="AL33" s="34"/>
-      <c r="AM33" s="50"/>
-      <c r="AN33" s="52"/>
+      <c r="AM33" s="56"/>
+      <c r="AN33" s="58"/>
     </row>
     <row r="34" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="78">
+      <c r="B34" s="59">
         <v>14</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="86"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="53"/>
       <c r="E34" s="7" t="s">
         <v>10</v>
       </c>
@@ -2782,13 +2781,13 @@
       <c r="AJ34" s="31"/>
       <c r="AK34" s="36"/>
       <c r="AL34" s="33"/>
-      <c r="AM34" s="49"/>
-      <c r="AN34" s="51"/>
+      <c r="AM34" s="55"/>
+      <c r="AN34" s="57"/>
     </row>
     <row r="35" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="88"/>
-      <c r="C35" s="85"/>
-      <c r="D35" s="87"/>
+      <c r="B35" s="60"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="9" t="s">
         <v>12</v>
       </c>
@@ -2827,15 +2826,15 @@
       <c r="AJ35" s="32"/>
       <c r="AK35" s="43"/>
       <c r="AL35" s="34"/>
-      <c r="AM35" s="50"/>
-      <c r="AN35" s="52"/>
+      <c r="AM35" s="56"/>
+      <c r="AN35" s="58"/>
     </row>
     <row r="36" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="67">
+      <c r="B36" s="49">
         <v>15</v>
       </c>
-      <c r="C36" s="47"/>
-      <c r="D36" s="86"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="53"/>
       <c r="E36" s="7" t="s">
         <v>10</v>
       </c>
@@ -2874,13 +2873,13 @@
       <c r="AJ36" s="31"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="33"/>
-      <c r="AM36" s="49"/>
-      <c r="AN36" s="51"/>
+      <c r="AM36" s="55"/>
+      <c r="AN36" s="57"/>
     </row>
     <row r="37" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="68"/>
-      <c r="C37" s="85"/>
-      <c r="D37" s="87"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="54"/>
       <c r="E37" s="9" t="s">
         <v>12</v>
       </c>
@@ -2919,15 +2918,15 @@
       <c r="AJ37" s="32"/>
       <c r="AK37" s="43"/>
       <c r="AL37" s="34"/>
-      <c r="AM37" s="50"/>
-      <c r="AN37" s="52"/>
+      <c r="AM37" s="56"/>
+      <c r="AN37" s="58"/>
     </row>
     <row r="38" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="78">
+      <c r="B38" s="59">
         <v>16</v>
       </c>
-      <c r="C38" s="47"/>
-      <c r="D38" s="86"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="53"/>
       <c r="E38" s="7" t="s">
         <v>10</v>
       </c>
@@ -2966,13 +2965,13 @@
       <c r="AJ38" s="31"/>
       <c r="AK38" s="36"/>
       <c r="AL38" s="33"/>
-      <c r="AM38" s="49"/>
-      <c r="AN38" s="51"/>
+      <c r="AM38" s="55"/>
+      <c r="AN38" s="57"/>
     </row>
     <row r="39" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="88"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="87"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="54"/>
       <c r="E39" s="9" t="s">
         <v>12</v>
       </c>
@@ -3011,15 +3010,15 @@
       <c r="AJ39" s="32"/>
       <c r="AK39" s="43"/>
       <c r="AL39" s="34"/>
-      <c r="AM39" s="50"/>
-      <c r="AN39" s="52"/>
+      <c r="AM39" s="56"/>
+      <c r="AN39" s="58"/>
     </row>
     <row r="40" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="67">
+      <c r="B40" s="49">
         <v>17</v>
       </c>
-      <c r="C40" s="47"/>
-      <c r="D40" s="86"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="53"/>
       <c r="E40" s="7" t="s">
         <v>10</v>
       </c>
@@ -3058,13 +3057,13 @@
       <c r="AJ40" s="31"/>
       <c r="AK40" s="36"/>
       <c r="AL40" s="33"/>
-      <c r="AM40" s="49"/>
-      <c r="AN40" s="51"/>
+      <c r="AM40" s="55"/>
+      <c r="AN40" s="57"/>
     </row>
     <row r="41" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="68"/>
-      <c r="C41" s="85"/>
-      <c r="D41" s="87"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="54"/>
       <c r="E41" s="9" t="s">
         <v>12</v>
       </c>
@@ -3103,15 +3102,15 @@
       <c r="AJ41" s="32"/>
       <c r="AK41" s="43"/>
       <c r="AL41" s="34"/>
-      <c r="AM41" s="50"/>
-      <c r="AN41" s="52"/>
+      <c r="AM41" s="56"/>
+      <c r="AN41" s="58"/>
     </row>
     <row r="42" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="78">
+      <c r="B42" s="59">
         <v>18</v>
       </c>
-      <c r="C42" s="47"/>
-      <c r="D42" s="86"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="53"/>
       <c r="E42" s="7" t="s">
         <v>10</v>
       </c>
@@ -3150,13 +3149,13 @@
       <c r="AJ42" s="31"/>
       <c r="AK42" s="36"/>
       <c r="AL42" s="33"/>
-      <c r="AM42" s="49"/>
-      <c r="AN42" s="51"/>
+      <c r="AM42" s="55"/>
+      <c r="AN42" s="57"/>
     </row>
     <row r="43" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="88"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="87"/>
+      <c r="B43" s="60"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="9" t="s">
         <v>12</v>
       </c>
@@ -3195,15 +3194,15 @@
       <c r="AJ43" s="32"/>
       <c r="AK43" s="43"/>
       <c r="AL43" s="34"/>
-      <c r="AM43" s="50"/>
-      <c r="AN43" s="52"/>
+      <c r="AM43" s="56"/>
+      <c r="AN43" s="58"/>
     </row>
     <row r="44" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="67">
+      <c r="B44" s="49">
         <v>19</v>
       </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="86"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="53"/>
       <c r="E44" s="7" t="s">
         <v>10</v>
       </c>
@@ -3242,13 +3241,13 @@
       <c r="AJ44" s="31"/>
       <c r="AK44" s="36"/>
       <c r="AL44" s="33"/>
-      <c r="AM44" s="49"/>
-      <c r="AN44" s="51"/>
+      <c r="AM44" s="55"/>
+      <c r="AN44" s="57"/>
     </row>
     <row r="45" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="68"/>
-      <c r="C45" s="85"/>
-      <c r="D45" s="87"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="54"/>
       <c r="E45" s="9" t="s">
         <v>12</v>
       </c>
@@ -3287,15 +3286,15 @@
       <c r="AJ45" s="32"/>
       <c r="AK45" s="43"/>
       <c r="AL45" s="34"/>
-      <c r="AM45" s="50"/>
-      <c r="AN45" s="52"/>
+      <c r="AM45" s="56"/>
+      <c r="AN45" s="58"/>
     </row>
     <row r="46" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="78">
+      <c r="B46" s="59">
         <v>20</v>
       </c>
-      <c r="C46" s="47"/>
-      <c r="D46" s="86"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="53"/>
       <c r="E46" s="7" t="s">
         <v>10</v>
       </c>
@@ -3334,13 +3333,13 @@
       <c r="AJ46" s="31"/>
       <c r="AK46" s="36"/>
       <c r="AL46" s="33"/>
-      <c r="AM46" s="49"/>
-      <c r="AN46" s="51"/>
+      <c r="AM46" s="55"/>
+      <c r="AN46" s="57"/>
     </row>
     <row r="47" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="79"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="91"/>
+      <c r="B47" s="74"/>
+      <c r="C47" s="67"/>
+      <c r="D47" s="68"/>
       <c r="E47" s="11" t="s">
         <v>12</v>
       </c>
@@ -3379,15 +3378,15 @@
       <c r="AJ47" s="35"/>
       <c r="AK47" s="37"/>
       <c r="AL47" s="34"/>
-      <c r="AM47" s="82"/>
-      <c r="AN47" s="66"/>
+      <c r="AM47" s="69"/>
+      <c r="AN47" s="70"/>
     </row>
     <row r="48" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="67">
+      <c r="B48" s="49">
         <v>21</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="89"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="61"/>
       <c r="E48" s="7" t="s">
         <v>10</v>
       </c>
@@ -3426,13 +3425,13 @@
       <c r="AJ48" s="31"/>
       <c r="AK48" s="36"/>
       <c r="AL48" s="33"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="51"/>
+      <c r="AM48" s="55"/>
+      <c r="AN48" s="57"/>
     </row>
     <row r="49" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="68"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="90"/>
+      <c r="B49" s="50"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="62"/>
       <c r="E49" s="9" t="s">
         <v>12</v>
       </c>
@@ -3471,15 +3470,15 @@
       <c r="AJ49" s="32"/>
       <c r="AK49" s="43"/>
       <c r="AL49" s="34"/>
-      <c r="AM49" s="50"/>
-      <c r="AN49" s="52"/>
+      <c r="AM49" s="56"/>
+      <c r="AN49" s="58"/>
     </row>
     <row r="50" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="78">
+      <c r="B50" s="59">
         <v>22</v>
       </c>
-      <c r="C50" s="47"/>
-      <c r="D50" s="89"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="61"/>
       <c r="E50" s="7" t="s">
         <v>10</v>
       </c>
@@ -3518,13 +3517,13 @@
       <c r="AJ50" s="31"/>
       <c r="AK50" s="36"/>
       <c r="AL50" s="33"/>
-      <c r="AM50" s="49"/>
-      <c r="AN50" s="51"/>
+      <c r="AM50" s="55"/>
+      <c r="AN50" s="57"/>
     </row>
     <row r="51" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="88"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="90"/>
+      <c r="B51" s="60"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="62"/>
       <c r="E51" s="9" t="s">
         <v>12</v>
       </c>
@@ -3563,15 +3562,15 @@
       <c r="AJ51" s="32"/>
       <c r="AK51" s="43"/>
       <c r="AL51" s="34"/>
-      <c r="AM51" s="50"/>
-      <c r="AN51" s="52"/>
+      <c r="AM51" s="56"/>
+      <c r="AN51" s="58"/>
     </row>
     <row r="52" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="67">
+      <c r="B52" s="49">
         <v>23</v>
       </c>
-      <c r="C52" s="47"/>
-      <c r="D52" s="89"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="61"/>
       <c r="E52" s="7" t="s">
         <v>10</v>
       </c>
@@ -3610,13 +3609,13 @@
       <c r="AJ52" s="31"/>
       <c r="AK52" s="36"/>
       <c r="AL52" s="33"/>
-      <c r="AM52" s="49"/>
-      <c r="AN52" s="51"/>
+      <c r="AM52" s="55"/>
+      <c r="AN52" s="57"/>
     </row>
     <row r="53" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="68"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="90"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="62"/>
       <c r="E53" s="9" t="s">
         <v>12</v>
       </c>
@@ -3655,15 +3654,15 @@
       <c r="AJ53" s="32"/>
       <c r="AK53" s="43"/>
       <c r="AL53" s="34"/>
-      <c r="AM53" s="50"/>
-      <c r="AN53" s="52"/>
+      <c r="AM53" s="56"/>
+      <c r="AN53" s="58"/>
     </row>
     <row r="54" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="78">
+      <c r="B54" s="59">
         <v>24</v>
       </c>
-      <c r="C54" s="47"/>
-      <c r="D54" s="89"/>
+      <c r="C54" s="51"/>
+      <c r="D54" s="61"/>
       <c r="E54" s="7" t="s">
         <v>10</v>
       </c>
@@ -3702,13 +3701,13 @@
       <c r="AJ54" s="31"/>
       <c r="AK54" s="36"/>
       <c r="AL54" s="33"/>
-      <c r="AM54" s="49"/>
-      <c r="AN54" s="51"/>
+      <c r="AM54" s="55"/>
+      <c r="AN54" s="57"/>
     </row>
     <row r="55" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="88"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="90"/>
+      <c r="B55" s="60"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="62"/>
       <c r="E55" s="9" t="s">
         <v>12</v>
       </c>
@@ -3747,15 +3746,15 @@
       <c r="AJ55" s="32"/>
       <c r="AK55" s="43"/>
       <c r="AL55" s="34"/>
-      <c r="AM55" s="50"/>
-      <c r="AN55" s="52"/>
+      <c r="AM55" s="56"/>
+      <c r="AN55" s="58"/>
     </row>
     <row r="56" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="67">
+      <c r="B56" s="49">
         <v>25</v>
       </c>
-      <c r="C56" s="47"/>
-      <c r="D56" s="86"/>
+      <c r="C56" s="51"/>
+      <c r="D56" s="53"/>
       <c r="E56" s="7" t="s">
         <v>10</v>
       </c>
@@ -3794,13 +3793,13 @@
       <c r="AJ56" s="31"/>
       <c r="AK56" s="36"/>
       <c r="AL56" s="33"/>
-      <c r="AM56" s="49"/>
-      <c r="AN56" s="51"/>
+      <c r="AM56" s="55"/>
+      <c r="AN56" s="57"/>
     </row>
     <row r="57" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="68"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="87"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="54"/>
       <c r="E57" s="9" t="s">
         <v>12</v>
       </c>
@@ -3839,15 +3838,15 @@
       <c r="AJ57" s="32"/>
       <c r="AK57" s="43"/>
       <c r="AL57" s="34"/>
-      <c r="AM57" s="50"/>
-      <c r="AN57" s="52"/>
+      <c r="AM57" s="56"/>
+      <c r="AN57" s="58"/>
     </row>
     <row r="58" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="78">
+      <c r="B58" s="59">
         <v>26</v>
       </c>
-      <c r="C58" s="47"/>
-      <c r="D58" s="86"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="53"/>
       <c r="E58" s="7" t="s">
         <v>10</v>
       </c>
@@ -3886,13 +3885,13 @@
       <c r="AJ58" s="31"/>
       <c r="AK58" s="36"/>
       <c r="AL58" s="33"/>
-      <c r="AM58" s="49"/>
-      <c r="AN58" s="51"/>
+      <c r="AM58" s="55"/>
+      <c r="AN58" s="57"/>
     </row>
     <row r="59" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="88"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="87"/>
+      <c r="B59" s="60"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="54"/>
       <c r="E59" s="9" t="s">
         <v>12</v>
       </c>
@@ -3931,15 +3930,15 @@
       <c r="AJ59" s="32"/>
       <c r="AK59" s="43"/>
       <c r="AL59" s="34"/>
-      <c r="AM59" s="50"/>
-      <c r="AN59" s="52"/>
+      <c r="AM59" s="56"/>
+      <c r="AN59" s="58"/>
     </row>
     <row r="60" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="67">
+      <c r="B60" s="49">
         <v>27</v>
       </c>
-      <c r="C60" s="47"/>
-      <c r="D60" s="86"/>
+      <c r="C60" s="51"/>
+      <c r="D60" s="53"/>
       <c r="E60" s="7" t="s">
         <v>10</v>
       </c>
@@ -3978,13 +3977,13 @@
       <c r="AJ60" s="31"/>
       <c r="AK60" s="36"/>
       <c r="AL60" s="33"/>
-      <c r="AM60" s="49"/>
-      <c r="AN60" s="51"/>
+      <c r="AM60" s="55"/>
+      <c r="AN60" s="57"/>
     </row>
     <row r="61" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="68"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="87"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="54"/>
       <c r="E61" s="9" t="s">
         <v>12</v>
       </c>
@@ -4023,15 +4022,15 @@
       <c r="AJ61" s="32"/>
       <c r="AK61" s="43"/>
       <c r="AL61" s="34"/>
-      <c r="AM61" s="50"/>
-      <c r="AN61" s="52"/>
+      <c r="AM61" s="56"/>
+      <c r="AN61" s="58"/>
     </row>
     <row r="62" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="78">
+      <c r="B62" s="59">
         <v>28</v>
       </c>
-      <c r="C62" s="47"/>
-      <c r="D62" s="86"/>
+      <c r="C62" s="51"/>
+      <c r="D62" s="53"/>
       <c r="E62" s="7" t="s">
         <v>10</v>
       </c>
@@ -4070,13 +4069,13 @@
       <c r="AJ62" s="31"/>
       <c r="AK62" s="36"/>
       <c r="AL62" s="33"/>
-      <c r="AM62" s="49"/>
-      <c r="AN62" s="51"/>
+      <c r="AM62" s="55"/>
+      <c r="AN62" s="57"/>
     </row>
     <row r="63" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="88"/>
-      <c r="C63" s="85"/>
-      <c r="D63" s="87"/>
+      <c r="B63" s="60"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="54"/>
       <c r="E63" s="9" t="s">
         <v>12</v>
       </c>
@@ -4115,15 +4114,15 @@
       <c r="AJ63" s="32"/>
       <c r="AK63" s="43"/>
       <c r="AL63" s="34"/>
-      <c r="AM63" s="50"/>
-      <c r="AN63" s="52"/>
+      <c r="AM63" s="56"/>
+      <c r="AN63" s="58"/>
     </row>
     <row r="64" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="67">
+      <c r="B64" s="49">
         <v>29</v>
       </c>
-      <c r="C64" s="47"/>
-      <c r="D64" s="86"/>
+      <c r="C64" s="51"/>
+      <c r="D64" s="53"/>
       <c r="E64" s="7" t="s">
         <v>10</v>
       </c>
@@ -4162,13 +4161,13 @@
       <c r="AJ64" s="31"/>
       <c r="AK64" s="36"/>
       <c r="AL64" s="33"/>
-      <c r="AM64" s="49"/>
-      <c r="AN64" s="51"/>
+      <c r="AM64" s="55"/>
+      <c r="AN64" s="57"/>
     </row>
     <row r="65" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="68"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="87"/>
+      <c r="B65" s="50"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="54"/>
       <c r="E65" s="9" t="s">
         <v>12</v>
       </c>
@@ -4207,15 +4206,15 @@
       <c r="AJ65" s="32"/>
       <c r="AK65" s="43"/>
       <c r="AL65" s="34"/>
-      <c r="AM65" s="50"/>
-      <c r="AN65" s="52"/>
+      <c r="AM65" s="56"/>
+      <c r="AN65" s="58"/>
     </row>
     <row r="66" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="78">
+      <c r="B66" s="59">
         <v>30</v>
       </c>
-      <c r="C66" s="47"/>
-      <c r="D66" s="86"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="53"/>
       <c r="E66" s="7" t="s">
         <v>10</v>
       </c>
@@ -4254,13 +4253,13 @@
       <c r="AJ66" s="31"/>
       <c r="AK66" s="36"/>
       <c r="AL66" s="33"/>
-      <c r="AM66" s="49"/>
-      <c r="AN66" s="51"/>
+      <c r="AM66" s="55"/>
+      <c r="AN66" s="57"/>
     </row>
     <row r="67" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="88"/>
-      <c r="C67" s="85"/>
-      <c r="D67" s="87"/>
+      <c r="B67" s="60"/>
+      <c r="C67" s="52"/>
+      <c r="D67" s="54"/>
       <c r="E67" s="9" t="s">
         <v>12</v>
       </c>
@@ -4299,15 +4298,15 @@
       <c r="AJ67" s="32"/>
       <c r="AK67" s="43"/>
       <c r="AL67" s="34"/>
-      <c r="AM67" s="50"/>
-      <c r="AN67" s="52"/>
+      <c r="AM67" s="56"/>
+      <c r="AN67" s="58"/>
     </row>
     <row r="68" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="67">
+      <c r="B68" s="49">
         <v>31</v>
       </c>
-      <c r="C68" s="47"/>
-      <c r="D68" s="86"/>
+      <c r="C68" s="51"/>
+      <c r="D68" s="53"/>
       <c r="E68" s="7" t="s">
         <v>10</v>
       </c>
@@ -4346,13 +4345,13 @@
       <c r="AJ68" s="31"/>
       <c r="AK68" s="36"/>
       <c r="AL68" s="33"/>
-      <c r="AM68" s="49"/>
-      <c r="AN68" s="51"/>
+      <c r="AM68" s="55"/>
+      <c r="AN68" s="57"/>
     </row>
     <row r="69" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="68"/>
-      <c r="C69" s="85"/>
-      <c r="D69" s="87"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="54"/>
       <c r="E69" s="9" t="s">
         <v>12</v>
       </c>
@@ -4391,15 +4390,15 @@
       <c r="AJ69" s="32"/>
       <c r="AK69" s="43"/>
       <c r="AL69" s="34"/>
-      <c r="AM69" s="50"/>
-      <c r="AN69" s="52"/>
+      <c r="AM69" s="56"/>
+      <c r="AN69" s="58"/>
     </row>
     <row r="70" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="78">
+      <c r="B70" s="59">
         <v>32</v>
       </c>
-      <c r="C70" s="47"/>
-      <c r="D70" s="86"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="53"/>
       <c r="E70" s="7" t="s">
         <v>10</v>
       </c>
@@ -4438,13 +4437,13 @@
       <c r="AJ70" s="31"/>
       <c r="AK70" s="36"/>
       <c r="AL70" s="33"/>
-      <c r="AM70" s="49"/>
-      <c r="AN70" s="51"/>
+      <c r="AM70" s="55"/>
+      <c r="AN70" s="57"/>
     </row>
     <row r="71" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="88"/>
-      <c r="C71" s="85"/>
-      <c r="D71" s="87"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="54"/>
       <c r="E71" s="9" t="s">
         <v>12</v>
       </c>
@@ -4483,15 +4482,15 @@
       <c r="AJ71" s="32"/>
       <c r="AK71" s="43"/>
       <c r="AL71" s="34"/>
-      <c r="AM71" s="50"/>
-      <c r="AN71" s="52"/>
+      <c r="AM71" s="56"/>
+      <c r="AN71" s="58"/>
     </row>
     <row r="72" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="67">
+      <c r="B72" s="49">
         <v>33</v>
       </c>
-      <c r="C72" s="47"/>
-      <c r="D72" s="86"/>
+      <c r="C72" s="51"/>
+      <c r="D72" s="53"/>
       <c r="E72" s="7" t="s">
         <v>10</v>
       </c>
@@ -4530,13 +4529,13 @@
       <c r="AJ72" s="31"/>
       <c r="AK72" s="36"/>
       <c r="AL72" s="33"/>
-      <c r="AM72" s="49"/>
-      <c r="AN72" s="51"/>
+      <c r="AM72" s="55"/>
+      <c r="AN72" s="57"/>
     </row>
     <row r="73" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="68"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="87"/>
+      <c r="B73" s="50"/>
+      <c r="C73" s="52"/>
+      <c r="D73" s="54"/>
       <c r="E73" s="9" t="s">
         <v>12</v>
       </c>
@@ -4575,15 +4574,15 @@
       <c r="AJ73" s="32"/>
       <c r="AK73" s="43"/>
       <c r="AL73" s="34"/>
-      <c r="AM73" s="50"/>
-      <c r="AN73" s="52"/>
+      <c r="AM73" s="56"/>
+      <c r="AN73" s="58"/>
     </row>
     <row r="74" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="78">
+      <c r="B74" s="59">
         <v>34</v>
       </c>
-      <c r="C74" s="47"/>
-      <c r="D74" s="89"/>
+      <c r="C74" s="51"/>
+      <c r="D74" s="61"/>
       <c r="E74" s="7" t="s">
         <v>10</v>
       </c>
@@ -4622,13 +4621,13 @@
       <c r="AJ74" s="31"/>
       <c r="AK74" s="36"/>
       <c r="AL74" s="33"/>
-      <c r="AM74" s="49"/>
-      <c r="AN74" s="51"/>
+      <c r="AM74" s="55"/>
+      <c r="AN74" s="57"/>
     </row>
     <row r="75" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="88"/>
-      <c r="C75" s="85"/>
-      <c r="D75" s="90"/>
+      <c r="B75" s="60"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="62"/>
       <c r="E75" s="9" t="s">
         <v>12</v>
       </c>
@@ -4667,15 +4666,15 @@
       <c r="AJ75" s="32"/>
       <c r="AK75" s="43"/>
       <c r="AL75" s="34"/>
-      <c r="AM75" s="50"/>
-      <c r="AN75" s="52"/>
+      <c r="AM75" s="56"/>
+      <c r="AN75" s="58"/>
     </row>
     <row r="76" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="67">
+      <c r="B76" s="49">
         <v>35</v>
       </c>
-      <c r="C76" s="47"/>
-      <c r="D76" s="89"/>
+      <c r="C76" s="51"/>
+      <c r="D76" s="61"/>
       <c r="E76" s="7" t="s">
         <v>10</v>
       </c>
@@ -4714,13 +4713,13 @@
       <c r="AJ76" s="31"/>
       <c r="AK76" s="36"/>
       <c r="AL76" s="33"/>
-      <c r="AM76" s="49"/>
-      <c r="AN76" s="51"/>
+      <c r="AM76" s="55"/>
+      <c r="AN76" s="57"/>
     </row>
     <row r="77" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="68"/>
-      <c r="C77" s="85"/>
-      <c r="D77" s="90"/>
+      <c r="B77" s="50"/>
+      <c r="C77" s="52"/>
+      <c r="D77" s="62"/>
       <c r="E77" s="9" t="s">
         <v>12</v>
       </c>
@@ -4759,15 +4758,15 @@
       <c r="AJ77" s="32"/>
       <c r="AK77" s="43"/>
       <c r="AL77" s="34"/>
-      <c r="AM77" s="50"/>
-      <c r="AN77" s="52"/>
+      <c r="AM77" s="56"/>
+      <c r="AN77" s="58"/>
     </row>
     <row r="78" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="78">
+      <c r="B78" s="59">
         <v>36</v>
       </c>
-      <c r="C78" s="58"/>
-      <c r="D78" s="93"/>
+      <c r="C78" s="63"/>
+      <c r="D78" s="65"/>
       <c r="E78" s="7" t="s">
         <v>10</v>
       </c>
@@ -4806,13 +4805,13 @@
       <c r="AJ78" s="31"/>
       <c r="AK78" s="36"/>
       <c r="AL78" s="33"/>
-      <c r="AM78" s="49"/>
-      <c r="AN78" s="51"/>
+      <c r="AM78" s="55"/>
+      <c r="AN78" s="57"/>
     </row>
     <row r="79" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="88"/>
-      <c r="C79" s="92"/>
-      <c r="D79" s="94"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="64"/>
+      <c r="D79" s="66"/>
       <c r="E79" s="9" t="s">
         <v>12</v>
       </c>
@@ -4851,15 +4850,15 @@
       <c r="AJ79" s="32"/>
       <c r="AK79" s="43"/>
       <c r="AL79" s="34"/>
-      <c r="AM79" s="50"/>
-      <c r="AN79" s="52"/>
+      <c r="AM79" s="56"/>
+      <c r="AN79" s="58"/>
     </row>
     <row r="80" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="67">
+      <c r="B80" s="49">
         <v>37</v>
       </c>
-      <c r="C80" s="47"/>
-      <c r="D80" s="89"/>
+      <c r="C80" s="51"/>
+      <c r="D80" s="61"/>
       <c r="E80" s="7" t="s">
         <v>10</v>
       </c>
@@ -4898,13 +4897,13 @@
       <c r="AJ80" s="31"/>
       <c r="AK80" s="36"/>
       <c r="AL80" s="33"/>
-      <c r="AM80" s="49"/>
-      <c r="AN80" s="51"/>
+      <c r="AM80" s="55"/>
+      <c r="AN80" s="57"/>
     </row>
     <row r="81" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="68"/>
-      <c r="C81" s="85"/>
-      <c r="D81" s="90"/>
+      <c r="B81" s="50"/>
+      <c r="C81" s="52"/>
+      <c r="D81" s="62"/>
       <c r="E81" s="9" t="s">
         <v>12</v>
       </c>
@@ -4943,15 +4942,15 @@
       <c r="AJ81" s="32"/>
       <c r="AK81" s="43"/>
       <c r="AL81" s="34"/>
-      <c r="AM81" s="50"/>
-      <c r="AN81" s="52"/>
+      <c r="AM81" s="56"/>
+      <c r="AN81" s="58"/>
     </row>
     <row r="82" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="78">
+      <c r="B82" s="59">
         <v>38</v>
       </c>
-      <c r="C82" s="47"/>
-      <c r="D82" s="89"/>
+      <c r="C82" s="51"/>
+      <c r="D82" s="61"/>
       <c r="E82" s="7" t="s">
         <v>10</v>
       </c>
@@ -4990,13 +4989,13 @@
       <c r="AJ82" s="31"/>
       <c r="AK82" s="36"/>
       <c r="AL82" s="33"/>
-      <c r="AM82" s="49"/>
-      <c r="AN82" s="51"/>
+      <c r="AM82" s="55"/>
+      <c r="AN82" s="57"/>
     </row>
     <row r="83" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="88"/>
-      <c r="C83" s="85"/>
-      <c r="D83" s="90"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="52"/>
+      <c r="D83" s="62"/>
       <c r="E83" s="9" t="s">
         <v>12</v>
       </c>
@@ -5035,15 +5034,15 @@
       <c r="AJ83" s="32"/>
       <c r="AK83" s="43"/>
       <c r="AL83" s="34"/>
-      <c r="AM83" s="50"/>
-      <c r="AN83" s="52"/>
+      <c r="AM83" s="56"/>
+      <c r="AN83" s="58"/>
     </row>
     <row r="84" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="67">
+      <c r="B84" s="49">
         <v>39</v>
       </c>
-      <c r="C84" s="47"/>
-      <c r="D84" s="89"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="61"/>
       <c r="E84" s="7" t="s">
         <v>10</v>
       </c>
@@ -5082,13 +5081,13 @@
       <c r="AJ84" s="31"/>
       <c r="AK84" s="36"/>
       <c r="AL84" s="33"/>
-      <c r="AM84" s="49"/>
-      <c r="AN84" s="51"/>
+      <c r="AM84" s="55"/>
+      <c r="AN84" s="57"/>
     </row>
     <row r="85" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="68"/>
-      <c r="C85" s="85"/>
-      <c r="D85" s="90"/>
+      <c r="B85" s="50"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="62"/>
       <c r="E85" s="9" t="s">
         <v>12</v>
       </c>
@@ -5127,15 +5126,15 @@
       <c r="AJ85" s="32"/>
       <c r="AK85" s="43"/>
       <c r="AL85" s="34"/>
-      <c r="AM85" s="50"/>
-      <c r="AN85" s="52"/>
+      <c r="AM85" s="56"/>
+      <c r="AN85" s="58"/>
     </row>
     <row r="86" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="78">
+      <c r="B86" s="59">
         <v>40</v>
       </c>
-      <c r="C86" s="47"/>
-      <c r="D86" s="89"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="61"/>
       <c r="E86" s="7" t="s">
         <v>10</v>
       </c>
@@ -5174,13 +5173,13 @@
       <c r="AJ86" s="31"/>
       <c r="AK86" s="36"/>
       <c r="AL86" s="33"/>
-      <c r="AM86" s="49"/>
-      <c r="AN86" s="51"/>
+      <c r="AM86" s="55"/>
+      <c r="AN86" s="57"/>
     </row>
     <row r="87" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="88"/>
-      <c r="C87" s="85"/>
-      <c r="D87" s="90"/>
+      <c r="B87" s="60"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="62"/>
       <c r="E87" s="9" t="s">
         <v>12</v>
       </c>
@@ -5219,15 +5218,15 @@
       <c r="AJ87" s="32"/>
       <c r="AK87" s="43"/>
       <c r="AL87" s="34"/>
-      <c r="AM87" s="50"/>
-      <c r="AN87" s="52"/>
+      <c r="AM87" s="56"/>
+      <c r="AN87" s="58"/>
     </row>
     <row r="88" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="67">
+      <c r="B88" s="49">
         <v>41</v>
       </c>
-      <c r="C88" s="47"/>
-      <c r="D88" s="86"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="53"/>
       <c r="E88" s="7" t="s">
         <v>10</v>
       </c>
@@ -5266,13 +5265,13 @@
       <c r="AJ88" s="31"/>
       <c r="AK88" s="36"/>
       <c r="AL88" s="33"/>
-      <c r="AM88" s="49"/>
-      <c r="AN88" s="51"/>
+      <c r="AM88" s="55"/>
+      <c r="AN88" s="57"/>
     </row>
     <row r="89" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="68"/>
-      <c r="C89" s="85"/>
-      <c r="D89" s="87"/>
+      <c r="B89" s="50"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="54"/>
       <c r="E89" s="9" t="s">
         <v>12</v>
       </c>
@@ -5311,15 +5310,15 @@
       <c r="AJ89" s="32"/>
       <c r="AK89" s="43"/>
       <c r="AL89" s="34"/>
-      <c r="AM89" s="50"/>
-      <c r="AN89" s="52"/>
+      <c r="AM89" s="56"/>
+      <c r="AN89" s="58"/>
     </row>
     <row r="90" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="78">
+      <c r="B90" s="59">
         <v>42</v>
       </c>
-      <c r="C90" s="47"/>
-      <c r="D90" s="86"/>
+      <c r="C90" s="51"/>
+      <c r="D90" s="53"/>
       <c r="E90" s="7" t="s">
         <v>10</v>
       </c>
@@ -5358,13 +5357,13 @@
       <c r="AJ90" s="31"/>
       <c r="AK90" s="36"/>
       <c r="AL90" s="33"/>
-      <c r="AM90" s="49"/>
-      <c r="AN90" s="51"/>
+      <c r="AM90" s="55"/>
+      <c r="AN90" s="57"/>
     </row>
     <row r="91" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="88"/>
-      <c r="C91" s="85"/>
-      <c r="D91" s="87"/>
+      <c r="B91" s="60"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="54"/>
       <c r="E91" s="9" t="s">
         <v>12</v>
       </c>
@@ -5403,15 +5402,15 @@
       <c r="AJ91" s="32"/>
       <c r="AK91" s="43"/>
       <c r="AL91" s="34"/>
-      <c r="AM91" s="50"/>
-      <c r="AN91" s="52"/>
+      <c r="AM91" s="56"/>
+      <c r="AN91" s="58"/>
     </row>
     <row r="92" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="67">
+      <c r="B92" s="49">
         <v>43</v>
       </c>
-      <c r="C92" s="47"/>
-      <c r="D92" s="86"/>
+      <c r="C92" s="51"/>
+      <c r="D92" s="53"/>
       <c r="E92" s="7" t="s">
         <v>10</v>
       </c>
@@ -5450,13 +5449,13 @@
       <c r="AJ92" s="31"/>
       <c r="AK92" s="36"/>
       <c r="AL92" s="33"/>
-      <c r="AM92" s="49"/>
-      <c r="AN92" s="51"/>
+      <c r="AM92" s="55"/>
+      <c r="AN92" s="57"/>
     </row>
     <row r="93" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="68"/>
-      <c r="C93" s="85"/>
-      <c r="D93" s="87"/>
+      <c r="B93" s="50"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="54"/>
       <c r="E93" s="9" t="s">
         <v>12</v>
       </c>
@@ -5495,15 +5494,15 @@
       <c r="AJ93" s="32"/>
       <c r="AK93" s="43"/>
       <c r="AL93" s="34"/>
-      <c r="AM93" s="50"/>
-      <c r="AN93" s="52"/>
+      <c r="AM93" s="56"/>
+      <c r="AN93" s="58"/>
     </row>
     <row r="94" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="78">
+      <c r="B94" s="59">
         <v>44</v>
       </c>
-      <c r="C94" s="47"/>
-      <c r="D94" s="86"/>
+      <c r="C94" s="51"/>
+      <c r="D94" s="53"/>
       <c r="E94" s="7" t="s">
         <v>10</v>
       </c>
@@ -5542,13 +5541,13 @@
       <c r="AJ94" s="31"/>
       <c r="AK94" s="36"/>
       <c r="AL94" s="33"/>
-      <c r="AM94" s="49"/>
-      <c r="AN94" s="51"/>
+      <c r="AM94" s="55"/>
+      <c r="AN94" s="57"/>
     </row>
     <row r="95" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="88"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="87"/>
+      <c r="B95" s="60"/>
+      <c r="C95" s="52"/>
+      <c r="D95" s="54"/>
       <c r="E95" s="9" t="s">
         <v>12</v>
       </c>
@@ -5587,15 +5586,15 @@
       <c r="AJ95" s="32"/>
       <c r="AK95" s="43"/>
       <c r="AL95" s="34"/>
-      <c r="AM95" s="50"/>
-      <c r="AN95" s="52"/>
+      <c r="AM95" s="56"/>
+      <c r="AN95" s="58"/>
     </row>
     <row r="96" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="67">
+      <c r="B96" s="49">
         <v>45</v>
       </c>
-      <c r="C96" s="47"/>
-      <c r="D96" s="86"/>
+      <c r="C96" s="51"/>
+      <c r="D96" s="53"/>
       <c r="E96" s="7" t="s">
         <v>10</v>
       </c>
@@ -5634,13 +5633,13 @@
       <c r="AJ96" s="31"/>
       <c r="AK96" s="36"/>
       <c r="AL96" s="33"/>
-      <c r="AM96" s="49"/>
-      <c r="AN96" s="51"/>
+      <c r="AM96" s="55"/>
+      <c r="AN96" s="57"/>
     </row>
     <row r="97" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="68"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="87"/>
+      <c r="B97" s="50"/>
+      <c r="C97" s="52"/>
+      <c r="D97" s="54"/>
       <c r="E97" s="9" t="s">
         <v>12</v>
       </c>
@@ -5679,15 +5678,15 @@
       <c r="AJ97" s="32"/>
       <c r="AK97" s="43"/>
       <c r="AL97" s="34"/>
-      <c r="AM97" s="50"/>
-      <c r="AN97" s="52"/>
+      <c r="AM97" s="56"/>
+      <c r="AN97" s="58"/>
     </row>
     <row r="98" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="78">
+      <c r="B98" s="59">
         <v>46</v>
       </c>
-      <c r="C98" s="47"/>
-      <c r="D98" s="86"/>
+      <c r="C98" s="51"/>
+      <c r="D98" s="53"/>
       <c r="E98" s="7" t="s">
         <v>10</v>
       </c>
@@ -5726,13 +5725,13 @@
       <c r="AJ98" s="31"/>
       <c r="AK98" s="36"/>
       <c r="AL98" s="33"/>
-      <c r="AM98" s="49"/>
-      <c r="AN98" s="51"/>
+      <c r="AM98" s="55"/>
+      <c r="AN98" s="57"/>
     </row>
     <row r="99" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="88"/>
-      <c r="C99" s="85"/>
-      <c r="D99" s="87"/>
+      <c r="B99" s="60"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="54"/>
       <c r="E99" s="9" t="s">
         <v>12</v>
       </c>
@@ -5771,15 +5770,15 @@
       <c r="AJ99" s="32"/>
       <c r="AK99" s="43"/>
       <c r="AL99" s="34"/>
-      <c r="AM99" s="50"/>
-      <c r="AN99" s="52"/>
+      <c r="AM99" s="56"/>
+      <c r="AN99" s="58"/>
     </row>
     <row r="100" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="67">
+      <c r="B100" s="49">
         <v>47</v>
       </c>
-      <c r="C100" s="47"/>
-      <c r="D100" s="86"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="53"/>
       <c r="E100" s="7" t="s">
         <v>10</v>
       </c>
@@ -5818,13 +5817,13 @@
       <c r="AJ100" s="31"/>
       <c r="AK100" s="36"/>
       <c r="AL100" s="33"/>
-      <c r="AM100" s="49"/>
-      <c r="AN100" s="51"/>
+      <c r="AM100" s="55"/>
+      <c r="AN100" s="57"/>
     </row>
     <row r="101" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="68"/>
-      <c r="C101" s="85"/>
-      <c r="D101" s="87"/>
+      <c r="B101" s="50"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="54"/>
       <c r="E101" s="9" t="s">
         <v>12</v>
       </c>
@@ -5863,15 +5862,15 @@
       <c r="AJ101" s="32"/>
       <c r="AK101" s="43"/>
       <c r="AL101" s="34"/>
-      <c r="AM101" s="50"/>
-      <c r="AN101" s="52"/>
+      <c r="AM101" s="56"/>
+      <c r="AN101" s="58"/>
     </row>
     <row r="102" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="78">
+      <c r="B102" s="59">
         <v>48</v>
       </c>
-      <c r="C102" s="47"/>
-      <c r="D102" s="86"/>
+      <c r="C102" s="51"/>
+      <c r="D102" s="53"/>
       <c r="E102" s="7" t="s">
         <v>10</v>
       </c>
@@ -5910,13 +5909,13 @@
       <c r="AJ102" s="31"/>
       <c r="AK102" s="36"/>
       <c r="AL102" s="33"/>
-      <c r="AM102" s="49"/>
-      <c r="AN102" s="51"/>
+      <c r="AM102" s="55"/>
+      <c r="AN102" s="57"/>
     </row>
     <row r="103" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="88"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="87"/>
+      <c r="B103" s="60"/>
+      <c r="C103" s="52"/>
+      <c r="D103" s="54"/>
       <c r="E103" s="9" t="s">
         <v>12</v>
       </c>
@@ -5955,15 +5954,15 @@
       <c r="AJ103" s="32"/>
       <c r="AK103" s="43"/>
       <c r="AL103" s="34"/>
-      <c r="AM103" s="50"/>
-      <c r="AN103" s="52"/>
+      <c r="AM103" s="56"/>
+      <c r="AN103" s="58"/>
     </row>
     <row r="104" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="67">
+      <c r="B104" s="49">
         <v>49</v>
       </c>
-      <c r="C104" s="47"/>
-      <c r="D104" s="86"/>
+      <c r="C104" s="51"/>
+      <c r="D104" s="53"/>
       <c r="E104" s="7" t="s">
         <v>10</v>
       </c>
@@ -6002,13 +6001,13 @@
       <c r="AJ104" s="31"/>
       <c r="AK104" s="36"/>
       <c r="AL104" s="33"/>
-      <c r="AM104" s="49"/>
-      <c r="AN104" s="51"/>
+      <c r="AM104" s="55"/>
+      <c r="AN104" s="57"/>
     </row>
     <row r="105" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="68"/>
-      <c r="C105" s="85"/>
-      <c r="D105" s="87"/>
+      <c r="B105" s="50"/>
+      <c r="C105" s="52"/>
+      <c r="D105" s="54"/>
       <c r="E105" s="9" t="s">
         <v>12</v>
       </c>
@@ -6047,15 +6046,15 @@
       <c r="AJ105" s="32"/>
       <c r="AK105" s="43"/>
       <c r="AL105" s="34"/>
-      <c r="AM105" s="50"/>
-      <c r="AN105" s="52"/>
+      <c r="AM105" s="56"/>
+      <c r="AN105" s="58"/>
     </row>
     <row r="106" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="78">
+      <c r="B106" s="59">
         <v>50</v>
       </c>
-      <c r="C106" s="47"/>
-      <c r="D106" s="86"/>
+      <c r="C106" s="51"/>
+      <c r="D106" s="53"/>
       <c r="E106" s="7" t="s">
         <v>10</v>
       </c>
@@ -6094,13 +6093,13 @@
       <c r="AJ106" s="31"/>
       <c r="AK106" s="36"/>
       <c r="AL106" s="33"/>
-      <c r="AM106" s="49"/>
-      <c r="AN106" s="51"/>
+      <c r="AM106" s="55"/>
+      <c r="AN106" s="57"/>
     </row>
     <row r="107" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="88"/>
-      <c r="C107" s="85"/>
-      <c r="D107" s="87"/>
+      <c r="B107" s="60"/>
+      <c r="C107" s="52"/>
+      <c r="D107" s="54"/>
       <c r="E107" s="9" t="s">
         <v>12</v>
       </c>
@@ -6139,15 +6138,15 @@
       <c r="AJ107" s="32"/>
       <c r="AK107" s="43"/>
       <c r="AL107" s="34"/>
-      <c r="AM107" s="50"/>
-      <c r="AN107" s="52"/>
+      <c r="AM107" s="56"/>
+      <c r="AN107" s="58"/>
     </row>
     <row r="108" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="67">
+      <c r="B108" s="49">
         <v>51</v>
       </c>
-      <c r="C108" s="47"/>
-      <c r="D108" s="86"/>
+      <c r="C108" s="51"/>
+      <c r="D108" s="53"/>
       <c r="E108" s="7" t="s">
         <v>10</v>
       </c>
@@ -6186,13 +6185,13 @@
       <c r="AJ108" s="31"/>
       <c r="AK108" s="36"/>
       <c r="AL108" s="33"/>
-      <c r="AM108" s="49"/>
-      <c r="AN108" s="51"/>
+      <c r="AM108" s="55"/>
+      <c r="AN108" s="57"/>
     </row>
     <row r="109" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="68"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="87"/>
+      <c r="B109" s="50"/>
+      <c r="C109" s="52"/>
+      <c r="D109" s="54"/>
       <c r="E109" s="9" t="s">
         <v>12</v>
       </c>
@@ -6231,15 +6230,15 @@
       <c r="AJ109" s="32"/>
       <c r="AK109" s="43"/>
       <c r="AL109" s="34"/>
-      <c r="AM109" s="50"/>
-      <c r="AN109" s="52"/>
+      <c r="AM109" s="56"/>
+      <c r="AN109" s="58"/>
     </row>
     <row r="110" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B110" s="78">
+      <c r="B110" s="59">
         <v>52</v>
       </c>
-      <c r="C110" s="47"/>
-      <c r="D110" s="86"/>
+      <c r="C110" s="51"/>
+      <c r="D110" s="53"/>
       <c r="E110" s="7" t="s">
         <v>10</v>
       </c>
@@ -6278,13 +6277,13 @@
       <c r="AJ110" s="31"/>
       <c r="AK110" s="36"/>
       <c r="AL110" s="33"/>
-      <c r="AM110" s="49"/>
-      <c r="AN110" s="51"/>
+      <c r="AM110" s="55"/>
+      <c r="AN110" s="57"/>
     </row>
     <row r="111" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="88"/>
-      <c r="C111" s="85"/>
-      <c r="D111" s="87"/>
+      <c r="B111" s="60"/>
+      <c r="C111" s="52"/>
+      <c r="D111" s="54"/>
       <c r="E111" s="9" t="s">
         <v>12</v>
       </c>
@@ -6323,15 +6322,15 @@
       <c r="AJ111" s="32"/>
       <c r="AK111" s="43"/>
       <c r="AL111" s="34"/>
-      <c r="AM111" s="50"/>
-      <c r="AN111" s="52"/>
+      <c r="AM111" s="56"/>
+      <c r="AN111" s="58"/>
     </row>
     <row r="112" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="67">
+      <c r="B112" s="49">
         <v>53</v>
       </c>
-      <c r="C112" s="47"/>
-      <c r="D112" s="86"/>
+      <c r="C112" s="51"/>
+      <c r="D112" s="53"/>
       <c r="E112" s="7" t="s">
         <v>10</v>
       </c>
@@ -6370,13 +6369,13 @@
       <c r="AJ112" s="31"/>
       <c r="AK112" s="36"/>
       <c r="AL112" s="33"/>
-      <c r="AM112" s="49"/>
-      <c r="AN112" s="51"/>
+      <c r="AM112" s="55"/>
+      <c r="AN112" s="57"/>
     </row>
     <row r="113" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="68"/>
-      <c r="C113" s="85"/>
-      <c r="D113" s="87"/>
+      <c r="B113" s="50"/>
+      <c r="C113" s="52"/>
+      <c r="D113" s="54"/>
       <c r="E113" s="9" t="s">
         <v>12</v>
       </c>
@@ -6415,15 +6414,15 @@
       <c r="AJ113" s="32"/>
       <c r="AK113" s="43"/>
       <c r="AL113" s="34"/>
-      <c r="AM113" s="50"/>
-      <c r="AN113" s="52"/>
+      <c r="AM113" s="56"/>
+      <c r="AN113" s="58"/>
     </row>
     <row r="114" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="78">
+      <c r="B114" s="59">
         <v>54</v>
       </c>
-      <c r="C114" s="58"/>
-      <c r="D114" s="80"/>
+      <c r="C114" s="63"/>
+      <c r="D114" s="72"/>
       <c r="E114" s="7" t="s">
         <v>10</v>
       </c>
@@ -6462,13 +6461,13 @@
       <c r="AJ114" s="31"/>
       <c r="AK114" s="36"/>
       <c r="AL114" s="33"/>
-      <c r="AM114" s="49"/>
-      <c r="AN114" s="51"/>
+      <c r="AM114" s="55"/>
+      <c r="AN114" s="57"/>
     </row>
     <row r="115" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="88"/>
-      <c r="C115" s="69"/>
-      <c r="D115" s="81"/>
+      <c r="B115" s="60"/>
+      <c r="C115" s="71"/>
+      <c r="D115" s="73"/>
       <c r="E115" s="11" t="s">
         <v>12</v>
       </c>
@@ -6507,15 +6506,15 @@
       <c r="AJ115" s="35"/>
       <c r="AK115" s="37"/>
       <c r="AL115" s="34"/>
-      <c r="AM115" s="82"/>
-      <c r="AN115" s="66"/>
+      <c r="AM115" s="69"/>
+      <c r="AN115" s="70"/>
     </row>
     <row r="116" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B116" s="67">
+      <c r="B116" s="49">
         <v>55</v>
       </c>
-      <c r="C116" s="47"/>
-      <c r="D116" s="86"/>
+      <c r="C116" s="51"/>
+      <c r="D116" s="53"/>
       <c r="E116" s="7" t="s">
         <v>10</v>
       </c>
@@ -6554,13 +6553,13 @@
       <c r="AJ116" s="31"/>
       <c r="AK116" s="36"/>
       <c r="AL116" s="33"/>
-      <c r="AM116" s="49"/>
-      <c r="AN116" s="51"/>
+      <c r="AM116" s="55"/>
+      <c r="AN116" s="57"/>
     </row>
     <row r="117" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="68"/>
-      <c r="C117" s="85"/>
-      <c r="D117" s="87"/>
+      <c r="B117" s="50"/>
+      <c r="C117" s="52"/>
+      <c r="D117" s="54"/>
       <c r="E117" s="9" t="s">
         <v>12</v>
       </c>
@@ -6599,15 +6598,15 @@
       <c r="AJ117" s="32"/>
       <c r="AK117" s="43"/>
       <c r="AL117" s="34"/>
-      <c r="AM117" s="50"/>
-      <c r="AN117" s="52"/>
+      <c r="AM117" s="56"/>
+      <c r="AN117" s="58"/>
     </row>
     <row r="118" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="78">
+      <c r="B118" s="59">
         <v>56</v>
       </c>
-      <c r="C118" s="47"/>
-      <c r="D118" s="86"/>
+      <c r="C118" s="51"/>
+      <c r="D118" s="53"/>
       <c r="E118" s="7" t="s">
         <v>10</v>
       </c>
@@ -6646,13 +6645,13 @@
       <c r="AJ118" s="31"/>
       <c r="AK118" s="36"/>
       <c r="AL118" s="33"/>
-      <c r="AM118" s="49"/>
-      <c r="AN118" s="51"/>
+      <c r="AM118" s="55"/>
+      <c r="AN118" s="57"/>
     </row>
     <row r="119" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="88"/>
-      <c r="C119" s="85"/>
-      <c r="D119" s="87"/>
+      <c r="B119" s="60"/>
+      <c r="C119" s="52"/>
+      <c r="D119" s="54"/>
       <c r="E119" s="9" t="s">
         <v>12</v>
       </c>
@@ -6691,15 +6690,15 @@
       <c r="AJ119" s="32"/>
       <c r="AK119" s="43"/>
       <c r="AL119" s="34"/>
-      <c r="AM119" s="50"/>
-      <c r="AN119" s="52"/>
+      <c r="AM119" s="56"/>
+      <c r="AN119" s="58"/>
     </row>
     <row r="120" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="67">
+      <c r="B120" s="49">
         <v>57</v>
       </c>
-      <c r="C120" s="47"/>
-      <c r="D120" s="89"/>
+      <c r="C120" s="51"/>
+      <c r="D120" s="61"/>
       <c r="E120" s="7" t="s">
         <v>10</v>
       </c>
@@ -6738,13 +6737,13 @@
       <c r="AJ120" s="31"/>
       <c r="AK120" s="36"/>
       <c r="AL120" s="33"/>
-      <c r="AM120" s="49"/>
-      <c r="AN120" s="51"/>
+      <c r="AM120" s="55"/>
+      <c r="AN120" s="57"/>
     </row>
     <row r="121" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="68"/>
-      <c r="C121" s="85"/>
-      <c r="D121" s="90"/>
+      <c r="B121" s="50"/>
+      <c r="C121" s="52"/>
+      <c r="D121" s="62"/>
       <c r="E121" s="9" t="s">
         <v>12</v>
       </c>
@@ -6783,15 +6782,15 @@
       <c r="AJ121" s="32"/>
       <c r="AK121" s="43"/>
       <c r="AL121" s="34"/>
-      <c r="AM121" s="50"/>
-      <c r="AN121" s="52"/>
+      <c r="AM121" s="56"/>
+      <c r="AN121" s="58"/>
     </row>
     <row r="122" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="78">
+      <c r="B122" s="59">
         <v>58</v>
       </c>
-      <c r="C122" s="47"/>
-      <c r="D122" s="89"/>
+      <c r="C122" s="51"/>
+      <c r="D122" s="61"/>
       <c r="E122" s="7" t="s">
         <v>10</v>
       </c>
@@ -6830,13 +6829,13 @@
       <c r="AJ122" s="31"/>
       <c r="AK122" s="36"/>
       <c r="AL122" s="33"/>
-      <c r="AM122" s="49"/>
-      <c r="AN122" s="51"/>
+      <c r="AM122" s="55"/>
+      <c r="AN122" s="57"/>
     </row>
     <row r="123" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="88"/>
-      <c r="C123" s="85"/>
-      <c r="D123" s="90"/>
+      <c r="B123" s="60"/>
+      <c r="C123" s="52"/>
+      <c r="D123" s="62"/>
       <c r="E123" s="9" t="s">
         <v>12</v>
       </c>
@@ -6875,15 +6874,15 @@
       <c r="AJ123" s="32"/>
       <c r="AK123" s="43"/>
       <c r="AL123" s="34"/>
-      <c r="AM123" s="50"/>
-      <c r="AN123" s="52"/>
+      <c r="AM123" s="56"/>
+      <c r="AN123" s="58"/>
     </row>
     <row r="124" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="67">
+      <c r="B124" s="49">
         <v>59</v>
       </c>
-      <c r="C124" s="47"/>
-      <c r="D124" s="89"/>
+      <c r="C124" s="51"/>
+      <c r="D124" s="61"/>
       <c r="E124" s="7" t="s">
         <v>10</v>
       </c>
@@ -6922,13 +6921,13 @@
       <c r="AJ124" s="31"/>
       <c r="AK124" s="36"/>
       <c r="AL124" s="33"/>
-      <c r="AM124" s="49"/>
-      <c r="AN124" s="51"/>
+      <c r="AM124" s="55"/>
+      <c r="AN124" s="57"/>
     </row>
     <row r="125" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="68"/>
-      <c r="C125" s="85"/>
-      <c r="D125" s="90"/>
+      <c r="B125" s="50"/>
+      <c r="C125" s="52"/>
+      <c r="D125" s="62"/>
       <c r="E125" s="9" t="s">
         <v>12</v>
       </c>
@@ -6967,15 +6966,15 @@
       <c r="AJ125" s="32"/>
       <c r="AK125" s="43"/>
       <c r="AL125" s="34"/>
-      <c r="AM125" s="50"/>
-      <c r="AN125" s="52"/>
+      <c r="AM125" s="56"/>
+      <c r="AN125" s="58"/>
     </row>
     <row r="126" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="78">
+      <c r="B126" s="59">
         <v>60</v>
       </c>
-      <c r="C126" s="47"/>
-      <c r="D126" s="86"/>
+      <c r="C126" s="51"/>
+      <c r="D126" s="53"/>
       <c r="E126" s="7" t="s">
         <v>10</v>
       </c>
@@ -7014,13 +7013,13 @@
       <c r="AJ126" s="31"/>
       <c r="AK126" s="36"/>
       <c r="AL126" s="33"/>
-      <c r="AM126" s="49"/>
-      <c r="AN126" s="51"/>
+      <c r="AM126" s="55"/>
+      <c r="AN126" s="57"/>
     </row>
     <row r="127" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="88"/>
-      <c r="C127" s="85"/>
-      <c r="D127" s="87"/>
+      <c r="B127" s="60"/>
+      <c r="C127" s="52"/>
+      <c r="D127" s="54"/>
       <c r="E127" s="9" t="s">
         <v>12</v>
       </c>
@@ -7059,15 +7058,15 @@
       <c r="AJ127" s="32"/>
       <c r="AK127" s="43"/>
       <c r="AL127" s="34"/>
-      <c r="AM127" s="50"/>
-      <c r="AN127" s="52"/>
+      <c r="AM127" s="56"/>
+      <c r="AN127" s="58"/>
     </row>
     <row r="128" spans="2:40" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="67">
+      <c r="B128" s="49">
         <v>61</v>
       </c>
-      <c r="C128" s="47"/>
-      <c r="D128" s="89"/>
+      <c r="C128" s="51"/>
+      <c r="D128" s="61"/>
       <c r="E128" s="7" t="s">
         <v>10</v>
       </c>
@@ -7106,13 +7105,13 @@
       <c r="AJ128" s="31"/>
       <c r="AK128" s="36"/>
       <c r="AL128" s="33"/>
-      <c r="AM128" s="49"/>
-      <c r="AN128" s="51"/>
+      <c r="AM128" s="55"/>
+      <c r="AN128" s="57"/>
     </row>
     <row r="129" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="68"/>
-      <c r="C129" s="85"/>
-      <c r="D129" s="90"/>
+      <c r="B129" s="50"/>
+      <c r="C129" s="52"/>
+      <c r="D129" s="62"/>
       <c r="E129" s="9" t="s">
         <v>12</v>
       </c>
@@ -7151,15 +7150,15 @@
       <c r="AJ129" s="32"/>
       <c r="AK129" s="43"/>
       <c r="AL129" s="34"/>
-      <c r="AM129" s="50"/>
-      <c r="AN129" s="52"/>
+      <c r="AM129" s="56"/>
+      <c r="AN129" s="58"/>
     </row>
     <row r="130" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="78">
+      <c r="B130" s="59">
         <v>62</v>
       </c>
-      <c r="C130" s="47"/>
-      <c r="D130" s="86"/>
+      <c r="C130" s="51"/>
+      <c r="D130" s="53"/>
       <c r="E130" s="7" t="s">
         <v>10</v>
       </c>
@@ -7198,13 +7197,13 @@
       <c r="AJ130" s="31"/>
       <c r="AK130" s="36"/>
       <c r="AL130" s="33"/>
-      <c r="AM130" s="49"/>
-      <c r="AN130" s="51"/>
+      <c r="AM130" s="55"/>
+      <c r="AN130" s="57"/>
     </row>
     <row r="131" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="88"/>
-      <c r="C131" s="48"/>
-      <c r="D131" s="91"/>
+      <c r="B131" s="60"/>
+      <c r="C131" s="67"/>
+      <c r="D131" s="68"/>
       <c r="E131" s="11" t="s">
         <v>12</v>
       </c>
@@ -7243,15 +7242,15 @@
       <c r="AJ131" s="35"/>
       <c r="AK131" s="37"/>
       <c r="AL131" s="34"/>
-      <c r="AM131" s="82"/>
-      <c r="AN131" s="66"/>
+      <c r="AM131" s="69"/>
+      <c r="AN131" s="70"/>
     </row>
     <row r="132" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="67">
+      <c r="B132" s="49">
         <v>63</v>
       </c>
-      <c r="C132" s="47"/>
-      <c r="D132" s="86"/>
+      <c r="C132" s="51"/>
+      <c r="D132" s="53"/>
       <c r="E132" s="7" t="s">
         <v>10</v>
       </c>
@@ -7290,13 +7289,13 @@
       <c r="AJ132" s="31"/>
       <c r="AK132" s="36"/>
       <c r="AL132" s="33"/>
-      <c r="AM132" s="49"/>
-      <c r="AN132" s="51"/>
+      <c r="AM132" s="55"/>
+      <c r="AN132" s="57"/>
     </row>
     <row r="133" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="68"/>
-      <c r="C133" s="85"/>
-      <c r="D133" s="87"/>
+      <c r="B133" s="50"/>
+      <c r="C133" s="52"/>
+      <c r="D133" s="54"/>
       <c r="E133" s="9" t="s">
         <v>12</v>
       </c>
@@ -7335,15 +7334,15 @@
       <c r="AJ133" s="32"/>
       <c r="AK133" s="43"/>
       <c r="AL133" s="34"/>
-      <c r="AM133" s="50"/>
-      <c r="AN133" s="52"/>
+      <c r="AM133" s="56"/>
+      <c r="AN133" s="58"/>
     </row>
     <row r="134" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B134" s="78">
+      <c r="B134" s="59">
         <v>64</v>
       </c>
-      <c r="C134" s="47"/>
-      <c r="D134" s="86"/>
+      <c r="C134" s="51"/>
+      <c r="D134" s="53"/>
       <c r="E134" s="7" t="s">
         <v>10</v>
       </c>
@@ -7382,13 +7381,13 @@
       <c r="AJ134" s="31"/>
       <c r="AK134" s="36"/>
       <c r="AL134" s="33"/>
-      <c r="AM134" s="49"/>
-      <c r="AN134" s="51"/>
+      <c r="AM134" s="55"/>
+      <c r="AN134" s="57"/>
     </row>
     <row r="135" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="88"/>
-      <c r="C135" s="85"/>
-      <c r="D135" s="87"/>
+      <c r="B135" s="60"/>
+      <c r="C135" s="52"/>
+      <c r="D135" s="54"/>
       <c r="E135" s="9" t="s">
         <v>12</v>
       </c>
@@ -7427,15 +7426,15 @@
       <c r="AJ135" s="32"/>
       <c r="AK135" s="43"/>
       <c r="AL135" s="34"/>
-      <c r="AM135" s="50"/>
-      <c r="AN135" s="52"/>
+      <c r="AM135" s="56"/>
+      <c r="AN135" s="58"/>
     </row>
     <row r="136" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" s="67">
+      <c r="B136" s="49">
         <v>65</v>
       </c>
-      <c r="C136" s="47"/>
-      <c r="D136" s="86"/>
+      <c r="C136" s="51"/>
+      <c r="D136" s="53"/>
       <c r="E136" s="7" t="s">
         <v>10</v>
       </c>
@@ -7474,13 +7473,13 @@
       <c r="AJ136" s="31"/>
       <c r="AK136" s="36"/>
       <c r="AL136" s="33"/>
-      <c r="AM136" s="49"/>
-      <c r="AN136" s="51"/>
+      <c r="AM136" s="55"/>
+      <c r="AN136" s="57"/>
     </row>
     <row r="137" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="68"/>
-      <c r="C137" s="85"/>
-      <c r="D137" s="87"/>
+      <c r="B137" s="50"/>
+      <c r="C137" s="52"/>
+      <c r="D137" s="54"/>
       <c r="E137" s="9" t="s">
         <v>12</v>
       </c>
@@ -7519,15 +7518,15 @@
       <c r="AJ137" s="32"/>
       <c r="AK137" s="43"/>
       <c r="AL137" s="34"/>
-      <c r="AM137" s="50"/>
-      <c r="AN137" s="52"/>
+      <c r="AM137" s="56"/>
+      <c r="AN137" s="58"/>
     </row>
     <row r="138" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="78">
+      <c r="B138" s="59">
         <v>66</v>
       </c>
-      <c r="C138" s="47"/>
-      <c r="D138" s="86"/>
+      <c r="C138" s="51"/>
+      <c r="D138" s="53"/>
       <c r="E138" s="7" t="s">
         <v>10</v>
       </c>
@@ -7566,13 +7565,13 @@
       <c r="AJ138" s="31"/>
       <c r="AK138" s="36"/>
       <c r="AL138" s="33"/>
-      <c r="AM138" s="49"/>
-      <c r="AN138" s="51"/>
+      <c r="AM138" s="55"/>
+      <c r="AN138" s="57"/>
     </row>
     <row r="139" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="88"/>
-      <c r="C139" s="85"/>
-      <c r="D139" s="87"/>
+      <c r="B139" s="60"/>
+      <c r="C139" s="52"/>
+      <c r="D139" s="54"/>
       <c r="E139" s="9" t="s">
         <v>12</v>
       </c>
@@ -7611,15 +7610,15 @@
       <c r="AJ139" s="32"/>
       <c r="AK139" s="43"/>
       <c r="AL139" s="34"/>
-      <c r="AM139" s="50"/>
-      <c r="AN139" s="52"/>
+      <c r="AM139" s="56"/>
+      <c r="AN139" s="58"/>
     </row>
     <row r="140" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="67">
+      <c r="B140" s="49">
         <v>67</v>
       </c>
-      <c r="C140" s="47"/>
-      <c r="D140" s="86"/>
+      <c r="C140" s="51"/>
+      <c r="D140" s="53"/>
       <c r="E140" s="7" t="s">
         <v>10</v>
       </c>
@@ -7658,13 +7657,13 @@
       <c r="AJ140" s="31"/>
       <c r="AK140" s="36"/>
       <c r="AL140" s="33"/>
-      <c r="AM140" s="49"/>
-      <c r="AN140" s="51"/>
+      <c r="AM140" s="55"/>
+      <c r="AN140" s="57"/>
     </row>
     <row r="141" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="68"/>
-      <c r="C141" s="85"/>
-      <c r="D141" s="87"/>
+      <c r="B141" s="50"/>
+      <c r="C141" s="52"/>
+      <c r="D141" s="54"/>
       <c r="E141" s="9" t="s">
         <v>12</v>
       </c>
@@ -7703,15 +7702,15 @@
       <c r="AJ141" s="32"/>
       <c r="AK141" s="43"/>
       <c r="AL141" s="34"/>
-      <c r="AM141" s="50"/>
-      <c r="AN141" s="52"/>
+      <c r="AM141" s="56"/>
+      <c r="AN141" s="58"/>
     </row>
     <row r="142" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="78">
+      <c r="B142" s="59">
         <v>68</v>
       </c>
-      <c r="C142" s="47"/>
-      <c r="D142" s="86"/>
+      <c r="C142" s="51"/>
+      <c r="D142" s="53"/>
       <c r="E142" s="7" t="s">
         <v>10</v>
       </c>
@@ -7750,13 +7749,13 @@
       <c r="AJ142" s="31"/>
       <c r="AK142" s="36"/>
       <c r="AL142" s="33"/>
-      <c r="AM142" s="49"/>
-      <c r="AN142" s="51"/>
+      <c r="AM142" s="55"/>
+      <c r="AN142" s="57"/>
     </row>
     <row r="143" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="88"/>
-      <c r="C143" s="85"/>
-      <c r="D143" s="87"/>
+      <c r="B143" s="60"/>
+      <c r="C143" s="52"/>
+      <c r="D143" s="54"/>
       <c r="E143" s="9" t="s">
         <v>12</v>
       </c>
@@ -7795,15 +7794,15 @@
       <c r="AJ143" s="32"/>
       <c r="AK143" s="43"/>
       <c r="AL143" s="34"/>
-      <c r="AM143" s="50"/>
-      <c r="AN143" s="52"/>
+      <c r="AM143" s="56"/>
+      <c r="AN143" s="58"/>
     </row>
     <row r="144" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B144" s="67">
+      <c r="B144" s="49">
         <v>69</v>
       </c>
-      <c r="C144" s="47"/>
-      <c r="D144" s="86"/>
+      <c r="C144" s="51"/>
+      <c r="D144" s="53"/>
       <c r="E144" s="7" t="s">
         <v>10</v>
       </c>
@@ -7842,13 +7841,13 @@
       <c r="AJ144" s="31"/>
       <c r="AK144" s="36"/>
       <c r="AL144" s="33"/>
-      <c r="AM144" s="49"/>
-      <c r="AN144" s="51"/>
+      <c r="AM144" s="55"/>
+      <c r="AN144" s="57"/>
     </row>
     <row r="145" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="68"/>
-      <c r="C145" s="85"/>
-      <c r="D145" s="87"/>
+      <c r="B145" s="50"/>
+      <c r="C145" s="52"/>
+      <c r="D145" s="54"/>
       <c r="E145" s="9" t="s">
         <v>12</v>
       </c>
@@ -7887,15 +7886,15 @@
       <c r="AJ145" s="32"/>
       <c r="AK145" s="43"/>
       <c r="AL145" s="34"/>
-      <c r="AM145" s="50"/>
-      <c r="AN145" s="52"/>
+      <c r="AM145" s="56"/>
+      <c r="AN145" s="58"/>
     </row>
     <row r="146" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B146" s="78">
+      <c r="B146" s="59">
         <v>70</v>
       </c>
-      <c r="C146" s="47"/>
-      <c r="D146" s="86"/>
+      <c r="C146" s="51"/>
+      <c r="D146" s="53"/>
       <c r="E146" s="7" t="s">
         <v>10</v>
       </c>
@@ -7934,13 +7933,13 @@
       <c r="AJ146" s="31"/>
       <c r="AK146" s="36"/>
       <c r="AL146" s="33"/>
-      <c r="AM146" s="49"/>
-      <c r="AN146" s="51"/>
+      <c r="AM146" s="55"/>
+      <c r="AN146" s="57"/>
     </row>
     <row r="147" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="88"/>
-      <c r="C147" s="85"/>
-      <c r="D147" s="87"/>
+      <c r="B147" s="60"/>
+      <c r="C147" s="52"/>
+      <c r="D147" s="54"/>
       <c r="E147" s="9" t="s">
         <v>12</v>
       </c>
@@ -7979,15 +7978,15 @@
       <c r="AJ147" s="32"/>
       <c r="AK147" s="43"/>
       <c r="AL147" s="34"/>
-      <c r="AM147" s="50"/>
-      <c r="AN147" s="52"/>
+      <c r="AM147" s="56"/>
+      <c r="AN147" s="58"/>
     </row>
     <row r="148" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B148" s="67">
+      <c r="B148" s="49">
         <v>71</v>
       </c>
-      <c r="C148" s="47"/>
-      <c r="D148" s="86"/>
+      <c r="C148" s="51"/>
+      <c r="D148" s="53"/>
       <c r="E148" s="7" t="s">
         <v>10</v>
       </c>
@@ -8026,13 +8025,13 @@
       <c r="AJ148" s="31"/>
       <c r="AK148" s="36"/>
       <c r="AL148" s="33"/>
-      <c r="AM148" s="49"/>
-      <c r="AN148" s="51"/>
+      <c r="AM148" s="55"/>
+      <c r="AN148" s="57"/>
     </row>
     <row r="149" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="68"/>
-      <c r="C149" s="85"/>
-      <c r="D149" s="87"/>
+      <c r="B149" s="50"/>
+      <c r="C149" s="52"/>
+      <c r="D149" s="54"/>
       <c r="E149" s="9" t="s">
         <v>12</v>
       </c>
@@ -8071,15 +8070,15 @@
       <c r="AJ149" s="32"/>
       <c r="AK149" s="43"/>
       <c r="AL149" s="34"/>
-      <c r="AM149" s="50"/>
-      <c r="AN149" s="52"/>
+      <c r="AM149" s="56"/>
+      <c r="AN149" s="58"/>
     </row>
     <row r="150" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="78">
+      <c r="B150" s="59">
         <v>72</v>
       </c>
-      <c r="C150" s="47"/>
-      <c r="D150" s="86"/>
+      <c r="C150" s="51"/>
+      <c r="D150" s="53"/>
       <c r="E150" s="7" t="s">
         <v>10</v>
       </c>
@@ -8118,13 +8117,13 @@
       <c r="AJ150" s="31"/>
       <c r="AK150" s="36"/>
       <c r="AL150" s="33"/>
-      <c r="AM150" s="49"/>
-      <c r="AN150" s="51"/>
+      <c r="AM150" s="55"/>
+      <c r="AN150" s="57"/>
     </row>
     <row r="151" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="88"/>
-      <c r="C151" s="48"/>
-      <c r="D151" s="91"/>
+      <c r="B151" s="60"/>
+      <c r="C151" s="67"/>
+      <c r="D151" s="68"/>
       <c r="E151" s="11" t="s">
         <v>12</v>
       </c>
@@ -8163,15 +8162,15 @@
       <c r="AJ151" s="35"/>
       <c r="AK151" s="37"/>
       <c r="AL151" s="34"/>
-      <c r="AM151" s="82"/>
-      <c r="AN151" s="66"/>
+      <c r="AM151" s="69"/>
+      <c r="AN151" s="70"/>
     </row>
     <row r="152" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="67">
+      <c r="B152" s="49">
         <v>73</v>
       </c>
-      <c r="C152" s="47"/>
-      <c r="D152" s="89"/>
+      <c r="C152" s="51"/>
+      <c r="D152" s="61"/>
       <c r="E152" s="7" t="s">
         <v>10</v>
       </c>
@@ -8210,13 +8209,13 @@
       <c r="AJ152" s="31"/>
       <c r="AK152" s="36"/>
       <c r="AL152" s="33"/>
-      <c r="AM152" s="49"/>
-      <c r="AN152" s="51"/>
+      <c r="AM152" s="55"/>
+      <c r="AN152" s="57"/>
     </row>
     <row r="153" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="68"/>
-      <c r="C153" s="85"/>
-      <c r="D153" s="90"/>
+      <c r="B153" s="50"/>
+      <c r="C153" s="52"/>
+      <c r="D153" s="62"/>
       <c r="E153" s="9" t="s">
         <v>12</v>
       </c>
@@ -8255,15 +8254,15 @@
       <c r="AJ153" s="32"/>
       <c r="AK153" s="43"/>
       <c r="AL153" s="34"/>
-      <c r="AM153" s="50"/>
-      <c r="AN153" s="52"/>
+      <c r="AM153" s="56"/>
+      <c r="AN153" s="58"/>
     </row>
     <row r="154" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B154" s="78">
+      <c r="B154" s="59">
         <v>74</v>
       </c>
-      <c r="C154" s="47"/>
-      <c r="D154" s="89"/>
+      <c r="C154" s="51"/>
+      <c r="D154" s="61"/>
       <c r="E154" s="7" t="s">
         <v>10</v>
       </c>
@@ -8302,13 +8301,13 @@
       <c r="AJ154" s="31"/>
       <c r="AK154" s="36"/>
       <c r="AL154" s="33"/>
-      <c r="AM154" s="49"/>
-      <c r="AN154" s="51"/>
+      <c r="AM154" s="55"/>
+      <c r="AN154" s="57"/>
     </row>
     <row r="155" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="88"/>
-      <c r="C155" s="85"/>
-      <c r="D155" s="90"/>
+      <c r="B155" s="60"/>
+      <c r="C155" s="52"/>
+      <c r="D155" s="62"/>
       <c r="E155" s="9" t="s">
         <v>12</v>
       </c>
@@ -8347,15 +8346,15 @@
       <c r="AJ155" s="32"/>
       <c r="AK155" s="43"/>
       <c r="AL155" s="34"/>
-      <c r="AM155" s="50"/>
-      <c r="AN155" s="52"/>
+      <c r="AM155" s="56"/>
+      <c r="AN155" s="58"/>
     </row>
     <row r="156" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B156" s="67">
+      <c r="B156" s="49">
         <v>75</v>
       </c>
-      <c r="C156" s="47"/>
-      <c r="D156" s="89"/>
+      <c r="C156" s="51"/>
+      <c r="D156" s="61"/>
       <c r="E156" s="7" t="s">
         <v>10</v>
       </c>
@@ -8394,13 +8393,13 @@
       <c r="AJ156" s="31"/>
       <c r="AK156" s="36"/>
       <c r="AL156" s="33"/>
-      <c r="AM156" s="49"/>
-      <c r="AN156" s="51"/>
+      <c r="AM156" s="55"/>
+      <c r="AN156" s="57"/>
     </row>
     <row r="157" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="68"/>
-      <c r="C157" s="85"/>
-      <c r="D157" s="90"/>
+      <c r="B157" s="50"/>
+      <c r="C157" s="52"/>
+      <c r="D157" s="62"/>
       <c r="E157" s="9" t="s">
         <v>12</v>
       </c>
@@ -8439,15 +8438,15 @@
       <c r="AJ157" s="32"/>
       <c r="AK157" s="43"/>
       <c r="AL157" s="34"/>
-      <c r="AM157" s="50"/>
-      <c r="AN157" s="52"/>
+      <c r="AM157" s="56"/>
+      <c r="AN157" s="58"/>
     </row>
     <row r="158" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="78">
+      <c r="B158" s="59">
         <v>76</v>
       </c>
-      <c r="C158" s="47"/>
-      <c r="D158" s="89"/>
+      <c r="C158" s="51"/>
+      <c r="D158" s="61"/>
       <c r="E158" s="7" t="s">
         <v>10</v>
       </c>
@@ -8486,13 +8485,13 @@
       <c r="AJ158" s="31"/>
       <c r="AK158" s="36"/>
       <c r="AL158" s="33"/>
-      <c r="AM158" s="49"/>
-      <c r="AN158" s="51"/>
+      <c r="AM158" s="55"/>
+      <c r="AN158" s="57"/>
     </row>
     <row r="159" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="88"/>
-      <c r="C159" s="85"/>
-      <c r="D159" s="90"/>
+      <c r="B159" s="60"/>
+      <c r="C159" s="52"/>
+      <c r="D159" s="62"/>
       <c r="E159" s="9" t="s">
         <v>12</v>
       </c>
@@ -8531,15 +8530,15 @@
       <c r="AJ159" s="32"/>
       <c r="AK159" s="43"/>
       <c r="AL159" s="34"/>
-      <c r="AM159" s="50"/>
-      <c r="AN159" s="52"/>
+      <c r="AM159" s="56"/>
+      <c r="AN159" s="58"/>
     </row>
     <row r="160" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="67">
+      <c r="B160" s="49">
         <v>77</v>
       </c>
-      <c r="C160" s="47"/>
-      <c r="D160" s="86"/>
+      <c r="C160" s="51"/>
+      <c r="D160" s="53"/>
       <c r="E160" s="7" t="s">
         <v>10</v>
       </c>
@@ -8578,13 +8577,13 @@
       <c r="AJ160" s="31"/>
       <c r="AK160" s="36"/>
       <c r="AL160" s="33"/>
-      <c r="AM160" s="49"/>
-      <c r="AN160" s="51"/>
+      <c r="AM160" s="55"/>
+      <c r="AN160" s="57"/>
     </row>
     <row r="161" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="68"/>
-      <c r="C161" s="85"/>
-      <c r="D161" s="87"/>
+      <c r="B161" s="50"/>
+      <c r="C161" s="52"/>
+      <c r="D161" s="54"/>
       <c r="E161" s="9" t="s">
         <v>12</v>
       </c>
@@ -8623,15 +8622,15 @@
       <c r="AJ161" s="32"/>
       <c r="AK161" s="43"/>
       <c r="AL161" s="34"/>
-      <c r="AM161" s="50"/>
-      <c r="AN161" s="52"/>
+      <c r="AM161" s="56"/>
+      <c r="AN161" s="58"/>
     </row>
     <row r="162" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B162" s="78">
+      <c r="B162" s="59">
         <v>78</v>
       </c>
-      <c r="C162" s="47"/>
-      <c r="D162" s="86"/>
+      <c r="C162" s="51"/>
+      <c r="D162" s="53"/>
       <c r="E162" s="7" t="s">
         <v>10</v>
       </c>
@@ -8670,13 +8669,13 @@
       <c r="AJ162" s="31"/>
       <c r="AK162" s="36"/>
       <c r="AL162" s="33"/>
-      <c r="AM162" s="49"/>
-      <c r="AN162" s="51"/>
+      <c r="AM162" s="55"/>
+      <c r="AN162" s="57"/>
     </row>
     <row r="163" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="88"/>
-      <c r="C163" s="85"/>
-      <c r="D163" s="87"/>
+      <c r="B163" s="60"/>
+      <c r="C163" s="52"/>
+      <c r="D163" s="54"/>
       <c r="E163" s="9" t="s">
         <v>12</v>
       </c>
@@ -8715,15 +8714,15 @@
       <c r="AJ163" s="32"/>
       <c r="AK163" s="43"/>
       <c r="AL163" s="34"/>
-      <c r="AM163" s="50"/>
-      <c r="AN163" s="52"/>
+      <c r="AM163" s="56"/>
+      <c r="AN163" s="58"/>
     </row>
     <row r="164" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B164" s="67">
+      <c r="B164" s="49">
         <v>79</v>
       </c>
-      <c r="C164" s="47"/>
-      <c r="D164" s="86"/>
+      <c r="C164" s="51"/>
+      <c r="D164" s="53"/>
       <c r="E164" s="7" t="s">
         <v>10</v>
       </c>
@@ -8762,13 +8761,13 @@
       <c r="AJ164" s="31"/>
       <c r="AK164" s="36"/>
       <c r="AL164" s="33"/>
-      <c r="AM164" s="49"/>
-      <c r="AN164" s="51"/>
+      <c r="AM164" s="55"/>
+      <c r="AN164" s="57"/>
     </row>
     <row r="165" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="68"/>
-      <c r="C165" s="85"/>
-      <c r="D165" s="87"/>
+      <c r="B165" s="50"/>
+      <c r="C165" s="52"/>
+      <c r="D165" s="54"/>
       <c r="E165" s="9" t="s">
         <v>12</v>
       </c>
@@ -8807,15 +8806,15 @@
       <c r="AJ165" s="32"/>
       <c r="AK165" s="43"/>
       <c r="AL165" s="34"/>
-      <c r="AM165" s="50"/>
-      <c r="AN165" s="52"/>
+      <c r="AM165" s="56"/>
+      <c r="AN165" s="58"/>
     </row>
     <row r="166" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B166" s="78">
+      <c r="B166" s="59">
         <v>80</v>
       </c>
-      <c r="C166" s="47"/>
-      <c r="D166" s="86"/>
+      <c r="C166" s="51"/>
+      <c r="D166" s="53"/>
       <c r="E166" s="7" t="s">
         <v>10</v>
       </c>
@@ -8854,13 +8853,13 @@
       <c r="AJ166" s="31"/>
       <c r="AK166" s="36"/>
       <c r="AL166" s="33"/>
-      <c r="AM166" s="49"/>
-      <c r="AN166" s="51"/>
+      <c r="AM166" s="55"/>
+      <c r="AN166" s="57"/>
     </row>
     <row r="167" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="88"/>
-      <c r="C167" s="85"/>
-      <c r="D167" s="87"/>
+      <c r="B167" s="60"/>
+      <c r="C167" s="52"/>
+      <c r="D167" s="54"/>
       <c r="E167" s="9" t="s">
         <v>12</v>
       </c>
@@ -8899,15 +8898,15 @@
       <c r="AJ167" s="32"/>
       <c r="AK167" s="43"/>
       <c r="AL167" s="34"/>
-      <c r="AM167" s="50"/>
-      <c r="AN167" s="52"/>
+      <c r="AM167" s="56"/>
+      <c r="AN167" s="58"/>
     </row>
     <row r="168" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="67">
+      <c r="B168" s="49">
         <v>81</v>
       </c>
-      <c r="C168" s="47"/>
-      <c r="D168" s="86"/>
+      <c r="C168" s="51"/>
+      <c r="D168" s="53"/>
       <c r="E168" s="7" t="s">
         <v>10</v>
       </c>
@@ -8946,13 +8945,13 @@
       <c r="AJ168" s="31"/>
       <c r="AK168" s="36"/>
       <c r="AL168" s="33"/>
-      <c r="AM168" s="49"/>
-      <c r="AN168" s="51"/>
+      <c r="AM168" s="55"/>
+      <c r="AN168" s="57"/>
     </row>
     <row r="169" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="68"/>
-      <c r="C169" s="85"/>
-      <c r="D169" s="87"/>
+      <c r="B169" s="50"/>
+      <c r="C169" s="52"/>
+      <c r="D169" s="54"/>
       <c r="E169" s="9" t="s">
         <v>12</v>
       </c>
@@ -8991,15 +8990,15 @@
       <c r="AJ169" s="32"/>
       <c r="AK169" s="43"/>
       <c r="AL169" s="34"/>
-      <c r="AM169" s="50"/>
-      <c r="AN169" s="52"/>
+      <c r="AM169" s="56"/>
+      <c r="AN169" s="58"/>
     </row>
     <row r="170" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B170" s="78">
+      <c r="B170" s="59">
         <v>82</v>
       </c>
-      <c r="C170" s="47"/>
-      <c r="D170" s="86"/>
+      <c r="C170" s="51"/>
+      <c r="D170" s="53"/>
       <c r="E170" s="7" t="s">
         <v>10</v>
       </c>
@@ -9038,13 +9037,13 @@
       <c r="AJ170" s="31"/>
       <c r="AK170" s="36"/>
       <c r="AL170" s="33"/>
-      <c r="AM170" s="49"/>
-      <c r="AN170" s="51"/>
+      <c r="AM170" s="55"/>
+      <c r="AN170" s="57"/>
     </row>
     <row r="171" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="88"/>
-      <c r="C171" s="85"/>
-      <c r="D171" s="87"/>
+      <c r="B171" s="60"/>
+      <c r="C171" s="52"/>
+      <c r="D171" s="54"/>
       <c r="E171" s="9" t="s">
         <v>12</v>
       </c>
@@ -9083,15 +9082,15 @@
       <c r="AJ171" s="32"/>
       <c r="AK171" s="43"/>
       <c r="AL171" s="34"/>
-      <c r="AM171" s="50"/>
-      <c r="AN171" s="52"/>
+      <c r="AM171" s="56"/>
+      <c r="AN171" s="58"/>
     </row>
     <row r="172" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B172" s="67">
+      <c r="B172" s="49">
         <v>83</v>
       </c>
-      <c r="C172" s="47"/>
-      <c r="D172" s="86"/>
+      <c r="C172" s="51"/>
+      <c r="D172" s="53"/>
       <c r="E172" s="7" t="s">
         <v>10</v>
       </c>
@@ -9130,13 +9129,13 @@
       <c r="AJ172" s="31"/>
       <c r="AK172" s="36"/>
       <c r="AL172" s="33"/>
-      <c r="AM172" s="49"/>
-      <c r="AN172" s="51"/>
+      <c r="AM172" s="55"/>
+      <c r="AN172" s="57"/>
     </row>
     <row r="173" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="68"/>
-      <c r="C173" s="85"/>
-      <c r="D173" s="87"/>
+      <c r="B173" s="50"/>
+      <c r="C173" s="52"/>
+      <c r="D173" s="54"/>
       <c r="E173" s="9" t="s">
         <v>12</v>
       </c>
@@ -9175,15 +9174,15 @@
       <c r="AJ173" s="32"/>
       <c r="AK173" s="43"/>
       <c r="AL173" s="34"/>
-      <c r="AM173" s="50"/>
-      <c r="AN173" s="52"/>
+      <c r="AM173" s="56"/>
+      <c r="AN173" s="58"/>
     </row>
     <row r="174" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B174" s="78">
+      <c r="B174" s="59">
         <v>84</v>
       </c>
-      <c r="C174" s="47"/>
-      <c r="D174" s="86"/>
+      <c r="C174" s="51"/>
+      <c r="D174" s="53"/>
       <c r="E174" s="7" t="s">
         <v>10</v>
       </c>
@@ -9222,13 +9221,13 @@
       <c r="AJ174" s="31"/>
       <c r="AK174" s="36"/>
       <c r="AL174" s="33"/>
-      <c r="AM174" s="49"/>
-      <c r="AN174" s="51"/>
+      <c r="AM174" s="55"/>
+      <c r="AN174" s="57"/>
     </row>
     <row r="175" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="88"/>
-      <c r="C175" s="85"/>
-      <c r="D175" s="87"/>
+      <c r="B175" s="60"/>
+      <c r="C175" s="52"/>
+      <c r="D175" s="54"/>
       <c r="E175" s="9" t="s">
         <v>12</v>
       </c>
@@ -9267,15 +9266,15 @@
       <c r="AJ175" s="32"/>
       <c r="AK175" s="43"/>
       <c r="AL175" s="34"/>
-      <c r="AM175" s="50"/>
-      <c r="AN175" s="52"/>
+      <c r="AM175" s="56"/>
+      <c r="AN175" s="58"/>
     </row>
     <row r="176" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B176" s="67">
+      <c r="B176" s="49">
         <v>85</v>
       </c>
-      <c r="C176" s="47"/>
-      <c r="D176" s="86"/>
+      <c r="C176" s="51"/>
+      <c r="D176" s="53"/>
       <c r="E176" s="7" t="s">
         <v>10</v>
       </c>
@@ -9314,13 +9313,13 @@
       <c r="AJ176" s="31"/>
       <c r="AK176" s="36"/>
       <c r="AL176" s="33"/>
-      <c r="AM176" s="49"/>
-      <c r="AN176" s="51"/>
+      <c r="AM176" s="55"/>
+      <c r="AN176" s="57"/>
     </row>
     <row r="177" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="68"/>
-      <c r="C177" s="85"/>
-      <c r="D177" s="87"/>
+      <c r="B177" s="50"/>
+      <c r="C177" s="52"/>
+      <c r="D177" s="54"/>
       <c r="E177" s="9" t="s">
         <v>12</v>
       </c>
@@ -9359,15 +9358,15 @@
       <c r="AJ177" s="32"/>
       <c r="AK177" s="43"/>
       <c r="AL177" s="34"/>
-      <c r="AM177" s="50"/>
-      <c r="AN177" s="52"/>
+      <c r="AM177" s="56"/>
+      <c r="AN177" s="58"/>
     </row>
     <row r="178" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="78">
+      <c r="B178" s="59">
         <v>86</v>
       </c>
-      <c r="C178" s="47"/>
-      <c r="D178" s="89"/>
+      <c r="C178" s="51"/>
+      <c r="D178" s="61"/>
       <c r="E178" s="7" t="s">
         <v>10</v>
       </c>
@@ -9406,13 +9405,13 @@
       <c r="AJ178" s="31"/>
       <c r="AK178" s="36"/>
       <c r="AL178" s="33"/>
-      <c r="AM178" s="49"/>
-      <c r="AN178" s="51"/>
+      <c r="AM178" s="55"/>
+      <c r="AN178" s="57"/>
     </row>
     <row r="179" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="88"/>
-      <c r="C179" s="85"/>
-      <c r="D179" s="90"/>
+      <c r="B179" s="60"/>
+      <c r="C179" s="52"/>
+      <c r="D179" s="62"/>
       <c r="E179" s="9" t="s">
         <v>12</v>
       </c>
@@ -9451,15 +9450,15 @@
       <c r="AJ179" s="32"/>
       <c r="AK179" s="43"/>
       <c r="AL179" s="34"/>
-      <c r="AM179" s="50"/>
-      <c r="AN179" s="52"/>
+      <c r="AM179" s="56"/>
+      <c r="AN179" s="58"/>
     </row>
     <row r="180" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B180" s="67">
+      <c r="B180" s="49">
         <v>87</v>
       </c>
-      <c r="C180" s="47"/>
-      <c r="D180" s="89"/>
+      <c r="C180" s="51"/>
+      <c r="D180" s="61"/>
       <c r="E180" s="7" t="s">
         <v>10</v>
       </c>
@@ -9498,13 +9497,13 @@
       <c r="AJ180" s="31"/>
       <c r="AK180" s="36"/>
       <c r="AL180" s="33"/>
-      <c r="AM180" s="49"/>
-      <c r="AN180" s="51"/>
+      <c r="AM180" s="55"/>
+      <c r="AN180" s="57"/>
     </row>
     <row r="181" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="68"/>
-      <c r="C181" s="85"/>
-      <c r="D181" s="90"/>
+      <c r="B181" s="50"/>
+      <c r="C181" s="52"/>
+      <c r="D181" s="62"/>
       <c r="E181" s="9" t="s">
         <v>12</v>
       </c>
@@ -9543,15 +9542,15 @@
       <c r="AJ181" s="32"/>
       <c r="AK181" s="43"/>
       <c r="AL181" s="34"/>
-      <c r="AM181" s="50"/>
-      <c r="AN181" s="52"/>
+      <c r="AM181" s="56"/>
+      <c r="AN181" s="58"/>
     </row>
     <row r="182" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="78">
+      <c r="B182" s="59">
         <v>88</v>
       </c>
-      <c r="C182" s="58"/>
-      <c r="D182" s="93"/>
+      <c r="C182" s="63"/>
+      <c r="D182" s="65"/>
       <c r="E182" s="7" t="s">
         <v>10</v>
       </c>
@@ -9590,13 +9589,13 @@
       <c r="AJ182" s="31"/>
       <c r="AK182" s="36"/>
       <c r="AL182" s="33"/>
-      <c r="AM182" s="49"/>
-      <c r="AN182" s="51"/>
+      <c r="AM182" s="55"/>
+      <c r="AN182" s="57"/>
     </row>
     <row r="183" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="88"/>
-      <c r="C183" s="92"/>
-      <c r="D183" s="94"/>
+      <c r="B183" s="60"/>
+      <c r="C183" s="64"/>
+      <c r="D183" s="66"/>
       <c r="E183" s="9" t="s">
         <v>12</v>
       </c>
@@ -9635,15 +9634,15 @@
       <c r="AJ183" s="32"/>
       <c r="AK183" s="43"/>
       <c r="AL183" s="34"/>
-      <c r="AM183" s="50"/>
-      <c r="AN183" s="52"/>
+      <c r="AM183" s="56"/>
+      <c r="AN183" s="58"/>
     </row>
     <row r="184" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B184" s="67">
+      <c r="B184" s="49">
         <v>89</v>
       </c>
-      <c r="C184" s="47"/>
-      <c r="D184" s="89"/>
+      <c r="C184" s="51"/>
+      <c r="D184" s="61"/>
       <c r="E184" s="7" t="s">
         <v>10</v>
       </c>
@@ -9682,13 +9681,13 @@
       <c r="AJ184" s="31"/>
       <c r="AK184" s="36"/>
       <c r="AL184" s="33"/>
-      <c r="AM184" s="49"/>
-      <c r="AN184" s="51"/>
+      <c r="AM184" s="55"/>
+      <c r="AN184" s="57"/>
     </row>
     <row r="185" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="68"/>
-      <c r="C185" s="85"/>
-      <c r="D185" s="90"/>
+      <c r="B185" s="50"/>
+      <c r="C185" s="52"/>
+      <c r="D185" s="62"/>
       <c r="E185" s="9" t="s">
         <v>12</v>
       </c>
@@ -9727,15 +9726,15 @@
       <c r="AJ185" s="32"/>
       <c r="AK185" s="43"/>
       <c r="AL185" s="34"/>
-      <c r="AM185" s="50"/>
-      <c r="AN185" s="52"/>
+      <c r="AM185" s="56"/>
+      <c r="AN185" s="58"/>
     </row>
     <row r="186" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B186" s="78">
+      <c r="B186" s="59">
         <v>90</v>
       </c>
-      <c r="C186" s="47"/>
-      <c r="D186" s="89"/>
+      <c r="C186" s="51"/>
+      <c r="D186" s="61"/>
       <c r="E186" s="7" t="s">
         <v>10</v>
       </c>
@@ -9774,13 +9773,13 @@
       <c r="AJ186" s="31"/>
       <c r="AK186" s="36"/>
       <c r="AL186" s="33"/>
-      <c r="AM186" s="49"/>
-      <c r="AN186" s="51"/>
+      <c r="AM186" s="55"/>
+      <c r="AN186" s="57"/>
     </row>
     <row r="187" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="88"/>
-      <c r="C187" s="85"/>
-      <c r="D187" s="90"/>
+      <c r="B187" s="60"/>
+      <c r="C187" s="52"/>
+      <c r="D187" s="62"/>
       <c r="E187" s="9" t="s">
         <v>12</v>
       </c>
@@ -9819,15 +9818,15 @@
       <c r="AJ187" s="32"/>
       <c r="AK187" s="43"/>
       <c r="AL187" s="34"/>
-      <c r="AM187" s="50"/>
-      <c r="AN187" s="52"/>
+      <c r="AM187" s="56"/>
+      <c r="AN187" s="58"/>
     </row>
     <row r="188" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B188" s="67">
+      <c r="B188" s="49">
         <v>91</v>
       </c>
-      <c r="C188" s="47"/>
-      <c r="D188" s="89"/>
+      <c r="C188" s="51"/>
+      <c r="D188" s="61"/>
       <c r="E188" s="7" t="s">
         <v>10</v>
       </c>
@@ -9866,13 +9865,13 @@
       <c r="AJ188" s="31"/>
       <c r="AK188" s="36"/>
       <c r="AL188" s="33"/>
-      <c r="AM188" s="49"/>
-      <c r="AN188" s="51"/>
+      <c r="AM188" s="55"/>
+      <c r="AN188" s="57"/>
     </row>
     <row r="189" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="68"/>
-      <c r="C189" s="85"/>
-      <c r="D189" s="90"/>
+      <c r="B189" s="50"/>
+      <c r="C189" s="52"/>
+      <c r="D189" s="62"/>
       <c r="E189" s="9" t="s">
         <v>12</v>
       </c>
@@ -9911,15 +9910,15 @@
       <c r="AJ189" s="32"/>
       <c r="AK189" s="43"/>
       <c r="AL189" s="34"/>
-      <c r="AM189" s="50"/>
-      <c r="AN189" s="52"/>
+      <c r="AM189" s="56"/>
+      <c r="AN189" s="58"/>
     </row>
     <row r="190" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B190" s="78">
+      <c r="B190" s="59">
         <v>92</v>
       </c>
-      <c r="C190" s="47"/>
-      <c r="D190" s="89"/>
+      <c r="C190" s="51"/>
+      <c r="D190" s="61"/>
       <c r="E190" s="7" t="s">
         <v>10</v>
       </c>
@@ -9958,13 +9957,13 @@
       <c r="AJ190" s="31"/>
       <c r="AK190" s="36"/>
       <c r="AL190" s="33"/>
-      <c r="AM190" s="49"/>
-      <c r="AN190" s="51"/>
+      <c r="AM190" s="55"/>
+      <c r="AN190" s="57"/>
     </row>
     <row r="191" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="88"/>
-      <c r="C191" s="85"/>
-      <c r="D191" s="90"/>
+      <c r="B191" s="60"/>
+      <c r="C191" s="52"/>
+      <c r="D191" s="62"/>
       <c r="E191" s="9" t="s">
         <v>12</v>
       </c>
@@ -10003,15 +10002,15 @@
       <c r="AJ191" s="32"/>
       <c r="AK191" s="43"/>
       <c r="AL191" s="34"/>
-      <c r="AM191" s="50"/>
-      <c r="AN191" s="52"/>
+      <c r="AM191" s="56"/>
+      <c r="AN191" s="58"/>
     </row>
     <row r="192" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B192" s="67">
+      <c r="B192" s="49">
         <v>93</v>
       </c>
-      <c r="C192" s="47"/>
-      <c r="D192" s="86"/>
+      <c r="C192" s="51"/>
+      <c r="D192" s="53"/>
       <c r="E192" s="7" t="s">
         <v>10</v>
       </c>
@@ -10050,13 +10049,13 @@
       <c r="AJ192" s="31"/>
       <c r="AK192" s="36"/>
       <c r="AL192" s="33"/>
-      <c r="AM192" s="49"/>
-      <c r="AN192" s="51"/>
+      <c r="AM192" s="55"/>
+      <c r="AN192" s="57"/>
     </row>
     <row r="193" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="68"/>
-      <c r="C193" s="85"/>
-      <c r="D193" s="87"/>
+      <c r="B193" s="50"/>
+      <c r="C193" s="52"/>
+      <c r="D193" s="54"/>
       <c r="E193" s="9" t="s">
         <v>12</v>
       </c>
@@ -10095,15 +10094,15 @@
       <c r="AJ193" s="32"/>
       <c r="AK193" s="43"/>
       <c r="AL193" s="34"/>
-      <c r="AM193" s="50"/>
-      <c r="AN193" s="52"/>
+      <c r="AM193" s="56"/>
+      <c r="AN193" s="58"/>
     </row>
     <row r="194" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="78">
+      <c r="B194" s="59">
         <v>94</v>
       </c>
-      <c r="C194" s="47"/>
-      <c r="D194" s="86"/>
+      <c r="C194" s="51"/>
+      <c r="D194" s="53"/>
       <c r="E194" s="7" t="s">
         <v>10</v>
       </c>
@@ -10142,13 +10141,13 @@
       <c r="AJ194" s="31"/>
       <c r="AK194" s="36"/>
       <c r="AL194" s="33"/>
-      <c r="AM194" s="49"/>
-      <c r="AN194" s="51"/>
+      <c r="AM194" s="55"/>
+      <c r="AN194" s="57"/>
     </row>
     <row r="195" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="88"/>
-      <c r="C195" s="85"/>
-      <c r="D195" s="87"/>
+      <c r="B195" s="60"/>
+      <c r="C195" s="52"/>
+      <c r="D195" s="54"/>
       <c r="E195" s="9" t="s">
         <v>12</v>
       </c>
@@ -10187,15 +10186,15 @@
       <c r="AJ195" s="32"/>
       <c r="AK195" s="43"/>
       <c r="AL195" s="34"/>
-      <c r="AM195" s="50"/>
-      <c r="AN195" s="52"/>
+      <c r="AM195" s="56"/>
+      <c r="AN195" s="58"/>
     </row>
     <row r="196" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B196" s="67">
+      <c r="B196" s="49">
         <v>95</v>
       </c>
-      <c r="C196" s="47"/>
-      <c r="D196" s="86"/>
+      <c r="C196" s="51"/>
+      <c r="D196" s="53"/>
       <c r="E196" s="7" t="s">
         <v>10</v>
       </c>
@@ -10234,13 +10233,13 @@
       <c r="AJ196" s="31"/>
       <c r="AK196" s="36"/>
       <c r="AL196" s="33"/>
-      <c r="AM196" s="49"/>
-      <c r="AN196" s="51"/>
+      <c r="AM196" s="55"/>
+      <c r="AN196" s="57"/>
     </row>
     <row r="197" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B197" s="68"/>
-      <c r="C197" s="85"/>
-      <c r="D197" s="87"/>
+      <c r="B197" s="50"/>
+      <c r="C197" s="52"/>
+      <c r="D197" s="54"/>
       <c r="E197" s="9" t="s">
         <v>12</v>
       </c>
@@ -10279,15 +10278,15 @@
       <c r="AJ197" s="32"/>
       <c r="AK197" s="43"/>
       <c r="AL197" s="34"/>
-      <c r="AM197" s="50"/>
-      <c r="AN197" s="52"/>
+      <c r="AM197" s="56"/>
+      <c r="AN197" s="58"/>
     </row>
     <row r="198" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B198" s="78">
+      <c r="B198" s="59">
         <v>96</v>
       </c>
-      <c r="C198" s="47"/>
-      <c r="D198" s="86"/>
+      <c r="C198" s="51"/>
+      <c r="D198" s="53"/>
       <c r="E198" s="7" t="s">
         <v>10</v>
       </c>
@@ -10326,13 +10325,13 @@
       <c r="AJ198" s="31"/>
       <c r="AK198" s="36"/>
       <c r="AL198" s="33"/>
-      <c r="AM198" s="49"/>
-      <c r="AN198" s="51"/>
+      <c r="AM198" s="55"/>
+      <c r="AN198" s="57"/>
     </row>
     <row r="199" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="88"/>
-      <c r="C199" s="85"/>
-      <c r="D199" s="87"/>
+      <c r="B199" s="60"/>
+      <c r="C199" s="52"/>
+      <c r="D199" s="54"/>
       <c r="E199" s="9" t="s">
         <v>12</v>
       </c>
@@ -10371,15 +10370,15 @@
       <c r="AJ199" s="32"/>
       <c r="AK199" s="43"/>
       <c r="AL199" s="34"/>
-      <c r="AM199" s="50"/>
-      <c r="AN199" s="52"/>
+      <c r="AM199" s="56"/>
+      <c r="AN199" s="58"/>
     </row>
     <row r="200" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B200" s="67">
+      <c r="B200" s="49">
         <v>97</v>
       </c>
-      <c r="C200" s="47"/>
-      <c r="D200" s="86"/>
+      <c r="C200" s="51"/>
+      <c r="D200" s="53"/>
       <c r="E200" s="7" t="s">
         <v>10</v>
       </c>
@@ -10418,13 +10417,13 @@
       <c r="AJ200" s="31"/>
       <c r="AK200" s="36"/>
       <c r="AL200" s="33"/>
-      <c r="AM200" s="49"/>
-      <c r="AN200" s="51"/>
+      <c r="AM200" s="55"/>
+      <c r="AN200" s="57"/>
     </row>
     <row r="201" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="68"/>
-      <c r="C201" s="85"/>
-      <c r="D201" s="87"/>
+      <c r="B201" s="50"/>
+      <c r="C201" s="52"/>
+      <c r="D201" s="54"/>
       <c r="E201" s="9" t="s">
         <v>12</v>
       </c>
@@ -10463,15 +10462,15 @@
       <c r="AJ201" s="32"/>
       <c r="AK201" s="43"/>
       <c r="AL201" s="34"/>
-      <c r="AM201" s="50"/>
-      <c r="AN201" s="52"/>
+      <c r="AM201" s="56"/>
+      <c r="AN201" s="58"/>
     </row>
     <row r="202" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B202" s="78">
+      <c r="B202" s="59">
         <v>98</v>
       </c>
-      <c r="C202" s="47"/>
-      <c r="D202" s="86"/>
+      <c r="C202" s="51"/>
+      <c r="D202" s="53"/>
       <c r="E202" s="7" t="s">
         <v>10</v>
       </c>
@@ -10510,13 +10509,13 @@
       <c r="AJ202" s="31"/>
       <c r="AK202" s="36"/>
       <c r="AL202" s="33"/>
-      <c r="AM202" s="49"/>
-      <c r="AN202" s="51"/>
+      <c r="AM202" s="55"/>
+      <c r="AN202" s="57"/>
     </row>
     <row r="203" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="88"/>
-      <c r="C203" s="85"/>
-      <c r="D203" s="87"/>
+      <c r="B203" s="60"/>
+      <c r="C203" s="52"/>
+      <c r="D203" s="54"/>
       <c r="E203" s="9" t="s">
         <v>12</v>
       </c>
@@ -10555,15 +10554,15 @@
       <c r="AJ203" s="32"/>
       <c r="AK203" s="43"/>
       <c r="AL203" s="34"/>
-      <c r="AM203" s="50"/>
-      <c r="AN203" s="52"/>
+      <c r="AM203" s="56"/>
+      <c r="AN203" s="58"/>
     </row>
     <row r="204" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B204" s="67">
+      <c r="B204" s="49">
         <v>99</v>
       </c>
-      <c r="C204" s="47"/>
-      <c r="D204" s="86"/>
+      <c r="C204" s="51"/>
+      <c r="D204" s="53"/>
       <c r="E204" s="7" t="s">
         <v>10</v>
       </c>
@@ -10602,13 +10601,13 @@
       <c r="AJ204" s="31"/>
       <c r="AK204" s="36"/>
       <c r="AL204" s="33"/>
-      <c r="AM204" s="49"/>
-      <c r="AN204" s="51"/>
+      <c r="AM204" s="55"/>
+      <c r="AN204" s="57"/>
     </row>
     <row r="205" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="68"/>
-      <c r="C205" s="85"/>
-      <c r="D205" s="87"/>
+      <c r="B205" s="50"/>
+      <c r="C205" s="52"/>
+      <c r="D205" s="54"/>
       <c r="E205" s="9" t="s">
         <v>12</v>
       </c>
@@ -10647,15 +10646,15 @@
       <c r="AJ205" s="32"/>
       <c r="AK205" s="43"/>
       <c r="AL205" s="34"/>
-      <c r="AM205" s="50"/>
-      <c r="AN205" s="52"/>
+      <c r="AM205" s="56"/>
+      <c r="AN205" s="58"/>
     </row>
     <row r="206" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="78">
+      <c r="B206" s="59">
         <v>100</v>
       </c>
-      <c r="C206" s="47"/>
-      <c r="D206" s="86"/>
+      <c r="C206" s="51"/>
+      <c r="D206" s="53"/>
       <c r="E206" s="7" t="s">
         <v>10</v>
       </c>
@@ -10694,13 +10693,13 @@
       <c r="AJ206" s="31"/>
       <c r="AK206" s="36"/>
       <c r="AL206" s="33"/>
-      <c r="AM206" s="49"/>
-      <c r="AN206" s="51"/>
+      <c r="AM206" s="55"/>
+      <c r="AN206" s="57"/>
     </row>
     <row r="207" spans="2:40" s="6" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B207" s="88"/>
-      <c r="C207" s="85"/>
-      <c r="D207" s="87"/>
+      <c r="B207" s="60"/>
+      <c r="C207" s="52"/>
+      <c r="D207" s="54"/>
       <c r="E207" s="9" t="s">
         <v>12</v>
       </c>
@@ -10739,8 +10738,8 @@
       <c r="AJ207" s="32"/>
       <c r="AK207" s="43"/>
       <c r="AL207" s="34"/>
-      <c r="AM207" s="50"/>
-      <c r="AN207" s="52"/>
+      <c r="AM207" s="56"/>
+      <c r="AN207" s="58"/>
     </row>
     <row r="208" spans="2:40" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="14"/>
@@ -10781,43 +10780,43 @@
     <row r="209" spans="2:41" s="13" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
-      <c r="D209" s="95"/>
-      <c r="E209" s="95"/>
-      <c r="F209" s="95"/>
-      <c r="G209" s="95"/>
-      <c r="H209" s="95"/>
-      <c r="I209" s="95"/>
-      <c r="J209" s="95"/>
-      <c r="K209" s="95"/>
-      <c r="L209" s="95"/>
-      <c r="M209" s="95"/>
-      <c r="N209" s="95"/>
-      <c r="O209" s="95"/>
-      <c r="P209" s="95"/>
-      <c r="Q209" s="95"/>
-      <c r="R209" s="95"/>
-      <c r="S209" s="95"/>
-      <c r="T209" s="95"/>
-      <c r="U209" s="95"/>
-      <c r="V209" s="95"/>
-      <c r="W209" s="95"/>
-      <c r="X209" s="95"/>
-      <c r="Y209" s="95"/>
-      <c r="Z209" s="95"/>
-      <c r="AA209" s="95"/>
-      <c r="AB209" s="95"/>
-      <c r="AC209" s="95"/>
-      <c r="AD209" s="95"/>
-      <c r="AE209" s="95"/>
-      <c r="AF209" s="95"/>
-      <c r="AG209" s="95"/>
-      <c r="AH209" s="95"/>
-      <c r="AI209" s="95"/>
-      <c r="AJ209" s="95"/>
-      <c r="AK209" s="95"/>
-      <c r="AL209" s="95"/>
-      <c r="AM209" s="95"/>
-      <c r="AN209" s="95"/>
+      <c r="D209" s="47"/>
+      <c r="E209" s="47"/>
+      <c r="F209" s="47"/>
+      <c r="G209" s="47"/>
+      <c r="H209" s="47"/>
+      <c r="I209" s="47"/>
+      <c r="J209" s="47"/>
+      <c r="K209" s="47"/>
+      <c r="L209" s="47"/>
+      <c r="M209" s="47"/>
+      <c r="N209" s="47"/>
+      <c r="O209" s="47"/>
+      <c r="P209" s="47"/>
+      <c r="Q209" s="47"/>
+      <c r="R209" s="47"/>
+      <c r="S209" s="47"/>
+      <c r="T209" s="47"/>
+      <c r="U209" s="47"/>
+      <c r="V209" s="47"/>
+      <c r="W209" s="47"/>
+      <c r="X209" s="47"/>
+      <c r="Y209" s="47"/>
+      <c r="Z209" s="47"/>
+      <c r="AA209" s="47"/>
+      <c r="AB209" s="47"/>
+      <c r="AC209" s="47"/>
+      <c r="AD209" s="47"/>
+      <c r="AE209" s="47"/>
+      <c r="AF209" s="47"/>
+      <c r="AG209" s="47"/>
+      <c r="AH209" s="47"/>
+      <c r="AI209" s="47"/>
+      <c r="AJ209" s="47"/>
+      <c r="AK209" s="47"/>
+      <c r="AL209" s="47"/>
+      <c r="AM209" s="47"/>
+      <c r="AN209" s="47"/>
     </row>
     <row r="210" spans="2:41" s="21" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B210" s="18"/>
@@ -10936,573 +10935,107 @@
     </row>
     <row r="213" spans="2:41" s="24" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C213" s="25"/>
-      <c r="D213" s="96"/>
-      <c r="E213" s="96"/>
-      <c r="F213" s="96"/>
-      <c r="G213" s="96"/>
-      <c r="H213" s="96"/>
-      <c r="I213" s="96"/>
+      <c r="D213" s="48"/>
+      <c r="E213" s="48"/>
+      <c r="F213" s="48"/>
+      <c r="G213" s="48"/>
+      <c r="H213" s="48"/>
+      <c r="I213" s="48"/>
       <c r="J213" s="26"/>
       <c r="K213" s="26"/>
       <c r="L213" s="26"/>
       <c r="M213" s="26"/>
       <c r="N213" s="26"/>
-      <c r="O213" s="96"/>
-      <c r="P213" s="96"/>
-      <c r="Q213" s="96"/>
-      <c r="R213" s="96"/>
-      <c r="S213" s="96"/>
-      <c r="T213" s="96"/>
-      <c r="U213" s="96"/>
-      <c r="V213" s="96"/>
-      <c r="W213" s="96"/>
-      <c r="X213" s="96"/>
+      <c r="O213" s="48"/>
+      <c r="P213" s="48"/>
+      <c r="Q213" s="48"/>
+      <c r="R213" s="48"/>
+      <c r="S213" s="48"/>
+      <c r="T213" s="48"/>
+      <c r="U213" s="48"/>
+      <c r="V213" s="48"/>
+      <c r="W213" s="48"/>
+      <c r="X213" s="48"/>
       <c r="Y213" s="26"/>
       <c r="Z213" s="26"/>
       <c r="AA213" s="26"/>
       <c r="AB213" s="26"/>
-      <c r="AC213" s="96"/>
-      <c r="AD213" s="96"/>
-      <c r="AE213" s="96"/>
-      <c r="AF213" s="96"/>
-      <c r="AG213" s="96"/>
-      <c r="AH213" s="96"/>
-      <c r="AI213" s="96"/>
-      <c r="AJ213" s="96"/>
-      <c r="AK213" s="96"/>
-      <c r="AL213" s="96"/>
+      <c r="AC213" s="48"/>
+      <c r="AD213" s="48"/>
+      <c r="AE213" s="48"/>
+      <c r="AF213" s="48"/>
+      <c r="AG213" s="48"/>
+      <c r="AH213" s="48"/>
+      <c r="AI213" s="48"/>
+      <c r="AJ213" s="48"/>
+      <c r="AK213" s="48"/>
+      <c r="AL213" s="48"/>
       <c r="AM213" s="26"/>
       <c r="AN213" s="26"/>
       <c r="AO213" s="26"/>
     </row>
     <row r="214" spans="2:41" s="26" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="25"/>
-      <c r="D214" s="96"/>
-      <c r="E214" s="96"/>
-      <c r="F214" s="96"/>
-      <c r="G214" s="96"/>
-      <c r="H214" s="96"/>
-      <c r="I214" s="96"/>
-      <c r="O214" s="96"/>
-      <c r="P214" s="96"/>
-      <c r="Q214" s="96"/>
-      <c r="R214" s="96"/>
-      <c r="S214" s="96"/>
-      <c r="T214" s="96"/>
-      <c r="U214" s="96"/>
-      <c r="V214" s="96"/>
-      <c r="W214" s="96"/>
-      <c r="X214" s="96"/>
-      <c r="AC214" s="96"/>
-      <c r="AD214" s="96"/>
-      <c r="AE214" s="96"/>
-      <c r="AF214" s="96"/>
-      <c r="AG214" s="96"/>
-      <c r="AH214" s="96"/>
-      <c r="AI214" s="96"/>
-      <c r="AJ214" s="96"/>
-      <c r="AK214" s="96"/>
-      <c r="AL214" s="96"/>
+      <c r="D214" s="48"/>
+      <c r="E214" s="48"/>
+      <c r="F214" s="48"/>
+      <c r="G214" s="48"/>
+      <c r="H214" s="48"/>
+      <c r="I214" s="48"/>
+      <c r="O214" s="48"/>
+      <c r="P214" s="48"/>
+      <c r="Q214" s="48"/>
+      <c r="R214" s="48"/>
+      <c r="S214" s="48"/>
+      <c r="T214" s="48"/>
+      <c r="U214" s="48"/>
+      <c r="V214" s="48"/>
+      <c r="W214" s="48"/>
+      <c r="X214" s="48"/>
+      <c r="AC214" s="48"/>
+      <c r="AD214" s="48"/>
+      <c r="AE214" s="48"/>
+      <c r="AF214" s="48"/>
+      <c r="AG214" s="48"/>
+      <c r="AH214" s="48"/>
+      <c r="AI214" s="48"/>
+      <c r="AJ214" s="48"/>
+      <c r="AK214" s="48"/>
+      <c r="AL214" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="552">
-    <mergeCell ref="D209:AN209"/>
-    <mergeCell ref="D213:I213"/>
-    <mergeCell ref="O213:X213"/>
-    <mergeCell ref="AC213:AL213"/>
-    <mergeCell ref="D214:I214"/>
-    <mergeCell ref="O214:X214"/>
-    <mergeCell ref="AC214:AL214"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="D204:D205"/>
-    <mergeCell ref="AM204:AM205"/>
-    <mergeCell ref="AN204:AN205"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="AM206:AM207"/>
-    <mergeCell ref="AN206:AN207"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="D200:D201"/>
-    <mergeCell ref="AM200:AM201"/>
-    <mergeCell ref="AN200:AN201"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="AM202:AM203"/>
-    <mergeCell ref="AN202:AN203"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="AM196:AM197"/>
-    <mergeCell ref="AN196:AN197"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="AM198:AM199"/>
-    <mergeCell ref="AN198:AN199"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:C193"/>
-    <mergeCell ref="D192:D193"/>
-    <mergeCell ref="AM192:AM193"/>
-    <mergeCell ref="AN192:AN193"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="C194:C195"/>
-    <mergeCell ref="D194:D195"/>
-    <mergeCell ref="AM194:AM195"/>
-    <mergeCell ref="AN194:AN195"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="D188:D189"/>
-    <mergeCell ref="AM188:AM189"/>
-    <mergeCell ref="AN188:AN189"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="D190:D191"/>
-    <mergeCell ref="AM190:AM191"/>
-    <mergeCell ref="AN190:AN191"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="AM184:AM185"/>
-    <mergeCell ref="AN184:AN185"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="AM186:AM187"/>
-    <mergeCell ref="AN186:AN187"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="C180:C181"/>
-    <mergeCell ref="D180:D181"/>
-    <mergeCell ref="AM180:AM181"/>
-    <mergeCell ref="AN180:AN181"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="C182:C183"/>
-    <mergeCell ref="D182:D183"/>
-    <mergeCell ref="AM182:AM183"/>
-    <mergeCell ref="AN182:AN183"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="D176:D177"/>
-    <mergeCell ref="AM176:AM177"/>
-    <mergeCell ref="AN176:AN177"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="D178:D179"/>
-    <mergeCell ref="AM178:AM179"/>
-    <mergeCell ref="AN178:AN179"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="AM172:AM173"/>
-    <mergeCell ref="AN172:AN173"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="AM174:AM175"/>
-    <mergeCell ref="AN174:AN175"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="C168:C169"/>
-    <mergeCell ref="D168:D169"/>
-    <mergeCell ref="AM168:AM169"/>
-    <mergeCell ref="AN168:AN169"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="AM170:AM171"/>
-    <mergeCell ref="AN170:AN171"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="AM164:AM165"/>
-    <mergeCell ref="AN164:AN165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="AM166:AM167"/>
-    <mergeCell ref="AN166:AN167"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="AM160:AM161"/>
-    <mergeCell ref="AN160:AN161"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="D162:D163"/>
-    <mergeCell ref="AM162:AM163"/>
-    <mergeCell ref="AN162:AN163"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="D156:D157"/>
-    <mergeCell ref="AM156:AM157"/>
-    <mergeCell ref="AN156:AN157"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="AM158:AM159"/>
-    <mergeCell ref="AN158:AN159"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="AM152:AM153"/>
-    <mergeCell ref="AN152:AN153"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="AM154:AM155"/>
-    <mergeCell ref="AN154:AN155"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="AM148:AM149"/>
-    <mergeCell ref="AN148:AN149"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="AM150:AM151"/>
-    <mergeCell ref="AN150:AN151"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="AM144:AM145"/>
-    <mergeCell ref="AN144:AN145"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="AM146:AM147"/>
-    <mergeCell ref="AN146:AN147"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="AM140:AM141"/>
-    <mergeCell ref="AN140:AN141"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="AM142:AM143"/>
-    <mergeCell ref="AN142:AN143"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="AM136:AM137"/>
-    <mergeCell ref="AN136:AN137"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="AM138:AM139"/>
-    <mergeCell ref="AN138:AN139"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:D133"/>
-    <mergeCell ref="AM132:AM133"/>
-    <mergeCell ref="AN132:AN133"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:D135"/>
-    <mergeCell ref="AM134:AM135"/>
-    <mergeCell ref="AN134:AN135"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="AM128:AM129"/>
-    <mergeCell ref="AN128:AN129"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="AM130:AM131"/>
-    <mergeCell ref="AN130:AN131"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="AM124:AM125"/>
-    <mergeCell ref="AN124:AN125"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="AM126:AM127"/>
-    <mergeCell ref="AN126:AN127"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="AM120:AM121"/>
-    <mergeCell ref="AN120:AN121"/>
-    <mergeCell ref="B122:B123"/>
-    <mergeCell ref="C122:C123"/>
-    <mergeCell ref="D122:D123"/>
-    <mergeCell ref="AM122:AM123"/>
-    <mergeCell ref="AN122:AN123"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="AM116:AM117"/>
-    <mergeCell ref="AN116:AN117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="AM118:AM119"/>
-    <mergeCell ref="AN118:AN119"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="AM112:AM113"/>
-    <mergeCell ref="AN112:AN113"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="AM114:AM115"/>
-    <mergeCell ref="AN114:AN115"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="AM108:AM109"/>
-    <mergeCell ref="AN108:AN109"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="D110:D111"/>
-    <mergeCell ref="AM110:AM111"/>
-    <mergeCell ref="AN110:AN111"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="AM104:AM105"/>
-    <mergeCell ref="AN104:AN105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="AM106:AM107"/>
-    <mergeCell ref="AN106:AN107"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="AM100:AM101"/>
-    <mergeCell ref="AN100:AN101"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="AM102:AM103"/>
-    <mergeCell ref="AN102:AN103"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="AM96:AM97"/>
-    <mergeCell ref="AN96:AN97"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="AM98:AM99"/>
-    <mergeCell ref="AN98:AN99"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="AM92:AM93"/>
-    <mergeCell ref="AN92:AN93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="AM94:AM95"/>
-    <mergeCell ref="AN94:AN95"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="AM88:AM89"/>
-    <mergeCell ref="AN88:AN89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="AM90:AM91"/>
-    <mergeCell ref="AN90:AN91"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="AM84:AM85"/>
-    <mergeCell ref="AN84:AN85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="AM86:AM87"/>
-    <mergeCell ref="AN86:AN87"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="AM80:AM81"/>
-    <mergeCell ref="AN80:AN81"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="AM82:AM83"/>
-    <mergeCell ref="AN82:AN83"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="AM76:AM77"/>
-    <mergeCell ref="AN76:AN77"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="AM78:AM79"/>
-    <mergeCell ref="AN78:AN79"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="AM72:AM73"/>
-    <mergeCell ref="AN72:AN73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="AM74:AM75"/>
-    <mergeCell ref="AN74:AN75"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="AM68:AM69"/>
-    <mergeCell ref="AN68:AN69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="AM70:AM71"/>
-    <mergeCell ref="AN70:AN71"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="AM64:AM65"/>
-    <mergeCell ref="AN64:AN65"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="AM66:AM67"/>
-    <mergeCell ref="AN66:AN67"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="AM60:AM61"/>
-    <mergeCell ref="AN60:AN61"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="AM62:AM63"/>
-    <mergeCell ref="AN62:AN63"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="AM56:AM57"/>
-    <mergeCell ref="AN56:AN57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="AM58:AM59"/>
-    <mergeCell ref="AN58:AN59"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="AM52:AM53"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="AM54:AM55"/>
-    <mergeCell ref="AN54:AN55"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="AM48:AM49"/>
-    <mergeCell ref="AN48:AN49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="AM50:AM51"/>
-    <mergeCell ref="AN50:AN51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="AM44:AM45"/>
-    <mergeCell ref="AN44:AN45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="AM46:AM47"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="AM40:AM41"/>
-    <mergeCell ref="AN40:AN41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="AM42:AM43"/>
-    <mergeCell ref="AN42:AN43"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="AM36:AM37"/>
-    <mergeCell ref="AN36:AN37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="AM38:AM39"/>
-    <mergeCell ref="AN38:AN39"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="AM32:AM33"/>
-    <mergeCell ref="AN32:AN33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="AM34:AM35"/>
-    <mergeCell ref="AN34:AN35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="AM28:AM29"/>
-    <mergeCell ref="AN28:AN29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="AM30:AM31"/>
-    <mergeCell ref="AN30:AN31"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="AM24:AM25"/>
-    <mergeCell ref="AN24:AN25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="AM26:AM27"/>
-    <mergeCell ref="AN26:AN27"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="AM20:AM21"/>
-    <mergeCell ref="AN20:AN21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="AM22:AM23"/>
-    <mergeCell ref="AN22:AN23"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="AM16:AM17"/>
-    <mergeCell ref="AN16:AN17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="AM18:AM19"/>
-    <mergeCell ref="AN18:AN19"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="AM12:AM13"/>
-    <mergeCell ref="AN12:AN13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="AM14:AM15"/>
-    <mergeCell ref="AN14:AN15"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="B1:AN1"/>
+    <mergeCell ref="B2:AN2"/>
+    <mergeCell ref="B3:AN3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="G5:N5"/>
+    <mergeCell ref="O5:AK5"/>
+    <mergeCell ref="AL5:AL7"/>
+    <mergeCell ref="AM5:AM7"/>
+    <mergeCell ref="AN5:AN7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
@@ -11527,37 +11060,503 @@
     <mergeCell ref="X6:X7"/>
     <mergeCell ref="AA6:AA7"/>
     <mergeCell ref="P6:P7"/>
-    <mergeCell ref="B1:AN1"/>
-    <mergeCell ref="B2:AN2"/>
-    <mergeCell ref="B3:AN3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="G5:N5"/>
-    <mergeCell ref="O5:AK5"/>
-    <mergeCell ref="AL5:AL7"/>
-    <mergeCell ref="AM5:AM7"/>
-    <mergeCell ref="AN5:AN7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="AM12:AM13"/>
+    <mergeCell ref="AN12:AN13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="AM14:AM15"/>
+    <mergeCell ref="AN14:AN15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="AM16:AM17"/>
+    <mergeCell ref="AN16:AN17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="AM18:AM19"/>
+    <mergeCell ref="AN18:AN19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="AM20:AM21"/>
+    <mergeCell ref="AN20:AN21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="AM22:AM23"/>
+    <mergeCell ref="AN22:AN23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="AM24:AM25"/>
+    <mergeCell ref="AN24:AN25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="AM26:AM27"/>
+    <mergeCell ref="AN26:AN27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="AM28:AM29"/>
+    <mergeCell ref="AN28:AN29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="AM30:AM31"/>
+    <mergeCell ref="AN30:AN31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="AM32:AM33"/>
+    <mergeCell ref="AN32:AN33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="AM34:AM35"/>
+    <mergeCell ref="AN34:AN35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="AM36:AM37"/>
+    <mergeCell ref="AN36:AN37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="AM38:AM39"/>
+    <mergeCell ref="AN38:AN39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="AM40:AM41"/>
+    <mergeCell ref="AN40:AN41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="AM42:AM43"/>
+    <mergeCell ref="AN42:AN43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="AM44:AM45"/>
+    <mergeCell ref="AN44:AN45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="AM46:AM47"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="AM48:AM49"/>
+    <mergeCell ref="AN48:AN49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="AM50:AM51"/>
+    <mergeCell ref="AN50:AN51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="AM52:AM53"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="AM54:AM55"/>
+    <mergeCell ref="AN54:AN55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="AM56:AM57"/>
+    <mergeCell ref="AN56:AN57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="AM58:AM59"/>
+    <mergeCell ref="AN58:AN59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="AM60:AM61"/>
+    <mergeCell ref="AN60:AN61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="AM62:AM63"/>
+    <mergeCell ref="AN62:AN63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="AM64:AM65"/>
+    <mergeCell ref="AN64:AN65"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="AM66:AM67"/>
+    <mergeCell ref="AN66:AN67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="AM68:AM69"/>
+    <mergeCell ref="AN68:AN69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="AM70:AM71"/>
+    <mergeCell ref="AN70:AN71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="AM72:AM73"/>
+    <mergeCell ref="AN72:AN73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="AM74:AM75"/>
+    <mergeCell ref="AN74:AN75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="AM76:AM77"/>
+    <mergeCell ref="AN76:AN77"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="AM78:AM79"/>
+    <mergeCell ref="AN78:AN79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="AM80:AM81"/>
+    <mergeCell ref="AN80:AN81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="AM82:AM83"/>
+    <mergeCell ref="AN82:AN83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="AM84:AM85"/>
+    <mergeCell ref="AN84:AN85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="AM86:AM87"/>
+    <mergeCell ref="AN86:AN87"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="AM88:AM89"/>
+    <mergeCell ref="AN88:AN89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="AM90:AM91"/>
+    <mergeCell ref="AN90:AN91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="AM92:AM93"/>
+    <mergeCell ref="AN92:AN93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="AM94:AM95"/>
+    <mergeCell ref="AN94:AN95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="AM96:AM97"/>
+    <mergeCell ref="AN96:AN97"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="AM98:AM99"/>
+    <mergeCell ref="AN98:AN99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="AM100:AM101"/>
+    <mergeCell ref="AN100:AN101"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="AM102:AM103"/>
+    <mergeCell ref="AN102:AN103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="AM104:AM105"/>
+    <mergeCell ref="AN104:AN105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="AM106:AM107"/>
+    <mergeCell ref="AN106:AN107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="AM108:AM109"/>
+    <mergeCell ref="AN108:AN109"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="AM110:AM111"/>
+    <mergeCell ref="AN110:AN111"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="AM112:AM113"/>
+    <mergeCell ref="AN112:AN113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="AM114:AM115"/>
+    <mergeCell ref="AN114:AN115"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="AM116:AM117"/>
+    <mergeCell ref="AN116:AN117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="AM118:AM119"/>
+    <mergeCell ref="AN118:AN119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="AM120:AM121"/>
+    <mergeCell ref="AN120:AN121"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="D122:D123"/>
+    <mergeCell ref="AM122:AM123"/>
+    <mergeCell ref="AN122:AN123"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="AM124:AM125"/>
+    <mergeCell ref="AN124:AN125"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="AM126:AM127"/>
+    <mergeCell ref="AN126:AN127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="AM128:AM129"/>
+    <mergeCell ref="AN128:AN129"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="AM130:AM131"/>
+    <mergeCell ref="AN130:AN131"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="AM132:AM133"/>
+    <mergeCell ref="AN132:AN133"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="AM134:AM135"/>
+    <mergeCell ref="AN134:AN135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="AM136:AM137"/>
+    <mergeCell ref="AN136:AN137"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="AM138:AM139"/>
+    <mergeCell ref="AN138:AN139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="AM140:AM141"/>
+    <mergeCell ref="AN140:AN141"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="AM142:AM143"/>
+    <mergeCell ref="AN142:AN143"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="AM144:AM145"/>
+    <mergeCell ref="AN144:AN145"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="AM146:AM147"/>
+    <mergeCell ref="AN146:AN147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="AM148:AM149"/>
+    <mergeCell ref="AN148:AN149"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="AM150:AM151"/>
+    <mergeCell ref="AN150:AN151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="AM152:AM153"/>
+    <mergeCell ref="AN152:AN153"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="AM154:AM155"/>
+    <mergeCell ref="AN154:AN155"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="D156:D157"/>
+    <mergeCell ref="AM156:AM157"/>
+    <mergeCell ref="AN156:AN157"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="AM158:AM159"/>
+    <mergeCell ref="AN158:AN159"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="AM160:AM161"/>
+    <mergeCell ref="AN160:AN161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="AM162:AM163"/>
+    <mergeCell ref="AN162:AN163"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="AM164:AM165"/>
+    <mergeCell ref="AN164:AN165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="AM166:AM167"/>
+    <mergeCell ref="AN166:AN167"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="D168:D169"/>
+    <mergeCell ref="AM168:AM169"/>
+    <mergeCell ref="AN168:AN169"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="D170:D171"/>
+    <mergeCell ref="AM170:AM171"/>
+    <mergeCell ref="AN170:AN171"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="AM172:AM173"/>
+    <mergeCell ref="AN172:AN173"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="AM174:AM175"/>
+    <mergeCell ref="AN174:AN175"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="D176:D177"/>
+    <mergeCell ref="AM176:AM177"/>
+    <mergeCell ref="AN176:AN177"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="D178:D179"/>
+    <mergeCell ref="AM178:AM179"/>
+    <mergeCell ref="AN178:AN179"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="C180:C181"/>
+    <mergeCell ref="D180:D181"/>
+    <mergeCell ref="AM180:AM181"/>
+    <mergeCell ref="AN180:AN181"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="C182:C183"/>
+    <mergeCell ref="D182:D183"/>
+    <mergeCell ref="AM182:AM183"/>
+    <mergeCell ref="AN182:AN183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="AM184:AM185"/>
+    <mergeCell ref="AN184:AN185"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="AM186:AM187"/>
+    <mergeCell ref="AN186:AN187"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="D188:D189"/>
+    <mergeCell ref="AM188:AM189"/>
+    <mergeCell ref="AN188:AN189"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="AM190:AM191"/>
+    <mergeCell ref="AN190:AN191"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:C193"/>
+    <mergeCell ref="D192:D193"/>
+    <mergeCell ref="AM192:AM193"/>
+    <mergeCell ref="AN192:AN193"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="C194:C195"/>
+    <mergeCell ref="D194:D195"/>
+    <mergeCell ref="AM194:AM195"/>
+    <mergeCell ref="AN194:AN195"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="AM196:AM197"/>
+    <mergeCell ref="AN196:AN197"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="AM198:AM199"/>
+    <mergeCell ref="AN198:AN199"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="D200:D201"/>
+    <mergeCell ref="AM200:AM201"/>
+    <mergeCell ref="AN200:AN201"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="AM202:AM203"/>
+    <mergeCell ref="AN202:AN203"/>
+    <mergeCell ref="D209:AN209"/>
+    <mergeCell ref="D213:I213"/>
+    <mergeCell ref="O213:X213"/>
+    <mergeCell ref="AC213:AL213"/>
+    <mergeCell ref="D214:I214"/>
+    <mergeCell ref="O214:X214"/>
+    <mergeCell ref="AC214:AL214"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
+    <mergeCell ref="AM204:AM205"/>
+    <mergeCell ref="AN204:AN205"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="AM206:AM207"/>
+    <mergeCell ref="AN206:AN207"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="76" orientation="landscape" r:id="rId1"/>
